--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A3C731-8B0A-4868-8C7B-70E1A6A75009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFF10B6-8136-44FD-86F8-892E78B98570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -641,9 +641,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="dd\.mm\.yy;@"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yy;@"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -683,68 +684,20 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Millares 3" xfId="2" xr:uid="{1746C45B-35CD-444D-849E-3B0966233946}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1136,7 +1089,7 @@
       <c r="E2" s="1">
         <v>2.4500000000000001E-2</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G2">
@@ -1174,7 +1127,7 @@
       <c r="E3" s="1">
         <v>5.8500000000000003E-2</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>46524</v>
       </c>
       <c r="G3">
@@ -1212,7 +1165,7 @@
       <c r="E4" s="1">
         <v>4.6249999999999999E-2</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>46675</v>
       </c>
       <c r="G4">
@@ -1250,7 +1203,7 @@
       <c r="E5" s="1">
         <v>0.05</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>46395</v>
       </c>
       <c r="G5">
@@ -1288,7 +1241,7 @@
       <c r="E6" s="1">
         <v>2.3E-2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>155</v>
       </c>
       <c r="G6">
@@ -1326,7 +1279,7 @@
       <c r="E7" s="1">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>157</v>
       </c>
       <c r="G7">
@@ -1364,7 +1317,7 @@
       <c r="E8" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>46764</v>
       </c>
       <c r="G8">
@@ -1402,7 +1355,7 @@
       <c r="E9" s="1">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>46794</v>
       </c>
       <c r="G9">
@@ -1440,7 +1393,7 @@
       <c r="E10" s="1">
         <v>0.05</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>46762</v>
       </c>
       <c r="G10">
@@ -1478,7 +1431,7 @@
       <c r="E11" s="1">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>163</v>
       </c>
       <c r="G11">
@@ -1516,7 +1469,7 @@
       <c r="E12" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>165</v>
       </c>
       <c r="G12">
@@ -1554,7 +1507,7 @@
       <c r="E13" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>47027</v>
       </c>
       <c r="G13">
@@ -1592,7 +1545,7 @@
       <c r="E14" s="1">
         <v>6.9500000000000006E-2</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>46827</v>
       </c>
       <c r="G14">
@@ -1630,7 +1583,7 @@
       <c r="E15" s="1">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>46980</v>
       </c>
       <c r="G15">
@@ -1668,7 +1621,7 @@
       <c r="E16" s="1">
         <v>6.7979999999999999E-2</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>47064</v>
       </c>
       <c r="G16">
@@ -1706,7 +1659,7 @@
       <c r="E17" s="1">
         <v>4.3749999999999997E-2</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>46919</v>
       </c>
       <c r="G17">
@@ -1744,7 +1697,7 @@
       <c r="E18" s="1">
         <v>8.6249999999999993E-2</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>47137</v>
       </c>
       <c r="G18">
@@ -1782,7 +1735,7 @@
       <c r="E19" s="1">
         <v>6.9919999999999996E-2</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>169</v>
       </c>
       <c r="G19">
@@ -1820,7 +1773,7 @@
       <c r="E20" s="1">
         <v>5.6250000000000001E-2</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>47126</v>
       </c>
       <c r="G20">
@@ -1858,7 +1811,7 @@
       <c r="E21" s="1">
         <v>3.4500000000000003E-2</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>47128</v>
       </c>
       <c r="G21">
@@ -1896,7 +1849,7 @@
       <c r="E22" s="1">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G22">
@@ -1934,7 +1887,7 @@
       <c r="E23" s="1">
         <v>0.05</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>47126</v>
       </c>
       <c r="G23">
@@ -1972,7 +1925,7 @@
       <c r="E24" s="1">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>47209</v>
       </c>
       <c r="G24">
@@ -2010,7 +1963,7 @@
       <c r="E25" s="1">
         <v>5.9499999999999997E-2</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>47314</v>
       </c>
       <c r="G25">
@@ -2048,7 +2001,7 @@
       <c r="E26" s="1">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>47437</v>
       </c>
       <c r="G26">
@@ -2086,7 +2039,7 @@
       <c r="E27" s="1">
         <v>4.6249999999999999E-2</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>47489</v>
       </c>
       <c r="G27">
@@ -2124,7 +2077,7 @@
       <c r="E28" s="1">
         <v>0.05</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>47485</v>
       </c>
       <c r="G28">
@@ -2162,7 +2115,7 @@
       <c r="E29" s="1">
         <v>3.875E-2</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>47802</v>
       </c>
       <c r="G29">
@@ -2200,7 +2153,7 @@
       <c r="E30" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>47763</v>
       </c>
       <c r="G30">
@@ -2238,7 +2191,7 @@
       <c r="E31" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>47727</v>
       </c>
       <c r="G31">
@@ -2276,7 +2229,7 @@
       <c r="E32" s="1">
         <v>8.7499999999999994E-2</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>47514</v>
       </c>
       <c r="G32">
@@ -2314,7 +2267,7 @@
       <c r="E33" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>47485</v>
       </c>
       <c r="G33">
@@ -2352,7 +2305,7 @@
       <c r="E34" s="1">
         <v>5.8749999999999997E-2</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>47557</v>
       </c>
       <c r="G34">
@@ -2390,7 +2343,7 @@
       <c r="E35" s="1">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>47757</v>
       </c>
       <c r="G35">
@@ -2428,7 +2381,7 @@
       <c r="E36" s="1">
         <v>5.0930000000000003E-2</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="3" t="s">
         <v>178</v>
       </c>
       <c r="G36">
@@ -2466,7 +2419,7 @@
       <c r="E37" s="1">
         <v>2.7E-2</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="3" t="s">
         <v>179</v>
       </c>
       <c r="G37">
@@ -2504,7 +2457,7 @@
       <c r="E38" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>180</v>
       </c>
       <c r="G38">
@@ -2542,7 +2495,7 @@
       <c r="E39" s="1">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>47702</v>
       </c>
       <c r="G39">
@@ -2580,7 +2533,7 @@
       <c r="E40" s="1">
         <v>4.3749999999999997E-2</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>47574</v>
       </c>
       <c r="G40">
@@ -2618,7 +2571,7 @@
       <c r="E41" s="1">
         <v>0.03</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>183</v>
       </c>
       <c r="G41">
@@ -2656,7 +2609,7 @@
       <c r="E42" s="1">
         <v>3.6249999999999998E-2</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>47618</v>
       </c>
       <c r="G42">
@@ -2694,7 +2647,7 @@
       <c r="E43" s="1">
         <v>0.05</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>47804</v>
       </c>
       <c r="G43">
@@ -2732,7 +2685,7 @@
       <c r="E44" s="1">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>47863</v>
       </c>
       <c r="G44">
@@ -2770,7 +2723,7 @@
       <c r="E45" s="1">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>47851</v>
       </c>
       <c r="G45">
@@ -2808,7 +2761,7 @@
       <c r="E46" s="1">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>186</v>
       </c>
       <c r="G46">
@@ -2846,7 +2799,7 @@
       <c r="E47" s="1">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>47908</v>
       </c>
       <c r="G47">
@@ -2884,7 +2837,7 @@
       <c r="E48" s="1">
         <v>2.726E-2</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="3" t="s">
         <v>187</v>
       </c>
       <c r="G48">
@@ -2922,7 +2875,7 @@
       <c r="E49" s="1">
         <v>3.6249999999999998E-2</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G49">
@@ -2960,7 +2913,7 @@
       <c r="E50" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G50">
@@ -2998,7 +2951,7 @@
       <c r="E51" s="1">
         <v>7.8750000000000001E-2</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="3" t="s">
         <v>190</v>
       </c>
       <c r="G51">
@@ -3036,7 +2989,7 @@
       <c r="E52" s="1">
         <v>3.3750000000000002E-2</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="3" t="s">
         <v>191</v>
       </c>
       <c r="G52">
@@ -3074,7 +3027,7 @@
       <c r="E53" s="1">
         <v>4.2790000000000002E-2</v>
       </c>
-      <c r="F53" s="2">
+      <c r="F53" s="3">
         <v>48288</v>
       </c>
       <c r="G53">
@@ -3112,7 +3065,7 @@
       <c r="E54" s="1">
         <v>3.0499999999999999E-2</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G54">
@@ -3150,7 +3103,7 @@
       <c r="E55" s="1">
         <v>5.3749999999999999E-2</v>
       </c>
-      <c r="F55" s="2">
+      <c r="F55" s="3">
         <v>48214</v>
       </c>
       <c r="G55">
@@ -3188,7 +3141,7 @@
       <c r="E56" s="1">
         <v>6.25E-2</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="3" t="s">
         <v>192</v>
       </c>
       <c r="G56">
@@ -3226,7 +3179,7 @@
       <c r="E57" s="1">
         <v>4.7419999999999997E-2</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="3" t="s">
         <v>196</v>
       </c>
       <c r="G57">
@@ -3264,7 +3217,7 @@
       <c r="E58" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="3" t="s">
         <v>197</v>
       </c>
       <c r="G58">
@@ -3302,7 +3255,7 @@
       <c r="E59" s="1">
         <v>4.7500000000000001E-2</v>
       </c>
-      <c r="F59" s="2">
+      <c r="F59" s="3">
         <v>48215</v>
       </c>
       <c r="G59">
@@ -3340,7 +3293,7 @@
       <c r="E60" s="1">
         <v>5.6500000000000002E-2</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="3">
         <v>48224</v>
       </c>
       <c r="G60">
@@ -3378,7 +3331,7 @@
       <c r="E61" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="F61" s="2">
+      <c r="F61" s="3">
         <v>48458</v>
       </c>
       <c r="G61">
@@ -3416,7 +3369,7 @@
       <c r="E62" s="1">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="F62" s="2">
+      <c r="F62" s="3">
         <v>48349</v>
       </c>
       <c r="G62">
@@ -3454,7 +3407,7 @@
       <c r="E63" s="1">
         <v>6.4210000000000003E-2</v>
       </c>
-      <c r="F63" s="2">
+      <c r="F63" s="3">
         <v>48793</v>
       </c>
       <c r="G63">
@@ -3492,7 +3445,7 @@
       <c r="E64" s="1">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="3">
         <v>49589</v>
       </c>
       <c r="G64">
@@ -3530,7 +3483,7 @@
       <c r="E65" s="1">
         <v>5.9799999999999999E-2</v>
       </c>
-      <c r="F65" s="2">
+      <c r="F65" s="3">
         <v>49351</v>
       </c>
       <c r="G65">
@@ -3568,7 +3521,7 @@
       <c r="E66" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="F66" s="2">
+      <c r="F66" s="3">
         <v>49379</v>
       </c>
       <c r="G66">
@@ -3606,7 +3559,7 @@
       <c r="E67" s="1">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="F67" s="2">
+      <c r="F67" s="3">
         <v>49324</v>
       </c>
       <c r="G67">

--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AFF10B6-8136-44FD-86F8-892E78B98570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B9EEA4-6BF9-478D-8CE6-2904BD5144A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="193">
   <si>
     <t>Industry</t>
   </si>
@@ -65,20 +65,12 @@
     <t>YTW %</t>
   </si>
   <si>
-    <t>Prev month
-YTW%</t>
-  </si>
-  <si>
     <t>Minimum Settlement</t>
   </si>
   <si>
     <t>ISIN</t>
   </si>
   <si>
-    <t>Outstanding
-US$</t>
-  </si>
-  <si>
     <t>Leasing and Rental</t>
   </si>
   <si>
@@ -160,24 +152,6 @@
     <t>US343412AF90</t>
   </si>
   <si>
-    <t>Xerox</t>
-  </si>
-  <si>
-    <t>Caa3/CCC+/CCC</t>
-  </si>
-  <si>
-    <t>USU98401AB58</t>
-  </si>
-  <si>
-    <t>Braskem</t>
-  </si>
-  <si>
-    <t>Caa3/CCC-/CC</t>
-  </si>
-  <si>
-    <t>USN15516AB83</t>
-  </si>
-  <si>
     <t>Specialty Retailers</t>
   </si>
   <si>
@@ -535,12 +509,6 @@
     <t>15/09/2028</t>
   </si>
   <si>
-    <t>IT equipment</t>
-  </si>
-  <si>
-    <t>15/08/2028</t>
-  </si>
-  <si>
     <t>Nordstrom</t>
   </si>
   <si>
@@ -635,6 +603,21 @@
   </si>
   <si>
     <t>14/05/2032</t>
+  </si>
+  <si>
+    <t>Recomendados</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>YTW% Prev</t>
+  </si>
+  <si>
+    <t>Outstanding</t>
   </si>
 </sst>
 </file>
@@ -644,7 +627,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd\.mm\.yy;@"/>
-    <numFmt numFmtId="167" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -688,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1027,15 +1010,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EFF2F4-11C0-433C-9540-66AEF48816EC}">
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="11.42578125" style="1"/>
     <col min="6" max="6" width="11.42578125" style="2"/>
     <col min="8" max="9" width="11.42578125" style="1"/>
+    <col min="13" max="13" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1061,36 +1045,39 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>192</v>
+      </c>
+      <c r="M1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" t="s">
-        <v>15</v>
       </c>
       <c r="E2" s="1">
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2026</v>
@@ -1105,24 +1092,27 @@
         <v>150000</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2">
         <v>3750000000</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>20</v>
       </c>
       <c r="E3" s="1">
         <v>5.8500000000000003E-2</v>
@@ -1143,24 +1133,27 @@
         <v>2000</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>1500000000</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
       </c>
       <c r="E4" s="1">
         <v>4.6249999999999999E-2</v>
@@ -1181,24 +1174,27 @@
         <v>150000</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>600000000</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E5" s="1">
         <v>0.05</v>
@@ -1219,30 +1215,33 @@
         <v>2000</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L5">
         <v>1500000000</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E6" s="1">
         <v>2.3E-2</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="G6">
         <v>2027</v>
@@ -1257,30 +1256,33 @@
         <v>2000</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L6">
         <v>748995000</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="E7" s="1">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G7">
         <v>2027</v>
@@ -1295,24 +1297,27 @@
         <v>200000</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L7">
         <v>89906000</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E8" s="1">
         <v>4.4999999999999998E-2</v>
@@ -1333,24 +1338,27 @@
         <v>2000</v>
       </c>
       <c r="K8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L8">
         <v>300000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E9" s="1">
         <v>2.1999999999999999E-2</v>
@@ -1371,24 +1379,27 @@
         <v>2000</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L9">
         <v>750000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1">
         <v>0.05</v>
@@ -1409,30 +1420,33 @@
         <v>2000</v>
       </c>
       <c r="K10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L10">
         <v>750000000</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E11" s="1">
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="G11">
         <v>2028</v>
@@ -1447,2138 +1461,2227 @@
         <v>2000</v>
       </c>
       <c r="K11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L11">
         <v>600000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" s="1">
-        <v>5.5E-2</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>165</v>
+        <v>6.9500000000000006E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>46827</v>
       </c>
       <c r="G12">
         <v>2028</v>
       </c>
       <c r="H12" s="1">
-        <v>0.44074999999999998</v>
+        <v>5.5849999999999997E-2</v>
       </c>
       <c r="I12" s="1">
-        <v>0.59940000000000004</v>
+        <v>5.4120000000000001E-2</v>
       </c>
       <c r="J12">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12">
+        <v>300000000</v>
+      </c>
+      <c r="M12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="L12">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>43</v>
-      </c>
       <c r="E13" s="1">
-        <v>4.4999999999999998E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="F13" s="3">
-        <v>47027</v>
+        <v>46980</v>
       </c>
       <c r="G13">
         <v>2028</v>
       </c>
       <c r="H13" s="1">
-        <v>0.32118999999999998</v>
+        <v>0.13891999999999999</v>
       </c>
       <c r="I13" s="1">
-        <v>0.60548999999999997</v>
+        <v>0.11001</v>
       </c>
       <c r="J13">
-        <v>200000</v>
+        <v>2000</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L13">
-        <v>1250000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>275000000</v>
+      </c>
+      <c r="M13" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="E14" s="1">
-        <v>6.9500000000000006E-2</v>
+        <v>6.7979999999999999E-2</v>
       </c>
       <c r="F14" s="3">
-        <v>46827</v>
+        <v>47064</v>
       </c>
       <c r="G14">
         <v>2028</v>
       </c>
       <c r="H14" s="1">
-        <v>5.5849999999999997E-2</v>
+        <v>5.3940000000000002E-2</v>
       </c>
       <c r="I14" s="1">
-        <v>5.4120000000000001E-2</v>
+        <v>5.1540000000000002E-2</v>
       </c>
       <c r="J14">
-        <v>1000</v>
+        <v>200000</v>
       </c>
       <c r="K14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="L14">
-        <v>300000000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1500000000</v>
+      </c>
+      <c r="M14" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E15" s="1">
-        <v>4.7500000000000001E-2</v>
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="F15" s="3">
-        <v>46980</v>
+        <v>46919</v>
       </c>
       <c r="G15">
         <v>2028</v>
       </c>
       <c r="H15" s="1">
-        <v>0.13891999999999999</v>
+        <v>5.2670000000000002E-2</v>
       </c>
       <c r="I15" s="1">
-        <v>0.11001</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J15">
         <v>2000</v>
       </c>
       <c r="K15" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15">
+        <v>800000000</v>
+      </c>
+      <c r="M15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="1">
+        <v>8.6249999999999993E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47137</v>
+      </c>
+      <c r="G16">
+        <v>2029</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6.6119999999999998E-2</v>
+      </c>
+      <c r="I16" s="1">
+        <v>6.1510000000000002E-2</v>
+      </c>
+      <c r="J16">
+        <v>1000</v>
+      </c>
+      <c r="K16" t="s">
         <v>50</v>
       </c>
-      <c r="L15">
-        <v>275000000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1">
-        <v>6.7979999999999999E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>47064</v>
-      </c>
-      <c r="G16">
-        <v>2028</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5.3940000000000002E-2</v>
-      </c>
-      <c r="I16" s="1">
-        <v>5.1540000000000002E-2</v>
-      </c>
-      <c r="J16">
-        <v>200000</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="L16">
+        <v>1200000000</v>
+      </c>
+      <c r="M16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6.9919999999999996E-2</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G17">
+        <v>2029</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>4.87E-2</v>
+      </c>
+      <c r="J17">
+        <v>2000</v>
+      </c>
+      <c r="K17" t="s">
         <v>51</v>
       </c>
-      <c r="L16">
-        <v>1500000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="L17">
+        <v>750000000</v>
+      </c>
+      <c r="M17" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="1">
-        <v>4.3749999999999997E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>46919</v>
-      </c>
-      <c r="G17">
-        <v>2028</v>
-      </c>
-      <c r="H17" s="1">
-        <v>5.2670000000000002E-2</v>
-      </c>
-      <c r="I17" s="1">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="J17">
-        <v>2000</v>
-      </c>
-      <c r="K17" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17">
-        <v>800000000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>57</v>
-      </c>
       <c r="E18" s="1">
-        <v>8.6249999999999993E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="F18" s="3">
-        <v>47137</v>
+        <v>47126</v>
       </c>
       <c r="G18">
         <v>2029</v>
       </c>
       <c r="H18" s="1">
-        <v>6.6119999999999998E-2</v>
+        <v>6.132E-2</v>
       </c>
       <c r="I18" s="1">
-        <v>6.1510000000000002E-2</v>
+        <v>5.9650000000000002E-2</v>
       </c>
       <c r="J18">
         <v>1000</v>
       </c>
       <c r="K18" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="L18">
-        <v>1200000000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>750000000</v>
+      </c>
+      <c r="M18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="E19" s="1">
-        <v>6.9919999999999996E-2</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>169</v>
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>47128</v>
       </c>
       <c r="G19">
         <v>2029</v>
       </c>
       <c r="H19" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>6.9470000000000004E-2</v>
       </c>
       <c r="I19" s="1">
-        <v>4.87E-2</v>
+        <v>7.2289999999999993E-2</v>
       </c>
       <c r="J19">
         <v>2000</v>
       </c>
       <c r="K19" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19">
+        <v>500000000</v>
+      </c>
+      <c r="M19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
         <v>59</v>
       </c>
-      <c r="L19">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
       <c r="E20" s="1">
-        <v>5.6250000000000001E-2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>47126</v>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>161</v>
       </c>
       <c r="G20">
         <v>2029</v>
       </c>
       <c r="H20" s="1">
-        <v>6.132E-2</v>
+        <v>5.5710000000000003E-2</v>
       </c>
       <c r="I20" s="1">
-        <v>5.9650000000000002E-2</v>
+        <v>5.357E-2</v>
       </c>
       <c r="J20">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L20">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>700000000</v>
+      </c>
+      <c r="M20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>141</v>
       </c>
       <c r="E21" s="1">
-        <v>3.4500000000000003E-2</v>
+        <v>0.05</v>
       </c>
       <c r="F21" s="3">
-        <v>47128</v>
+        <v>47126</v>
       </c>
       <c r="G21">
         <v>2029</v>
       </c>
       <c r="H21" s="1">
-        <v>6.9470000000000004E-2</v>
+        <v>4.9529999999999998E-2</v>
       </c>
       <c r="I21" s="1">
-        <v>7.2289999999999993E-2</v>
+        <v>4.6399999999999997E-2</v>
       </c>
       <c r="J21">
         <v>2000</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="L21">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>750000000</v>
+      </c>
+      <c r="M21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E22" s="1">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>171</v>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>47209</v>
       </c>
       <c r="G22">
         <v>2029</v>
       </c>
       <c r="H22" s="1">
-        <v>5.5710000000000003E-2</v>
+        <v>5.1090000000000003E-2</v>
       </c>
       <c r="I22" s="1">
-        <v>5.357E-2</v>
+        <v>4.8039999999999999E-2</v>
       </c>
       <c r="J22">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K22" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L22">
-        <v>700000000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>600000000</v>
+      </c>
+      <c r="M22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="E23" s="1">
-        <v>0.05</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="F23" s="3">
-        <v>47126</v>
+        <v>47314</v>
       </c>
       <c r="G23">
         <v>2029</v>
       </c>
       <c r="H23" s="1">
-        <v>4.9529999999999998E-2</v>
+        <v>5.8810000000000001E-2</v>
       </c>
       <c r="I23" s="1">
-        <v>4.6399999999999997E-2</v>
+        <v>5.5960000000000003E-2</v>
       </c>
       <c r="J23">
         <v>2000</v>
       </c>
       <c r="K23" t="s">
+        <v>68</v>
+      </c>
+      <c r="L23">
+        <v>850000000</v>
+      </c>
+      <c r="M23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
         <v>69</v>
       </c>
-      <c r="L23">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>71</v>
-      </c>
       <c r="E24" s="1">
-        <v>3.7499999999999999E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="F24" s="3">
-        <v>47209</v>
+        <v>47437</v>
       </c>
       <c r="G24">
         <v>2029</v>
       </c>
       <c r="H24" s="1">
-        <v>5.1090000000000003E-2</v>
+        <v>4.9669999999999999E-2</v>
       </c>
       <c r="I24" s="1">
-        <v>4.8039999999999999E-2</v>
+        <v>4.648E-2</v>
       </c>
       <c r="J24">
+        <v>2000</v>
+      </c>
+      <c r="K24" t="s">
+        <v>70</v>
+      </c>
+      <c r="L24">
+        <v>1000000000</v>
+      </c>
+      <c r="M24" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1">
+        <v>4.6249999999999999E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>47489</v>
+      </c>
+      <c r="G25">
+        <v>2030</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5.5710000000000003E-2</v>
+      </c>
+      <c r="I25" s="1">
+        <v>5.5199999999999999E-2</v>
+      </c>
+      <c r="J25">
         <v>1000</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K25" t="s">
         <v>72</v>
       </c>
-      <c r="L24">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="L25">
+        <v>2750000000</v>
+      </c>
+      <c r="M25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>150</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" t="s">
+        <v>22</v>
+      </c>
+      <c r="D26" t="s">
         <v>73</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E26" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F26" s="3">
+        <v>47485</v>
+      </c>
+      <c r="G26">
+        <v>2030</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6.0789999999999997E-2</v>
+      </c>
+      <c r="I26" s="1">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="J26">
+        <v>1000</v>
+      </c>
+      <c r="K26" t="s">
         <v>74</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="1">
-        <v>5.9499999999999997E-2</v>
-      </c>
-      <c r="F25" s="3">
-        <v>47314</v>
-      </c>
-      <c r="G25">
-        <v>2029</v>
-      </c>
-      <c r="H25" s="1">
-        <v>5.8810000000000001E-2</v>
-      </c>
-      <c r="I25" s="1">
-        <v>5.5960000000000003E-2</v>
-      </c>
-      <c r="J25">
-        <v>2000</v>
-      </c>
-      <c r="K25" t="s">
-        <v>76</v>
-      </c>
-      <c r="L25">
-        <v>850000000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" s="1">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="F26" s="3">
-        <v>47437</v>
-      </c>
-      <c r="G26">
-        <v>2029</v>
-      </c>
-      <c r="H26" s="1">
-        <v>4.9669999999999999E-2</v>
-      </c>
-      <c r="I26" s="1">
-        <v>4.648E-2</v>
-      </c>
-      <c r="J26">
-        <v>2000</v>
-      </c>
-      <c r="K26" t="s">
-        <v>78</v>
-      </c>
       <c r="L26">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>550000000</v>
+      </c>
+      <c r="M26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E27" s="1">
-        <v>4.6249999999999999E-2</v>
+        <v>3.875E-2</v>
       </c>
       <c r="F27" s="3">
-        <v>47489</v>
+        <v>47802</v>
       </c>
       <c r="G27">
         <v>2030</v>
       </c>
       <c r="H27" s="1">
-        <v>5.5710000000000003E-2</v>
+        <v>6.0019999999999997E-2</v>
       </c>
       <c r="I27" s="1">
-        <v>5.5199999999999999E-2</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="J27">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K27" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L27">
-        <v>2750000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>650000000</v>
+      </c>
+      <c r="M27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E28" s="1">
-        <v>0.05</v>
+        <v>4.7E-2</v>
       </c>
       <c r="F28" s="3">
-        <v>47485</v>
+        <v>47763</v>
       </c>
       <c r="G28">
         <v>2030</v>
       </c>
       <c r="H28" s="1">
-        <v>6.0789999999999997E-2</v>
+        <v>5.2499999999999998E-2</v>
       </c>
       <c r="I28" s="1">
-        <v>5.9799999999999999E-2</v>
+        <v>4.8759999999999998E-2</v>
       </c>
       <c r="J28">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="K28" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L28">
-        <v>550000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>600000000</v>
+      </c>
+      <c r="M28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="E29" s="1">
-        <v>3.875E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="F29" s="3">
-        <v>47802</v>
+        <v>47727</v>
       </c>
       <c r="G29">
         <v>2030</v>
       </c>
       <c r="H29" s="1">
-        <v>6.0019999999999997E-2</v>
+        <v>6.1379999999999997E-2</v>
       </c>
       <c r="I29" s="1">
-        <v>5.8000000000000003E-2</v>
+        <v>5.7230000000000003E-2</v>
       </c>
       <c r="J29">
         <v>2000</v>
       </c>
       <c r="K29" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L29">
-        <v>650000000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>750000000</v>
+      </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E30" s="1">
-        <v>4.7E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="F30" s="3">
-        <v>47763</v>
+        <v>47514</v>
       </c>
       <c r="G30">
         <v>2030</v>
       </c>
       <c r="H30" s="1">
-        <v>5.2499999999999998E-2</v>
+        <v>9.4950000000000007E-2</v>
       </c>
       <c r="I30" s="1">
-        <v>4.8759999999999998E-2</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="J30">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="K30" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="L30">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>550000000</v>
+      </c>
+      <c r="M30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="E31" s="1">
-        <v>5.5E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F31" s="3">
-        <v>47727</v>
+        <v>47485</v>
       </c>
       <c r="G31">
         <v>2030</v>
       </c>
       <c r="H31" s="1">
-        <v>6.1379999999999997E-2</v>
+        <v>5.5079999999999997E-2</v>
       </c>
       <c r="I31" s="1">
-        <v>5.7230000000000003E-2</v>
+        <v>5.5449999999999999E-2</v>
       </c>
       <c r="J31">
         <v>2000</v>
       </c>
       <c r="K31" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L31">
         <v>750000000</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E32" s="1">
-        <v>8.7499999999999994E-2</v>
+        <v>5.8749999999999997E-2</v>
       </c>
       <c r="F32" s="3">
-        <v>47514</v>
+        <v>47557</v>
       </c>
       <c r="G32">
         <v>2030</v>
       </c>
       <c r="H32" s="1">
-        <v>9.4950000000000007E-2</v>
+        <v>5.885E-2</v>
       </c>
       <c r="I32" s="1">
-        <v>8.9499999999999996E-2</v>
+        <v>5.8939999999999999E-2</v>
       </c>
       <c r="J32">
-        <v>200000</v>
+        <v>2000</v>
       </c>
       <c r="K32" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L32">
-        <v>550000000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>425000000</v>
+      </c>
+      <c r="M32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="E33" s="1">
-        <v>7.0000000000000007E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F33" s="3">
-        <v>47485</v>
+        <v>47757</v>
       </c>
       <c r="G33">
         <v>2030</v>
       </c>
       <c r="H33" s="1">
-        <v>5.5079999999999997E-2</v>
+        <v>5.5129999999999998E-2</v>
       </c>
       <c r="I33" s="1">
-        <v>5.5449999999999999E-2</v>
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="J33">
         <v>2000</v>
       </c>
       <c r="K33" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="L33">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>75000000</v>
+      </c>
+      <c r="M33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="E34" s="1">
-        <v>5.8749999999999997E-2</v>
-      </c>
-      <c r="F34" s="3">
-        <v>47557</v>
+        <v>5.0930000000000003E-2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>168</v>
       </c>
       <c r="G34">
         <v>2030</v>
       </c>
       <c r="H34" s="1">
-        <v>5.885E-2</v>
+        <v>5.3679999999999999E-2</v>
       </c>
       <c r="I34" s="1">
-        <v>5.8939999999999999E-2</v>
+        <v>5.067E-2</v>
       </c>
       <c r="J34">
         <v>2000</v>
       </c>
       <c r="K34" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L34">
-        <v>425000000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>375896000</v>
+      </c>
+      <c r="M34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>145</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E35" s="1">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F35" s="3">
-        <v>47757</v>
+        <v>2.7E-2</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>169</v>
       </c>
       <c r="G35">
         <v>2030</v>
       </c>
       <c r="H35" s="1">
-        <v>5.5129999999999998E-2</v>
+        <v>5.2819999999999999E-2</v>
       </c>
       <c r="I35" s="1">
-        <v>5.1999999999999998E-2</v>
+        <v>5.0310000000000001E-2</v>
       </c>
       <c r="J35">
         <v>2000</v>
       </c>
       <c r="K35" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="L35">
-        <v>75000000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1449500000</v>
+      </c>
+      <c r="M35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>177</v>
+        <v>63</v>
       </c>
       <c r="E36" s="1">
-        <v>5.0930000000000003E-2</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="G36">
         <v>2030</v>
       </c>
       <c r="H36" s="1">
-        <v>5.3679999999999999E-2</v>
+        <v>4.7690000000000003E-2</v>
       </c>
       <c r="I36" s="1">
-        <v>5.067E-2</v>
+        <v>4.5809999999999997E-2</v>
       </c>
       <c r="J36">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="K36" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L36">
-        <v>375896000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>750000000</v>
+      </c>
+      <c r="M36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>154</v>
+        <v>94</v>
       </c>
       <c r="E37" s="1">
-        <v>2.7E-2</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>179</v>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F37" s="3">
+        <v>47702</v>
       </c>
       <c r="G37">
         <v>2030</v>
       </c>
       <c r="H37" s="1">
-        <v>5.2819999999999999E-2</v>
+        <v>5.1580000000000001E-2</v>
       </c>
       <c r="I37" s="1">
-        <v>5.0310000000000001E-2</v>
+        <v>4.827E-2</v>
       </c>
       <c r="J37">
         <v>2000</v>
       </c>
       <c r="K37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L37">
-        <v>1449500000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1500000000</v>
+      </c>
+      <c r="M37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E38" s="1">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>180</v>
+        <v>4.3749999999999997E-2</v>
+      </c>
+      <c r="F38" s="3">
+        <v>47574</v>
       </c>
       <c r="G38">
         <v>2030</v>
       </c>
       <c r="H38" s="1">
-        <v>4.7690000000000003E-2</v>
+        <v>6.2100000000000002E-2</v>
       </c>
       <c r="I38" s="1">
-        <v>4.5809999999999997E-2</v>
+        <v>5.8110000000000002E-2</v>
       </c>
       <c r="J38">
-        <v>200000</v>
+        <v>2000</v>
       </c>
       <c r="K38" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L38">
-        <v>750000000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>500000000</v>
+      </c>
+      <c r="M38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E39" s="1">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="F39" s="3">
-        <v>47702</v>
+        <v>0.03</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>173</v>
       </c>
       <c r="G39">
         <v>2030</v>
       </c>
       <c r="H39" s="1">
-        <v>5.1580000000000001E-2</v>
+        <v>5.7750000000000003E-2</v>
       </c>
       <c r="I39" s="1">
-        <v>4.827E-2</v>
+        <v>5.6869999999999997E-2</v>
       </c>
       <c r="J39">
         <v>2000</v>
       </c>
       <c r="K39" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="L39">
-        <v>1500000000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2200000000</v>
+      </c>
+      <c r="M39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="C40" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="E40" s="1">
-        <v>4.3749999999999997E-2</v>
+        <v>3.6249999999999998E-2</v>
       </c>
       <c r="F40" s="3">
-        <v>47574</v>
+        <v>47618</v>
       </c>
       <c r="G40">
         <v>2030</v>
       </c>
       <c r="H40" s="1">
-        <v>6.2100000000000002E-2</v>
+        <v>5.2109999999999997E-2</v>
       </c>
       <c r="I40" s="1">
-        <v>5.8110000000000002E-2</v>
+        <v>5.253E-2</v>
       </c>
       <c r="J40">
         <v>2000</v>
       </c>
       <c r="K40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L40">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>917517000</v>
+      </c>
+      <c r="M40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>182</v>
+        <v>62</v>
       </c>
       <c r="B41" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="E41" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>183</v>
+        <v>0.05</v>
+      </c>
+      <c r="F41" s="3">
+        <v>47804</v>
       </c>
       <c r="G41">
         <v>2030</v>
       </c>
       <c r="H41" s="1">
-        <v>5.7750000000000003E-2</v>
+        <v>5.391E-2</v>
       </c>
       <c r="I41" s="1">
-        <v>5.6869999999999997E-2</v>
+        <v>4.9239999999999999E-2</v>
       </c>
       <c r="J41">
         <v>2000</v>
       </c>
       <c r="K41" t="s">
+        <v>104</v>
+      </c>
+      <c r="L41">
+        <v>600000000</v>
+      </c>
+      <c r="M41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" t="s">
+        <v>166</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="1">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="F42" s="3">
+        <v>47863</v>
+      </c>
+      <c r="G42">
+        <v>2031</v>
+      </c>
+      <c r="H42" s="1">
+        <v>5.423E-2</v>
+      </c>
+      <c r="I42" s="1">
+        <v>5.1090000000000003E-2</v>
+      </c>
+      <c r="J42">
+        <v>2000</v>
+      </c>
+      <c r="K42" t="s">
+        <v>105</v>
+      </c>
+      <c r="L42">
+        <v>650000000</v>
+      </c>
+      <c r="M42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" t="s">
+        <v>98</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="F43" s="3">
+        <v>47851</v>
+      </c>
+      <c r="G43">
+        <v>2031</v>
+      </c>
+      <c r="H43" s="1">
+        <v>5.9319999999999998E-2</v>
+      </c>
+      <c r="I43" s="1">
+        <v>5.6680000000000001E-2</v>
+      </c>
+      <c r="J43">
+        <v>2000</v>
+      </c>
+      <c r="K43" t="s">
+        <v>106</v>
+      </c>
+      <c r="L43">
+        <v>2200000000</v>
+      </c>
+      <c r="M43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44" t="s">
         <v>107</v>
       </c>
-      <c r="L41">
-        <v>2200000000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>108</v>
-      </c>
-      <c r="B42" t="s">
-        <v>109</v>
-      </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
-      <c r="D42" t="s">
-        <v>110</v>
-      </c>
-      <c r="E42" s="1">
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="F42" s="3">
-        <v>47618</v>
-      </c>
-      <c r="G42">
-        <v>2030</v>
-      </c>
-      <c r="H42" s="1">
-        <v>5.2109999999999997E-2</v>
-      </c>
-      <c r="I42" s="1">
-        <v>5.253E-2</v>
-      </c>
-      <c r="J42">
-        <v>2000</v>
-      </c>
-      <c r="K42" t="s">
-        <v>111</v>
-      </c>
-      <c r="L42">
-        <v>917517000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
-      <c r="D43" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F43" s="3">
-        <v>47804</v>
-      </c>
-      <c r="G43">
-        <v>2030</v>
-      </c>
-      <c r="H43" s="1">
-        <v>5.391E-2</v>
-      </c>
-      <c r="I43" s="1">
-        <v>4.9239999999999999E-2</v>
-      </c>
-      <c r="J43">
-        <v>2000</v>
-      </c>
-      <c r="K43" t="s">
-        <v>112</v>
-      </c>
-      <c r="L43">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>175</v>
+      </c>
+      <c r="E44" s="1">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="F44" s="3">
-        <v>47863</v>
       </c>
       <c r="G44">
         <v>2031</v>
       </c>
       <c r="H44" s="1">
-        <v>5.423E-2</v>
+        <v>4.8669999999999998E-2</v>
       </c>
       <c r="I44" s="1">
-        <v>5.1090000000000003E-2</v>
+        <v>4.4540000000000003E-2</v>
       </c>
       <c r="J44">
         <v>2000</v>
       </c>
       <c r="K44" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="L44">
-        <v>650000000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1000000000</v>
+      </c>
+      <c r="M44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="B45" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="E45" s="1">
-        <v>2.5000000000000001E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="F45" s="3">
-        <v>47851</v>
+        <v>47908</v>
       </c>
       <c r="G45">
         <v>2031</v>
       </c>
       <c r="H45" s="1">
-        <v>5.9319999999999998E-2</v>
+        <v>5.5660000000000001E-2</v>
       </c>
       <c r="I45" s="1">
-        <v>5.6680000000000001E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="J45">
         <v>2000</v>
       </c>
       <c r="K45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="L45">
-        <v>2200000000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>823936000</v>
+      </c>
+      <c r="M45" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="E46" s="1">
-        <v>5.2999999999999999E-2</v>
+        <v>2.726E-2</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G46">
         <v>2031</v>
       </c>
       <c r="H46" s="1">
-        <v>4.8669999999999998E-2</v>
+        <v>5.0180000000000002E-2</v>
       </c>
       <c r="I46" s="1">
-        <v>4.4540000000000003E-2</v>
+        <v>4.6289999999999998E-2</v>
       </c>
       <c r="J46">
         <v>2000</v>
       </c>
       <c r="K46" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="L46">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1250000000</v>
+      </c>
+      <c r="M46" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E47" s="1">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="F47" s="3">
-        <v>47908</v>
+        <v>3.6249999999999998E-2</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="G47">
         <v>2031</v>
       </c>
       <c r="H47" s="1">
-        <v>5.5660000000000001E-2</v>
+        <v>5.2920000000000002E-2</v>
       </c>
       <c r="I47" s="1">
-        <v>5.2999999999999999E-2</v>
+        <v>4.9070000000000003E-2</v>
       </c>
       <c r="J47">
         <v>2000</v>
       </c>
       <c r="K47" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="L47">
-        <v>823936000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>500000000</v>
+      </c>
+      <c r="M47" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="E48" s="1">
-        <v>2.726E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G48">
         <v>2031</v>
       </c>
       <c r="H48" s="1">
-        <v>5.0180000000000002E-2</v>
+        <v>8.7279999999999996E-2</v>
       </c>
       <c r="I48" s="1">
-        <v>4.6289999999999998E-2</v>
+        <v>7.0449999999999999E-2</v>
       </c>
       <c r="J48">
         <v>2000</v>
       </c>
       <c r="K48" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="L48">
-        <v>1250000000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>300000000</v>
+      </c>
+      <c r="M48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="E49" s="1">
-        <v>3.6249999999999998E-2</v>
+        <v>7.8750000000000001E-2</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G49">
         <v>2031</v>
       </c>
       <c r="H49" s="1">
-        <v>5.2920000000000002E-2</v>
+        <v>5.0860000000000002E-2</v>
       </c>
       <c r="I49" s="1">
-        <v>4.9070000000000003E-2</v>
+        <v>4.9279999999999997E-2</v>
       </c>
       <c r="J49">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K49" t="s">
+        <v>118</v>
+      </c>
+      <c r="L49">
+        <v>484677000</v>
+      </c>
+      <c r="M49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" t="s">
+        <v>119</v>
+      </c>
+      <c r="E50" s="1">
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G50">
+        <v>2032</v>
+      </c>
+      <c r="H50" s="1">
+        <v>5.6079999999999998E-2</v>
+      </c>
+      <c r="I50" s="1">
+        <v>5.2019999999999997E-2</v>
+      </c>
+      <c r="J50">
+        <v>200000</v>
+      </c>
+      <c r="K50" t="s">
         <v>120</v>
       </c>
-      <c r="L49">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>189</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="L50">
+        <v>650000000</v>
+      </c>
+      <c r="M50" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51" s="1">
+        <v>4.2790000000000002E-2</v>
+      </c>
+      <c r="F51" s="3">
+        <v>48288</v>
+      </c>
+      <c r="G51">
+        <v>2032</v>
+      </c>
+      <c r="H51" s="1">
+        <v>6.157E-2</v>
+      </c>
+      <c r="I51" s="1">
+        <v>6.1839999999999999E-2</v>
+      </c>
+      <c r="J51">
+        <v>2000</v>
+      </c>
+      <c r="K51" t="s">
         <v>121</v>
       </c>
-      <c r="C50" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="L51">
+        <v>2760600000</v>
+      </c>
+      <c r="M51" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" t="s">
         <v>122</v>
       </c>
-      <c r="E50" s="1">
-        <v>2.4E-2</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G50">
-        <v>2031</v>
-      </c>
-      <c r="H50" s="1">
-        <v>8.7279999999999996E-2</v>
-      </c>
-      <c r="I50" s="1">
-        <v>7.0449999999999999E-2</v>
-      </c>
-      <c r="J50">
-        <v>2000</v>
-      </c>
-      <c r="K50" t="s">
-        <v>123</v>
-      </c>
-      <c r="L50">
-        <v>300000000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" t="s">
-        <v>125</v>
-      </c>
-      <c r="E51" s="1">
-        <v>7.8750000000000001E-2</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G51">
-        <v>2031</v>
-      </c>
-      <c r="H51" s="1">
-        <v>5.0860000000000002E-2</v>
-      </c>
-      <c r="I51" s="1">
-        <v>4.9279999999999997E-2</v>
-      </c>
-      <c r="J51">
-        <v>1000</v>
-      </c>
-      <c r="K51" t="s">
-        <v>126</v>
-      </c>
-      <c r="L51">
-        <v>484677000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" t="s">
-        <v>28</v>
-      </c>
       <c r="C52" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="E52" s="1">
-        <v>3.3750000000000002E-2</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G52">
         <v>2032</v>
       </c>
       <c r="H52" s="1">
-        <v>5.6079999999999998E-2</v>
+        <v>5.2600000000000001E-2</v>
       </c>
       <c r="I52" s="1">
-        <v>5.2019999999999997E-2</v>
+        <v>4.9119999999999997E-2</v>
       </c>
       <c r="J52">
-        <v>200000</v>
+        <v>2000</v>
       </c>
       <c r="K52" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="L52">
-        <v>650000000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>500000000</v>
+      </c>
+      <c r="M52" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="B53" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="E53" s="1">
-        <v>4.2790000000000002E-2</v>
+        <v>5.3749999999999999E-2</v>
       </c>
       <c r="F53" s="3">
-        <v>48288</v>
+        <v>48214</v>
       </c>
       <c r="G53">
         <v>2032</v>
       </c>
       <c r="H53" s="1">
-        <v>6.157E-2</v>
+        <v>5.0970000000000001E-2</v>
       </c>
       <c r="I53" s="1">
-        <v>6.1839999999999999E-2</v>
+        <v>4.9099999999999998E-2</v>
       </c>
       <c r="J53">
         <v>2000</v>
       </c>
       <c r="K53" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="L53">
-        <v>2760600000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1000000000</v>
+      </c>
+      <c r="M53" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="E54" s="1">
-        <v>3.0499999999999999E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G54">
         <v>2032</v>
       </c>
       <c r="H54" s="1">
-        <v>5.2600000000000001E-2</v>
+        <v>5.8349999999999999E-2</v>
       </c>
       <c r="I54" s="1">
-        <v>4.9119999999999997E-2</v>
+        <v>5.6919999999999998E-2</v>
       </c>
       <c r="J54">
         <v>2000</v>
       </c>
       <c r="K54" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="L54">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>600000000</v>
+      </c>
+      <c r="M54" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="E55" s="1">
-        <v>5.3749999999999999E-2</v>
-      </c>
-      <c r="F55" s="3">
-        <v>48214</v>
+        <v>4.7419999999999997E-2</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>186</v>
       </c>
       <c r="G55">
         <v>2032</v>
       </c>
       <c r="H55" s="1">
-        <v>5.0970000000000001E-2</v>
+        <v>5.0750000000000003E-2</v>
       </c>
       <c r="I55" s="1">
-        <v>4.9099999999999998E-2</v>
+        <v>4.6850000000000003E-2</v>
       </c>
       <c r="J55">
         <v>2000</v>
       </c>
       <c r="K55" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L55">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>900000000</v>
+      </c>
+      <c r="M55" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="E56" s="1">
-        <v>6.25E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G56">
         <v>2032</v>
       </c>
       <c r="H56" s="1">
-        <v>5.8349999999999999E-2</v>
+        <v>9.0060000000000001E-2</v>
       </c>
       <c r="I56" s="1">
-        <v>5.6919999999999998E-2</v>
+        <v>7.3709999999999998E-2</v>
       </c>
       <c r="J56">
         <v>2000</v>
       </c>
       <c r="K56" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="L56">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <v>300000000</v>
+      </c>
+      <c r="M56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>143</v>
+        <v>48</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
+        <v>18</v>
       </c>
       <c r="E57" s="1">
-        <v>4.7419999999999997E-2</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>196</v>
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>48215</v>
       </c>
       <c r="G57">
         <v>2032</v>
       </c>
       <c r="H57" s="1">
-        <v>5.0750000000000003E-2</v>
+        <v>5.4879999999999998E-2</v>
       </c>
       <c r="I57" s="1">
-        <v>4.6850000000000003E-2</v>
+        <v>5.0799999999999998E-2</v>
       </c>
       <c r="J57">
         <v>2000</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L57">
-        <v>900000000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1150000000</v>
+      </c>
+      <c r="M57" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C58" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E58" s="1">
-        <v>4.7E-2</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>197</v>
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="F58" s="3">
+        <v>48224</v>
       </c>
       <c r="G58">
         <v>2032</v>
       </c>
       <c r="H58" s="1">
-        <v>9.0060000000000001E-2</v>
+        <v>5.3589999999999999E-2</v>
       </c>
       <c r="I58" s="1">
-        <v>7.3709999999999998E-2</v>
+        <v>4.793E-2</v>
       </c>
       <c r="J58">
         <v>2000</v>
       </c>
       <c r="K58" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L58">
-        <v>300000000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>500000000</v>
+      </c>
+      <c r="M58" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B59" t="s">
-        <v>137</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" s="1">
-        <v>4.7500000000000001E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="F59" s="3">
-        <v>48215</v>
+        <v>48458</v>
       </c>
       <c r="G59">
         <v>2032</v>
       </c>
       <c r="H59" s="1">
-        <v>5.4879999999999998E-2</v>
+        <v>5.5039999999999999E-2</v>
       </c>
       <c r="I59" s="1">
-        <v>5.0799999999999998E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="J59">
         <v>2000</v>
       </c>
       <c r="K59" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="L59">
-        <v>1150000000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <v>500000000</v>
+      </c>
+      <c r="M59" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="E60" s="1">
-        <v>5.6500000000000002E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="F60" s="3">
-        <v>48224</v>
+        <v>48349</v>
       </c>
       <c r="G60">
         <v>2032</v>
       </c>
       <c r="H60" s="1">
-        <v>5.3589999999999999E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="I60" s="1">
-        <v>4.793E-2</v>
+        <v>7.8100000000000003E-2</v>
       </c>
       <c r="J60">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="K60" t="s">
+        <v>134</v>
+      </c>
+      <c r="L60">
+        <v>250000000</v>
+      </c>
+      <c r="M60" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>135</v>
+      </c>
+      <c r="B61" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="1">
+        <v>6.4210000000000003E-2</v>
+      </c>
+      <c r="F61" s="3">
+        <v>48793</v>
+      </c>
+      <c r="G61">
+        <v>2033</v>
+      </c>
+      <c r="H61" s="1">
+        <v>5.2949999999999997E-2</v>
+      </c>
+      <c r="I61" s="1">
+        <v>4.99E-2</v>
+      </c>
+      <c r="J61">
+        <v>2000</v>
+      </c>
+      <c r="K61" t="s">
+        <v>137</v>
+      </c>
+      <c r="L61">
+        <v>1250000000</v>
+      </c>
+      <c r="M61" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" t="s">
+        <v>77</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" s="1">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="F62" s="3">
+        <v>49589</v>
+      </c>
+      <c r="G62">
+        <v>2035</v>
+      </c>
+      <c r="H62" s="1">
+        <v>5.9220000000000002E-2</v>
+      </c>
+      <c r="I62" s="1">
+        <v>5.6520000000000001E-2</v>
+      </c>
+      <c r="J62">
+        <v>2000</v>
+      </c>
+      <c r="K62" t="s">
+        <v>138</v>
+      </c>
+      <c r="L62">
+        <v>600000000</v>
+      </c>
+      <c r="M62" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>139</v>
+      </c>
+      <c r="B63" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>63</v>
+      </c>
+      <c r="E63" s="1">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="F63" s="3">
+        <v>49351</v>
+      </c>
+      <c r="G63">
+        <v>2035</v>
+      </c>
+      <c r="H63" s="1">
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="I63" s="1">
+        <v>5.3469999999999997E-2</v>
+      </c>
+      <c r="J63">
+        <v>2000</v>
+      </c>
+      <c r="K63" t="s">
         <v>140</v>
       </c>
-      <c r="L60">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" t="s">
-        <v>176</v>
-      </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="1">
+      <c r="L63">
+        <v>650000000</v>
+      </c>
+      <c r="M63" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>141</v>
+      </c>
+      <c r="E64" s="1">
         <v>5.5E-2</v>
       </c>
-      <c r="F61" s="3">
-        <v>48458</v>
-      </c>
-      <c r="G61">
-        <v>2032</v>
-      </c>
-      <c r="H61" s="1">
-        <v>5.5039999999999999E-2</v>
-      </c>
-      <c r="I61" s="1">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="J61">
-        <v>2000</v>
-      </c>
-      <c r="K61" t="s">
-        <v>141</v>
-      </c>
-      <c r="L61">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" t="s">
-        <v>175</v>
-      </c>
-      <c r="C62" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" t="s">
-        <v>93</v>
-      </c>
-      <c r="E62" s="1">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="F62" s="3">
-        <v>48349</v>
-      </c>
-      <c r="G62">
-        <v>2032</v>
-      </c>
-      <c r="H62" s="1">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="I62" s="1">
-        <v>7.8100000000000003E-2</v>
-      </c>
-      <c r="J62">
-        <v>1000</v>
-      </c>
-      <c r="K62" t="s">
-        <v>142</v>
-      </c>
-      <c r="L62">
-        <v>250000000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>143</v>
-      </c>
-      <c r="B63" t="s">
-        <v>118</v>
-      </c>
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
-        <v>144</v>
-      </c>
-      <c r="E63" s="1">
-        <v>6.4210000000000003E-2</v>
-      </c>
-      <c r="F63" s="3">
-        <v>48793</v>
-      </c>
-      <c r="G63">
-        <v>2033</v>
-      </c>
-      <c r="H63" s="1">
-        <v>5.2949999999999997E-2</v>
-      </c>
-      <c r="I63" s="1">
-        <v>4.99E-2</v>
-      </c>
-      <c r="J63">
-        <v>2000</v>
-      </c>
-      <c r="K63" t="s">
-        <v>145</v>
-      </c>
-      <c r="L63">
-        <v>1250000000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>14</v>
-      </c>
-      <c r="D64" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="1">
-        <v>5.3999999999999999E-2</v>
-      </c>
       <c r="F64" s="3">
-        <v>49589</v>
+        <v>49379</v>
       </c>
       <c r="G64">
         <v>2035</v>
       </c>
       <c r="H64" s="1">
-        <v>5.9220000000000002E-2</v>
+        <v>5.7180000000000002E-2</v>
       </c>
       <c r="I64" s="1">
-        <v>5.6520000000000001E-2</v>
+        <v>5.3650000000000003E-2</v>
       </c>
       <c r="J64">
         <v>2000</v>
       </c>
       <c r="K64" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="L64">
-        <v>600000000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <v>750000000</v>
+      </c>
+      <c r="M64" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="B65" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E65" s="1">
-        <v>5.9799999999999999E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F65" s="3">
-        <v>49351</v>
+        <v>49324</v>
       </c>
       <c r="G65">
         <v>2035</v>
       </c>
       <c r="H65" s="1">
-        <v>5.6500000000000002E-2</v>
+        <v>5.6770000000000001E-2</v>
       </c>
       <c r="I65" s="1">
-        <v>5.3469999999999997E-2</v>
+        <v>5.4170000000000003E-2</v>
       </c>
       <c r="J65">
         <v>2000</v>
       </c>
       <c r="K65" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="L65">
-        <v>650000000</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>149</v>
-      </c>
-      <c r="E66" s="1">
-        <v>5.5E-2</v>
-      </c>
-      <c r="F66" s="3">
-        <v>49379</v>
-      </c>
-      <c r="G66">
-        <v>2035</v>
-      </c>
-      <c r="H66" s="1">
-        <v>5.7180000000000002E-2</v>
-      </c>
-      <c r="I66" s="1">
-        <v>5.3650000000000003E-2</v>
-      </c>
-      <c r="J66">
-        <v>2000</v>
-      </c>
-      <c r="K66" t="s">
-        <v>150</v>
-      </c>
-      <c r="L66">
         <v>750000000</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="1">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="F67" s="3">
-        <v>49324</v>
-      </c>
-      <c r="G67">
-        <v>2035</v>
-      </c>
-      <c r="H67" s="1">
-        <v>5.6770000000000001E-2</v>
-      </c>
-      <c r="I67" s="1">
-        <v>5.4170000000000003E-2</v>
-      </c>
-      <c r="J67">
-        <v>2000</v>
-      </c>
-      <c r="K67" t="s">
-        <v>151</v>
-      </c>
-      <c r="L67">
-        <v>750000000</v>
+      <c r="M65" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992C3D4D-BFC2-494D-9D56-89C8F35F8A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BE0ABE-7A5F-4715-AD7A-1077DD54A78A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -569,10 +569,6 @@
     <t>Gspread</t>
   </si>
   <si>
-    <t>Outstanding
-US$</t>
-  </si>
-  <si>
     <t>Aercap Holdings</t>
   </si>
   <si>
@@ -606,7 +602,10 @@
     <t>Methanex US Operations</t>
   </si>
   <si>
-    <t>YTW t-15</t>
+    <t>Outstanding US$</t>
+  </si>
+  <si>
+    <t>YTW% t-15</t>
   </si>
 </sst>
 </file>
@@ -672,58 +671,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1105,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="P1" t="s">
         <v>170</v>
@@ -1113,7 +1061,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1163,7 +1111,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -1213,7 +1161,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1613,19 +1561,19 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" t="s">
         <v>185</v>
       </c>
-      <c r="B12" t="s">
-        <v>186</v>
-      </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F12" s="5">
         <v>5.5E-2</v>
@@ -1652,7 +1600,7 @@
         <v>2000</v>
       </c>
       <c r="N12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O12">
         <v>750000000</v>
@@ -1663,19 +1611,19 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B13" t="s">
         <v>147</v>
       </c>
       <c r="C13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F13" s="5">
         <v>4.4999999999999998E-2</v>
@@ -1702,7 +1650,7 @@
         <v>200000</v>
       </c>
       <c r="N13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="O13">
         <v>1250000000</v>
@@ -1813,7 +1761,7 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
@@ -3813,7 +3761,7 @@
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B56" t="s">
         <v>168</v>

--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7B9C9-7301-420D-A5D2-5C6AF0997A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F91A523-6618-4D62-96C7-1494A64AAC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="162">
   <si>
     <t>Industry</t>
   </si>
@@ -514,106 +517,19 @@
     <t>US674599EL59</t>
   </si>
   <si>
-    <t>-/BB+/-</t>
-  </si>
-  <si>
-    <t>Pharmaceutical Preparation and Biotechnology</t>
-  </si>
-  <si>
-    <t>-/BB+/BBB</t>
-  </si>
-  <si>
-    <t>22/06/2027</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Baa3/BBB-/BBB-</t>
-  </si>
-  <si>
-    <t>Infrastructure and Special Construction</t>
-  </si>
-  <si>
-    <t>Ba1/BB+/Withdrawn</t>
-  </si>
-  <si>
-    <t>15/09/2028</t>
-  </si>
-  <si>
-    <t>13/06/2029</t>
-  </si>
-  <si>
-    <t>Fertilizers</t>
-  </si>
-  <si>
-    <t>15/12/2029</t>
-  </si>
-  <si>
-    <t>Withdrawn/BBB-/BBB-</t>
-  </si>
-  <si>
-    <t>Ba1/BB/BB</t>
-  </si>
-  <si>
-    <t>15/01/2030</t>
-  </si>
-  <si>
-    <t>22/06/2030</t>
-  </si>
-  <si>
-    <t>28/07/2030</t>
-  </si>
-  <si>
-    <t>Ferrous metals</t>
-  </si>
-  <si>
-    <t>Insurance and Reinsurance</t>
-  </si>
-  <si>
-    <t>15/10/2030</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>-/BBB-/BBB</t>
-  </si>
-  <si>
-    <t>15/01/2031</t>
-  </si>
-  <si>
-    <t>25/03/2031</t>
-  </si>
-  <si>
-    <t>15/05/2031</t>
-  </si>
-  <si>
-    <t>Domestic Appliances</t>
-  </si>
-  <si>
-    <t>15/09/2031</t>
-  </si>
-  <si>
-    <t>15/03/2032</t>
-  </si>
-  <si>
-    <t>Withdrawn/BB+/BBB-</t>
-  </si>
-  <si>
-    <t>Methanex US Operations</t>
-  </si>
-  <si>
-    <t>Food and Beverage Production</t>
-  </si>
-  <si>
-    <t>-/-/BB+</t>
-  </si>
-  <si>
-    <t>16/03/2032</t>
-  </si>
-  <si>
-    <t>14/05/2032</t>
+    <t>Falabella</t>
+  </si>
+  <si>
+    <t>USP82290AR17</t>
+  </si>
+  <si>
+    <t>US277432BB57</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -/BB+/BBB-</t>
+  </si>
+  <si>
+    <t>USP3984LAA81</t>
   </si>
 </sst>
 </file>
@@ -672,7 +588,7 @@
       <name val="Comfortaa"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -695,6 +611,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -813,7 +735,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -933,6 +855,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1109,7 +1034,7 @@
         <name val="Comfortaa"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="168" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1179,7 +1104,7 @@
         <name val="Comfortaa"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
+      <numFmt numFmtId="168" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1522,19 +1447,19 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <right style="medium">
           <color indexed="64"/>
         </right>
         <top style="medium">
           <color indexed="64"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -1550,9 +1475,1954 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Ladder"/>
+      <sheetName val="Dinamica"/>
+      <sheetName val="Ladder (including ARG issuers)"/>
+      <sheetName val="Ladder (incl ARG) 1 bond"/>
+      <sheetName val="1Q24"/>
+      <sheetName val="2Q24"/>
+      <sheetName val="3Q24"/>
+      <sheetName val="4Q24"/>
+      <sheetName val="1Q25"/>
+      <sheetName val="2Q25"/>
+      <sheetName val="Cbonds export 05.20.2025"/>
+      <sheetName val="3Q25"/>
+      <sheetName val="4Q25"/>
+      <sheetName val="1Q26"/>
+      <sheetName val="ETFs Blackrock"/>
+      <sheetName val="Prospects &amp; Others"/>
+      <sheetName val="Bonos Lantia 2025"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>ISSUER</v>
+          </cell>
+          <cell r="C14" t="str">
+            <v>ISSUER INDUSTRY</v>
+          </cell>
+          <cell r="D14" t="str">
+            <v>ISSUER RATING M/S&amp;P/F FOREIGN CURRENCY</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>COUPON, % P.A.</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>MATURITY DATE</v>
+          </cell>
+          <cell r="J14" t="str">
+            <v>FACE VALUE / MINIMUM SETTLEMENT AMOUNT</v>
+          </cell>
+          <cell r="K14" t="str">
+            <v>ISIN</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Warner Bros. Discovery</v>
+          </cell>
+          <cell r="C15" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D15" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="F15">
+            <v>3.95E-2</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>15/06/2025</v>
+          </cell>
+          <cell r="J15">
+            <v>2000</v>
+          </cell>
+          <cell r="K15" t="str">
+            <v>US811065AG61</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Viatris</v>
+          </cell>
+          <cell r="C16" t="str">
+            <v>Pharmaceutical Preparation and Biotechnology</v>
+          </cell>
+          <cell r="D16" t="str">
+            <v>-/BB+/BBB</v>
+          </cell>
+          <cell r="F16">
+            <v>1.6500000000000001E-2</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>22/06/2025</v>
+          </cell>
+          <cell r="J16">
+            <v>2000</v>
+          </cell>
+          <cell r="K16" t="str">
+            <v>US92556VAB27</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>Aercap Holdings</v>
+          </cell>
+          <cell r="C17" t="str">
+            <v>Leasing and Rental</v>
+          </cell>
+          <cell r="D17" t="str">
+            <v>-/BBB+/BBB+</v>
+          </cell>
+          <cell r="F17">
+            <v>6.5000000000000002E-2</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v>15/07/2025</v>
+          </cell>
+          <cell r="J17">
+            <v>150000</v>
+          </cell>
+          <cell r="K17" t="str">
+            <v>US00774MAN56</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Xerox Holdings Corporation</v>
+          </cell>
+          <cell r="C18" t="str">
+            <v>IT equipment</v>
+          </cell>
+          <cell r="D18" t="str">
+            <v>B2/B+/Withdrawn</v>
+          </cell>
+          <cell r="F18">
+            <v>0.05</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v>15/08/2025</v>
+          </cell>
+          <cell r="J18">
+            <v>2000</v>
+          </cell>
+          <cell r="K18" t="str">
+            <v>USU98401AA75</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>General Motors</v>
+          </cell>
+          <cell r="C19" t="str">
+            <v>Motor Vehicle Production</v>
+          </cell>
+          <cell r="D19" t="str">
+            <v>-/BBB/BBB</v>
+          </cell>
+          <cell r="F19">
+            <v>6.1249999999999999E-2</v>
+          </cell>
+          <cell r="G19">
+            <v>45667</v>
+          </cell>
+          <cell r="J19">
+            <v>2000</v>
+          </cell>
+          <cell r="K19" t="str">
+            <v>US37045VAV27</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Ford Motor</v>
+          </cell>
+          <cell r="C20" t="str">
+            <v>Motor Vehicle Production</v>
+          </cell>
+          <cell r="D20" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="F20">
+            <v>7.1249999999999994E-2</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>15/11/2025</v>
+          </cell>
+          <cell r="J20">
+            <v>5000</v>
+          </cell>
+          <cell r="K20" t="str">
+            <v>US345370BN94</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>Telecom Argentina</v>
+          </cell>
+          <cell r="C21" t="str">
+            <v>Communication Services</v>
+          </cell>
+          <cell r="D21" t="str">
+            <v>Caa1/B-/B-</v>
+          </cell>
+          <cell r="F21">
+            <v>0.08</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>18/07/2026</v>
+          </cell>
+          <cell r="J21">
+            <v>1000</v>
+          </cell>
+          <cell r="K21" t="str">
+            <v>USP9028NAV30</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Banco Galicia</v>
+          </cell>
+          <cell r="C22" t="str">
+            <v>Banks</v>
+          </cell>
+          <cell r="D22" t="str">
+            <v>Caa2/B-/-</v>
+          </cell>
+          <cell r="F22">
+            <v>7.9619999999999996E-2</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v>19/07/2026</v>
+          </cell>
+          <cell r="J22">
+            <v>200000</v>
+          </cell>
+          <cell r="K22" t="str">
+            <v>USP0R66CAA64</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Sirius XM Radio Inc</v>
+          </cell>
+          <cell r="C23" t="str">
+            <v>Other sectors</v>
+          </cell>
+          <cell r="D23" t="str">
+            <v>-/-/-</v>
+          </cell>
+          <cell r="F23">
+            <v>3.125E-2</v>
+          </cell>
+          <cell r="G23">
+            <v>46031</v>
+          </cell>
+          <cell r="J23">
+            <v>2000</v>
+          </cell>
+          <cell r="K23" t="str">
+            <v>USU82764AU27</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>FMC</v>
+          </cell>
+          <cell r="C24" t="str">
+            <v>Fertilizers</v>
+          </cell>
+          <cell r="D24" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="F24">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="G24">
+            <v>46032</v>
+          </cell>
+          <cell r="J24">
+            <v>2000</v>
+          </cell>
+          <cell r="K24" t="str">
+            <v>US302491AT29</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Aercap Holdings</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Leasing and Rental</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>-/BBB+/BBB+</v>
+          </cell>
+          <cell r="F25">
+            <v>2.4500000000000001E-2</v>
+          </cell>
+          <cell r="G25" t="str">
+            <v>29/10/2026</v>
+          </cell>
+          <cell r="J25">
+            <v>150000</v>
+          </cell>
+          <cell r="K25" t="str">
+            <v>US00774MAV72</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>Ford Motor</v>
+          </cell>
+          <cell r="C26" t="str">
+            <v>Motor Vehicle Production</v>
+          </cell>
+          <cell r="D26" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="F26">
+            <v>4.3459999999999999E-2</v>
+          </cell>
+          <cell r="G26">
+            <v>46246</v>
+          </cell>
+          <cell r="J26">
+            <v>2000</v>
+          </cell>
+          <cell r="K26" t="str">
+            <v>US345370CR99</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>Eastman Chemical</v>
+          </cell>
+          <cell r="C27" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D27" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="F27">
+            <v>7.5999999999999998E-2</v>
+          </cell>
+          <cell r="G27">
+            <v>46389</v>
+          </cell>
+          <cell r="J27">
+            <v>1000</v>
+          </cell>
+          <cell r="K27" t="str">
+            <v>US277432AD23</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>Chemours</v>
+          </cell>
+          <cell r="C28" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D28" t="str">
+            <v>Ba3/BB-/-</v>
+          </cell>
+          <cell r="F28">
+            <v>5.3749999999999999E-2</v>
+          </cell>
+          <cell r="G28" t="str">
+            <v>15/05/2027</v>
+          </cell>
+          <cell r="J28">
+            <v>2000</v>
+          </cell>
+          <cell r="K28" t="str">
+            <v>US163851AE83</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>Ally Financial</v>
+          </cell>
+          <cell r="C29" t="str">
+            <v>Banks</v>
+          </cell>
+          <cell r="D29" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F29">
+            <v>4.7500000000000001E-2</v>
+          </cell>
+          <cell r="G29">
+            <v>46636</v>
+          </cell>
+          <cell r="J29">
+            <v>2000</v>
+          </cell>
+          <cell r="K29" t="str">
+            <v>US02005NBQ25</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>Viatris</v>
+          </cell>
+          <cell r="C30" t="str">
+            <v>Pharmaceutical Preparation and Biotechnology</v>
+          </cell>
+          <cell r="D30" t="str">
+            <v>-/BB+/BBB</v>
+          </cell>
+          <cell r="F30">
+            <v>2.3E-2</v>
+          </cell>
+          <cell r="G30" t="str">
+            <v>22/06/2027</v>
+          </cell>
+          <cell r="J30">
+            <v>2000</v>
+          </cell>
+          <cell r="K30" t="str">
+            <v>US92556VAC00</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>Viatris</v>
+          </cell>
+          <cell r="C31" t="str">
+            <v>Pharmaceutical Preparation and Biotechnology</v>
+          </cell>
+          <cell r="D31" t="str">
+            <v>-/BB+/BBB</v>
+          </cell>
+          <cell r="F31">
+            <v>2.3E-2</v>
+          </cell>
+          <cell r="G31" t="str">
+            <v>22/06/2027</v>
+          </cell>
+          <cell r="J31">
+            <v>2000</v>
+          </cell>
+          <cell r="K31" t="str">
+            <v>USU9156BAC91</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>YPF</v>
+          </cell>
+          <cell r="C32" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D32" t="str">
+            <v>Caa1/B-/CCC+</v>
+          </cell>
+          <cell r="F32">
+            <v>6.9500000000000006E-2</v>
+          </cell>
+          <cell r="G32" t="str">
+            <v>21/07/2027</v>
+          </cell>
+          <cell r="J32">
+            <v>10000</v>
+          </cell>
+          <cell r="K32" t="str">
+            <v>USP989MJBL47</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Sirius XM Holdings</v>
+          </cell>
+          <cell r="C33" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D33" t="str">
+            <v>-/BB+/-</v>
+          </cell>
+          <cell r="F33">
+            <v>0.05</v>
+          </cell>
+          <cell r="G33">
+            <v>46395</v>
+          </cell>
+          <cell r="J33">
+            <v>2000</v>
+          </cell>
+          <cell r="K33" t="str">
+            <v>USU82764AM01</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>General Motors</v>
+          </cell>
+          <cell r="C34" t="str">
+            <v>Motor Vehicle Production</v>
+          </cell>
+          <cell r="D34" t="str">
+            <v>-/BBB/BBB</v>
+          </cell>
+          <cell r="F34">
+            <v>6.8000000000000005E-2</v>
+          </cell>
+          <cell r="G34">
+            <v>46397</v>
+          </cell>
+          <cell r="J34">
+            <v>2000</v>
+          </cell>
+          <cell r="K34" t="str">
+            <v>US37045VAU44</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Methanex</v>
+          </cell>
+          <cell r="C35" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D35" t="str">
+            <v>Ba1/BB/BB+</v>
+          </cell>
+          <cell r="F35">
+            <v>5.1249999999999997E-2</v>
+          </cell>
+          <cell r="G35" t="str">
+            <v>15/10/2027</v>
+          </cell>
+          <cell r="J35">
+            <v>2000</v>
+          </cell>
+          <cell r="K35" t="str">
+            <v>US59151KAM09</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>Falabella</v>
+          </cell>
+          <cell r="C36" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D36" t="str">
+            <v>-/BB+/BB+</v>
+          </cell>
+          <cell r="F36">
+            <v>3.7499999999999999E-2</v>
+          </cell>
+          <cell r="G36" t="str">
+            <v>30/10/2027</v>
+          </cell>
+          <cell r="J36">
+            <v>200000</v>
+          </cell>
+          <cell r="K36" t="str">
+            <v>USP82290AR17</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>Braskem</v>
+          </cell>
+          <cell r="C37" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D37" t="str">
+            <v>Ba3/BB+/BB+</v>
+          </cell>
+          <cell r="F37">
+            <v>4.4999999999999998E-2</v>
+          </cell>
+          <cell r="G37">
+            <v>47027</v>
+          </cell>
+          <cell r="J37">
+            <v>200000</v>
+          </cell>
+          <cell r="K37" t="str">
+            <v>USN15516AB83</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>Embraer</v>
+          </cell>
+          <cell r="C38" t="str">
+            <v>Aircraft Production and Defense</v>
+          </cell>
+          <cell r="D38" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F38">
+            <v>6.9500000000000006E-2</v>
+          </cell>
+          <cell r="G38" t="str">
+            <v>17/01/2028</v>
+          </cell>
+          <cell r="J38">
+            <v>200000</v>
+          </cell>
+          <cell r="K38" t="str">
+            <v>USN29505AA70</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>Petrobras</v>
+          </cell>
+          <cell r="C39" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D39" t="str">
+            <v>Ba1/BB/BB</v>
+          </cell>
+          <cell r="F39">
+            <v>5.9990000000000002E-2</v>
+          </cell>
+          <cell r="G39" t="str">
+            <v>27/01/2028</v>
+          </cell>
+          <cell r="J39">
+            <v>2000</v>
+          </cell>
+          <cell r="K39" t="str">
+            <v>USN6945AAK36</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>EQT</v>
+          </cell>
+          <cell r="C40" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D40" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F40">
+            <v>5.7000000000000002E-2</v>
+          </cell>
+          <cell r="G40">
+            <v>46756</v>
+          </cell>
+          <cell r="J40">
+            <v>2000</v>
+          </cell>
+          <cell r="K40" t="str">
+            <v>US26884LAQ23</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>Xerox Holdings Corporation</v>
+          </cell>
+          <cell r="C41" t="str">
+            <v>IT equipment</v>
+          </cell>
+          <cell r="D41" t="str">
+            <v>B2/B+/Withdrawn</v>
+          </cell>
+          <cell r="F41">
+            <v>5.5E-2</v>
+          </cell>
+          <cell r="G41" t="str">
+            <v>15/08/2028</v>
+          </cell>
+          <cell r="J41">
+            <v>2000</v>
+          </cell>
+          <cell r="K41" t="str">
+            <v>USU98401AB58</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>Fluor</v>
+          </cell>
+          <cell r="C42" t="str">
+            <v>Infrastructure and Special Construction</v>
+          </cell>
+          <cell r="D42" t="str">
+            <v>Ba1/BB+/Withdrawn</v>
+          </cell>
+          <cell r="F42">
+            <v>4.2500000000000003E-2</v>
+          </cell>
+          <cell r="G42" t="str">
+            <v>15/09/2028</v>
+          </cell>
+          <cell r="J42">
+            <v>2000</v>
+          </cell>
+          <cell r="K42" t="str">
+            <v>US343412AF90</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>General Motors</v>
+          </cell>
+          <cell r="C43" t="str">
+            <v>Motor Vehicle Production</v>
+          </cell>
+          <cell r="D43" t="str">
+            <v>-/BBB/BBB</v>
+          </cell>
+          <cell r="F43">
+            <v>0.05</v>
+          </cell>
+          <cell r="G43">
+            <v>46762</v>
+          </cell>
+          <cell r="J43">
+            <v>2000</v>
+          </cell>
+          <cell r="K43" t="str">
+            <v>US37045VAS97</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>Mercer International</v>
+          </cell>
+          <cell r="C44" t="str">
+            <v>Pulp, Paper and Wood</v>
+          </cell>
+          <cell r="D44" t="str">
+            <v>B2/B/B+</v>
+          </cell>
+          <cell r="F44">
+            <v>0.12875</v>
+          </cell>
+          <cell r="G44">
+            <v>46762</v>
+          </cell>
+          <cell r="J44">
+            <v>2000</v>
+          </cell>
+          <cell r="K44" t="str">
+            <v>USU58839AL29</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>Ally Financial</v>
+          </cell>
+          <cell r="C45" t="str">
+            <v>Banks</v>
+          </cell>
+          <cell r="D45" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F45">
+            <v>2.1999999999999999E-2</v>
+          </cell>
+          <cell r="G45">
+            <v>46794</v>
+          </cell>
+          <cell r="J45">
+            <v>2000</v>
+          </cell>
+          <cell r="K45" t="str">
+            <v>US02005NBP42</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>Eastman Chemical</v>
+          </cell>
+          <cell r="C46" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D46" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="F46">
+            <v>4.4999999999999998E-2</v>
+          </cell>
+          <cell r="G46">
+            <v>46764</v>
+          </cell>
+          <cell r="J46">
+            <v>2000</v>
+          </cell>
+          <cell r="K46" t="str">
+            <v>US277432AW04</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>EQT</v>
+          </cell>
+          <cell r="C47" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D47" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F47">
+            <v>0.05</v>
+          </cell>
+          <cell r="G47" t="str">
+            <v>15/01/2029</v>
+          </cell>
+          <cell r="J47">
+            <v>2000</v>
+          </cell>
+          <cell r="K47" t="str">
+            <v>US26884LAL36</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>Petrobras</v>
+          </cell>
+          <cell r="C48" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D48" t="str">
+            <v>Ba1/BB/BB</v>
+          </cell>
+          <cell r="F48">
+            <v>5.7500000000000002E-2</v>
+          </cell>
+          <cell r="G48">
+            <v>47120</v>
+          </cell>
+          <cell r="J48">
+            <v>2000</v>
+          </cell>
+          <cell r="K48" t="str">
+            <v>US71647NAZ24</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>Occidental Petroleum</v>
+          </cell>
+          <cell r="C49" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D49" t="str">
+            <v>Withdrawn/BB+/BBB-</v>
+          </cell>
+          <cell r="F49">
+            <v>8.4500000000000006E-2</v>
+          </cell>
+          <cell r="G49" t="str">
+            <v>15/02/2029</v>
+          </cell>
+          <cell r="J49">
+            <v>1000</v>
+          </cell>
+          <cell r="K49" t="str">
+            <v>US674599BT13</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>Valero Energy</v>
+          </cell>
+          <cell r="C50" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D50" t="str">
+            <v>-/BBB/BBB</v>
+          </cell>
+          <cell r="F50">
+            <v>0.04</v>
+          </cell>
+          <cell r="G50">
+            <v>47122</v>
+          </cell>
+          <cell r="J50">
+            <v>2000</v>
+          </cell>
+          <cell r="K50" t="str">
+            <v>US91913YAW03</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>Discovery Communications, LLC</v>
+          </cell>
+          <cell r="C51" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D51" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F51">
+            <v>4.1250000000000002E-2</v>
+          </cell>
+          <cell r="G51" t="str">
+            <v>15/05/2029</v>
+          </cell>
+          <cell r="J51">
+            <v>2000</v>
+          </cell>
+          <cell r="K51" t="str">
+            <v>US25470DBF50</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>Ally Financial</v>
+          </cell>
+          <cell r="C52" t="str">
+            <v>Banks</v>
+          </cell>
+          <cell r="D52" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F52">
+            <v>6.9919999999999996E-2</v>
+          </cell>
+          <cell r="G52" t="str">
+            <v>13/06/2029</v>
+          </cell>
+          <cell r="J52">
+            <v>2000</v>
+          </cell>
+          <cell r="K52" t="str">
+            <v>US02005NBT63</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>Eastman Chemical</v>
+          </cell>
+          <cell r="C53" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D53" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="F53">
+            <v>0.05</v>
+          </cell>
+          <cell r="G53">
+            <v>47126</v>
+          </cell>
+          <cell r="J53">
+            <v>2000</v>
+          </cell>
+          <cell r="K53" t="str">
+            <v>US277432AZ35</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>Olin</v>
+          </cell>
+          <cell r="C54" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D54" t="str">
+            <v>-/BB+/BBB-</v>
+          </cell>
+          <cell r="F54">
+            <v>5.6250000000000001E-2</v>
+          </cell>
+          <cell r="G54">
+            <v>47126</v>
+          </cell>
+          <cell r="J54">
+            <v>1000</v>
+          </cell>
+          <cell r="K54" t="str">
+            <v>US680665AL00</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>Fluor</v>
+          </cell>
+          <cell r="C55" t="str">
+            <v>Infrastructure and Special Construction</v>
+          </cell>
+          <cell r="D55" t="str">
+            <v>Ba1/BB+/Withdrawn</v>
+          </cell>
+          <cell r="F55">
+            <v>1.125E-2</v>
+          </cell>
+          <cell r="G55" t="str">
+            <v>15/08/2029</v>
+          </cell>
+          <cell r="J55">
+            <v>1000</v>
+          </cell>
+          <cell r="K55" t="str">
+            <v>US343412AJ13</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>FMC</v>
+          </cell>
+          <cell r="C56" t="str">
+            <v>Fertilizers</v>
+          </cell>
+          <cell r="D56" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="F56">
+            <v>3.4500000000000003E-2</v>
+          </cell>
+          <cell r="G56">
+            <v>47128</v>
+          </cell>
+          <cell r="J56">
+            <v>2000</v>
+          </cell>
+          <cell r="K56" t="str">
+            <v>US302491AU91</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>Centene</v>
+          </cell>
+          <cell r="C57" t="str">
+            <v>Insurance and Reinsurance</v>
+          </cell>
+          <cell r="D57" t="str">
+            <v>-/-/BBB</v>
+          </cell>
+          <cell r="F57">
+            <v>4.6249999999999999E-2</v>
+          </cell>
+          <cell r="G57" t="str">
+            <v>15/12/2029</v>
+          </cell>
+          <cell r="J57">
+            <v>2000</v>
+          </cell>
+          <cell r="K57" t="str">
+            <v>US15135BAT89</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>Methanex</v>
+          </cell>
+          <cell r="C58" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D58" t="str">
+            <v>Ba1/BB/BB+</v>
+          </cell>
+          <cell r="F58">
+            <v>5.2499999999999998E-2</v>
+          </cell>
+          <cell r="G58" t="str">
+            <v>15/12/2029</v>
+          </cell>
+          <cell r="J58">
+            <v>2000</v>
+          </cell>
+          <cell r="K58" t="str">
+            <v>US59151KAL26</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
+            <v>Petrobras</v>
+          </cell>
+          <cell r="C59" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D59" t="str">
+            <v>Ba1/BB/BB</v>
+          </cell>
+          <cell r="F59">
+            <v>5.0930000000000003E-2</v>
+          </cell>
+          <cell r="G59" t="str">
+            <v>15/01/2030</v>
+          </cell>
+          <cell r="J59">
+            <v>2000</v>
+          </cell>
+          <cell r="K59" t="str">
+            <v>US71647NBE85</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>EQT</v>
+          </cell>
+          <cell r="C60" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D60" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F60">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+          <cell r="G60">
+            <v>47485</v>
+          </cell>
+          <cell r="J60">
+            <v>2000</v>
+          </cell>
+          <cell r="K60" t="str">
+            <v>US26884LAG41</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Olin</v>
+          </cell>
+          <cell r="C61" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D61" t="str">
+            <v>-/BB+/BBB-</v>
+          </cell>
+          <cell r="F61">
+            <v>0.05</v>
+          </cell>
+          <cell r="G61">
+            <v>47485</v>
+          </cell>
+          <cell r="J61">
+            <v>1000</v>
+          </cell>
+          <cell r="K61" t="str">
+            <v>US680665AK27</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62" t="str">
+            <v>Tapestry</v>
+          </cell>
+          <cell r="C62" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D62" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="F62">
+            <v>5.0999999999999997E-2</v>
+          </cell>
+          <cell r="G62">
+            <v>47790</v>
+          </cell>
+          <cell r="J62">
+            <v>2000</v>
+          </cell>
+          <cell r="K62" t="str">
+            <v>US876030AK37</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63" t="str">
+            <v>Discovery Communications, LLC</v>
+          </cell>
+          <cell r="C63" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D63" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F63">
+            <v>3.6249999999999998E-2</v>
+          </cell>
+          <cell r="G63" t="str">
+            <v>15/05/2030</v>
+          </cell>
+          <cell r="J63">
+            <v>2000</v>
+          </cell>
+          <cell r="K63" t="str">
+            <v>US25470DBJ72</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64" t="str">
+            <v>Viatris</v>
+          </cell>
+          <cell r="C64" t="str">
+            <v>Pharmaceutical Preparation and Biotechnology</v>
+          </cell>
+          <cell r="D64" t="str">
+            <v>-/BB+/BBB</v>
+          </cell>
+          <cell r="F64">
+            <v>2.7E-2</v>
+          </cell>
+          <cell r="G64" t="str">
+            <v>22/06/2030</v>
+          </cell>
+          <cell r="J64">
+            <v>2000</v>
+          </cell>
+          <cell r="K64" t="str">
+            <v>US92556VAD82</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65" t="str">
+            <v>Vale</v>
+          </cell>
+          <cell r="C65" t="str">
+            <v>Ferrous metals</v>
+          </cell>
+          <cell r="D65" t="str">
+            <v>Baa2/BBB-/BBB</v>
+          </cell>
+          <cell r="F65">
+            <v>3.7499999999999999E-2</v>
+          </cell>
+          <cell r="G65">
+            <v>47702</v>
+          </cell>
+          <cell r="J65">
+            <v>2000</v>
+          </cell>
+          <cell r="K65" t="str">
+            <v>US91911TAQ67</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="B66" t="str">
+            <v>Occidental Petroleum</v>
+          </cell>
+          <cell r="C66" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D66" t="str">
+            <v>Withdrawn/BB+/BBB-</v>
+          </cell>
+          <cell r="F66">
+            <v>8.8749999999999996E-2</v>
+          </cell>
+          <cell r="G66" t="str">
+            <v>15/07/2030</v>
+          </cell>
+          <cell r="J66">
+            <v>2000</v>
+          </cell>
+          <cell r="K66" t="str">
+            <v>US674599EA94</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67" t="str">
+            <v>Embraer</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>Aircraft Production and Defense</v>
+          </cell>
+          <cell r="D67" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="F67">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+          <cell r="G67" t="str">
+            <v>28/07/2030</v>
+          </cell>
+          <cell r="J67">
+            <v>200000</v>
+          </cell>
+          <cell r="K67" t="str">
+            <v>USN29505AB53</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68" t="str">
+            <v>Centene</v>
+          </cell>
+          <cell r="C68" t="str">
+            <v>Insurance and Reinsurance</v>
+          </cell>
+          <cell r="D68" t="str">
+            <v>-/-/BBB</v>
+          </cell>
+          <cell r="F68">
+            <v>0.03</v>
+          </cell>
+          <cell r="G68" t="str">
+            <v>15/10/2030</v>
+          </cell>
+          <cell r="J68">
+            <v>2000</v>
+          </cell>
+          <cell r="K68" t="str">
+            <v>US15135BAW19</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69" t="str">
+            <v>Petrobras</v>
+          </cell>
+          <cell r="C69" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D69" t="str">
+            <v>Ba1/BB/BB</v>
+          </cell>
+          <cell r="F69">
+            <v>5.6000000000000001E-2</v>
+          </cell>
+          <cell r="G69">
+            <v>47908</v>
+          </cell>
+          <cell r="J69">
+            <v>2000</v>
+          </cell>
+          <cell r="K69" t="str">
+            <v>US71647NBH17</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70" t="str">
+            <v>Micron Technology</v>
+          </cell>
+          <cell r="C70" t="str">
+            <v>Semiconductors</v>
+          </cell>
+          <cell r="D70" t="str">
+            <v>-/BBB-/BBB</v>
+          </cell>
+          <cell r="F70">
+            <v>5.2999999999999999E-2</v>
+          </cell>
+          <cell r="G70" t="str">
+            <v>15/01/2031</v>
+          </cell>
+          <cell r="J70">
+            <v>2000</v>
+          </cell>
+          <cell r="K70" t="str">
+            <v>US595112CD31</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71" t="str">
+            <v>Hanesbrands</v>
+          </cell>
+          <cell r="C71" t="str">
+            <v>Apparel</v>
+          </cell>
+          <cell r="D71" t="str">
+            <v>-/B+/-</v>
+          </cell>
+          <cell r="F71">
+            <v>0.09</v>
+          </cell>
+          <cell r="G71" t="str">
+            <v>15/02/2031</v>
+          </cell>
+          <cell r="J71">
+            <v>2000</v>
+          </cell>
+          <cell r="K71" t="str">
+            <v>USU24437AG73</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72" t="str">
+            <v>Centene</v>
+          </cell>
+          <cell r="C72" t="str">
+            <v>Insurance and Reinsurance</v>
+          </cell>
+          <cell r="D72" t="str">
+            <v>-/-/BBB</v>
+          </cell>
+          <cell r="F72">
+            <v>2.5000000000000001E-2</v>
+          </cell>
+          <cell r="G72">
+            <v>47851</v>
+          </cell>
+          <cell r="J72">
+            <v>2000</v>
+          </cell>
+          <cell r="K72" t="str">
+            <v>US15135BAX91</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="B73" t="str">
+            <v>British American Tobacco</v>
+          </cell>
+          <cell r="C73" t="str">
+            <v>Tobacco</v>
+          </cell>
+          <cell r="D73" t="str">
+            <v>Baa1/BBB+/BBB+</v>
+          </cell>
+          <cell r="F73">
+            <v>2.726E-2</v>
+          </cell>
+          <cell r="G73" t="str">
+            <v>25/03/2031</v>
+          </cell>
+          <cell r="J73">
+            <v>2000</v>
+          </cell>
+          <cell r="K73" t="str">
+            <v>US05526DBS36</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="B74" t="str">
+            <v>Warner Media</v>
+          </cell>
+          <cell r="C74" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D74" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F74">
+            <v>7.6249999999999998E-2</v>
+          </cell>
+          <cell r="G74" t="str">
+            <v>15/04/2031</v>
+          </cell>
+          <cell r="J74">
+            <v>1000</v>
+          </cell>
+          <cell r="K74" t="str">
+            <v>US00184AAC99</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="B75" t="str">
+            <v>EQT</v>
+          </cell>
+          <cell r="C75" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D75" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F75">
+            <v>3.6249999999999998E-2</v>
+          </cell>
+          <cell r="G75" t="str">
+            <v>15/05/2031</v>
+          </cell>
+          <cell r="J75">
+            <v>2000</v>
+          </cell>
+          <cell r="K75" t="str">
+            <v>USU2689EAB66</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="B76" t="str">
+            <v>Whirlpool</v>
+          </cell>
+          <cell r="C76" t="str">
+            <v>Domestic Appliances</v>
+          </cell>
+          <cell r="D76" t="str">
+            <v>Ba1/BB+/BB+</v>
+          </cell>
+          <cell r="F76">
+            <v>2.4E-2</v>
+          </cell>
+          <cell r="G76" t="str">
+            <v>15/05/2031</v>
+          </cell>
+          <cell r="J76">
+            <v>2000</v>
+          </cell>
+          <cell r="K76" t="str">
+            <v>US963320AY28</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="B77" t="str">
+            <v>Occidental Petroleum</v>
+          </cell>
+          <cell r="C77" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D77" t="str">
+            <v>Withdrawn/BB+/BBB-</v>
+          </cell>
+          <cell r="F77">
+            <v>7.8750000000000001E-2</v>
+          </cell>
+          <cell r="G77" t="str">
+            <v>15/09/2031</v>
+          </cell>
+          <cell r="J77">
+            <v>1000</v>
+          </cell>
+          <cell r="K77" t="str">
+            <v>US674599DE26</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="B78" t="str">
+            <v>Occidental Petroleum</v>
+          </cell>
+          <cell r="C78" t="str">
+            <v>Oil and Gas Extraction and Refining</v>
+          </cell>
+          <cell r="D78" t="str">
+            <v>Withdrawn/BB+/BBB-</v>
+          </cell>
+          <cell r="F78">
+            <v>5.3749999999999999E-2</v>
+          </cell>
+          <cell r="G78">
+            <v>48214</v>
+          </cell>
+          <cell r="J78">
+            <v>2000</v>
+          </cell>
+          <cell r="K78" t="str">
+            <v>US674599EK76</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="B79" t="str">
+            <v>Falabella</v>
+          </cell>
+          <cell r="C79" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D79" t="str">
+            <v>-/BB+/BB+</v>
+          </cell>
+          <cell r="F79">
+            <v>3.3750000000000002E-2</v>
+          </cell>
+          <cell r="G79" t="str">
+            <v>15/01/2032</v>
+          </cell>
+          <cell r="J79">
+            <v>200000</v>
+          </cell>
+          <cell r="K79" t="str">
+            <v>USP3984LAA81</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="B80" t="str">
+            <v>Methanex US Operations</v>
+          </cell>
+          <cell r="C80" t="str">
+            <v>Food and Beverage Production</v>
+          </cell>
+          <cell r="D80" t="str">
+            <v>-/-/BB+</v>
+          </cell>
+          <cell r="F80">
+            <v>6.25E-2</v>
+          </cell>
+          <cell r="G80" t="str">
+            <v>15/03/2032</v>
+          </cell>
+          <cell r="J80">
+            <v>2000</v>
+          </cell>
+          <cell r="K80" t="str">
+            <v>USU59224AA07</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="B81" t="str">
+            <v>Tapestry</v>
+          </cell>
+          <cell r="C81" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D81" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="F81">
+            <v>3.0499999999999999E-2</v>
+          </cell>
+          <cell r="G81" t="str">
+            <v>15/03/2032</v>
+          </cell>
+          <cell r="J81">
+            <v>2000</v>
+          </cell>
+          <cell r="K81" t="str">
+            <v>US876030AA54</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82" t="str">
+            <v>British American Tobacco</v>
+          </cell>
+          <cell r="C82" t="str">
+            <v>Tobacco</v>
+          </cell>
+          <cell r="D82" t="str">
+            <v>Baa1/BBB+/BBB+</v>
+          </cell>
+          <cell r="F82">
+            <v>4.7419999999999997E-2</v>
+          </cell>
+          <cell r="G82" t="str">
+            <v>16/03/2032</v>
+          </cell>
+          <cell r="J82">
+            <v>2000</v>
+          </cell>
+          <cell r="K82" t="str">
+            <v>US05526DBW48</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83" t="str">
+            <v>Warner Media</v>
+          </cell>
+          <cell r="C83" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D83" t="str">
+            <v>Withdrawn/BBB-/BBB-</v>
+          </cell>
+          <cell r="F83">
+            <v>7.6999999999999999E-2</v>
+          </cell>
+          <cell r="G83">
+            <v>48218</v>
+          </cell>
+          <cell r="J83">
+            <v>1000</v>
+          </cell>
+          <cell r="K83" t="str">
+            <v>US00184AAG04</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="B84" t="str">
+            <v>Whirlpool</v>
+          </cell>
+          <cell r="C84" t="str">
+            <v>Domestic Appliances</v>
+          </cell>
+          <cell r="D84" t="str">
+            <v>Ba1/BB+/BB+</v>
+          </cell>
+          <cell r="F84">
+            <v>4.7E-2</v>
+          </cell>
+          <cell r="G84" t="str">
+            <v>14/05/2032</v>
+          </cell>
+          <cell r="J84">
+            <v>2000</v>
+          </cell>
+          <cell r="K84" t="str">
+            <v>US963320AZ92</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85" t="str">
+            <v>Micron Technology</v>
+          </cell>
+          <cell r="C85" t="str">
+            <v>Semiconductors</v>
+          </cell>
+          <cell r="D85" t="str">
+            <v>-/BBB-/BBB</v>
+          </cell>
+          <cell r="F85">
+            <v>5.6500000000000002E-2</v>
+          </cell>
+          <cell r="G85">
+            <v>48224</v>
+          </cell>
+          <cell r="J85">
+            <v>2000</v>
+          </cell>
+          <cell r="K85" t="str">
+            <v>US595112CG61</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="B86" t="str">
+            <v>Mercer International</v>
+          </cell>
+          <cell r="C86" t="str">
+            <v>Pulp, Paper and Wood</v>
+          </cell>
+          <cell r="D86" t="str">
+            <v>B2/B/B+</v>
+          </cell>
+          <cell r="G86" t="str">
+            <v>15/01/2026</v>
+          </cell>
+          <cell r="J86">
+            <v>2000</v>
+          </cell>
+          <cell r="K86" t="str">
+            <v>US588056AW17</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="B87" t="str">
+            <v>Hanesbrands</v>
+          </cell>
+          <cell r="C87" t="str">
+            <v>Apparel</v>
+          </cell>
+          <cell r="D87" t="str">
+            <v>-/B+/-</v>
+          </cell>
+          <cell r="G87" t="str">
+            <v>15/05/2026</v>
+          </cell>
+          <cell r="J87">
+            <v>2000</v>
+          </cell>
+          <cell r="K87" t="str">
+            <v>USU24437AE26</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="B88" t="str">
+            <v>Pampa Energia</v>
+          </cell>
+          <cell r="C88" t="str">
+            <v>Power</v>
+          </cell>
+          <cell r="D88" t="str">
+            <v>Caa1/B-/B-</v>
+          </cell>
+          <cell r="G88" t="str">
+            <v>24/01/2027</v>
+          </cell>
+          <cell r="J88">
+            <v>150000</v>
+          </cell>
+          <cell r="K88" t="str">
+            <v>USP7464EAA49</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="B89" t="str">
+            <v>Embraer</v>
+          </cell>
+          <cell r="C89" t="str">
+            <v>Aircraft Production and Defense</v>
+          </cell>
+          <cell r="D89" t="str">
+            <v>Baa3/BBB-/BBB-</v>
+          </cell>
+          <cell r="G89">
+            <v>46389</v>
+          </cell>
+          <cell r="J89">
+            <v>2000</v>
+          </cell>
+          <cell r="K89" t="str">
+            <v>US29082HAB87</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="B90" t="str">
+            <v>Olin</v>
+          </cell>
+          <cell r="C90" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D90" t="str">
+            <v>-/BB+/BBB-</v>
+          </cell>
+          <cell r="G90" t="str">
+            <v>15/09/2027</v>
+          </cell>
+          <cell r="J90">
+            <v>1000</v>
+          </cell>
+          <cell r="K90" t="str">
+            <v>US680665AJ53</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="B91" t="str">
+            <v>Tapestry</v>
+          </cell>
+          <cell r="C91" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D91" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="G91" t="str">
+            <v>27/11/2028</v>
+          </cell>
+          <cell r="J91">
+            <v>2000</v>
+          </cell>
+          <cell r="K91" t="str">
+            <v>US876030AD93</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="B92" t="str">
+            <v>Tapestry</v>
+          </cell>
+          <cell r="C92" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D92" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="G92" t="str">
+            <v>27/11/2030</v>
+          </cell>
+          <cell r="J92">
+            <v>2000</v>
+          </cell>
+          <cell r="K92" t="str">
+            <v>US876030AE76</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="B93" t="str">
+            <v>Aercap Holdings</v>
+          </cell>
+          <cell r="C93" t="str">
+            <v>Leasing and Rental</v>
+          </cell>
+          <cell r="D93" t="str">
+            <v>-/BBB+/BBB+</v>
+          </cell>
+          <cell r="G93" t="str">
+            <v>29/10/2024</v>
+          </cell>
+          <cell r="J93">
+            <v>150000</v>
+          </cell>
+          <cell r="K93" t="str">
+            <v>US00774MBB00</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="B94" t="str">
+            <v>Warner Bros. Discovery</v>
+          </cell>
+          <cell r="C94" t="str">
+            <v>Media</v>
+          </cell>
+          <cell r="D94" t="str">
+            <v>-/BBB-/BBB-</v>
+          </cell>
+          <cell r="G94" t="str">
+            <v>15/11/2024</v>
+          </cell>
+          <cell r="J94">
+            <v>2000</v>
+          </cell>
+          <cell r="K94" t="str">
+            <v>US811065AC57</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="B95" t="str">
+            <v>Fluor</v>
+          </cell>
+          <cell r="C95" t="str">
+            <v>Infrastructure and Special Construction</v>
+          </cell>
+          <cell r="D95" t="str">
+            <v>Ba1/BB+/Withdrawn</v>
+          </cell>
+          <cell r="G95" t="str">
+            <v>15/12/2024</v>
+          </cell>
+          <cell r="J95">
+            <v>2000</v>
+          </cell>
+          <cell r="K95" t="str">
+            <v>US343412AC69</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="B96" t="str">
+            <v>Falabella</v>
+          </cell>
+          <cell r="C96" t="str">
+            <v>Specialty Retailers</v>
+          </cell>
+          <cell r="D96" t="str">
+            <v>-/BB+/BB+</v>
+          </cell>
+          <cell r="G96" t="str">
+            <v>27/01/2025</v>
+          </cell>
+          <cell r="J96">
+            <v>200000</v>
+          </cell>
+          <cell r="K96" t="str">
+            <v>USP82290AG51</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="B97" t="str">
+            <v>Eastman Chemical</v>
+          </cell>
+          <cell r="C97" t="str">
+            <v>Chemical and petrochemical industry</v>
+          </cell>
+          <cell r="D97" t="str">
+            <v>Baa2/BBB/Withdrawn</v>
+          </cell>
+          <cell r="G97" t="str">
+            <v>15/03/2025</v>
+          </cell>
+          <cell r="J97">
+            <v>2000</v>
+          </cell>
+          <cell r="K97" t="str">
+            <v>US277432AR19</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}" name="Bonos" displayName="Bonos" ref="A1:P65" totalsRowShown="0" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:P65" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}" name="Bonos" displayName="Bonos" ref="A1:P68" totalsRowShown="0" headerRowBorderDxfId="18" tableBorderDxfId="17">
+  <autoFilter ref="A1:P68" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{76188F60-7837-4F00-8224-C103412ED55F}" name="Issuer" dataDxfId="16"/>
     <tableColumn id="2" xr3:uid="{A0C27939-9758-4C04-BF30-2F9454BC2BB9}" name="Industry" dataDxfId="15"/>
@@ -1892,9 +3762,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EFF2F4-11C0-433C-9540-66AEF48816EC}">
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="1"/>
     <col min="6" max="6" width="11.42578125" style="2"/>
     <col min="8" max="9" width="11.42578125" style="1"/>
@@ -1976,16 +3847,16 @@
         <v>2026</v>
       </c>
       <c r="I2" s="13">
-        <v>99.394999999999996</v>
+        <v>99.45</v>
       </c>
       <c r="J2" s="13">
+        <v>4.2832431600931002</v>
+      </c>
+      <c r="K2" s="13">
+        <v>23.380165207560001</v>
+      </c>
+      <c r="L2" s="13">
         <v>4.1399328878331998</v>
-      </c>
-      <c r="K2" s="13">
-        <v>19.69807550745</v>
-      </c>
-      <c r="L2" s="10">
-        <v>4.2700000000000002E-2</v>
       </c>
       <c r="M2" s="14">
         <v>150000</v>
@@ -2026,16 +3897,16 @@
         <v>2027</v>
       </c>
       <c r="I3" s="13">
-        <v>100.80500000000001</v>
+        <v>100.705</v>
       </c>
       <c r="J3" s="13">
+        <v>5.0570708139880001</v>
+      </c>
+      <c r="K3" s="13">
+        <v>100.39198362429001</v>
+      </c>
+      <c r="L3" s="13">
         <v>5.0021200493173996</v>
-      </c>
-      <c r="K3" s="13">
-        <v>101.8043343774</v>
-      </c>
-      <c r="L3" s="10">
-        <v>5.0720000000000001E-2</v>
       </c>
       <c r="M3" s="14">
         <v>2000</v>
@@ -2076,16 +3947,16 @@
         <v>2027</v>
       </c>
       <c r="I4" s="13">
-        <v>100.1258</v>
+        <v>100.02975000000001</v>
       </c>
       <c r="J4" s="13">
+        <v>4.6481210859009998</v>
+      </c>
+      <c r="K4" s="13">
+        <v>58.889795147146003</v>
+      </c>
+      <c r="L4" s="13">
         <v>4.5733580557196003</v>
-      </c>
-      <c r="K4" s="13">
-        <v>55.915565060120997</v>
-      </c>
-      <c r="L4" s="10">
-        <v>4.7059999999999998E-2</v>
       </c>
       <c r="M4" s="14">
         <v>150000</v>
@@ -2101,11 +3972,13 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>92</v>
+      <c r="A5" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Sirius XM Holdings</v>
+      </c>
+      <c r="B5" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Media</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>20</v>
@@ -2113,31 +3986,36 @@
       <c r="D5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>157</v>
+      <c r="E5" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BB+/-</v>
       </c>
       <c r="F5" s="10">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
         <v>0.05</v>
       </c>
       <c r="G5" s="11">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
         <v>46395</v>
       </c>
       <c r="H5" s="12">
+        <f>YEAR(G5)</f>
         <v>2027</v>
       </c>
       <c r="I5" s="13">
         <v>99.8125</v>
       </c>
       <c r="J5" s="13">
+        <v>5.2465634689330001</v>
+      </c>
+      <c r="K5" s="13">
+        <v>119.09045695966999</v>
+      </c>
+      <c r="L5" s="13">
         <v>5.2345351627822003</v>
       </c>
-      <c r="K5" s="13">
-        <v>123.63574526072</v>
-      </c>
-      <c r="L5" s="10">
-        <v>5.4760000000000003E-2</v>
-      </c>
       <c r="M5" s="14">
+        <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N5" s="18" t="s">
@@ -2151,11 +4029,13 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>158</v>
+      <c r="A6" s="19" t="str">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Viatris</v>
+      </c>
+      <c r="B6" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Pharmaceutical Preparation and Biotechnology</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>23</v>
@@ -2163,31 +4043,36 @@
       <c r="D6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>159</v>
+      <c r="E6" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BB+/BBB</v>
       </c>
       <c r="F6" s="10">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
         <v>2.3E-2</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>160</v>
+      <c r="G6" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>22/06/2027</v>
       </c>
       <c r="H6" s="12">
+        <f>YEAR(G6)</f>
         <v>2027</v>
       </c>
       <c r="I6" s="13">
-        <v>97.746499999999997</v>
+        <v>97.765500000000003</v>
       </c>
       <c r="J6" s="13">
+        <v>4.7662251119193</v>
+      </c>
+      <c r="K6" s="13">
+        <v>71.170314572267003</v>
+      </c>
+      <c r="L6" s="13">
         <v>4.6397379099930003</v>
       </c>
-      <c r="K6" s="13">
-        <v>64.842873067845005</v>
-      </c>
-      <c r="L6" s="10">
-        <v>4.8959999999999997E-2</v>
-      </c>
       <c r="M6" s="14">
+        <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N6" s="15" t="s">
@@ -2201,147 +4086,168 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="10">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G7" s="11">
-        <v>46764</v>
-      </c>
-      <c r="H7" s="12">
-        <v>2028</v>
-      </c>
-      <c r="I7" s="13">
-        <v>99.733000000000004</v>
-      </c>
-      <c r="J7" s="13">
-        <v>4.6684643359624003</v>
-      </c>
-      <c r="K7" s="13">
-        <v>57.325894601066999</v>
-      </c>
-      <c r="L7" s="10">
-        <v>4.777E-2</v>
-      </c>
-      <c r="M7" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N7" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="16">
-        <v>300000000</v>
+      <c r="A7" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Falabella</v>
+      </c>
+      <c r="B7" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Specialty Retailers</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BB+/BB+</v>
+      </c>
+      <c r="F7" s="23">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="G7" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>30/10/2027</v>
+      </c>
+      <c r="H7" s="25">
+        <f>YEAR(G7)</f>
+        <v>2027</v>
+      </c>
+      <c r="I7" s="26">
+        <v>97.98</v>
+      </c>
+      <c r="J7" s="26">
+        <v>5.4298213376745998</v>
+      </c>
+      <c r="K7" s="26">
+        <v>136.96816535228001</v>
+      </c>
+      <c r="L7" s="26">
+        <v>5.3351024156840996</v>
+      </c>
+      <c r="M7" s="27">
+        <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>200000</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="O7" s="29">
+        <v>89906000</v>
       </c>
       <c r="P7" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>161</v>
+      <c r="A8" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Eastman Chemical</v>
+      </c>
+      <c r="B8" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>162</v>
+      <c r="E8" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa2/BBB/Withdrawn</v>
       </c>
       <c r="F8" s="10">
-        <v>2.1999999999999999E-2</v>
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G8" s="11">
-        <v>46794</v>
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>46764</v>
       </c>
       <c r="H8" s="12">
+        <f>YEAR(G8)</f>
         <v>2028</v>
       </c>
       <c r="I8" s="13">
-        <v>94.635000000000005</v>
+        <v>99.575299999999999</v>
       </c>
       <c r="J8" s="13">
-        <v>4.6571310242374002</v>
+        <v>4.7422361014980003</v>
       </c>
       <c r="K8" s="13">
-        <v>56.410784825633002</v>
-      </c>
-      <c r="L8" s="10">
-        <v>4.8619999999999997E-2</v>
+        <v>65.449731028407996</v>
+      </c>
+      <c r="L8" s="13">
+        <v>4.6684643359624003</v>
       </c>
       <c r="M8" s="14">
+        <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N8" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O8" s="16">
-        <v>750000000</v>
+        <v>300000000</v>
       </c>
       <c r="P8" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>15</v>
+      <c r="A9" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Ally Financial</v>
+      </c>
+      <c r="B9" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Banks</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>30</v>
+      <c r="E9" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa3/BBB-/BBB-</v>
       </c>
       <c r="F9" s="10">
-        <v>0.05</v>
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="G9" s="11">
-        <v>46762</v>
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>46794</v>
       </c>
       <c r="H9" s="12">
+        <f>YEAR(G9)</f>
         <v>2028</v>
       </c>
       <c r="I9" s="13">
-        <v>100.6795</v>
+        <v>94.56</v>
       </c>
       <c r="J9" s="13">
-        <v>4.7356345400144004</v>
+        <v>4.7570508823191</v>
       </c>
       <c r="K9" s="13">
-        <v>65.404062954652005</v>
-      </c>
-      <c r="L9" s="10">
-        <v>4.8419999999999998E-2</v>
+        <v>67.029007466332999</v>
+      </c>
+      <c r="L9" s="13">
+        <v>4.6571310242374002</v>
       </c>
       <c r="M9" s="14">
+        <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N9" s="15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O9" s="16">
         <v>750000000</v>
@@ -2352,99 +4258,106 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="F10" s="10">
-        <v>4.2500000000000003E-2</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>165</v>
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="11">
+        <v>46762</v>
       </c>
       <c r="H10" s="12">
         <v>2028</v>
       </c>
       <c r="I10" s="13">
-        <v>98.128</v>
+        <v>100.57445</v>
       </c>
       <c r="J10" s="13">
-        <v>5.2044530096086996</v>
+        <v>4.7781681020595004</v>
       </c>
       <c r="K10" s="13">
-        <v>112.50936140397999</v>
-      </c>
-      <c r="L10" s="10">
-        <v>5.2699999999999997E-2</v>
+        <v>69.635516701835996</v>
+      </c>
+      <c r="L10" s="13">
+        <v>4.7356345400144004</v>
       </c>
       <c r="M10" s="14">
         <v>2000</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="O10" s="16">
-        <v>600000000</v>
+        <v>750000000</v>
       </c>
       <c r="P10" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>34</v>
+      <c r="A11" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Fluor</v>
+      </c>
+      <c r="B11" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Infrastructure and Special Construction</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>35</v>
+      <c r="E11" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Ba1/BB+/Withdrawn</v>
       </c>
       <c r="F11" s="10">
-        <v>6.9500000000000006E-2</v>
-      </c>
-      <c r="G11" s="11">
-        <v>46827</v>
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="G11" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/09/2028</v>
       </c>
       <c r="H11" s="12">
+        <f t="shared" ref="H11:H60" si="0">YEAR(G11)</f>
         <v>2028</v>
       </c>
       <c r="I11" s="13">
-        <v>103.035</v>
+        <v>99.028400000000005</v>
       </c>
       <c r="J11" s="13">
-        <v>5.1733104559676999</v>
+        <v>4.7753751860465004</v>
       </c>
       <c r="K11" s="13">
-        <v>113.18920553245999</v>
-      </c>
-      <c r="L11" s="10">
-        <v>5.5849999999999997E-2</v>
+        <v>69.447301204604997</v>
+      </c>
+      <c r="L11" s="13">
+        <v>5.2044530096086996</v>
       </c>
       <c r="M11" s="14">
-        <v>1000</v>
+        <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="O11" s="16">
-        <v>300000000</v>
+        <v>600000000</v>
       </c>
       <c r="P11" s="17" t="s">
         <v>142</v>
@@ -2452,49 +4365,51 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="8" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>16</v>
+        <v>34</v>
+      </c>
+      <c r="C12" s="9" t="str">
+        <f>+A12</f>
+        <v>Nordstrom</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F12" s="10">
-        <v>6.7979999999999999E-2</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G12" s="11">
-        <v>47064</v>
+        <v>46827</v>
       </c>
       <c r="H12" s="12">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="I12" s="13">
-        <v>103.65</v>
+        <v>103.351</v>
       </c>
       <c r="J12" s="13">
-        <v>5.2212942271933001</v>
+        <v>4.9123728446805996</v>
       </c>
       <c r="K12" s="13">
-        <v>113.48747333788999</v>
-      </c>
-      <c r="L12" s="10">
-        <v>5.3940000000000002E-2</v>
+        <v>84.543917559760999</v>
+      </c>
+      <c r="L12" s="13">
+        <v>5.1733104559676999</v>
       </c>
       <c r="M12" s="14">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O12" s="16">
-        <v>1500000000</v>
+        <v>300000000</v>
       </c>
       <c r="P12" s="17" t="s">
         <v>142</v>
@@ -2502,49 +4417,50 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="8" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="F13" s="10">
-        <v>0.04</v>
+        <v>6.7979999999999999E-2</v>
       </c>
       <c r="G13" s="11">
-        <v>46949</v>
+        <v>47064</v>
       </c>
       <c r="H13" s="12">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="I13" s="13">
-        <v>97.67</v>
+        <v>103.23</v>
       </c>
       <c r="J13" s="13">
-        <v>5.26</v>
+        <v>5.3738107752827</v>
       </c>
       <c r="K13" s="13">
-        <v>119.32</v>
-      </c>
-      <c r="L13" s="10">
-        <v>5.2999999999999999E-2</v>
+        <v>128.99535451521001</v>
+      </c>
+      <c r="L13" s="13">
+        <v>5.2212942271933001</v>
       </c>
       <c r="M13" s="14">
-        <v>1000</v>
+        <v>200000</v>
       </c>
       <c r="N13" s="15" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="O13" s="16">
-        <v>2000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="P13" s="17" t="s">
         <v>142</v>
@@ -2552,49 +4468,49 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="8" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>134</v>
+        <v>92</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="F14" s="10">
-        <v>5.7500000000000002E-2</v>
+        <v>0.04</v>
       </c>
       <c r="G14" s="11">
-        <v>47072</v>
+        <v>46949</v>
       </c>
       <c r="H14" s="12">
         <v>2028</v>
       </c>
       <c r="I14" s="13">
-        <v>100.33499999999999</v>
+        <v>97.474999999999994</v>
       </c>
       <c r="J14" s="13">
-        <v>5.6758060419575997</v>
+        <v>5.4043003750673</v>
       </c>
       <c r="K14" s="13">
-        <v>158.61433137061999</v>
-      </c>
-      <c r="L14" s="10">
-        <v>0.06</v>
+        <v>132.83722632353999</v>
+      </c>
+      <c r="L14" s="13">
+        <v>5.26</v>
       </c>
       <c r="M14" s="14">
         <v>1000</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O14" s="16">
-        <v>800000000</v>
+        <v>2000000000</v>
       </c>
       <c r="P14" s="17" t="s">
         <v>142</v>
@@ -2602,46 +4518,46 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>39</v>
+        <v>152</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
       <c r="F15" s="10">
-        <v>4.3749999999999997E-2</v>
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="G15" s="11">
-        <v>46919</v>
+        <v>47072</v>
       </c>
       <c r="H15" s="12">
         <v>2028</v>
       </c>
       <c r="I15" s="13">
-        <v>98.764899999999997</v>
+        <v>99.805000000000007</v>
       </c>
       <c r="J15" s="13">
-        <v>5.0951748613912002</v>
+        <v>5.9208334278288</v>
       </c>
       <c r="K15" s="13">
-        <v>103.19991257154</v>
-      </c>
-      <c r="L15" s="10">
-        <v>5.2670000000000002E-2</v>
+        <v>183.55708706243001</v>
+      </c>
+      <c r="L15" s="13">
+        <v>5.6758060419575997</v>
       </c>
       <c r="M15" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="15" t="s">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="O15" s="16">
         <v>800000000</v>
@@ -2652,49 +4568,50 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="8" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F16" s="10">
-        <v>8.6249999999999993E-2</v>
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="G16" s="11">
-        <v>47137</v>
+        <v>46919</v>
       </c>
       <c r="H16" s="12">
-        <v>2029</v>
+        <f t="shared" si="0"/>
+        <v>2028</v>
       </c>
       <c r="I16" s="13">
-        <v>106.9375</v>
+        <v>98.55565</v>
       </c>
       <c r="J16" s="13">
-        <v>5.7889043132677998</v>
+        <v>5.2324358555585997</v>
       </c>
       <c r="K16" s="13">
-        <v>169.67415894119</v>
-      </c>
-      <c r="L16" s="10">
-        <v>6.6119999999999998E-2</v>
+        <v>115.79460654344</v>
+      </c>
+      <c r="L16" s="13">
+        <v>5.0951748613912002</v>
       </c>
       <c r="M16" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="O16" s="16">
-        <v>1200000000</v>
+        <v>800000000</v>
       </c>
       <c r="P16" s="17" t="s">
         <v>142</v>
@@ -2702,98 +4619,107 @@
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="8" t="s">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>27</v>
+        <v>42</v>
+      </c>
+      <c r="C17" s="9" t="str">
+        <f>+A17</f>
+        <v>Ecopetrol</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="F17" s="10">
-        <v>6.9919999999999996E-2</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>166</v>
+        <v>8.6249999999999993E-2</v>
+      </c>
+      <c r="G17" s="11">
+        <v>47137</v>
       </c>
       <c r="H17" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I17" s="13">
-        <v>103.86</v>
+        <v>106.2165</v>
       </c>
       <c r="J17" s="13">
-        <v>4.9966088021799999</v>
+        <v>6.0333288027999998</v>
       </c>
       <c r="K17" s="13">
-        <v>93.641326483057995</v>
-      </c>
-      <c r="L17" s="10">
-        <v>5.1999999999999998E-2</v>
+        <v>194.69832060189</v>
+      </c>
+      <c r="L17" s="13">
+        <v>5.7889043132677998</v>
       </c>
       <c r="M17" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O17" s="16">
-        <v>750000000</v>
+        <v>1200000000</v>
       </c>
       <c r="P17" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F18" s="23">
-        <v>5.6250000000000001E-2</v>
-      </c>
-      <c r="G18" s="24">
-        <v>47126</v>
-      </c>
-      <c r="H18" s="25">
+      <c r="A18" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Ally Financial</v>
+      </c>
+      <c r="B18" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Banks</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa3/BBB-/BBB-</v>
+      </c>
+      <c r="F18" s="10">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>6.9919999999999996E-2</v>
+      </c>
+      <c r="G18" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>13/06/2029</v>
+      </c>
+      <c r="H18" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I18" s="26">
-        <v>99.540300000000002</v>
-      </c>
-      <c r="J18" s="26">
-        <v>5.8698164938724</v>
-      </c>
-      <c r="K18" s="26">
-        <v>173.64121244994001</v>
-      </c>
-      <c r="L18" s="23">
-        <v>6.132E-2</v>
-      </c>
-      <c r="M18" s="27">
-        <v>1000</v>
-      </c>
-      <c r="N18" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="O18" s="29">
+      <c r="I18" s="13">
+        <v>103.715</v>
+      </c>
+      <c r="J18" s="13">
+        <v>5.0119989796673998</v>
+      </c>
+      <c r="K18" s="13">
+        <v>93.861399046453997</v>
+      </c>
+      <c r="L18" s="13">
+        <v>4.9966088021799999</v>
+      </c>
+      <c r="M18" s="14">
+        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="O18" s="16">
         <v>750000000</v>
       </c>
       <c r="P18" s="17" t="s">
@@ -2801,200 +4727,225 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>167</v>
+      <c r="A19" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Olin</v>
+      </c>
+      <c r="B19" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" s="23">
-        <v>3.4500000000000003E-2</v>
+        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="G19" s="24">
-        <v>47128</v>
+        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47126</v>
       </c>
       <c r="H19" s="25">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I19" s="26">
-        <v>92.436999999999998</v>
+        <v>99.4435</v>
       </c>
       <c r="J19" s="26">
-        <v>6.1031278451061004</v>
+        <v>5.9098961663083003</v>
       </c>
       <c r="K19" s="26">
-        <v>194.99048976679001</v>
-      </c>
-      <c r="L19" s="23">
-        <v>6.9470000000000004E-2</v>
+        <v>180.33250281859</v>
+      </c>
+      <c r="L19" s="26">
+        <v>5.8698164938724</v>
       </c>
       <c r="M19" s="27">
-        <v>2000</v>
+        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>1000</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="O19" s="29">
-        <v>500000000</v>
+        <v>750000000</v>
       </c>
       <c r="P19" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="10">
-        <v>5.2499999999999998E-2</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="H20" s="12">
+      <c r="A20" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>FMC</v>
+      </c>
+      <c r="B20" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Fertilizers</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="23">
+        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="G20" s="24">
+        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47128</v>
+      </c>
+      <c r="H20" s="25">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I20" s="13">
-        <v>99.736199999999997</v>
-      </c>
-      <c r="J20" s="13">
-        <v>5.4047418010010997</v>
-      </c>
-      <c r="K20" s="13">
-        <v>124.16475223083</v>
-      </c>
-      <c r="L20" s="10">
-        <v>5.5710000000000003E-2</v>
-      </c>
-      <c r="M20" s="14">
+      <c r="I20" s="26">
+        <v>93.067499999999995</v>
+      </c>
+      <c r="J20" s="26">
+        <v>5.9164627873917004</v>
+      </c>
+      <c r="K20" s="26">
+        <v>179.88791852900999</v>
+      </c>
+      <c r="L20" s="26">
+        <v>6.1031278451061004</v>
+      </c>
+      <c r="M20" s="27">
+        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N20" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="O20" s="16">
-        <v>700000000</v>
+      <c r="N20" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="O20" s="29">
+        <v>500000000</v>
       </c>
       <c r="P20" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>134</v>
+      <c r="A21" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Methanex</v>
+      </c>
+      <c r="B21" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="F21" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="G21" s="11">
-        <v>47126</v>
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="G21" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/12/2029</v>
       </c>
       <c r="H21" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I21" s="13">
-        <v>100.785</v>
+        <v>99.635000000000005</v>
       </c>
       <c r="J21" s="13">
-        <v>4.7809946854473004</v>
+        <v>5.4383914326443996</v>
       </c>
       <c r="K21" s="13">
-        <v>64.524650966509</v>
-      </c>
-      <c r="L21" s="10">
-        <v>4.9529999999999998E-2</v>
+        <v>131.50867729941999</v>
+      </c>
+      <c r="L21" s="13">
+        <v>5.4047418010010997</v>
       </c>
       <c r="M21" s="14">
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O21" s="16">
-        <v>750000000</v>
+        <v>700000000</v>
       </c>
       <c r="P21" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>56</v>
+      <c r="A22" s="19" t="str">
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Eastman Chemical</v>
+      </c>
+      <c r="B22" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>57</v>
+      <c r="E22" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa2/BBB/Withdrawn</v>
       </c>
       <c r="F22" s="10">
-        <v>3.7499999999999999E-2</v>
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>0.05</v>
       </c>
       <c r="G22" s="11">
-        <v>47209</v>
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47126</v>
       </c>
       <c r="H22" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I22" s="13">
-        <v>96.992000000000004</v>
+        <v>100.545</v>
       </c>
       <c r="J22" s="13">
-        <v>4.9732958652243999</v>
+        <v>4.8633165071222004</v>
       </c>
       <c r="K22" s="13">
-        <v>85.481956524826998</v>
-      </c>
-      <c r="L22" s="10">
-        <v>5.1090000000000003E-2</v>
+        <v>75.549590736349998</v>
+      </c>
+      <c r="L22" s="13">
+        <v>4.7809946854473004</v>
       </c>
       <c r="M22" s="14">
-        <v>1000</v>
+        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O22" s="16">
-        <v>600000000</v>
+        <v>750000000</v>
       </c>
       <c r="P22" s="17" t="s">
         <v>142</v>
@@ -3002,49 +4953,51 @@
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="8" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>152</v>
+        <v>56</v>
+      </c>
+      <c r="C23" s="9" t="str">
+        <f>+A23</f>
+        <v>Mattel</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>153</v>
+        <v>57</v>
       </c>
       <c r="F23" s="10">
-        <v>4.5999999999999999E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G23" s="11">
-        <v>47437</v>
+        <v>47209</v>
       </c>
       <c r="H23" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I23" s="13">
-        <v>96.123000000000005</v>
+        <v>97.070999999999998</v>
       </c>
       <c r="J23" s="13">
-        <v>5.9796398973778002</v>
+        <v>4.9660398867562003</v>
       </c>
       <c r="K23" s="13">
-        <v>182.10845866493</v>
-      </c>
-      <c r="L23" s="10">
-        <v>0.06</v>
+        <v>86.719568477107998</v>
+      </c>
+      <c r="L23" s="13">
+        <v>4.9732958652243999</v>
       </c>
       <c r="M23" s="14">
         <v>1000</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>155</v>
+        <v>58</v>
       </c>
       <c r="O23" s="16">
-        <v>650000000</v>
+        <v>600000000</v>
       </c>
       <c r="P23" s="17" t="s">
         <v>142</v>
@@ -3052,49 +5005,49 @@
     </row>
     <row r="24" spans="1:16">
       <c r="A24" s="8" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>60</v>
+        <v>152</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
       <c r="F24" s="10">
-        <v>5.9499999999999997E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="G24" s="11">
-        <v>47314</v>
+        <v>47437</v>
       </c>
       <c r="H24" s="12">
         <v>2029</v>
       </c>
       <c r="I24" s="13">
-        <v>101.125</v>
+        <v>95.307500000000005</v>
       </c>
       <c r="J24" s="13">
-        <v>5.6229573345007999</v>
+        <v>6.2886966914741</v>
       </c>
       <c r="K24" s="13">
-        <v>149.38362378893001</v>
-      </c>
-      <c r="L24" s="10">
-        <v>5.8810000000000001E-2</v>
+        <v>216.81147745448999</v>
+      </c>
+      <c r="L24" s="13">
+        <v>5.9796398973778002</v>
       </c>
       <c r="M24" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>62</v>
+        <v>155</v>
       </c>
       <c r="O24" s="16">
-        <v>850000000</v>
+        <v>650000000</v>
       </c>
       <c r="P24" s="17" t="s">
         <v>142</v>
@@ -3102,149 +5055,157 @@
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="8" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F25" s="10">
-        <v>5.3999999999999999E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="G25" s="11">
-        <v>47437</v>
+        <v>47314</v>
       </c>
       <c r="H25" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I25" s="13">
-        <v>101.99</v>
+        <v>100.99</v>
       </c>
       <c r="J25" s="13">
-        <v>4.8014897953651996</v>
+        <v>5.666805627924</v>
       </c>
       <c r="K25" s="13">
-        <v>65.131790947823006</v>
-      </c>
-      <c r="L25" s="10">
-        <v>4.9669999999999999E-2</v>
+        <v>156.25027537597001</v>
+      </c>
+      <c r="L25" s="13">
+        <v>5.6229573345007999</v>
       </c>
       <c r="M25" s="14">
         <v>2000</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O25" s="16">
-        <v>1000000000</v>
+        <v>850000000</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="23">
-        <v>0.05</v>
-      </c>
-      <c r="G26" s="24">
-        <v>47485</v>
-      </c>
-      <c r="H26" s="25">
-        <v>2030</v>
-      </c>
-      <c r="I26" s="26">
-        <v>97.125</v>
-      </c>
-      <c r="J26" s="26">
-        <v>5.9763491100649997</v>
-      </c>
-      <c r="K26" s="26">
-        <v>180.91527891249001</v>
-      </c>
-      <c r="L26" s="23">
-        <v>6.0789999999999997E-2</v>
-      </c>
-      <c r="M26" s="27">
-        <v>1000</v>
-      </c>
-      <c r="N26" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="O26" s="29">
-        <v>550000000</v>
+      <c r="A26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G26" s="11">
+        <v>47437</v>
+      </c>
+      <c r="H26" s="12">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="I26" s="13">
+        <v>101.77</v>
+      </c>
+      <c r="J26" s="13">
+        <v>4.8640697328705</v>
+      </c>
+      <c r="K26" s="13">
+        <v>74.826815748252002</v>
+      </c>
+      <c r="L26" s="13">
+        <v>4.8014897953651996</v>
+      </c>
+      <c r="M26" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="O26" s="16">
+        <v>1000000000</v>
       </c>
       <c r="P26" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="A27" s="30" t="str">
+        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Olin</v>
+      </c>
+      <c r="B27" s="31" t="str">
+        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="10">
-        <v>3.875E-2</v>
-      </c>
-      <c r="G27" s="11">
-        <v>47802</v>
-      </c>
-      <c r="H27" s="12">
+      <c r="E27" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="23">
+        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>0.05</v>
+      </c>
+      <c r="G27" s="24">
+        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47485</v>
+      </c>
+      <c r="H27" s="25">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="I27" s="13">
-        <v>92.655000000000001</v>
-      </c>
-      <c r="J27" s="13">
-        <v>5.8657650211977996</v>
-      </c>
-      <c r="K27" s="13">
-        <v>163.99099441888001</v>
-      </c>
-      <c r="L27" s="10">
-        <v>6.0019999999999997E-2</v>
-      </c>
-      <c r="M27" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N27" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="O27" s="16">
-        <v>650000000</v>
+      <c r="I27" s="26">
+        <v>97.5</v>
+      </c>
+      <c r="J27" s="26">
+        <v>5.8680201805944998</v>
+      </c>
+      <c r="K27" s="26">
+        <v>174.22270862929</v>
+      </c>
+      <c r="L27" s="26">
+        <v>5.9763491100649997</v>
+      </c>
+      <c r="M27" s="27">
+        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="N27" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="O27" s="29">
+        <v>550000000</v>
       </c>
       <c r="P27" s="17" t="s">
         <v>142</v>
@@ -3252,149 +5213,152 @@
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="8" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>70</v>
+        <v>21</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="F28" s="10">
-        <v>4.7E-2</v>
+        <v>3.875E-2</v>
       </c>
       <c r="G28" s="11">
-        <v>47763</v>
+        <v>47802</v>
       </c>
       <c r="H28" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I28" s="13">
-        <v>98.833169999999996</v>
+        <v>93.045000000000002</v>
       </c>
       <c r="J28" s="13">
-        <v>5.0649725136379002</v>
+        <v>5.7805265387676004</v>
       </c>
       <c r="K28" s="13">
-        <v>85.091025115693</v>
-      </c>
-      <c r="L28" s="10">
-        <v>5.2499999999999998E-2</v>
+        <v>161.64086280793001</v>
+      </c>
+      <c r="L28" s="13">
+        <v>5.8657650211977996</v>
       </c>
       <c r="M28" s="14">
         <v>2000</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O28" s="16">
-        <v>600000000</v>
+        <v>650000000</v>
       </c>
       <c r="P28" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="20" t="s">
-        <v>60</v>
+      <c r="A29" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F29" s="32">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G29" s="33">
-        <v>47727</v>
+      <c r="E29" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="10">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G29" s="11">
+        <v>47763</v>
       </c>
       <c r="H29" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I29" s="13">
-        <v>98.965000000000003</v>
+        <v>98.2928</v>
       </c>
       <c r="J29" s="13">
-        <v>5.8612427880234002</v>
+        <v>5.2167283875081001</v>
       </c>
       <c r="K29" s="13">
-        <v>165.93059514529</v>
-      </c>
-      <c r="L29" s="10">
-        <v>6.1379999999999997E-2</v>
-      </c>
-      <c r="M29" s="34">
+        <v>106.09039282237001</v>
+      </c>
+      <c r="L29" s="13">
+        <v>5.0649725136379002</v>
+      </c>
+      <c r="M29" s="14">
         <v>2000</v>
       </c>
-      <c r="N29" s="35" t="s">
-        <v>72</v>
+      <c r="N29" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="O29" s="16">
-        <v>750000000</v>
+        <v>600000000</v>
       </c>
       <c r="P29" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>138</v>
+      <c r="A30" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F30" s="10">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="G30" s="11">
-        <v>47514</v>
+        <v>12</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="32">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G30" s="33">
+        <v>47727</v>
       </c>
       <c r="H30" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I30" s="13">
-        <v>98.35</v>
+        <v>98.825000000000003</v>
       </c>
       <c r="J30" s="13">
-        <v>9.5060902364221995</v>
+        <v>5.9051997759867003</v>
       </c>
       <c r="K30" s="13">
-        <v>535.53935268037003</v>
-      </c>
-      <c r="L30" s="10">
-        <v>9.4950000000000007E-2</v>
-      </c>
-      <c r="M30" s="14">
-        <v>200000</v>
-      </c>
-      <c r="N30" s="15" t="s">
-        <v>74</v>
+        <v>175.74953149757999</v>
+      </c>
+      <c r="L30" s="13">
+        <v>5.8612427880234002</v>
+      </c>
+      <c r="M30" s="34">
+        <v>2000</v>
+      </c>
+      <c r="N30" s="35" t="s">
+        <v>72</v>
       </c>
       <c r="O30" s="16">
-        <v>550000000</v>
+        <v>750000000</v>
       </c>
       <c r="P30" s="17" t="s">
         <v>142</v>
@@ -3402,399 +5366,438 @@
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="8" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>75</v>
+      <c r="C31" s="9" t="str">
+        <f>+A31</f>
+        <v>Geopark</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F31" s="32">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G31" s="33">
-        <v>47485</v>
+        <v>73</v>
+      </c>
+      <c r="F31" s="10">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="G31" s="11">
+        <v>47514</v>
       </c>
       <c r="H31" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I31" s="13">
-        <v>106.6</v>
+        <v>98.35</v>
       </c>
       <c r="J31" s="13">
-        <v>5.0483463023033996</v>
+        <v>9.5170455367630993</v>
       </c>
       <c r="K31" s="13">
-        <v>88.823434889802996</v>
-      </c>
-      <c r="L31" s="10">
-        <v>5.5079999999999997E-2</v>
-      </c>
-      <c r="M31" s="34">
-        <v>2000</v>
-      </c>
-      <c r="N31" s="35" t="s">
-        <v>76</v>
+        <v>540.09375815400995</v>
+      </c>
+      <c r="L31" s="13">
+        <v>9.5060902364221995</v>
+      </c>
+      <c r="M31" s="14">
+        <v>200000</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="O31" s="16">
-        <v>750000000</v>
+        <v>550000000</v>
       </c>
       <c r="P31" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>34</v>
+      <c r="A32" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>EQT</v>
+      </c>
+      <c r="B32" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="10">
-        <v>5.8749999999999997E-2</v>
-      </c>
-      <c r="G32" s="11">
-        <v>47557</v>
+        <v>12</v>
+      </c>
+      <c r="E32" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Withdrawn/BBB-/BBB-</v>
+      </c>
+      <c r="F32" s="32">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G32" s="33">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47485</v>
       </c>
       <c r="H32" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I32" s="13">
-        <v>100.533</v>
+        <v>106.28435</v>
       </c>
       <c r="J32" s="13">
-        <v>5.7934766468827998</v>
+        <v>5.1146249720602004</v>
       </c>
       <c r="K32" s="13">
-        <v>162.03911397205999</v>
-      </c>
-      <c r="L32" s="10">
-        <v>5.885E-2</v>
-      </c>
-      <c r="M32" s="14">
+        <v>99.309735596096999</v>
+      </c>
+      <c r="L32" s="13">
+        <v>5.0483463023033996</v>
+      </c>
+      <c r="M32" s="34">
+        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N32" s="15" t="s">
-        <v>78</v>
+      <c r="N32" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="O32" s="16">
-        <v>425000000</v>
+        <v>750000000</v>
       </c>
       <c r="P32" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>140</v>
+      <c r="A33" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="9" t="str">
+        <f>+A33</f>
+        <v>Macy´s</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="32">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G33" s="33">
-        <v>47757</v>
+        <v>21</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="10">
+        <v>5.8749999999999997E-2</v>
+      </c>
+      <c r="G33" s="11">
+        <v>47557</v>
       </c>
       <c r="H33" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I33" s="13">
-        <v>96.926649999999995</v>
+        <v>100.1765</v>
       </c>
       <c r="J33" s="13">
-        <v>5.3782875807729003</v>
+        <v>5.9026780275639998</v>
       </c>
       <c r="K33" s="13">
-        <v>116.46605437066999</v>
-      </c>
-      <c r="L33" s="10">
-        <v>5.5129999999999998E-2</v>
-      </c>
-      <c r="M33" s="34">
+        <v>177.33893406474999</v>
+      </c>
+      <c r="L33" s="13">
+        <v>5.7934766468827998</v>
+      </c>
+      <c r="M33" s="14">
         <v>2000</v>
       </c>
-      <c r="N33" s="35" t="s">
-        <v>79</v>
+      <c r="N33" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="O33" s="16">
-        <v>75000000</v>
+        <v>425000000</v>
       </c>
       <c r="P33" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>80</v>
+      <c r="C34" s="20" t="str">
+        <f>+A34</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F34" s="10">
-        <v>5.0930000000000003E-2</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>171</v>
+        <v>12</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G34" s="33">
+        <v>47757</v>
       </c>
       <c r="H34" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I34" s="13">
-        <v>99.543499999999995</v>
+        <v>97.102950000000007</v>
       </c>
       <c r="J34" s="13">
-        <v>5.3014347264678996</v>
+        <v>5.3399688621105996</v>
       </c>
       <c r="K34" s="13">
-        <v>113.76383664657</v>
-      </c>
-      <c r="L34" s="10">
-        <v>5.3679999999999999E-2</v>
-      </c>
-      <c r="M34" s="14">
+        <v>118.43510796036</v>
+      </c>
+      <c r="L34" s="13">
+        <v>5.3782875807729003</v>
+      </c>
+      <c r="M34" s="34">
         <v>2000</v>
       </c>
-      <c r="N34" s="15" t="s">
-        <v>81</v>
+      <c r="N34" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="O34" s="16">
-        <v>375896000</v>
+        <v>75000000</v>
       </c>
       <c r="P34" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>158</v>
+      <c r="A35" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Petrobras</v>
+      </c>
+      <c r="B35" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>159</v>
+      <c r="E35" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Ba1/BB/BB</v>
       </c>
       <c r="F35" s="10">
-        <v>2.7E-2</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>172</v>
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.0930000000000003E-2</v>
+      </c>
+      <c r="G35" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/01/2030</v>
       </c>
       <c r="H35" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I35" s="13">
-        <v>91.597800000000007</v>
+        <v>99.224500000000006</v>
       </c>
       <c r="J35" s="13">
-        <v>5.0983610157478996</v>
+        <v>5.4081318780318997</v>
       </c>
       <c r="K35" s="13">
-        <v>89.512265382262001</v>
-      </c>
-      <c r="L35" s="10">
-        <v>5.2819999999999999E-2</v>
+        <v>128.44369795827001</v>
+      </c>
+      <c r="L35" s="13">
+        <v>5.3014347264678996</v>
       </c>
       <c r="M35" s="14">
+        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O35" s="16">
-        <v>1449500000</v>
+        <v>375896000</v>
       </c>
       <c r="P35" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>129</v>
+      <c r="A36" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Viatris</v>
+      </c>
+      <c r="B36" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Pharmaceutical Preparation and Biotechnology</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>57</v>
+        <v>21</v>
+      </c>
+      <c r="E36" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BB+/BBB</v>
       </c>
       <c r="F36" s="10">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>173</v>
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>2.7E-2</v>
+      </c>
+      <c r="G36" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>22/06/2030</v>
       </c>
       <c r="H36" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I36" s="13">
-        <v>108.4</v>
+        <v>91.300049999999999</v>
       </c>
       <c r="J36" s="13">
-        <v>4.8028528899121001</v>
+        <v>5.2241215897703999</v>
       </c>
       <c r="K36" s="13">
-        <v>76.010527540115007</v>
-      </c>
-      <c r="L36" s="10">
-        <v>4.7690000000000003E-2</v>
+        <v>107.27688652632</v>
+      </c>
+      <c r="L36" s="13">
+        <v>5.0983610157478996</v>
       </c>
       <c r="M36" s="14">
-        <v>200000</v>
+        <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N36" s="15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O36" s="16">
-        <v>750000000</v>
+        <v>1449500000</v>
       </c>
       <c r="P36" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>174</v>
+      <c r="A37" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Embraer</v>
+      </c>
+      <c r="B37" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Aircraft Production and Defense</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F37" s="10">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G37" s="11">
-        <v>47702</v>
+        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G37" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>28/07/2030</v>
       </c>
       <c r="H37" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I37" s="13">
-        <v>95.4345</v>
+        <v>108.4</v>
       </c>
       <c r="J37" s="13">
-        <v>5.0673822743828003</v>
+        <v>4.8028528899121001</v>
       </c>
       <c r="K37" s="13">
-        <v>86.687420632503006</v>
-      </c>
-      <c r="L37" s="10">
-        <v>5.1580000000000001E-2</v>
+        <v>76.010527540115007</v>
+      </c>
+      <c r="L37" s="13">
+        <v>4.8028528899121001</v>
       </c>
       <c r="M37" s="14">
-        <v>2000</v>
+        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>200000</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="O37" s="16">
-        <v>1500000000</v>
+        <v>750000000</v>
       </c>
       <c r="P37" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>34</v>
+      <c r="A38" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Vale</v>
+      </c>
+      <c r="B38" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Ferrous metals</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="F38" s="10">
-        <v>4.3749999999999997E-2</v>
+        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G38" s="11">
-        <v>47574</v>
+        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47702</v>
       </c>
       <c r="H38" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I38" s="13">
-        <v>96.194999999999993</v>
+        <v>95.340500000000006</v>
       </c>
       <c r="J38" s="13">
-        <v>5.5730541855544997</v>
+        <v>5.1140232684006</v>
       </c>
       <c r="K38" s="13">
-        <v>139.03976293167</v>
-      </c>
-      <c r="L38" s="10">
-        <v>6.2100000000000002E-2</v>
+        <v>96.726032319241995</v>
+      </c>
+      <c r="L38" s="13">
+        <v>5.0673822743828003</v>
       </c>
       <c r="M38" s="14">
+        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N38" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O38" s="16">
-        <v>500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="P38" s="17" t="s">
         <v>142</v>
@@ -3802,99 +5805,107 @@
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="8" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>89</v>
+        <v>34</v>
+      </c>
+      <c r="C39" s="9" t="str">
+        <f>+A39</f>
+        <v>Nordstrom</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="F39" s="10">
-        <v>0.03</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>176</v>
+        <v>4.3749999999999997E-2</v>
+      </c>
+      <c r="G39" s="11">
+        <v>47574</v>
       </c>
       <c r="H39" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I39" s="13">
-        <v>90.412350000000004</v>
+        <v>96.63</v>
       </c>
       <c r="J39" s="13">
-        <v>5.5926404224787003</v>
+        <v>5.4537213017957997</v>
       </c>
       <c r="K39" s="13">
-        <v>136.78484197880999</v>
-      </c>
-      <c r="L39" s="10">
-        <v>5.7750000000000003E-2</v>
+        <v>131.84206806991</v>
+      </c>
+      <c r="L39" s="13">
+        <v>5.5730541855544997</v>
       </c>
       <c r="M39" s="14">
         <v>2000</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="O39" s="16">
-        <v>2200000000</v>
+        <v>500000000</v>
       </c>
       <c r="P39" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>92</v>
+      <c r="A40" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Centene</v>
+      </c>
+      <c r="B40" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Insurance and Reinsurance</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="36">
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="G40" s="11">
-        <v>47618</v>
+        <v>90</v>
+      </c>
+      <c r="F40" s="10">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>0.03</v>
+      </c>
+      <c r="G40" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/10/2030</v>
       </c>
       <c r="H40" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I40" s="13">
-        <v>94.709000000000003</v>
+        <v>90.455849999999998</v>
       </c>
       <c r="J40" s="13">
-        <v>5.1856108017900002</v>
+        <v>5.6146107857010001</v>
       </c>
       <c r="K40" s="13">
-        <v>113.69079197003001</v>
-      </c>
-      <c r="L40" s="10">
-        <v>5.2109999999999997E-2</v>
+        <v>145.12849207442</v>
+      </c>
+      <c r="L40" s="13">
+        <v>5.5926404224787003</v>
       </c>
       <c r="M40" s="14">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O40" s="16">
-        <v>917517000</v>
+        <v>2200000000</v>
       </c>
       <c r="P40" s="17" t="s">
         <v>142</v>
@@ -3902,49 +5913,50 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="8" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F41" s="10">
-        <v>0.05</v>
+        <v>94</v>
+      </c>
+      <c r="F41" s="36">
+        <v>3.6249999999999998E-2</v>
       </c>
       <c r="G41" s="11">
-        <v>47804</v>
+        <v>47618</v>
       </c>
       <c r="H41" s="12">
+        <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I41" s="13">
-        <v>99.745000000000005</v>
+        <v>80.66</v>
       </c>
       <c r="J41" s="13">
-        <v>5.1281219620645997</v>
+        <v>9.9952818659825997</v>
       </c>
       <c r="K41" s="13">
-        <v>90.727479618116007</v>
-      </c>
-      <c r="L41" s="10">
-        <v>5.391E-2</v>
+        <v>593.69553893602995</v>
+      </c>
+      <c r="L41" s="13">
+        <v>5.1856108017900002</v>
       </c>
       <c r="M41" s="14">
         <v>2000</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O41" s="16">
-        <v>600000000</v>
+        <v>917517000</v>
       </c>
       <c r="P41" s="17" t="s">
         <v>142</v>
@@ -3952,49 +5964,51 @@
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>140</v>
+        <v>56</v>
+      </c>
+      <c r="C42" s="9" t="str">
+        <f>+A42</f>
+        <v>Mattel</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="36">
-        <v>5.7500000000000002E-2</v>
+        <v>61</v>
+      </c>
+      <c r="F42" s="10">
+        <v>0.05</v>
       </c>
       <c r="G42" s="11">
-        <v>47863</v>
+        <v>47804</v>
       </c>
       <c r="H42" s="12">
-        <v>2031</v>
+        <f t="shared" si="0"/>
+        <v>2030</v>
       </c>
       <c r="I42" s="13">
-        <v>102.455</v>
+        <v>99.494249999999994</v>
       </c>
       <c r="J42" s="13">
-        <v>5.2067291788855998</v>
+        <v>5.1950145746962004</v>
       </c>
       <c r="K42" s="13">
-        <v>98.575855302196004</v>
-      </c>
-      <c r="L42" s="10">
-        <v>5.423E-2</v>
+        <v>103.44711103354</v>
+      </c>
+      <c r="L42" s="13">
+        <v>5.1281219620645997</v>
       </c>
       <c r="M42" s="14">
         <v>2000</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O42" s="16">
-        <v>650000000</v>
+        <v>600000000</v>
       </c>
       <c r="P42" s="17" t="s">
         <v>142</v>
@@ -4002,149 +6016,164 @@
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="8" t="s">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>89</v>
+        <v>42</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f>+A43</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="F43" s="10">
-        <v>2.5000000000000001E-2</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="36">
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="G43" s="11">
-        <v>47851</v>
+        <v>47863</v>
       </c>
       <c r="H43" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I43" s="13">
-        <v>87.467500000000001</v>
+        <v>102.045</v>
       </c>
       <c r="J43" s="13">
-        <v>5.6366512377394002</v>
+        <v>5.3044691221645</v>
       </c>
       <c r="K43" s="13">
-        <v>138.50838393305</v>
-      </c>
-      <c r="L43" s="10">
-        <v>5.9319999999999998E-2</v>
+        <v>114.38797755776</v>
+      </c>
+      <c r="L43" s="13">
+        <v>5.2067291788855998</v>
       </c>
       <c r="M43" s="14">
         <v>2000</v>
       </c>
-      <c r="N43" s="37" t="s">
-        <v>98</v>
+      <c r="N43" s="15" t="s">
+        <v>97</v>
       </c>
       <c r="O43" s="16">
-        <v>2200000000</v>
+        <v>650000000</v>
       </c>
       <c r="P43" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>99</v>
+      <c r="A44" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Centene</v>
+      </c>
+      <c r="B44" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Insurance and Reinsurance</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="F44" s="32">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G44" s="33" t="s">
-        <v>179</v>
+        <v>21</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="10">
+        <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G44" s="11">
+        <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47851</v>
       </c>
       <c r="H44" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I44" s="13">
-        <v>102.62</v>
+        <v>87.472499999999997</v>
       </c>
       <c r="J44" s="13">
-        <v>4.7117258045619002</v>
+        <v>5.6745121526288997</v>
       </c>
       <c r="K44" s="13">
-        <v>48.764287063314001</v>
-      </c>
-      <c r="L44" s="10">
-        <v>4.8669999999999998E-2</v>
-      </c>
-      <c r="M44" s="34">
+        <v>149.18257120941999</v>
+      </c>
+      <c r="L44" s="13">
+        <v>5.6366512377394002</v>
+      </c>
+      <c r="M44" s="14">
+        <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N44" s="15" t="s">
-        <v>100</v>
+      <c r="N44" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="O44" s="16">
-        <v>1000000000</v>
+        <v>2200000000</v>
       </c>
       <c r="P44" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>80</v>
+      <c r="A45" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Micron Technology</v>
+      </c>
+      <c r="B45" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Semiconductors</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" s="10">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="G45" s="11">
-        <v>47908</v>
+        <v>12</v>
+      </c>
+      <c r="E45" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BBB-/BBB</v>
+      </c>
+      <c r="F45" s="32">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G45" s="33" t="str">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/01/2031</v>
       </c>
       <c r="H45" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I45" s="13">
-        <v>101.072</v>
+        <v>102.07</v>
       </c>
       <c r="J45" s="13">
-        <v>5.4017667057769998</v>
+        <v>4.8424845463382002</v>
       </c>
       <c r="K45" s="13">
-        <v>118.26512311741</v>
-      </c>
-      <c r="L45" s="10">
-        <v>5.5660000000000001E-2</v>
-      </c>
-      <c r="M45" s="14">
+        <v>67.974237180621998</v>
+      </c>
+      <c r="L45" s="13">
+        <v>4.7117258045619002</v>
+      </c>
+      <c r="M45" s="34">
+        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O45" s="16">
-        <v>823936000</v>
+        <v>1000000000</v>
       </c>
       <c r="P45" s="17" t="s">
         <v>142</v>
@@ -4152,349 +6181,388 @@
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>102</v>
+        <v>25</v>
+      </c>
+      <c r="B46" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>25</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E46" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="F46" s="10">
-        <v>2.726E-2</v>
-      </c>
-      <c r="G46" s="11" t="s">
-        <v>180</v>
+      <c r="E46" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F46" s="32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G46" s="33">
+        <v>47899</v>
       </c>
       <c r="H46" s="12">
         <v>2031</v>
       </c>
-      <c r="I46" s="13">
-        <v>91.46</v>
-      </c>
-      <c r="J46" s="13">
-        <v>4.7999393948671001</v>
-      </c>
-      <c r="K46" s="13">
-        <v>54.458166391596002</v>
-      </c>
-      <c r="L46" s="10">
-        <v>5.0180000000000002E-2</v>
-      </c>
-      <c r="M46" s="14">
+      <c r="I46" s="43">
+        <v>97.59</v>
+      </c>
+      <c r="J46" s="43">
+        <v>5.1539999999999999</v>
+      </c>
+      <c r="K46" s="43">
+        <v>91.02</v>
+      </c>
+      <c r="L46" s="13">
+        <v>5.1539999999999999</v>
+      </c>
+      <c r="M46" s="34">
         <v>2000</v>
       </c>
       <c r="N46" s="15" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="O46" s="16">
-        <v>1250000000</v>
+        <v>600000000</v>
       </c>
       <c r="P46" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>42</v>
+      <c r="A47" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Petrobras</v>
+      </c>
+      <c r="B47" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>80</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Ba1/BB/BB</v>
       </c>
       <c r="F47" s="10">
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="G47" s="11" t="s">
-        <v>181</v>
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G47" s="11">
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47908</v>
       </c>
       <c r="H47" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I47" s="13">
-        <v>93.924999999999997</v>
+        <v>100.818</v>
       </c>
       <c r="J47" s="13">
-        <v>5.0978896042555002</v>
+        <v>5.4649379355078</v>
       </c>
       <c r="K47" s="13">
-        <v>83.875248078192001</v>
-      </c>
-      <c r="L47" s="10">
-        <v>5.2920000000000002E-2</v>
+        <v>129.98804491460999</v>
+      </c>
+      <c r="L47" s="13">
+        <v>5.4017667057769998</v>
       </c>
       <c r="M47" s="14">
+        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O47" s="16">
-        <v>500000000</v>
+        <v>823936000</v>
       </c>
       <c r="P47" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="F48" s="23">
-        <v>2.4E-2</v>
-      </c>
-      <c r="G48" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="H48" s="25">
+      <c r="A48" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>British American Tobacco</v>
+      </c>
+      <c r="B48" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Tobacco</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa1/BBB+/BBB+</v>
+      </c>
+      <c r="F48" s="10">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>2.726E-2</v>
+      </c>
+      <c r="G48" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>25/03/2031</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="I48" s="26">
-        <v>75.94</v>
-      </c>
-      <c r="J48" s="26">
-        <v>8.6660091505333998</v>
-      </c>
-      <c r="K48" s="26">
-        <v>440.02339908489</v>
-      </c>
-      <c r="L48" s="23">
-        <v>8.7279999999999996E-2</v>
-      </c>
-      <c r="M48" s="27">
+      <c r="I48" s="13">
+        <v>91.26</v>
+      </c>
+      <c r="J48" s="13">
+        <v>4.8767534636613004</v>
+      </c>
+      <c r="K48" s="13">
+        <v>69.125403489383004</v>
+      </c>
+      <c r="L48" s="13">
+        <v>4.7999393948671001</v>
+      </c>
+      <c r="M48" s="14">
+        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N48" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="O48" s="29">
-        <v>300000000</v>
+      <c r="N48" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="O48" s="16">
+        <v>1250000000</v>
       </c>
       <c r="P48" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>42</v>
+      <c r="A49" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>EQT</v>
+      </c>
+      <c r="B49" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F49" s="36">
-        <v>7.8750000000000001E-2</v>
-      </c>
-      <c r="G49" s="11" t="s">
-        <v>183</v>
+        <v>75</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Withdrawn/BBB-/BBB-</v>
+      </c>
+      <c r="F49" s="10">
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.6249999999999998E-2</v>
+      </c>
+      <c r="G49" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/05/2031</v>
       </c>
       <c r="H49" s="12">
+        <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I49" s="13">
-        <v>113.6675</v>
+        <v>93.474999999999994</v>
       </c>
       <c r="J49" s="13">
-        <v>4.9498674514266998</v>
+        <v>5.2268554977413002</v>
       </c>
       <c r="K49" s="13">
-        <v>70.050735469623007</v>
-      </c>
-      <c r="L49" s="10">
-        <v>5.0860000000000002E-2</v>
+        <v>103.85503999808</v>
+      </c>
+      <c r="L49" s="13">
+        <v>5.0978896042555002</v>
       </c>
       <c r="M49" s="14">
-        <v>1000</v>
+        <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="O49" s="16">
-        <v>484677000</v>
+        <v>500000000</v>
       </c>
       <c r="P49" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" s="36">
-        <v>4.2790000000000002E-2</v>
-      </c>
-      <c r="G50" s="11">
-        <v>48288</v>
-      </c>
-      <c r="H50" s="12">
-        <v>2032</v>
-      </c>
-      <c r="I50" s="13">
-        <v>91.094250000000002</v>
-      </c>
-      <c r="J50" s="13">
-        <v>6.2331151566388003</v>
-      </c>
-      <c r="K50" s="13">
-        <v>193.36512481278001</v>
-      </c>
-      <c r="L50" s="10">
-        <v>6.157E-2</v>
-      </c>
-      <c r="M50" s="14">
+      <c r="A50" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Whirlpool</v>
+      </c>
+      <c r="B50" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Domestic Appliances</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="23">
+        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>2.4E-2</v>
+      </c>
+      <c r="G50" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/05/2031</v>
+      </c>
+      <c r="H50" s="25">
+        <f t="shared" si="0"/>
+        <v>2031</v>
+      </c>
+      <c r="I50" s="26">
+        <v>74.83</v>
+      </c>
+      <c r="J50" s="26">
+        <v>9.0926741364232999</v>
+      </c>
+      <c r="K50" s="26">
+        <v>489.94439984998002</v>
+      </c>
+      <c r="L50" s="26">
+        <v>8.6660091505333998</v>
+      </c>
+      <c r="M50" s="27">
+        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N50" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="O50" s="16">
-        <v>2760600000</v>
+      <c r="N50" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="O50" s="29">
+        <v>300000000</v>
       </c>
       <c r="P50" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>34</v>
+      <c r="A51" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Occidental Petroleum</v>
+      </c>
+      <c r="B51" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="F51" s="36">
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="G51" s="11" t="s">
-        <v>184</v>
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>7.8750000000000001E-2</v>
+      </c>
+      <c r="G51" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/09/2031</v>
       </c>
       <c r="H51" s="12">
-        <v>2032</v>
+        <f t="shared" si="0"/>
+        <v>2031</v>
       </c>
       <c r="I51" s="13">
-        <v>90.674999999999997</v>
+        <v>112.6699</v>
       </c>
       <c r="J51" s="13">
-        <v>4.9921546996049999</v>
+        <v>5.1303234644179003</v>
       </c>
       <c r="K51" s="13">
-        <v>67.936566834725994</v>
-      </c>
-      <c r="L51" s="36">
-        <v>5.2600000000000001E-2</v>
+        <v>94.948125726268998</v>
+      </c>
+      <c r="L51" s="13">
+        <v>4.9498674514266998</v>
       </c>
       <c r="M51" s="14">
-        <v>2000</v>
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>1000</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="O51" s="16">
-        <v>500000000</v>
+        <v>484677000</v>
       </c>
       <c r="P51" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="9" t="s">
+      <c r="A52" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Falabella</v>
+      </c>
+      <c r="B52" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Specialty Retailers</v>
+      </c>
+      <c r="C52" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E52" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="F52" s="36">
-        <v>5.3749999999999999E-2</v>
-      </c>
-      <c r="G52" s="11">
-        <v>48214</v>
-      </c>
-      <c r="H52" s="12">
+      <c r="E52" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F52" s="23">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="G52" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/01/2032</v>
+      </c>
+      <c r="H52" s="25">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I52" s="13">
-        <v>102.738</v>
-      </c>
-      <c r="J52" s="13">
-        <v>4.8638137088405999</v>
-      </c>
-      <c r="K52" s="13">
-        <v>58.643614984541998</v>
-      </c>
-      <c r="L52" s="10">
-        <v>5.0970000000000001E-2</v>
-      </c>
-      <c r="M52" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N52" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="O52" s="16">
-        <v>1000000000</v>
+      <c r="I52" s="26">
+        <v>90.457499999999996</v>
+      </c>
+      <c r="J52" s="26">
+        <v>5.4688768811572004</v>
+      </c>
+      <c r="K52" s="26">
+        <v>125.09910315875</v>
+      </c>
+      <c r="L52" s="26">
+        <v>5.3674177412753004</v>
+      </c>
+      <c r="M52" s="27">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>200000</v>
+      </c>
+      <c r="N52" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="O52" s="29">
+        <v>650000000</v>
       </c>
       <c r="P52" s="17" t="s">
         <v>142</v>
@@ -4502,299 +6570,334 @@
     </row>
     <row r="53" spans="1:16">
       <c r="A53" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="F53" s="32">
-        <v>6.25E-2</v>
-      </c>
-      <c r="G53" s="33" t="s">
-        <v>184</v>
+        <v>93</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="36">
+        <v>4.2790000000000002E-2</v>
+      </c>
+      <c r="G53" s="11">
+        <v>48288</v>
       </c>
       <c r="H53" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I53" s="13">
-        <v>102.25</v>
+        <v>90.445499999999996</v>
       </c>
       <c r="J53" s="13">
-        <v>5.8657497923847002</v>
+        <v>6.4012437882361999</v>
       </c>
       <c r="K53" s="13">
-        <v>158.16329348997999</v>
-      </c>
-      <c r="L53" s="10">
-        <v>5.8349999999999999E-2</v>
+        <v>218.13974059820001</v>
+      </c>
+      <c r="L53" s="13">
+        <v>6.2331151566388003</v>
       </c>
       <c r="M53" s="14">
         <v>2000</v>
       </c>
-      <c r="N53" s="35" t="s">
-        <v>115</v>
+      <c r="N53" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="O53" s="16">
-        <v>600000000</v>
+        <v>2760600000</v>
       </c>
       <c r="P53" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>125</v>
+      <c r="A54" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Tapestry</v>
+      </c>
+      <c r="B54" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Specialty Retailers</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="9" t="s">
-        <v>126</v>
+      <c r="E54" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa2/BBB/Withdrawn</v>
       </c>
       <c r="F54" s="36">
-        <v>4.7419999999999997E-2</v>
-      </c>
-      <c r="G54" s="11" t="s">
-        <v>189</v>
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G54" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/03/2032</v>
       </c>
       <c r="H54" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I54" s="13">
-        <v>99.768500000000003</v>
+        <v>90.4</v>
       </c>
       <c r="J54" s="13">
-        <v>4.8443604233849999</v>
+        <v>5.0720630206267003</v>
       </c>
       <c r="K54" s="13">
-        <v>54.651337794322998</v>
-      </c>
-      <c r="L54" s="10">
-        <v>5.0750000000000003E-2</v>
+        <v>84.111858144086</v>
+      </c>
+      <c r="L54" s="13">
+        <v>4.9921546996049999</v>
       </c>
       <c r="M54" s="14">
+        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N54" s="15" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O54" s="16">
-        <v>900000000</v>
+        <v>500000000</v>
       </c>
       <c r="P54" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" s="22" t="s">
+      <c r="A55" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Occidental Petroleum</v>
+      </c>
+      <c r="B55" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F55" s="23">
-        <v>4.7E-2</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="H55" s="25">
+      <c r="E55" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Withdrawn/BB+/BBB-</v>
+      </c>
+      <c r="F55" s="36">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.3749999999999999E-2</v>
+      </c>
+      <c r="G55" s="11">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>48214</v>
+      </c>
+      <c r="H55" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I55" s="26">
-        <v>79.930000000000007</v>
-      </c>
-      <c r="J55" s="26">
-        <v>9.3807757333051001</v>
-      </c>
-      <c r="K55" s="26">
-        <v>507.82625764645002</v>
-      </c>
-      <c r="L55" s="23">
-        <v>9.0060000000000001E-2</v>
-      </c>
-      <c r="M55" s="27">
+      <c r="I55" s="13">
+        <v>101.77</v>
+      </c>
+      <c r="J55" s="13">
+        <v>5.0642586010107999</v>
+      </c>
+      <c r="K55" s="13">
+        <v>85.485963290301001</v>
+      </c>
+      <c r="L55" s="13">
+        <v>4.8638137088405999</v>
+      </c>
+      <c r="M55" s="14">
+        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N55" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="O55" s="29">
-        <v>300000000</v>
+      <c r="N55" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="O55" s="16">
+        <v>1000000000</v>
       </c>
       <c r="P55" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="36">
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="G56" s="11">
-        <v>48215</v>
+      <c r="A56" s="19" t="str">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Methanex US Operations</v>
+      </c>
+      <c r="B56" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Food and Beverage Production</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/-/BB+</v>
+      </c>
+      <c r="F56" s="32">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G56" s="33" t="str">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/03/2032</v>
       </c>
       <c r="H56" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I56" s="13">
-        <v>97.817999999999998</v>
+        <v>101.011</v>
       </c>
       <c r="J56" s="13">
-        <v>5.2686449671825999</v>
+        <v>6.1261381346982002</v>
       </c>
       <c r="K56" s="13">
-        <v>98.073380220895999</v>
-      </c>
-      <c r="L56" s="10">
-        <v>5.4879999999999998E-2</v>
+        <v>191.88007492214001</v>
+      </c>
+      <c r="L56" s="13">
+        <v>5.8657497923847002</v>
       </c>
       <c r="M56" s="14">
+        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N56" s="15" t="s">
-        <v>120</v>
+      <c r="N56" s="35" t="s">
+        <v>115</v>
       </c>
       <c r="O56" s="16">
-        <v>1150000000</v>
+        <v>600000000</v>
       </c>
       <c r="P56" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>177</v>
+      <c r="A57" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>British American Tobacco</v>
+      </c>
+      <c r="B57" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Tobacco</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="9" t="s">
-        <v>121</v>
+      <c r="E57" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa1/BBB+/BBB+</v>
       </c>
       <c r="F57" s="36">
-        <v>5.6500000000000002E-2</v>
-      </c>
-      <c r="G57" s="11">
-        <v>48224</v>
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.7419999999999997E-2</v>
+      </c>
+      <c r="G57" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>16/03/2032</v>
       </c>
       <c r="H57" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I57" s="13">
-        <v>103.315</v>
+        <v>99.3155</v>
       </c>
       <c r="J57" s="13">
-        <v>5.0980394520193997</v>
+        <v>4.9393697303708999</v>
       </c>
       <c r="K57" s="13">
-        <v>77.223725710382993</v>
-      </c>
-      <c r="L57" s="10">
-        <v>5.3589999999999999E-2</v>
+        <v>72.074971640130002</v>
+      </c>
+      <c r="L57" s="13">
+        <v>4.8443604233849999</v>
       </c>
       <c r="M57" s="14">
+        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="O57" s="16">
-        <v>500000000</v>
+        <v>900000000</v>
       </c>
       <c r="P57" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="10">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G58" s="11">
-        <v>48458</v>
-      </c>
-      <c r="H58" s="12">
+      <c r="A58" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Whirlpool</v>
+      </c>
+      <c r="B58" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Domestic Appliances</v>
+      </c>
+      <c r="C58" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F58" s="23">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.7E-2</v>
+      </c>
+      <c r="G58" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>14/05/2032</v>
+      </c>
+      <c r="H58" s="25">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I58" s="13">
-        <v>100.959</v>
-      </c>
-      <c r="J58" s="13">
-        <v>5.3856085213808997</v>
-      </c>
-      <c r="K58" s="13">
-        <v>107.12675155554</v>
-      </c>
-      <c r="L58" s="36">
-        <v>5.5039999999999999E-2</v>
-      </c>
-      <c r="M58" s="14">
+      <c r="I58" s="26">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="J58" s="26">
+        <v>9.5653205508415997</v>
+      </c>
+      <c r="K58" s="26">
+        <v>534.30350032287004</v>
+      </c>
+      <c r="L58" s="26">
+        <v>9.3807757333051001</v>
+      </c>
+      <c r="M58" s="27">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N58" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="O58" s="16">
-        <v>500000000</v>
+      <c r="N58" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="O58" s="29">
+        <v>300000000</v>
       </c>
       <c r="P58" s="17" t="s">
         <v>142</v>
@@ -4802,99 +6905,106 @@
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="8" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="F59" s="36">
-        <v>6.9000000000000006E-2</v>
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="G59" s="11">
-        <v>48349</v>
+        <v>48215</v>
       </c>
       <c r="H59" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I59" s="13">
-        <v>96.5</v>
+        <v>97.382000000000005</v>
       </c>
       <c r="J59" s="13">
-        <v>7.8280887021760002</v>
+        <v>5.3686118665361002</v>
       </c>
       <c r="K59" s="13">
-        <v>356.48803014060002</v>
-      </c>
-      <c r="L59" s="10">
-        <v>7.2999999999999995E-2</v>
+        <v>115.79947915907999</v>
+      </c>
+      <c r="L59" s="13">
+        <v>5.2686449671825999</v>
       </c>
       <c r="M59" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O59" s="16">
-        <v>250000000</v>
+        <v>1150000000</v>
       </c>
       <c r="P59" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>125</v>
+      <c r="A60" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Micron Technology</v>
+      </c>
+      <c r="B60" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Semiconductors</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E60" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="F60" s="40">
-        <v>6.4210000000000003E-2</v>
-      </c>
-      <c r="G60" s="33">
-        <v>48793</v>
-      </c>
-      <c r="H60" s="41">
-        <v>2033</v>
+      <c r="E60" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F60" s="36">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.6500000000000002E-2</v>
+      </c>
+      <c r="G60" s="11">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>48224</v>
+      </c>
+      <c r="H60" s="12">
+        <f t="shared" si="0"/>
+        <v>2032</v>
       </c>
       <c r="I60" s="13">
-        <v>108.25</v>
+        <v>103.16925000000001</v>
       </c>
       <c r="J60" s="13">
-        <v>5.0918269119830004</v>
+        <v>5.1199812746477997</v>
       </c>
       <c r="K60" s="13">
-        <v>74.142324322467999</v>
-      </c>
-      <c r="L60" s="32">
-        <v>5.2949999999999997E-2</v>
-      </c>
-      <c r="M60" s="34">
+        <v>87.806085161064004</v>
+      </c>
+      <c r="L60" s="13">
+        <v>5.0980394520193997</v>
+      </c>
+      <c r="M60" s="14">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N60" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="O60" s="42">
-        <v>1250000000</v>
+      <c r="N60" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="O60" s="16">
+        <v>500000000</v>
       </c>
       <c r="P60" s="17" t="s">
         <v>142</v>
@@ -4902,149 +7012,151 @@
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>108</v>
+        <v>42</v>
+      </c>
+      <c r="C61" s="9" t="str">
+        <f>+A61</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
       <c r="F61" s="10">
-        <v>5.6000000000000001E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G61" s="11">
-        <v>49218</v>
+        <v>48458</v>
       </c>
       <c r="H61" s="12">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="I61" s="13">
-        <v>102.9545</v>
+        <v>101.663</v>
       </c>
       <c r="J61" s="13">
-        <v>5.1724981641551997</v>
+        <v>5.2464322657264004</v>
       </c>
       <c r="K61" s="13">
-        <v>75.495824162983993</v>
-      </c>
-      <c r="L61" s="10">
-        <v>5.1999999999999998E-2</v>
+        <v>101.38634535505</v>
+      </c>
+      <c r="L61" s="13">
+        <v>5.3856085213808997</v>
       </c>
       <c r="M61" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="O61" s="16">
-        <v>1200000000</v>
+        <v>500000000</v>
       </c>
       <c r="P61" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="39" t="s">
-        <v>69</v>
+      <c r="A62" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>69</v>
+        <v>34</v>
+      </c>
+      <c r="C62" s="9" t="str">
+        <f>+A62</f>
+        <v>Macy´s</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F62" s="10">
-        <v>5.3999999999999999E-2</v>
+        <v>77</v>
+      </c>
+      <c r="F62" s="36">
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G62" s="11">
-        <v>49589</v>
+        <v>48349</v>
       </c>
       <c r="H62" s="12">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="I62" s="13">
-        <v>98.106999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="J62" s="13">
-        <v>5.7431229949776004</v>
+        <v>7.8368882215886</v>
       </c>
       <c r="K62" s="13">
-        <v>128.12367312126</v>
-      </c>
-      <c r="L62" s="10">
-        <v>5.9220000000000002E-2</v>
+        <v>364.54290681703998</v>
+      </c>
+      <c r="L62" s="13">
+        <v>7.8280887021760002</v>
       </c>
       <c r="M62" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N62" s="15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="O62" s="16">
-        <v>600000000</v>
+        <v>250000000</v>
       </c>
       <c r="P62" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="8" t="s">
-        <v>83</v>
+      <c r="A63" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F63" s="10">
-        <v>5.9799999999999999E-2</v>
-      </c>
-      <c r="G63" s="11">
-        <v>49351</v>
-      </c>
-      <c r="H63" s="12">
-        <v>2035</v>
+      <c r="E63" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="40">
+        <v>6.4210000000000003E-2</v>
+      </c>
+      <c r="G63" s="33">
+        <v>48793</v>
+      </c>
+      <c r="H63" s="41">
+        <v>2033</v>
       </c>
       <c r="I63" s="13">
-        <v>104.64575000000001</v>
+        <v>107.76</v>
       </c>
       <c r="J63" s="13">
-        <v>5.3727784157435998</v>
+        <v>5.1640210219803997</v>
       </c>
       <c r="K63" s="13">
-        <v>94.943278907543998</v>
-      </c>
-      <c r="L63" s="10">
-        <v>5.6500000000000002E-2</v>
-      </c>
-      <c r="M63" s="14">
+        <v>90.100799827076997</v>
+      </c>
+      <c r="L63" s="13">
+        <v>5.0918269119830004</v>
+      </c>
+      <c r="M63" s="34">
         <v>2000</v>
       </c>
-      <c r="N63" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="O63" s="16">
-        <v>650000000</v>
+      <c r="N63" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="O63" s="42">
+        <v>1250000000</v>
       </c>
       <c r="P63" s="17" t="s">
         <v>142</v>
@@ -5052,177 +7164,332 @@
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>34</v>
+        <v>134</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F64" s="36">
-        <v>5.5E-2</v>
+        <v>153</v>
+      </c>
+      <c r="F64" s="10">
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="G64" s="11">
-        <v>49379</v>
+        <v>49218</v>
       </c>
       <c r="H64" s="12">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="I64" s="13">
-        <v>100.825</v>
+        <v>101.79</v>
       </c>
       <c r="J64" s="13">
-        <v>5.4514660395618</v>
+        <v>5.3474082910789997</v>
       </c>
       <c r="K64" s="13">
-        <v>101.63373483238</v>
-      </c>
-      <c r="L64" s="10">
-        <v>5.7180000000000002E-2</v>
+        <v>102.32605446818</v>
+      </c>
+      <c r="L64" s="13">
+        <v>5.1724981641551997</v>
       </c>
       <c r="M64" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N64" s="15" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="O64" s="16">
-        <v>750000000</v>
+        <v>1200000000</v>
       </c>
       <c r="P64" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" s="8" t="s">
-        <v>119</v>
+      <c r="A65" s="39" t="s">
+        <v>69</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="36">
-        <v>5.7000000000000002E-2</v>
+        <v>70</v>
+      </c>
+      <c r="F65" s="10">
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G65" s="11">
-        <v>49324</v>
+        <v>49589</v>
       </c>
       <c r="H65" s="12">
+        <f>YEAR(G65)</f>
         <v>2035</v>
       </c>
       <c r="I65" s="13">
-        <v>101.6</v>
+        <v>96.627459999999999</v>
       </c>
       <c r="J65" s="13">
-        <v>5.5378214915232</v>
+        <v>5.9627747994528999</v>
       </c>
       <c r="K65" s="13">
-        <v>111.66625180721</v>
-      </c>
-      <c r="L65" s="10">
-        <v>5.6770000000000001E-2</v>
+        <v>159.65978946299001</v>
+      </c>
+      <c r="L65" s="13">
+        <v>5.7431229949776004</v>
       </c>
       <c r="M65" s="14">
         <v>2000</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="O65" s="16">
-        <v>750000000</v>
+        <v>600000000</v>
       </c>
       <c r="P65" s="17" t="s">
         <v>142</v>
       </c>
     </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" s="10">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="G66" s="11">
+        <v>49351</v>
+      </c>
+      <c r="H66" s="12">
+        <v>2035</v>
+      </c>
+      <c r="I66" s="13">
+        <v>104.18174999999999</v>
+      </c>
+      <c r="J66" s="13">
+        <v>5.4373842285820997</v>
+      </c>
+      <c r="K66" s="13">
+        <v>110.72756212295999</v>
+      </c>
+      <c r="L66" s="13">
+        <v>5.3727784157435998</v>
+      </c>
+      <c r="M66" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N66" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="O66" s="16">
+        <v>650000000</v>
+      </c>
+      <c r="P66" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F67" s="36">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G67" s="11">
+        <v>49379</v>
+      </c>
+      <c r="H67" s="12">
+        <f>YEAR(G67)</f>
+        <v>2035</v>
+      </c>
+      <c r="I67" s="13">
+        <v>100.16</v>
+      </c>
+      <c r="J67" s="13">
+        <v>5.5503247750032996</v>
+      </c>
+      <c r="K67" s="13">
+        <v>120.89879267489</v>
+      </c>
+      <c r="L67" s="13">
+        <v>5.4514660395618</v>
+      </c>
+      <c r="M67" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N67" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="O67" s="16">
+        <v>750000000</v>
+      </c>
+      <c r="P67" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="36">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="G68" s="11">
+        <v>49324</v>
+      </c>
+      <c r="H68" s="12">
+        <v>2035</v>
+      </c>
+      <c r="I68" s="13">
+        <v>100.685</v>
+      </c>
+      <c r="J68" s="13">
+        <v>5.6758894124054997</v>
+      </c>
+      <c r="K68" s="13">
+        <v>134.82334868976</v>
+      </c>
+      <c r="L68" s="13">
+        <v>5.5378214915232</v>
+      </c>
+      <c r="M68" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N68" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="O68" s="16">
+        <v>750000000</v>
+      </c>
+      <c r="P68" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N65">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="N2:N68">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{9940A9BB-80FC-4185-B25A-29B25029E0A1}"/>
-    <hyperlink ref="N3" r:id="rId2" xr:uid="{0DA6F926-D662-46BF-AA23-1B1D8678424E}"/>
-    <hyperlink ref="N4" r:id="rId3" xr:uid="{801AD434-E44D-43C2-AF26-98CBC8802D45}"/>
-    <hyperlink ref="N5" r:id="rId4" xr:uid="{E68568D1-1BA2-4AF4-BE24-3A1CBBF2C551}"/>
-    <hyperlink ref="N6" r:id="rId5" xr:uid="{C569DADD-3A88-4B78-B435-60BF33CB1FCB}"/>
-    <hyperlink ref="N7" r:id="rId6" xr:uid="{E3BD4F25-DA02-43A2-8D15-6D19B050E2A5}"/>
-    <hyperlink ref="N8" r:id="rId7" xr:uid="{92C42F6A-3F2F-4021-B6F3-4A95998DE030}"/>
-    <hyperlink ref="N9" r:id="rId8" xr:uid="{3362482E-D622-4F13-816F-C5E396DC4662}"/>
-    <hyperlink ref="N10" r:id="rId9" xr:uid="{3CC8E3AB-C9A6-4E24-B2DF-3D54A5810A94}"/>
-    <hyperlink ref="N11" r:id="rId10" xr:uid="{7576B1B0-6F03-42FB-83AD-6CB072B9F5DC}"/>
-    <hyperlink ref="N12" r:id="rId11" xr:uid="{AEAA5550-35F8-4288-9700-04B8E2B8A448}"/>
-    <hyperlink ref="N16" r:id="rId12" xr:uid="{A3B4B342-733E-4A0A-9971-705B009655B2}"/>
-    <hyperlink ref="N17" r:id="rId13" xr:uid="{56FF6638-DC89-4529-B05A-8A4B1EFA3911}"/>
-    <hyperlink ref="N18" r:id="rId14" xr:uid="{32B58AC0-8E62-4DD4-A178-E2894F6FEAA9}"/>
-    <hyperlink ref="N19" r:id="rId15" xr:uid="{8840DA22-DC38-4940-B1E8-2A92EF8C7184}"/>
-    <hyperlink ref="N20" r:id="rId16" xr:uid="{49A5D354-17DD-4058-B1F7-BEB6744E69F7}"/>
-    <hyperlink ref="N21" r:id="rId17" xr:uid="{A850AAA6-8F1C-427E-8826-DACA60FA61D4}"/>
-    <hyperlink ref="N22" r:id="rId18" xr:uid="{C64B6D9C-EE04-4CFA-A2CE-B17297E18FFE}"/>
-    <hyperlink ref="N24" r:id="rId19" xr:uid="{2BC28AA3-3F51-4294-8B4B-0783E872E238}"/>
-    <hyperlink ref="N25" r:id="rId20" xr:uid="{1E05E9A7-7A50-4834-B67B-FAA4E0F78C27}"/>
-    <hyperlink ref="N26" r:id="rId21" xr:uid="{D7E807A2-E65B-4749-BAC5-C285DEE096DC}"/>
-    <hyperlink ref="N28" r:id="rId22" xr:uid="{7147D7D5-2864-4A49-9B5F-FBC5AAD7E92B}"/>
-    <hyperlink ref="N29" r:id="rId23" xr:uid="{D9AEEFE0-0700-4790-A75D-014DA3E9A6BE}"/>
-    <hyperlink ref="N30" r:id="rId24" xr:uid="{B809DCA3-8BFC-43FD-BED9-720FB13BDAF8}"/>
-    <hyperlink ref="N31" r:id="rId25" xr:uid="{BE8373A2-56F4-48AB-962D-8473E7A0F614}"/>
-    <hyperlink ref="N32" r:id="rId26" xr:uid="{0D6F06BD-7FCC-43CB-BF35-90185BD43B97}"/>
-    <hyperlink ref="N33" r:id="rId27" xr:uid="{77488EC3-F357-4724-85E3-60EC449492BA}"/>
-    <hyperlink ref="N34" r:id="rId28" xr:uid="{7EDC9A64-A8A6-4A40-B2A0-1F852CD39E06}"/>
-    <hyperlink ref="N35" r:id="rId29" xr:uid="{66CD0782-73B6-4412-9BE0-E18458468160}"/>
-    <hyperlink ref="N36" r:id="rId30" xr:uid="{890DC8B9-1CF5-4B03-AA82-807F1A9DF41F}"/>
-    <hyperlink ref="N37" r:id="rId31" xr:uid="{4C7D6DFE-E13E-4E2E-BFAC-721F7DCB338A}"/>
-    <hyperlink ref="N38" r:id="rId32" xr:uid="{BAD23E05-F7B7-42E2-945D-604BC76A3D88}"/>
-    <hyperlink ref="N39" r:id="rId33" xr:uid="{2F549D10-2C5D-4209-9266-27AB0AB3CB17}"/>
-    <hyperlink ref="N40" r:id="rId34" xr:uid="{3C59AE49-2780-4919-8291-5FEA18D48542}"/>
-    <hyperlink ref="N42" r:id="rId35" xr:uid="{187AF8EB-0EC3-4B29-9770-7BF4304FA85B}"/>
-    <hyperlink ref="N44" r:id="rId36" xr:uid="{325BB778-6CDC-4BDE-8907-22697C8B13E8}"/>
-    <hyperlink ref="N45" r:id="rId37" xr:uid="{FF053768-E489-4B8F-BE7B-656C617335E9}"/>
-    <hyperlink ref="N46" r:id="rId38" xr:uid="{120E67E5-EDC9-4E29-AA18-D97575A2253A}"/>
-    <hyperlink ref="N47" r:id="rId39" xr:uid="{B4254DDA-A8DF-480B-9217-D636592139CA}"/>
-    <hyperlink ref="N48" r:id="rId40" xr:uid="{CD85CD42-FE49-4E09-A2FF-C4071A0D9BC8}"/>
-    <hyperlink ref="N49" r:id="rId41" xr:uid="{17D28DE2-B082-4299-AD9A-7D15601D61A3}"/>
-    <hyperlink ref="N50" r:id="rId42" xr:uid="{83F43AC4-D15F-4761-A22D-1300995B7D82}"/>
-    <hyperlink ref="N51" r:id="rId43" xr:uid="{339D9314-DB8E-418E-8A8F-E7A15487340C}"/>
-    <hyperlink ref="N52" r:id="rId44" xr:uid="{9D8E1DAD-631E-4466-BA67-0CD09BF8CD84}"/>
-    <hyperlink ref="N53" r:id="rId45" xr:uid="{D94FD75B-22CD-4580-BB9D-DB03B56AC40C}"/>
-    <hyperlink ref="N54" r:id="rId46" xr:uid="{0F0ED580-E401-401E-A6B2-CDCED35594DC}"/>
-    <hyperlink ref="N56" r:id="rId47" xr:uid="{B9854860-D325-4DA9-8AED-22A29DD0ECFE}"/>
-    <hyperlink ref="N57" r:id="rId48" xr:uid="{B890CBC1-35B1-4042-8E73-91A5418A2A4E}"/>
-    <hyperlink ref="N62" r:id="rId49" xr:uid="{DF16427E-ABD3-4C68-89CD-46CD564ADBD6}"/>
-    <hyperlink ref="N63" r:id="rId50" xr:uid="{D8153407-E0C1-4170-9B4D-CFDED16402B8}"/>
-    <hyperlink ref="N64" r:id="rId51" xr:uid="{FF3125ED-A38D-4284-B062-AAD498AF7E89}"/>
-    <hyperlink ref="N41" r:id="rId52" xr:uid="{9BF5B2E3-B4E2-4108-8E38-D8AD62C70B7E}"/>
-    <hyperlink ref="N58" r:id="rId53" xr:uid="{7182BC6B-1784-4CB9-83D8-C3BA53FE47F5}"/>
-    <hyperlink ref="N65" r:id="rId54" xr:uid="{477317F5-E3D4-4E1D-81FC-C15671BAEB18}"/>
-    <hyperlink ref="N59" r:id="rId55" xr:uid="{5A888400-0FDF-4D93-A2F0-2988AB57583C}"/>
-    <hyperlink ref="N60" r:id="rId56" xr:uid="{85FC6F5A-E1D7-47D4-835B-E3AF37CB416D}"/>
-    <hyperlink ref="N43" r:id="rId57" xr:uid="{F05AF1FC-246F-4B0E-AC3D-9F173B70F596}"/>
-    <hyperlink ref="N55" r:id="rId58" xr:uid="{F770B95D-54C9-4F7E-9E78-E1816E22998E}"/>
-    <hyperlink ref="N15" r:id="rId59" xr:uid="{0B4A0866-C56E-4EDA-85E2-6DF10D2EA5BB}"/>
-    <hyperlink ref="N27" r:id="rId60" xr:uid="{F2499CCC-0DE7-4C96-8476-485738A69652}"/>
-    <hyperlink ref="N14" r:id="rId61" xr:uid="{7BB93CC3-3EB5-4AAE-B616-21B830EA0220}"/>
-    <hyperlink ref="N23" r:id="rId62" xr:uid="{AE16ACF5-26FB-4EEE-B385-CC713EBADB67}"/>
-    <hyperlink ref="N13" r:id="rId63" xr:uid="{41BC6424-9240-4EC7-8836-E2A5E9B4F2C7}"/>
-    <hyperlink ref="N61" r:id="rId64" xr:uid="{56483B0D-4D73-4967-B07A-3D0E9133BC55}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{F8829E3F-53D2-4C6C-9556-A1DDA13CBEA8}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{493DE554-0834-4A5C-9D88-925D18050DB3}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{5BE5A1EF-BB44-461F-9180-7B475B0E9396}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{9ED42145-4DEF-4A63-82CC-C2C56C5E4860}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{D4C53924-1412-406C-9692-2B99F5D2879B}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{B8987634-CF7E-407B-AF46-09E5211D981E}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{7D8E48B7-C6EA-48B6-AC74-0C8C0968DE3E}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{845603A1-124D-4CA4-9856-9CC87EB7B9EF}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{5BBB0919-A125-4DC8-8FEB-868401D698E1}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{13B976B5-58F3-4D39-84F9-716FB2088569}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{E3B7D5A1-5A80-4B4C-8CFE-D76B19230139}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{B7CF9816-C500-4E7F-9269-2E696758B64B}"/>
+    <hyperlink ref="N17" r:id="rId13" xr:uid="{DE9DE913-BE83-48B3-9EDE-01DBAEB6486C}"/>
+    <hyperlink ref="N18" r:id="rId14" xr:uid="{435F6EF0-D8DA-4369-AB88-5D6430E3D047}"/>
+    <hyperlink ref="N19" r:id="rId15" xr:uid="{A4315895-83ED-4A4A-AFD7-25F372EAE814}"/>
+    <hyperlink ref="N20" r:id="rId16" xr:uid="{733C5B94-3883-4A88-9D48-9DA42C7476E7}"/>
+    <hyperlink ref="N21" r:id="rId17" xr:uid="{0E366B85-C215-4A7A-AD99-CDB93D72F7A7}"/>
+    <hyperlink ref="N22" r:id="rId18" xr:uid="{D4C2FA22-5BF8-4424-9CF7-8674E4A4106E}"/>
+    <hyperlink ref="N23" r:id="rId19" xr:uid="{322D778A-F1DD-4155-93A9-D5A6649DCF18}"/>
+    <hyperlink ref="N25" r:id="rId20" xr:uid="{EE50CE36-62A1-45DA-8F9C-E9E8F2808CF5}"/>
+    <hyperlink ref="N26" r:id="rId21" xr:uid="{21C5FF06-59F8-43DA-8AA1-2A52D01B5CB0}"/>
+    <hyperlink ref="N27" r:id="rId22" xr:uid="{F1FB2C44-DB61-43EC-A295-C27A79EEB202}"/>
+    <hyperlink ref="N29" r:id="rId23" xr:uid="{B67E00C8-419D-47DD-8CD4-7CA49E15BBF6}"/>
+    <hyperlink ref="N30" r:id="rId24" xr:uid="{E8F014BA-433D-4D7C-8B18-B51CE4B26F61}"/>
+    <hyperlink ref="N31" r:id="rId25" xr:uid="{3CC9971E-673D-44AD-B09A-6DB728D567F8}"/>
+    <hyperlink ref="N32" r:id="rId26" xr:uid="{02126DEA-8F82-41A4-9362-17A9C6D5E32B}"/>
+    <hyperlink ref="N33" r:id="rId27" xr:uid="{E7297F32-7C00-464C-AE99-69C36D1F1613}"/>
+    <hyperlink ref="N34" r:id="rId28" xr:uid="{F9131CCF-336C-4B24-B612-EEFD07BA775C}"/>
+    <hyperlink ref="N35" r:id="rId29" xr:uid="{BE9AE4CC-C3E1-4950-8D8B-270F02BF60B7}"/>
+    <hyperlink ref="N36" r:id="rId30" xr:uid="{624DE41A-68F3-48A5-869E-9700F9F71410}"/>
+    <hyperlink ref="N37" r:id="rId31" xr:uid="{A65F62BC-F37C-42BA-83ED-AB7D11F575A8}"/>
+    <hyperlink ref="N38" r:id="rId32" xr:uid="{40472BA3-E6DE-4439-9C52-41A140BBFC69}"/>
+    <hyperlink ref="N39" r:id="rId33" xr:uid="{4C8E626B-99D3-4420-9D92-F7AF982CD314}"/>
+    <hyperlink ref="N40" r:id="rId34" xr:uid="{D2EC59FA-A0E3-4B53-8889-82B0E55B21FE}"/>
+    <hyperlink ref="N41" r:id="rId35" xr:uid="{8FEE7385-3A2F-4BAE-B5B6-F5C4FE76B9BD}"/>
+    <hyperlink ref="N43" r:id="rId36" xr:uid="{1A2448D3-5A04-40FC-93A7-202A7D2069DE}"/>
+    <hyperlink ref="N45" r:id="rId37" xr:uid="{4566D9FA-63AE-4BE1-8327-384D1C03C900}"/>
+    <hyperlink ref="N47" r:id="rId38" xr:uid="{B518D265-7B19-4F7B-8C03-DEA09B0FB131}"/>
+    <hyperlink ref="N48" r:id="rId39" xr:uid="{4FBDB43C-AA47-4274-B352-31FF46C64F23}"/>
+    <hyperlink ref="N49" r:id="rId40" xr:uid="{1B7FF16F-B3D7-4BD0-A55C-FEDF4C93A0D0}"/>
+    <hyperlink ref="N50" r:id="rId41" xr:uid="{CE5DA5BA-1B3C-4844-9BFB-4DC0CFD3230D}"/>
+    <hyperlink ref="N51" r:id="rId42" xr:uid="{DDAC8608-E69D-4C8A-87A8-47130B585733}"/>
+    <hyperlink ref="N52" r:id="rId43" xr:uid="{C0A06BC2-023C-4659-8A6A-5A62E40D8F99}"/>
+    <hyperlink ref="N53" r:id="rId44" xr:uid="{908C235D-39F8-4709-B39E-0D750931FB85}"/>
+    <hyperlink ref="N54" r:id="rId45" xr:uid="{CA51059E-F0E2-448B-8395-327C75774534}"/>
+    <hyperlink ref="N55" r:id="rId46" xr:uid="{49C22A9E-9A0A-45EF-A986-867B41D22D38}"/>
+    <hyperlink ref="N56" r:id="rId47" xr:uid="{B818704F-053B-42E7-9E1A-033FC04780AC}"/>
+    <hyperlink ref="N57" r:id="rId48" xr:uid="{B2EC6875-55BE-4D4B-B44E-26B8D6E5B9BB}"/>
+    <hyperlink ref="N59" r:id="rId49" xr:uid="{E2C3E74C-A8FD-4744-9053-8C3F3D942DA0}"/>
+    <hyperlink ref="N60" r:id="rId50" xr:uid="{B1C63365-D207-4FD0-9BEF-62F44B06177D}"/>
+    <hyperlink ref="N65" r:id="rId51" xr:uid="{3DA7AD4B-F2D7-461E-8B1D-68CDC9F77197}"/>
+    <hyperlink ref="N66" r:id="rId52" xr:uid="{FAA16BC6-FB5D-4113-91BB-16E0EF112781}"/>
+    <hyperlink ref="N67" r:id="rId53" xr:uid="{1826AE20-917E-4600-97B8-3427D3AF5A7F}"/>
+    <hyperlink ref="N42" r:id="rId54" xr:uid="{84509A1E-478B-4F2F-A76B-7D3FDAC32567}"/>
+    <hyperlink ref="N61" r:id="rId55" xr:uid="{37272A85-48A2-49F3-B6B1-A1BF5108BB3B}"/>
+    <hyperlink ref="N68" r:id="rId56" xr:uid="{93FF6E81-D3CF-4DB1-A2BA-5C814E85A40B}"/>
+    <hyperlink ref="N62" r:id="rId57" xr:uid="{FA7152BA-C1C8-42D1-9AC6-1F8CE936EB1A}"/>
+    <hyperlink ref="N63" r:id="rId58" xr:uid="{30637A7A-0395-47CC-98DA-ED03C0640776}"/>
+    <hyperlink ref="N44" r:id="rId59" xr:uid="{3AAC5A48-F5CC-4389-AF46-D80EE222264C}"/>
+    <hyperlink ref="N58" r:id="rId60" xr:uid="{00C2204D-C3E0-426A-9CB0-6AE837769FCF}"/>
+    <hyperlink ref="N16" r:id="rId61" xr:uid="{46A1D7B2-C8AD-46A1-8875-A73F63E8C736}"/>
+    <hyperlink ref="N28" r:id="rId62" xr:uid="{1BFAF898-57E1-4C20-BA97-46B6F415E771}"/>
+    <hyperlink ref="N15" r:id="rId63" xr:uid="{568174ED-C9E1-47A7-9854-64812BFE8100}"/>
+    <hyperlink ref="N24" r:id="rId64" xr:uid="{E9207531-E5F0-470E-88F4-C6689BEA9BE5}"/>
+    <hyperlink ref="N14" r:id="rId65" xr:uid="{5F461451-0EE4-4113-8D8C-4CFED78CCF2D}"/>
+    <hyperlink ref="N64" r:id="rId66" xr:uid="{7C12EC03-B82E-4172-A765-7023385900B3}"/>
+    <hyperlink ref="N46" r:id="rId67" xr:uid="{D97CBE76-AC55-4BFA-8F7B-C7F4879E4141}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId65"/>
+    <tablePart r:id="rId68"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F91A523-6618-4D62-96C7-1494A64AAC6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B1B998-071F-40EA-8800-7147CC2DB9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="176">
   <si>
     <t>Industry</t>
   </si>
@@ -465,12 +465,6 @@
   </si>
   <si>
     <t>HF Sinclair</t>
-  </si>
-  <si>
-    <t>Recomendados</t>
-  </si>
-  <si>
-    <t>NO</t>
   </si>
   <si>
     <t>Issuer</t>
@@ -530,6 +524,54 @@
   </si>
   <si>
     <t>USP3984LAA81</t>
+  </si>
+  <si>
+    <t>Decisión</t>
+  </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Xerox</t>
+  </si>
+  <si>
+    <t>Caa3/CCC+/CCC</t>
+  </si>
+  <si>
+    <t>USU98401AB58</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Braskem</t>
+  </si>
+  <si>
+    <t>Caa3/CCC-/CC</t>
+  </si>
+  <si>
+    <t>USN15516AB83</t>
+  </si>
+  <si>
+    <t>Clearwater Paper</t>
+  </si>
+  <si>
+    <t>Pulp, Paper and Wood</t>
+  </si>
+  <si>
+    <t>Ba3/B+</t>
+  </si>
+  <si>
+    <t>USU18510AE44</t>
+  </si>
+  <si>
+    <t>Hold</t>
+  </si>
+  <si>
+    <t>DaVita</t>
+  </si>
+  <si>
+    <t>USU23888AE71</t>
   </si>
 </sst>
 </file>
@@ -867,17 +909,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -1447,6 +1479,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <right style="medium">
           <color indexed="64"/>
         </right>
@@ -1456,11 +1495,24 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3421,25 +3473,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}" name="Bonos" displayName="Bonos" ref="A1:P68" totalsRowShown="0" headerRowBorderDxfId="18" tableBorderDxfId="17">
-  <autoFilter ref="A1:P68" xr:uid="{F93BACB1-81B0-43AE-B65A-86CA031982F3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F9929528-1208-47D6-904C-61B41F15758C}" name="Bonos3" displayName="Bonos3" ref="A1:P72" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
+  <autoFilter ref="A1:P72" xr:uid="{F9929528-1208-47D6-904C-61B41F15758C}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{76188F60-7837-4F00-8224-C103412ED55F}" name="Issuer" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{A0C27939-9758-4C04-BF30-2F9454BC2BB9}" name="Industry" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{90D0E022-058D-441F-A798-A5EF6CB608B0}" name="Guarantor/Organization" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{08C8A67D-38C6-434F-B219-1791BCEDCB3B}" name="IG - HY" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{68B19C09-072B-426E-AB72-A1C1EB6FE24E}" name="Rating" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{394B9EEC-A40C-4C4C-9E44-7AF91ED26A4F}" name="Coupon %" dataDxfId="11" dataCellStyle="Porcentaje"/>
-    <tableColumn id="7" xr3:uid="{505C32AD-BB24-40BD-9551-5971808B3A69}" name="Maturity" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{70BE0778-4C1D-4CA1-9998-6E0F762EC188}" name="Year" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{0EC7E809-3B27-40E3-8FD8-B60C3ED1D181}" name="Price" dataDxfId="8" dataCellStyle="Porcentaje"/>
-    <tableColumn id="9" xr3:uid="{9BB915F3-BCD1-4C2C-9717-55600A9AE2FB}" name="YTW %" dataDxfId="7" dataCellStyle="Porcentaje"/>
-    <tableColumn id="21" xr3:uid="{E783A1B2-283D-4DD8-8B9C-D0B85752867C}" name="Gspread" dataDxfId="6" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{82133380-5CC8-4E83-90BB-8A2DDDD7F774}" name="Prev month_x000a_YTW%" dataDxfId="5" dataCellStyle="Porcentaje"/>
-    <tableColumn id="16" xr3:uid="{9554AC5E-795F-4E8C-9A87-D3AA50886E84}" name="Minimum Settlement" dataDxfId="4" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{4D5AD119-91C6-49CD-A5C2-061FE4B7B014}" name="ISIN" dataDxfId="3" dataCellStyle="Hipervínculo"/>
-    <tableColumn id="18" xr3:uid="{F88886C4-7F63-400D-BBEB-C06C34E17398}" name="Outstanding_x000a_US$" dataDxfId="2" dataCellStyle="Millares 3"/>
-    <tableColumn id="22" xr3:uid="{817F9505-2B1D-4A7A-B1A0-299BC30E9F89}" name="Recomendados" dataDxfId="1" dataCellStyle="Porcentaje"/>
+    <tableColumn id="1" xr3:uid="{2AFCD4C4-5B9C-440A-9683-35FF11067181}" name="Issuer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{5C55692A-D8F0-41F9-9F66-0666D68A9ABF}" name="Industry" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{F1C64926-17FF-455B-AAC3-F27FBB15B9BC}" name="Guarantor/Organization" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{AD770398-EFFC-4459-B3A5-1E0BD5A40F05}" name="IG - HY" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{517E0FA1-FB77-43EF-9252-4C47F0184D4E}" name="Rating" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{22CBE1BC-7885-451C-869B-CCD041D42F18}" name="Coupon %" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{39F8CD2C-0C47-4F14-B173-0CF32C2C5AC8}" name="Maturity" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{0CEC3680-E808-41F4-A878-27D6F8507BA9}" name="Year" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{DF407AB1-75BC-418E-BDF1-6D1121F02A3A}" name="Price" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{A384B870-24EE-4569-810D-C0F88E32F8DC}" name="YTW %" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{C8875639-D318-48B8-9F02-B7B7D622D498}" name="Gspread" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{649422D8-F09A-49AD-9529-4F730B728D67}" name="Prev month_x000a_YTW%" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{7C91DDB0-4115-49B6-A0DA-292DA98FEF04}" name="Minimum Settlement" dataDxfId="3" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{A4070786-5EAC-40CB-848C-778505997A11}" name="ISIN" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{7B2144E0-E5F2-4A2B-8D7B-1695805B7A02}" name="Outstanding_x000a_US$" dataDxfId="1" dataCellStyle="Millares 3"/>
+    <tableColumn id="22" xr3:uid="{4E6F3B99-052C-4999-8442-C6D182EEDFED}" name="Decisión" dataDxfId="0" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3762,7 +3814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EFF2F4-11C0-433C-9540-66AEF48816EC}">
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -3773,7 +3825,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="48" thickBot="1">
       <c r="A1" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3797,16 +3849,16 @@
         <v>6</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>8</v>
@@ -3815,15 +3867,15 @@
         <v>9</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>10</v>
@@ -3841,7 +3893,7 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H2" s="12">
         <v>2026</v>
@@ -3868,12 +3920,12 @@
         <v>3750000000</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>15</v>
@@ -3918,12 +3970,12 @@
         <v>1500000000</v>
       </c>
       <c r="P3" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="8" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>10</v>
@@ -3968,7 +4020,7 @@
         <v>600000000</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4025,7 +4077,7 @@
         <v>1500000000</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -4082,7 +4134,7 @@
         <v>748995000</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -4095,7 +4147,7 @@
         <v>Specialty Retailers</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>21</v>
@@ -4133,13 +4185,13 @@
         <v>200000</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O7" s="29">
         <v>89906000</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4196,7 +4248,7 @@
         <v>300000000</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4253,7 +4305,7 @@
         <v>750000000</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -4303,7 +4355,7 @@
         <v>750000000</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -4334,7 +4386,7 @@
         <v>15/09/2028</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" ref="H11:H60" si="0">YEAR(G11)</f>
+        <f t="shared" ref="H11:H64" si="0">YEAR(G11)</f>
         <v>2028</v>
       </c>
       <c r="I11" s="13">
@@ -4360,1710 +4412,1714 @@
         <v>600000000</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="9" t="str">
-        <f>+A12</f>
-        <v>Nordstrom</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="A12" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Xerox Holdings Corporation</v>
+      </c>
+      <c r="B12" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>IT equipment</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="10">
-        <v>6.9500000000000006E-2</v>
-      </c>
-      <c r="G12" s="11">
-        <v>46827</v>
-      </c>
-      <c r="H12" s="12">
+      <c r="E12" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="23">
+        <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.5E-2</v>
+      </c>
+      <c r="G12" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/08/2028</v>
+      </c>
+      <c r="H12" s="25">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="I12" s="13">
-        <v>103.351</v>
-      </c>
-      <c r="J12" s="13">
-        <v>4.9123728446805996</v>
-      </c>
-      <c r="K12" s="13">
-        <v>84.543917559760999</v>
-      </c>
-      <c r="L12" s="13">
-        <v>5.1733104559676999</v>
-      </c>
-      <c r="M12" s="14">
-        <v>1000</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="16">
-        <v>300000000</v>
+      <c r="I12" s="26">
+        <v>59</v>
+      </c>
+      <c r="J12" s="26">
+        <v>37.372258361656002</v>
+      </c>
+      <c r="K12" s="26">
+        <v>3329.6521496261998</v>
+      </c>
+      <c r="L12" s="26">
+        <v>34.740173119189002</v>
+      </c>
+      <c r="M12" s="27">
+        <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="O12" s="29">
+        <v>750000000</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="10">
-        <v>6.7979999999999999E-2</v>
-      </c>
-      <c r="G13" s="11">
-        <v>47064</v>
-      </c>
-      <c r="H13" s="12">
+      <c r="A13" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Braskem</v>
+      </c>
+      <c r="B13" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="23">
+        <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G13" s="24">
+        <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47027</v>
+      </c>
+      <c r="H13" s="25">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="I13" s="13">
-        <v>103.23</v>
-      </c>
-      <c r="J13" s="13">
-        <v>5.3738107752827</v>
-      </c>
-      <c r="K13" s="13">
-        <v>128.99535451521001</v>
-      </c>
-      <c r="L13" s="13">
-        <v>5.2212942271933001</v>
-      </c>
-      <c r="M13" s="14">
+      <c r="I13" s="26">
+        <v>59.997999999999998</v>
+      </c>
+      <c r="J13" s="26">
+        <v>47.992506623183999</v>
+      </c>
+      <c r="K13" s="26">
+        <v>4392.9748486176004</v>
+      </c>
+      <c r="L13" s="26">
+        <v>39.639584176063003</v>
+      </c>
+      <c r="M13" s="27">
+        <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>200000</v>
       </c>
-      <c r="N13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="16">
-        <v>1500000000</v>
+      <c r="N13" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="O13" s="29">
+        <v>1250000000</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="8" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+      <c r="C14" s="9" t="str">
+        <f>+A14</f>
+        <v>Nordstrom</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="F14" s="10">
-        <v>0.04</v>
+        <v>6.9500000000000006E-2</v>
       </c>
       <c r="G14" s="11">
-        <v>46949</v>
+        <v>46827</v>
       </c>
       <c r="H14" s="12">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="I14" s="13">
-        <v>97.474999999999994</v>
+        <v>103.351</v>
       </c>
       <c r="J14" s="13">
-        <v>5.4043003750673</v>
+        <v>4.9123728446805996</v>
       </c>
       <c r="K14" s="13">
-        <v>132.83722632353999</v>
+        <v>84.543917559760999</v>
       </c>
       <c r="L14" s="13">
-        <v>5.26</v>
+        <v>5.1733104559676999</v>
       </c>
       <c r="M14" s="14">
         <v>1000</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="O14" s="16">
-        <v>2000000000</v>
+        <v>300000000</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D15" s="9" t="s">
+      <c r="A15" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="22" t="str">
+        <f>+A15</f>
+        <v>Clearwater Paper</v>
+      </c>
+      <c r="D15" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F15" s="10">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="G15" s="11">
-        <v>47072</v>
-      </c>
-      <c r="H15" s="12">
+      <c r="E15" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" s="23">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G15" s="24">
+        <v>46980</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="I15" s="13">
-        <v>99.805000000000007</v>
-      </c>
-      <c r="J15" s="13">
-        <v>5.9208334278288</v>
-      </c>
-      <c r="K15" s="13">
-        <v>183.55708706243001</v>
-      </c>
-      <c r="L15" s="13">
-        <v>5.6758060419575997</v>
-      </c>
-      <c r="M15" s="14">
-        <v>1000</v>
-      </c>
-      <c r="N15" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="O15" s="16">
-        <v>800000000</v>
+      <c r="I15" s="26">
+        <v>81.990549999999999</v>
+      </c>
+      <c r="J15" s="26">
+        <v>15.600562809316999</v>
+      </c>
+      <c r="K15" s="26">
+        <v>1152.3102255069</v>
+      </c>
+      <c r="L15" s="26">
+        <v>15.547750959159</v>
+      </c>
+      <c r="M15" s="27">
+        <v>2000</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="O15" s="29">
+        <v>275000000</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="8" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F16" s="10">
-        <v>4.3749999999999997E-2</v>
+        <v>6.7979999999999999E-2</v>
       </c>
       <c r="G16" s="11">
-        <v>46919</v>
+        <v>47064</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
       <c r="I16" s="13">
-        <v>98.55565</v>
+        <v>103.23</v>
       </c>
       <c r="J16" s="13">
-        <v>5.2324358555585997</v>
+        <v>5.3738107752827</v>
       </c>
       <c r="K16" s="13">
-        <v>115.79460654344</v>
+        <v>128.99535451521001</v>
       </c>
       <c r="L16" s="13">
-        <v>5.0951748613912002</v>
+        <v>5.2212942271933001</v>
       </c>
       <c r="M16" s="14">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O16" s="16">
-        <v>800000000</v>
+        <v>1500000000</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:16">
       <c r="A17" s="8" t="s">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="9" t="str">
-        <f>+A17</f>
-        <v>Ecopetrol</v>
+        <v>92</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="G17" s="11">
+        <v>46949</v>
+      </c>
+      <c r="H17" s="12">
+        <v>2028</v>
+      </c>
+      <c r="I17" s="13">
+        <v>97.474999999999994</v>
+      </c>
+      <c r="J17" s="13">
+        <v>5.4043003750673</v>
+      </c>
+      <c r="K17" s="13">
+        <v>132.83722632353999</v>
+      </c>
+      <c r="L17" s="13">
+        <v>5.26</v>
+      </c>
+      <c r="M17" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N17" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="O17" s="16">
+        <v>2000000000</v>
+      </c>
+      <c r="P17" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="10">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="G18" s="11">
+        <v>47072</v>
+      </c>
+      <c r="H18" s="12">
+        <v>2028</v>
+      </c>
+      <c r="I18" s="13">
+        <v>99.805000000000007</v>
+      </c>
+      <c r="J18" s="13">
+        <v>5.9208334278288</v>
+      </c>
+      <c r="K18" s="13">
+        <v>183.55708706243001</v>
+      </c>
+      <c r="L18" s="13">
+        <v>5.6758060419575997</v>
+      </c>
+      <c r="M18" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N18" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="O18" s="16">
+        <v>800000000</v>
+      </c>
+      <c r="P18" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="10">
+        <v>4.3749999999999997E-2</v>
+      </c>
+      <c r="G19" s="11">
+        <v>46919</v>
+      </c>
+      <c r="H19" s="12">
+        <f t="shared" si="0"/>
+        <v>2028</v>
+      </c>
+      <c r="I19" s="13">
+        <v>98.55565</v>
+      </c>
+      <c r="J19" s="13">
+        <v>5.2324358555585997</v>
+      </c>
+      <c r="K19" s="13">
+        <v>115.79460654344</v>
+      </c>
+      <c r="L19" s="13">
+        <v>5.0951748613912002</v>
+      </c>
+      <c r="M19" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="16">
+        <v>800000000</v>
+      </c>
+      <c r="P19" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="9" t="str">
+        <f>+A20</f>
+        <v>Ecopetrol</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F20" s="10">
         <v>8.6249999999999993E-2</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G20" s="11">
         <v>47137</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H20" s="12">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I20" s="13">
         <v>106.2165</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J20" s="13">
         <v>6.0333288027999998</v>
       </c>
-      <c r="K17" s="13">
+      <c r="K20" s="13">
         <v>194.69832060189</v>
       </c>
-      <c r="L17" s="13">
+      <c r="L20" s="13">
         <v>5.7889043132677998</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M20" s="14">
         <v>1000</v>
       </c>
-      <c r="N17" s="15" t="s">
+      <c r="N20" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O20" s="16">
         <v>1200000000</v>
       </c>
-      <c r="P17" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Ally Financial</v>
-      </c>
-      <c r="B18" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Banks</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Baa3/BBB-/BBB-</v>
-      </c>
-      <c r="F18" s="10">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>6.9919999999999996E-2</v>
-      </c>
-      <c r="G18" s="11" t="str">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>13/06/2029</v>
-      </c>
-      <c r="H18" s="12">
-        <f t="shared" si="0"/>
-        <v>2029</v>
-      </c>
-      <c r="I18" s="13">
-        <v>103.715</v>
-      </c>
-      <c r="J18" s="13">
-        <v>5.0119989796673998</v>
-      </c>
-      <c r="K18" s="13">
-        <v>93.861399046453997</v>
-      </c>
-      <c r="L18" s="13">
-        <v>4.9966088021799999</v>
-      </c>
-      <c r="M18" s="14">
-        <f>+_xlfn.XLOOKUP($N18,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="O18" s="16">
-        <v>750000000</v>
-      </c>
-      <c r="P18" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="21" t="str">
-        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Olin</v>
-      </c>
-      <c r="B19" s="22" t="str">
-        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Chemical and petrochemical industry</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="23">
-        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.6250000000000001E-2</v>
-      </c>
-      <c r="G19" s="24">
-        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47126</v>
-      </c>
-      <c r="H19" s="25">
-        <f t="shared" si="0"/>
-        <v>2029</v>
-      </c>
-      <c r="I19" s="26">
-        <v>99.4435</v>
-      </c>
-      <c r="J19" s="26">
-        <v>5.9098961663083003</v>
-      </c>
-      <c r="K19" s="26">
-        <v>180.33250281859</v>
-      </c>
-      <c r="L19" s="26">
-        <v>5.8698164938724</v>
-      </c>
-      <c r="M19" s="27">
-        <f>+_xlfn.XLOOKUP($N19,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>1000</v>
-      </c>
-      <c r="N19" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="O19" s="29">
-        <v>750000000</v>
-      </c>
-      <c r="P19" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="21" t="str">
-        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>FMC</v>
-      </c>
-      <c r="B20" s="22" t="str">
-        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Fertilizers</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="23">
-        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>3.4500000000000003E-2</v>
-      </c>
-      <c r="G20" s="24">
-        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47128</v>
-      </c>
-      <c r="H20" s="25">
-        <f t="shared" si="0"/>
-        <v>2029</v>
-      </c>
-      <c r="I20" s="26">
-        <v>93.067499999999995</v>
-      </c>
-      <c r="J20" s="26">
-        <v>5.9164627873917004</v>
-      </c>
-      <c r="K20" s="26">
-        <v>179.88791852900999</v>
-      </c>
-      <c r="L20" s="26">
-        <v>6.1031278451061004</v>
-      </c>
-      <c r="M20" s="27">
-        <f>+_xlfn.XLOOKUP($N20,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
-      </c>
-      <c r="N20" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="O20" s="29">
-        <v>500000000</v>
-      </c>
       <c r="P20" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Methanex</v>
+        <v>Ally Financial</v>
       </c>
       <c r="B21" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Chemical and petrochemical industry</v>
+        <v>Banks</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>53</v>
+        <v>12</v>
+      </c>
+      <c r="E21" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa3/BBB-/BBB-</v>
       </c>
       <c r="F21" s="10">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.2499999999999998E-2</v>
+        <v>6.9919999999999996E-2</v>
       </c>
       <c r="G21" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/12/2029</v>
+        <v>13/06/2029</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I21" s="13">
-        <v>99.635000000000005</v>
+        <v>103.715</v>
       </c>
       <c r="J21" s="13">
-        <v>5.4383914326443996</v>
+        <v>5.0119989796673998</v>
       </c>
       <c r="K21" s="13">
-        <v>131.50867729941999</v>
+        <v>93.861399046453997</v>
       </c>
       <c r="L21" s="13">
-        <v>5.4047418010010997</v>
+        <v>4.9966088021799999</v>
       </c>
       <c r="M21" s="14">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="O21" s="16">
-        <v>700000000</v>
+        <v>750000000</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="19" t="str">
+      <c r="A22" s="21" t="str">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Eastman Chemical</v>
-      </c>
-      <c r="B22" s="20" t="str">
+        <v>Olin</v>
+      </c>
+      <c r="B22" s="22" t="str">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
         <v>Chemical and petrochemical industry</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Baa2/BBB/Withdrawn</v>
-      </c>
-      <c r="F22" s="10">
+      <c r="C22" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="23">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="11">
+        <v>5.6250000000000001E-2</v>
+      </c>
+      <c r="G22" s="24">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
         <v>47126</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="25">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I22" s="13">
-        <v>100.545</v>
-      </c>
-      <c r="J22" s="13">
-        <v>4.8633165071222004</v>
-      </c>
-      <c r="K22" s="13">
-        <v>75.549590736349998</v>
-      </c>
-      <c r="L22" s="13">
-        <v>4.7809946854473004</v>
-      </c>
-      <c r="M22" s="14">
+      <c r="I22" s="26">
+        <v>99.4435</v>
+      </c>
+      <c r="J22" s="26">
+        <v>5.9098961663083003</v>
+      </c>
+      <c r="K22" s="26">
+        <v>180.33250281859</v>
+      </c>
+      <c r="L22" s="26">
+        <v>5.8698164938724</v>
+      </c>
+      <c r="M22" s="27">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
-      </c>
-      <c r="N22" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="O22" s="16">
+        <v>1000</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O22" s="29">
         <v>750000000</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="9" t="str">
-        <f>+A23</f>
-        <v>Mattel</v>
-      </c>
-      <c r="D23" s="9" t="s">
+      <c r="A23" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>FMC</v>
+      </c>
+      <c r="B23" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Fertilizers</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" s="10">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G23" s="11">
-        <v>47209</v>
-      </c>
-      <c r="H23" s="12">
+      <c r="E23" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F23" s="23">
+        <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="G23" s="24">
+        <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47128</v>
+      </c>
+      <c r="H23" s="25">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="I23" s="13">
-        <v>97.070999999999998</v>
-      </c>
-      <c r="J23" s="13">
-        <v>4.9660398867562003</v>
-      </c>
-      <c r="K23" s="13">
-        <v>86.719568477107998</v>
-      </c>
-      <c r="L23" s="13">
-        <v>4.9732958652243999</v>
-      </c>
-      <c r="M23" s="14">
-        <v>1000</v>
-      </c>
-      <c r="N23" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O23" s="16">
-        <v>600000000</v>
+      <c r="I23" s="26">
+        <v>93.067499999999995</v>
+      </c>
+      <c r="J23" s="26">
+        <v>5.9164627873917004</v>
+      </c>
+      <c r="K23" s="26">
+        <v>179.88791852900999</v>
+      </c>
+      <c r="L23" s="26">
+        <v>6.1031278451061004</v>
+      </c>
+      <c r="M23" s="27">
+        <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="O23" s="29">
+        <v>500000000</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>134</v>
+      <c r="A24" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Methanex</v>
+      </c>
+      <c r="B24" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F24" s="10">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="G24" s="11">
-        <v>47437</v>
+        <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.2499999999999998E-2</v>
+      </c>
+      <c r="G24" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/12/2029</v>
       </c>
       <c r="H24" s="12">
+        <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I24" s="13">
-        <v>95.307500000000005</v>
+        <v>99.635000000000005</v>
       </c>
       <c r="J24" s="13">
-        <v>6.2886966914741</v>
+        <v>5.4383914326443996</v>
       </c>
       <c r="K24" s="13">
-        <v>216.81147745448999</v>
+        <v>131.50867729941999</v>
       </c>
       <c r="L24" s="13">
-        <v>5.9796398973778002</v>
+        <v>5.4047418010010997</v>
       </c>
       <c r="M24" s="14">
-        <v>1000</v>
+        <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N24" s="15" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="O24" s="16">
-        <v>650000000</v>
+        <v>700000000</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>59</v>
+      <c r="A25" s="19" t="str">
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Eastman Chemical</v>
+      </c>
+      <c r="B25" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="9" t="s">
-        <v>61</v>
+      <c r="E25" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa2/BBB/Withdrawn</v>
       </c>
       <c r="F25" s="10">
-        <v>5.9499999999999997E-2</v>
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>0.05</v>
       </c>
       <c r="G25" s="11">
-        <v>47314</v>
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47126</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I25" s="13">
-        <v>100.99</v>
+        <v>100.545</v>
       </c>
       <c r="J25" s="13">
-        <v>5.666805627924</v>
+        <v>4.8633165071222004</v>
       </c>
       <c r="K25" s="13">
-        <v>156.25027537597001</v>
+        <v>75.549590736349998</v>
       </c>
       <c r="L25" s="13">
-        <v>5.6229573345007999</v>
+        <v>4.7809946854473004</v>
       </c>
       <c r="M25" s="14">
+        <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="O25" s="16">
-        <v>850000000</v>
+        <v>750000000</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:16">
       <c r="A26" s="8" t="s">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>29</v>
+        <v>56</v>
+      </c>
+      <c r="C26" s="9" t="str">
+        <f>+A26</f>
+        <v>Mattel</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F26" s="10">
-        <v>5.3999999999999999E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G26" s="11">
-        <v>47437</v>
+        <v>47209</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
       <c r="I26" s="13">
-        <v>101.77</v>
+        <v>97.070999999999998</v>
       </c>
       <c r="J26" s="13">
-        <v>4.8640697328705</v>
+        <v>4.9660398867562003</v>
       </c>
       <c r="K26" s="13">
-        <v>74.826815748252002</v>
+        <v>86.719568477107998</v>
       </c>
       <c r="L26" s="13">
-        <v>4.8014897953651996</v>
+        <v>4.9732958652243999</v>
       </c>
       <c r="M26" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="O26" s="16">
-        <v>1000000000</v>
+        <v>600000000</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="30" t="str">
-        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Olin</v>
-      </c>
-      <c r="B27" s="31" t="str">
-        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Chemical and petrochemical industry</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="22" t="s">
+      <c r="A27" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="23">
-        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>0.05</v>
-      </c>
-      <c r="G27" s="24">
-        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47485</v>
-      </c>
-      <c r="H27" s="25">
-        <f t="shared" si="0"/>
-        <v>2030</v>
-      </c>
-      <c r="I27" s="26">
-        <v>97.5</v>
-      </c>
-      <c r="J27" s="26">
-        <v>5.8680201805944998</v>
-      </c>
-      <c r="K27" s="26">
-        <v>174.22270862929</v>
-      </c>
-      <c r="L27" s="26">
-        <v>5.9763491100649997</v>
-      </c>
-      <c r="M27" s="27">
-        <f>+_xlfn.XLOOKUP($N27,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+      <c r="E27" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" s="10">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="G27" s="11">
+        <v>47437</v>
+      </c>
+      <c r="H27" s="12">
+        <v>2029</v>
+      </c>
+      <c r="I27" s="13">
+        <v>95.307500000000005</v>
+      </c>
+      <c r="J27" s="13">
+        <v>6.2886966914741</v>
+      </c>
+      <c r="K27" s="13">
+        <v>216.81147745448999</v>
+      </c>
+      <c r="L27" s="13">
+        <v>5.9796398973778002</v>
+      </c>
+      <c r="M27" s="14">
         <v>1000</v>
       </c>
-      <c r="N27" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="O27" s="29">
-        <v>550000000</v>
+      <c r="N27" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="O27" s="16">
+        <v>650000000</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="8" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>40</v>
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="F28" s="10">
-        <v>3.875E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="G28" s="11">
-        <v>47802</v>
+        <v>47314</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="0"/>
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="I28" s="13">
-        <v>93.045000000000002</v>
+        <v>100.99</v>
       </c>
       <c r="J28" s="13">
-        <v>5.7805265387676004</v>
+        <v>5.666805627924</v>
       </c>
       <c r="K28" s="13">
-        <v>161.64086280793001</v>
+        <v>156.25027537597001</v>
       </c>
       <c r="L28" s="13">
-        <v>5.8657650211977996</v>
+        <v>5.6229573345007999</v>
       </c>
       <c r="M28" s="14">
         <v>2000</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="O28" s="16">
-        <v>650000000</v>
+        <v>850000000</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="8" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F29" s="10">
-        <v>4.7E-2</v>
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G29" s="11">
-        <v>47763</v>
+        <v>47437</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="0"/>
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="I29" s="13">
-        <v>98.2928</v>
+        <v>101.77</v>
       </c>
       <c r="J29" s="13">
-        <v>5.2167283875081001</v>
+        <v>4.8640697328705</v>
       </c>
       <c r="K29" s="13">
-        <v>106.09039282237001</v>
+        <v>74.826815748252002</v>
       </c>
       <c r="L29" s="13">
-        <v>5.0649725136379002</v>
+        <v>4.8014897953651996</v>
       </c>
       <c r="M29" s="14">
         <v>2000</v>
       </c>
       <c r="N29" s="15" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O29" s="16">
-        <v>600000000</v>
+        <v>1000000000</v>
       </c>
       <c r="P29" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="32">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G30" s="33">
-        <v>47727</v>
-      </c>
-      <c r="H30" s="12">
+      <c r="A30" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="23">
+        <v>4.6249999999999999E-2</v>
+      </c>
+      <c r="G30" s="24">
+        <v>47489</v>
+      </c>
+      <c r="H30" s="25">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="I30" s="13">
-        <v>98.825000000000003</v>
-      </c>
-      <c r="J30" s="13">
-        <v>5.9051997759867003</v>
-      </c>
-      <c r="K30" s="13">
-        <v>175.74953149757999</v>
-      </c>
-      <c r="L30" s="13">
-        <v>5.8612427880234002</v>
-      </c>
-      <c r="M30" s="34">
-        <v>2000</v>
-      </c>
-      <c r="N30" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="O30" s="16">
-        <v>750000000</v>
+      <c r="I30" s="26">
+        <v>97.005549999999999</v>
+      </c>
+      <c r="J30" s="26">
+        <v>5.5630820350621999</v>
+      </c>
+      <c r="K30" s="26">
+        <v>142.04326012195</v>
+      </c>
+      <c r="L30" s="26">
+        <v>5.5877308093684004</v>
+      </c>
+      <c r="M30" s="27">
+        <v>1000</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="O30" s="29">
+        <v>2750000000</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="9" t="str">
-        <f>+A31</f>
-        <v>Geopark</v>
-      </c>
-      <c r="D31" s="9" t="s">
+      <c r="A31" s="30" t="str">
+        <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Olin</v>
+      </c>
+      <c r="B31" s="31" t="str">
+        <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Chemical and petrochemical industry</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="10">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="G31" s="11">
-        <v>47514</v>
-      </c>
-      <c r="H31" s="12">
+      <c r="E31" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="23">
+        <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>0.05</v>
+      </c>
+      <c r="G31" s="24">
+        <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47485</v>
+      </c>
+      <c r="H31" s="25">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="I31" s="13">
-        <v>98.35</v>
-      </c>
-      <c r="J31" s="13">
-        <v>9.5170455367630993</v>
-      </c>
-      <c r="K31" s="13">
-        <v>540.09375815400995</v>
-      </c>
-      <c r="L31" s="13">
-        <v>9.5060902364221995</v>
-      </c>
-      <c r="M31" s="14">
-        <v>200000</v>
-      </c>
-      <c r="N31" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="O31" s="16">
+      <c r="I31" s="26">
+        <v>97.5</v>
+      </c>
+      <c r="J31" s="26">
+        <v>5.8680201805944998</v>
+      </c>
+      <c r="K31" s="26">
+        <v>174.22270862929</v>
+      </c>
+      <c r="L31" s="26">
+        <v>5.9763491100649997</v>
+      </c>
+      <c r="M31" s="27">
+        <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>1000</v>
+      </c>
+      <c r="N31" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="O31" s="29">
         <v>550000000</v>
       </c>
       <c r="P31" s="17" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>EQT</v>
-      </c>
-      <c r="B32" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Oil and Gas Extraction and Refining</v>
+      <c r="A32" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>38</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Withdrawn/BBB-/BBB-</v>
-      </c>
-      <c r="F32" s="32">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G32" s="33">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47485</v>
+        <v>21</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="10">
+        <v>3.875E-2</v>
+      </c>
+      <c r="G32" s="11">
+        <v>47802</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I32" s="13">
-        <v>106.28435</v>
+        <v>93.045000000000002</v>
       </c>
       <c r="J32" s="13">
-        <v>5.1146249720602004</v>
+        <v>5.7805265387676004</v>
       </c>
       <c r="K32" s="13">
-        <v>99.309735596096999</v>
+        <v>161.64086280793001</v>
       </c>
       <c r="L32" s="13">
-        <v>5.0483463023033996</v>
-      </c>
-      <c r="M32" s="34">
-        <f>+_xlfn.XLOOKUP($N32,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>5.8657650211977996</v>
+      </c>
+      <c r="M32" s="14">
         <v>2000</v>
       </c>
-      <c r="N32" s="35" t="s">
-        <v>76</v>
+      <c r="N32" s="15" t="s">
+        <v>67</v>
       </c>
       <c r="O32" s="16">
-        <v>750000000</v>
+        <v>650000000</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="8" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="9" t="str">
-        <f>+A33</f>
-        <v>Macy´s</v>
+        <v>68</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F33" s="10">
-        <v>5.8749999999999997E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="G33" s="11">
-        <v>47557</v>
+        <v>47763</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I33" s="13">
-        <v>100.1765</v>
+        <v>98.2928</v>
       </c>
       <c r="J33" s="13">
-        <v>5.9026780275639998</v>
+        <v>5.2167283875081001</v>
       </c>
       <c r="K33" s="13">
-        <v>177.33893406474999</v>
+        <v>106.09039282237001</v>
       </c>
       <c r="L33" s="13">
-        <v>5.7934766468827998</v>
+        <v>5.0649725136379002</v>
       </c>
       <c r="M33" s="14">
         <v>2000</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="O33" s="16">
-        <v>425000000</v>
+        <v>600000000</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="19" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="20" t="str">
-        <f>+A34</f>
-        <v>HF Sinclair</v>
+        <v>59</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F34" s="32">
-        <v>4.4999999999999998E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G34" s="33">
-        <v>47757</v>
+        <v>47727</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I34" s="13">
-        <v>97.102950000000007</v>
+        <v>98.825000000000003</v>
       </c>
       <c r="J34" s="13">
-        <v>5.3399688621105996</v>
+        <v>5.9051997759867003</v>
       </c>
       <c r="K34" s="13">
-        <v>118.43510796036</v>
+        <v>175.74953149757999</v>
       </c>
       <c r="L34" s="13">
-        <v>5.3782875807729003</v>
+        <v>5.8612427880234002</v>
       </c>
       <c r="M34" s="34">
         <v>2000</v>
       </c>
       <c r="N34" s="35" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="O34" s="16">
-        <v>75000000</v>
+        <v>750000000</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Petrobras</v>
-      </c>
-      <c r="B35" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Oil and Gas Extraction and Refining</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>80</v>
+      <c r="A35" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="9" t="str">
+        <f>+A35</f>
+        <v>Geopark</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Ba1/BB/BB</v>
+      <c r="E35" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="F35" s="10">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.0930000000000003E-2</v>
-      </c>
-      <c r="G35" s="11" t="str">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/01/2030</v>
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="G35" s="11">
+        <v>47514</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I35" s="13">
-        <v>99.224500000000006</v>
+        <v>98.35</v>
       </c>
       <c r="J35" s="13">
-        <v>5.4081318780318997</v>
+        <v>9.5170455367630993</v>
       </c>
       <c r="K35" s="13">
-        <v>128.44369795827001</v>
+        <v>540.09375815400995</v>
       </c>
       <c r="L35" s="13">
-        <v>5.3014347264678996</v>
+        <v>9.5060902364221995</v>
       </c>
       <c r="M35" s="14">
-        <f>+_xlfn.XLOOKUP($N35,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="N35" s="15" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="O35" s="16">
-        <v>375896000</v>
+        <v>550000000</v>
       </c>
       <c r="P35" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Viatris</v>
+        <v>EQT</v>
       </c>
       <c r="B36" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Pharmaceutical Preparation and Biotechnology</v>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E36" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>-/BB+/BBB</v>
-      </c>
-      <c r="F36" s="10">
+        <v>Withdrawn/BBB-/BBB-</v>
+      </c>
+      <c r="F36" s="32">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>2.7E-2</v>
-      </c>
-      <c r="G36" s="11" t="str">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G36" s="33">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>22/06/2030</v>
+        <v>47485</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I36" s="13">
-        <v>91.300049999999999</v>
+        <v>106.28435</v>
       </c>
       <c r="J36" s="13">
-        <v>5.2241215897703999</v>
+        <v>5.1146249720602004</v>
       </c>
       <c r="K36" s="13">
-        <v>107.27688652632</v>
+        <v>99.309735596096999</v>
       </c>
       <c r="L36" s="13">
-        <v>5.0983610157478996</v>
-      </c>
-      <c r="M36" s="14">
+        <v>5.0483463023033996</v>
+      </c>
+      <c r="M36" s="34">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N36" s="15" t="s">
-        <v>82</v>
+      <c r="N36" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="O36" s="16">
-        <v>1449500000</v>
+        <v>750000000</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Embraer</v>
-      </c>
-      <c r="B37" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Aircraft Production and Defense</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>83</v>
+      <c r="A37" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="9" t="str">
+        <f>+A37</f>
+        <v>Macy´s</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F37" s="10">
-        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G37" s="11" t="str">
-        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>28/07/2030</v>
+        <v>5.8749999999999997E-2</v>
+      </c>
+      <c r="G37" s="11">
+        <v>47557</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I37" s="13">
-        <v>108.4</v>
+        <v>100.1765</v>
       </c>
       <c r="J37" s="13">
-        <v>4.8028528899121001</v>
+        <v>5.9026780275639998</v>
       </c>
       <c r="K37" s="13">
-        <v>76.010527540115007</v>
+        <v>177.33893406474999</v>
       </c>
       <c r="L37" s="13">
-        <v>4.8028528899121001</v>
+        <v>5.7934766468827998</v>
       </c>
       <c r="M37" s="14">
-        <f>+_xlfn.XLOOKUP($N37,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>200000</v>
+        <v>2000</v>
       </c>
       <c r="N37" s="15" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="O37" s="16">
-        <v>750000000</v>
+        <v>425000000</v>
       </c>
       <c r="P37" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Vale</v>
-      </c>
-      <c r="B38" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Ferrous metals</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>85</v>
+      <c r="A38" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="20" t="str">
+        <f>+A38</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="10">
-        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="G38" s="11">
-        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47702</v>
+      <c r="E38" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G38" s="33">
+        <v>47757</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I38" s="13">
-        <v>95.340500000000006</v>
+        <v>97.102950000000007</v>
       </c>
       <c r="J38" s="13">
-        <v>5.1140232684006</v>
+        <v>5.3399688621105996</v>
       </c>
       <c r="K38" s="13">
-        <v>96.726032319241995</v>
+        <v>118.43510796036</v>
       </c>
       <c r="L38" s="13">
-        <v>5.0673822743828003</v>
-      </c>
-      <c r="M38" s="14">
-        <f>+_xlfn.XLOOKUP($N38,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>5.3782875807729003</v>
+      </c>
+      <c r="M38" s="34">
         <v>2000</v>
       </c>
-      <c r="N38" s="15" t="s">
-        <v>87</v>
+      <c r="N38" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="O38" s="16">
-        <v>1500000000</v>
+        <v>75000000</v>
       </c>
       <c r="P38" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="9" t="str">
-        <f>+A39</f>
-        <v>Nordstrom</v>
+      <c r="A39" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Petrobras</v>
+      </c>
+      <c r="B39" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>43</v>
+      <c r="E39" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Ba1/BB/BB</v>
       </c>
       <c r="F39" s="10">
-        <v>4.3749999999999997E-2</v>
-      </c>
-      <c r="G39" s="11">
-        <v>47574</v>
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.0930000000000003E-2</v>
+      </c>
+      <c r="G39" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/01/2030</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I39" s="13">
-        <v>96.63</v>
+        <v>99.224500000000006</v>
       </c>
       <c r="J39" s="13">
-        <v>5.4537213017957997</v>
+        <v>5.4081318780318997</v>
       </c>
       <c r="K39" s="13">
-        <v>131.84206806991</v>
+        <v>128.44369795827001</v>
       </c>
       <c r="L39" s="13">
-        <v>5.5730541855544997</v>
+        <v>5.3014347264678996</v>
       </c>
       <c r="M39" s="14">
+        <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N39" s="15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="O39" s="16">
-        <v>500000000</v>
+        <v>375896000</v>
       </c>
       <c r="P39" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Centene</v>
+        <v>Viatris</v>
       </c>
       <c r="B40" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Insurance and Reinsurance</v>
+        <v>Pharmaceutical Preparation and Biotechnology</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>90</v>
+      <c r="E40" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/BB+/BBB</v>
       </c>
       <c r="F40" s="10">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>0.03</v>
+        <v>2.7E-2</v>
       </c>
       <c r="G40" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/10/2030</v>
+        <v>22/06/2030</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I40" s="13">
-        <v>90.455849999999998</v>
+        <v>91.300049999999999</v>
       </c>
       <c r="J40" s="13">
-        <v>5.6146107857010001</v>
+        <v>5.2241215897703999</v>
       </c>
       <c r="K40" s="13">
-        <v>145.12849207442</v>
+        <v>107.27688652632</v>
       </c>
       <c r="L40" s="13">
-        <v>5.5926404224787003</v>
+        <v>5.0983610157478996</v>
       </c>
       <c r="M40" s="14">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O40" s="16">
-        <v>2200000000</v>
+        <v>1449500000</v>
       </c>
       <c r="P40" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>92</v>
+      <c r="A41" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N41,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Embraer</v>
+      </c>
+      <c r="B41" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N41,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Aircraft Production and Defense</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="36">
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="G41" s="11">
-        <v>47618</v>
+        <v>57</v>
+      </c>
+      <c r="F41" s="10">
+        <f>+_xlfn.XLOOKUP($N41,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G41" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N41,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>28/07/2030</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I41" s="13">
-        <v>80.66</v>
+        <v>108.4</v>
       </c>
       <c r="J41" s="13">
-        <v>9.9952818659825997</v>
+        <v>4.8028528899121001</v>
       </c>
       <c r="K41" s="13">
-        <v>593.69553893602995</v>
+        <v>76.010527540115007</v>
       </c>
       <c r="L41" s="13">
-        <v>5.1856108017900002</v>
+        <v>4.8028528899121001</v>
       </c>
       <c r="M41" s="14">
-        <v>2000</v>
+        <f>+_xlfn.XLOOKUP($N41,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>200000</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="O41" s="16">
-        <v>917517000</v>
+        <v>750000000</v>
       </c>
       <c r="P41" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C42" s="9" t="str">
-        <f>+A42</f>
-        <v>Mattel</v>
+      <c r="A42" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Vale</v>
+      </c>
+      <c r="B42" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Ferrous metals</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F42" s="10">
-        <v>0.05</v>
+        <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G42" s="11">
-        <v>47804</v>
+        <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>47702</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
       <c r="I42" s="13">
-        <v>99.494249999999994</v>
+        <v>95.340500000000006</v>
       </c>
       <c r="J42" s="13">
-        <v>5.1950145746962004</v>
+        <v>5.1140232684006</v>
       </c>
       <c r="K42" s="13">
-        <v>103.44711103354</v>
+        <v>96.726032319241995</v>
       </c>
       <c r="L42" s="13">
-        <v>5.1281219620645997</v>
+        <v>5.0673822743828003</v>
       </c>
       <c r="M42" s="14">
+        <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="O42" s="16">
-        <v>600000000</v>
+        <v>1500000000</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C43" s="9" t="str">
         <f>+A43</f>
-        <v>HF Sinclair</v>
+        <v>Nordstrom</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="36">
-        <v>5.7500000000000002E-2</v>
+        <v>43</v>
+      </c>
+      <c r="F43" s="10">
+        <v>4.3749999999999997E-2</v>
       </c>
       <c r="G43" s="11">
-        <v>47863</v>
+        <v>47574</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" si="0"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I43" s="13">
-        <v>102.045</v>
+        <v>96.63</v>
       </c>
       <c r="J43" s="13">
-        <v>5.3044691221645</v>
+        <v>5.4537213017957997</v>
       </c>
       <c r="K43" s="13">
-        <v>114.38797755776</v>
+        <v>131.84206806991</v>
       </c>
       <c r="L43" s="13">
-        <v>5.2067291788855998</v>
+        <v>5.5730541855544997</v>
       </c>
       <c r="M43" s="14">
         <v>2000</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="O43" s="16">
-        <v>650000000</v>
+        <v>500000000</v>
       </c>
       <c r="P43" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -6086,594 +6142,585 @@
       </c>
       <c r="F44" s="10">
         <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="G44" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="G44" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47851</v>
+        <v>15/10/2030</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="0"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I44" s="13">
-        <v>87.472499999999997</v>
+        <v>90.455849999999998</v>
       </c>
       <c r="J44" s="13">
-        <v>5.6745121526288997</v>
+        <v>5.6146107857010001</v>
       </c>
       <c r="K44" s="13">
-        <v>149.18257120941999</v>
+        <v>145.12849207442</v>
       </c>
       <c r="L44" s="13">
-        <v>5.6366512377394002</v>
+        <v>5.5926404224787003</v>
       </c>
       <c r="M44" s="14">
         <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N44" s="37" t="s">
-        <v>98</v>
+      <c r="N44" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="O44" s="16">
         <v>2200000000</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Micron Technology</v>
-      </c>
-      <c r="B45" s="20" t="str">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Semiconductors</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>99</v>
+      <c r="A45" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E45" s="20" t="str">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>-/BBB-/BBB</v>
-      </c>
-      <c r="F45" s="32">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G45" s="33" t="str">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/01/2031</v>
+      <c r="E45" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="36">
+        <v>3.6249999999999998E-2</v>
+      </c>
+      <c r="G45" s="11">
+        <v>47618</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="0"/>
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="I45" s="13">
-        <v>102.07</v>
+        <v>80.66</v>
       </c>
       <c r="J45" s="13">
-        <v>4.8424845463382002</v>
+        <v>9.9952818659825997</v>
       </c>
       <c r="K45" s="13">
-        <v>67.974237180621998</v>
+        <v>593.69553893602995</v>
       </c>
       <c r="L45" s="13">
-        <v>4.7117258045619002</v>
-      </c>
-      <c r="M45" s="34">
-        <f>+_xlfn.XLOOKUP($N45,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>5.1856108017900002</v>
+      </c>
+      <c r="M45" s="14">
         <v>2000</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O45" s="16">
-        <v>1000000000</v>
+        <v>917517000</v>
       </c>
       <c r="P45" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>25</v>
+        <v>137</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C46" s="9" t="str">
+        <f>+A46</f>
+        <v>Mattel</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E46" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="F46" s="32">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G46" s="33">
-        <v>47899</v>
+      <c r="E46" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="G46" s="11">
+        <v>47804</v>
       </c>
       <c r="H46" s="12">
-        <v>2031</v>
-      </c>
-      <c r="I46" s="43">
-        <v>97.59</v>
-      </c>
-      <c r="J46" s="43">
-        <v>5.1539999999999999</v>
-      </c>
-      <c r="K46" s="43">
-        <v>91.02</v>
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="I46" s="13">
+        <v>99.494249999999994</v>
+      </c>
+      <c r="J46" s="13">
+        <v>5.1950145746962004</v>
+      </c>
+      <c r="K46" s="13">
+        <v>103.44711103354</v>
       </c>
       <c r="L46" s="13">
-        <v>5.1539999999999999</v>
-      </c>
-      <c r="M46" s="34">
+        <v>5.1281219620645997</v>
+      </c>
+      <c r="M46" s="14">
         <v>2000</v>
       </c>
       <c r="N46" s="15" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="O46" s="16">
         <v>600000000</v>
       </c>
       <c r="P46" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Petrobras</v>
-      </c>
-      <c r="B47" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Oil and Gas Extraction and Refining</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>80</v>
+      <c r="A47" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C47" s="9" t="str">
+        <f>+A47</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Ba1/BB/BB</v>
-      </c>
-      <c r="F47" s="10">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.6000000000000001E-2</v>
+        <v>12</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="36">
+        <v>5.7500000000000002E-2</v>
       </c>
       <c r="G47" s="11">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>47908</v>
+        <v>47863</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I47" s="13">
-        <v>100.818</v>
+        <v>102.045</v>
       </c>
       <c r="J47" s="13">
-        <v>5.4649379355078</v>
+        <v>5.3044691221645</v>
       </c>
       <c r="K47" s="13">
-        <v>129.98804491460999</v>
+        <v>114.38797755776</v>
       </c>
       <c r="L47" s="13">
-        <v>5.4017667057769998</v>
+        <v>5.2067291788855998</v>
       </c>
       <c r="M47" s="14">
-        <f>+_xlfn.XLOOKUP($N47,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O47" s="16">
-        <v>823936000</v>
+        <v>650000000</v>
       </c>
       <c r="P47" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>British American Tobacco</v>
+        <v>Centene</v>
       </c>
       <c r="B48" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Tobacco</v>
+        <v>Insurance and Reinsurance</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Baa1/BBB+/BBB+</v>
+        <v>21</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="F48" s="10">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>2.726E-2</v>
-      </c>
-      <c r="G48" s="11" t="str">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="G48" s="11">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>25/03/2031</v>
+        <v>47851</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I48" s="13">
-        <v>91.26</v>
+        <v>87.472499999999997</v>
       </c>
       <c r="J48" s="13">
-        <v>4.8767534636613004</v>
+        <v>5.6745121526288997</v>
       </c>
       <c r="K48" s="13">
-        <v>69.125403489383004</v>
+        <v>149.18257120941999</v>
       </c>
       <c r="L48" s="13">
-        <v>4.7999393948671001</v>
+        <v>5.6366512377394002</v>
       </c>
       <c r="M48" s="14">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N48" s="15" t="s">
-        <v>103</v>
+      <c r="N48" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="O48" s="16">
-        <v>1250000000</v>
+        <v>2200000000</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>EQT</v>
-      </c>
-      <c r="B49" s="9" t="str">
+        <v>Micron Technology</v>
+      </c>
+      <c r="B49" s="20" t="str">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Oil and Gas Extraction and Refining</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D49" s="20" t="s">
+        <v>Semiconductors</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="9" t="str">
+      <c r="E49" s="20" t="str">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Withdrawn/BBB-/BBB-</v>
-      </c>
-      <c r="F49" s="10">
+        <v>-/BBB-/BBB</v>
+      </c>
+      <c r="F49" s="32">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="G49" s="11" t="str">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="G49" s="33" t="str">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/05/2031</v>
+        <v>15/01/2031</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I49" s="13">
-        <v>93.474999999999994</v>
+        <v>102.07</v>
       </c>
       <c r="J49" s="13">
-        <v>5.2268554977413002</v>
+        <v>4.8424845463382002</v>
       </c>
       <c r="K49" s="13">
-        <v>103.85503999808</v>
+        <v>67.974237180621998</v>
       </c>
       <c r="L49" s="13">
-        <v>5.0978896042555002</v>
-      </c>
-      <c r="M49" s="14">
+        <v>4.7117258045619002</v>
+      </c>
+      <c r="M49" s="34">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O49" s="16">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="P49" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="21" t="str">
-        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Whirlpool</v>
-      </c>
-      <c r="B50" s="22" t="str">
-        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Domestic Appliances</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="F50" s="23">
-        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>2.4E-2</v>
-      </c>
-      <c r="G50" s="24" t="str">
-        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/05/2031</v>
-      </c>
-      <c r="H50" s="25">
-        <f t="shared" si="0"/>
+      <c r="A50" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F50" s="32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G50" s="33">
+        <v>47899</v>
+      </c>
+      <c r="H50" s="12">
         <v>2031</v>
       </c>
-      <c r="I50" s="26">
-        <v>74.83</v>
-      </c>
-      <c r="J50" s="26">
-        <v>9.0926741364232999</v>
-      </c>
-      <c r="K50" s="26">
-        <v>489.94439984998002</v>
-      </c>
-      <c r="L50" s="26">
-        <v>8.6660091505333998</v>
-      </c>
-      <c r="M50" s="27">
-        <f>+_xlfn.XLOOKUP($N50,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+      <c r="I50" s="43">
+        <v>97.59</v>
+      </c>
+      <c r="J50" s="43">
+        <v>5.1539999999999999</v>
+      </c>
+      <c r="K50" s="43">
+        <v>91.02</v>
+      </c>
+      <c r="L50" s="13">
+        <v>5.1539999999999999</v>
+      </c>
+      <c r="M50" s="34">
         <v>2000</v>
       </c>
-      <c r="N50" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="O50" s="29">
-        <v>300000000</v>
+      <c r="N50" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="O50" s="16">
+        <v>600000000</v>
       </c>
       <c r="P50" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Occidental Petroleum</v>
+        <v>Petrobras</v>
       </c>
       <c r="B51" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
         <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="F51" s="36">
+      <c r="E51" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Ba1/BB/BB</v>
+      </c>
+      <c r="F51" s="10">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>7.8750000000000001E-2</v>
-      </c>
-      <c r="G51" s="11" t="str">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G51" s="11">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/09/2031</v>
+        <v>47908</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
       <c r="I51" s="13">
-        <v>112.6699</v>
+        <v>100.818</v>
       </c>
       <c r="J51" s="13">
-        <v>5.1303234644179003</v>
+        <v>5.4649379355078</v>
       </c>
       <c r="K51" s="13">
-        <v>94.948125726268998</v>
+        <v>129.98804491460999</v>
       </c>
       <c r="L51" s="13">
-        <v>4.9498674514266998</v>
+        <v>5.4017667057769998</v>
       </c>
       <c r="M51" s="14">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N51" s="15" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="O51" s="16">
-        <v>484677000</v>
+        <v>823936000</v>
       </c>
       <c r="P51" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="21" t="str">
+      <c r="A52" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Falabella</v>
-      </c>
-      <c r="B52" s="22" t="str">
+        <v>British American Tobacco</v>
+      </c>
+      <c r="B52" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Specialty Retailers</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="F52" s="23">
+        <v>Tobacco</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa1/BBB+/BBB+</v>
+      </c>
+      <c r="F52" s="10">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="G52" s="24" t="str">
+        <v>2.726E-2</v>
+      </c>
+      <c r="G52" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/01/2032</v>
-      </c>
-      <c r="H52" s="25">
+        <v>25/03/2031</v>
+      </c>
+      <c r="H52" s="12">
         <f t="shared" si="0"/>
-        <v>2032</v>
-      </c>
-      <c r="I52" s="26">
-        <v>90.457499999999996</v>
-      </c>
-      <c r="J52" s="26">
-        <v>5.4688768811572004</v>
-      </c>
-      <c r="K52" s="26">
-        <v>125.09910315875</v>
-      </c>
-      <c r="L52" s="26">
-        <v>5.3674177412753004</v>
-      </c>
-      <c r="M52" s="27">
+        <v>2031</v>
+      </c>
+      <c r="I52" s="13">
+        <v>91.26</v>
+      </c>
+      <c r="J52" s="13">
+        <v>4.8767534636613004</v>
+      </c>
+      <c r="K52" s="13">
+        <v>69.125403489383004</v>
+      </c>
+      <c r="L52" s="13">
+        <v>4.7999393948671001</v>
+      </c>
+      <c r="M52" s="14">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>200000</v>
-      </c>
-      <c r="N52" s="28" t="s">
+        <v>2000</v>
+      </c>
+      <c r="N52" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="O52" s="16">
+        <v>1250000000</v>
+      </c>
+      <c r="P52" s="17" t="s">
         <v>161</v>
-      </c>
-      <c r="O52" s="29">
-        <v>650000000</v>
-      </c>
-      <c r="P52" s="17" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>92</v>
+      <c r="A53" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>EQT</v>
+      </c>
+      <c r="B53" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D53" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D53" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" s="36">
-        <v>4.2790000000000002E-2</v>
-      </c>
-      <c r="G53" s="11">
-        <v>48288</v>
+      <c r="E53" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Withdrawn/BBB-/BBB-</v>
+      </c>
+      <c r="F53" s="10">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>3.6249999999999998E-2</v>
+      </c>
+      <c r="G53" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>15/05/2031</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="0"/>
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="I53" s="13">
-        <v>90.445499999999996</v>
+        <v>93.474999999999994</v>
       </c>
       <c r="J53" s="13">
-        <v>6.4012437882361999</v>
+        <v>5.2268554977413002</v>
       </c>
       <c r="K53" s="13">
-        <v>218.13974059820001</v>
+        <v>103.85503999808</v>
       </c>
       <c r="L53" s="13">
-        <v>6.2331151566388003</v>
+        <v>5.0978896042555002</v>
       </c>
       <c r="M53" s="14">
+        <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N53" s="15" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="O53" s="16">
-        <v>2760600000</v>
+        <v>500000000</v>
       </c>
       <c r="P53" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="8" t="str">
+      <c r="A54" s="21" t="str">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Tapestry</v>
-      </c>
-      <c r="B54" s="9" t="str">
+        <v>Whirlpool</v>
+      </c>
+      <c r="B54" s="22" t="str">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Specialty Retailers</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Baa2/BBB/Withdrawn</v>
-      </c>
-      <c r="F54" s="36">
+        <v>Domestic Appliances</v>
+      </c>
+      <c r="C54" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="F54" s="23">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="G54" s="11" t="str">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G54" s="24" t="str">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/03/2032</v>
-      </c>
-      <c r="H54" s="12">
+        <v>15/05/2031</v>
+      </c>
+      <c r="H54" s="25">
         <f t="shared" si="0"/>
-        <v>2032</v>
-      </c>
-      <c r="I54" s="13">
-        <v>90.4</v>
-      </c>
-      <c r="J54" s="13">
-        <v>5.0720630206267003</v>
-      </c>
-      <c r="K54" s="13">
-        <v>84.111858144086</v>
-      </c>
-      <c r="L54" s="13">
-        <v>4.9921546996049999</v>
-      </c>
-      <c r="M54" s="14">
+        <v>2031</v>
+      </c>
+      <c r="I54" s="26">
+        <v>74.83</v>
+      </c>
+      <c r="J54" s="26">
+        <v>9.0926741364232999</v>
+      </c>
+      <c r="K54" s="26">
+        <v>489.94439984998002</v>
+      </c>
+      <c r="L54" s="26">
+        <v>8.6660091505333998</v>
+      </c>
+      <c r="M54" s="27">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N54" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="O54" s="16">
-        <v>500000000</v>
+      <c r="N54" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="O54" s="29">
+        <v>300000000</v>
       </c>
       <c r="P54" s="17" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -6691,805 +6738,1029 @@
       <c r="D55" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Withdrawn/BB+/BBB-</v>
+      <c r="E55" s="9" t="s">
+        <v>109</v>
       </c>
       <c r="F55" s="36">
         <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.3749999999999999E-2</v>
-      </c>
-      <c r="G55" s="11">
+        <v>7.8750000000000001E-2</v>
+      </c>
+      <c r="G55" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>48214</v>
+        <v>15/09/2031</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="0"/>
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="I55" s="13">
-        <v>101.77</v>
+        <v>112.6699</v>
       </c>
       <c r="J55" s="13">
-        <v>5.0642586010107999</v>
+        <v>5.1303234644179003</v>
       </c>
       <c r="K55" s="13">
-        <v>85.485963290301001</v>
+        <v>94.948125726268998</v>
       </c>
       <c r="L55" s="13">
-        <v>4.8638137088405999</v>
+        <v>4.9498674514266998</v>
       </c>
       <c r="M55" s="14">
         <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="O55" s="16">
-        <v>1000000000</v>
+        <v>484677000</v>
       </c>
       <c r="P55" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="19" t="str">
+      <c r="A56" s="21" t="str">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Methanex US Operations</v>
-      </c>
-      <c r="B56" s="20" t="str">
+        <v>Falabella</v>
+      </c>
+      <c r="B56" s="22" t="str">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Food and Beverage Production</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D56" s="20" t="s">
+        <v>Specialty Retailers</v>
+      </c>
+      <c r="C56" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D56" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E56" s="20" t="str">
-        <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>-/-/BB+</v>
-      </c>
-      <c r="F56" s="32">
+      <c r="E56" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="F56" s="23">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>6.25E-2</v>
-      </c>
-      <c r="G56" s="33" t="str">
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="G56" s="24" t="str">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>15/03/2032</v>
-      </c>
-      <c r="H56" s="12">
+        <v>15/01/2032</v>
+      </c>
+      <c r="H56" s="25">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I56" s="13">
-        <v>101.011</v>
-      </c>
-      <c r="J56" s="13">
-        <v>6.1261381346982002</v>
-      </c>
-      <c r="K56" s="13">
-        <v>191.88007492214001</v>
-      </c>
-      <c r="L56" s="13">
-        <v>5.8657497923847002</v>
-      </c>
-      <c r="M56" s="14">
+      <c r="I56" s="26">
+        <v>90.457499999999996</v>
+      </c>
+      <c r="J56" s="26">
+        <v>5.4688768811572004</v>
+      </c>
+      <c r="K56" s="26">
+        <v>125.09910315875</v>
+      </c>
+      <c r="L56" s="26">
+        <v>5.3674177412753004</v>
+      </c>
+      <c r="M56" s="27">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
-        <v>2000</v>
-      </c>
-      <c r="N56" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="O56" s="16">
-        <v>600000000</v>
+        <v>200000</v>
+      </c>
+      <c r="N56" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="O56" s="29">
+        <v>650000000</v>
       </c>
       <c r="P56" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="8" t="str">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>British American Tobacco</v>
-      </c>
-      <c r="B57" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Tobacco</v>
+      <c r="A57" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="9" t="str">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
-        <v>Baa1/BBB+/BBB+</v>
+      <c r="E57" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="F57" s="36">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>4.7419999999999997E-2</v>
-      </c>
-      <c r="G57" s="11" t="str">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>16/03/2032</v>
+        <v>4.2790000000000002E-2</v>
+      </c>
+      <c r="G57" s="11">
+        <v>48288</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I57" s="13">
-        <v>99.3155</v>
+        <v>90.445499999999996</v>
       </c>
       <c r="J57" s="13">
-        <v>4.9393697303708999</v>
+        <v>6.4012437882361999</v>
       </c>
       <c r="K57" s="13">
-        <v>72.074971640130002</v>
+        <v>218.13974059820001</v>
       </c>
       <c r="L57" s="13">
-        <v>4.8443604233849999</v>
+        <v>6.2331151566388003</v>
       </c>
       <c r="M57" s="14">
-        <f>+_xlfn.XLOOKUP($N57,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="O57" s="16">
-        <v>900000000</v>
+        <v>2760600000</v>
       </c>
       <c r="P57" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="21" t="str">
+      <c r="A58" s="8" t="str">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Whirlpool</v>
-      </c>
-      <c r="B58" s="22" t="str">
+        <v>Tapestry</v>
+      </c>
+      <c r="B58" s="9" t="str">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Domestic Appliances</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D58" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="F58" s="23">
+        <v>Specialty Retailers</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa2/BBB/Withdrawn</v>
+      </c>
+      <c r="F58" s="36">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>4.7E-2</v>
-      </c>
-      <c r="G58" s="24" t="str">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G58" s="11" t="str">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>14/05/2032</v>
-      </c>
-      <c r="H58" s="25">
+        <v>15/03/2032</v>
+      </c>
+      <c r="H58" s="12">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I58" s="26">
-        <v>79.400000000000006</v>
-      </c>
-      <c r="J58" s="26">
-        <v>9.5653205508415997</v>
-      </c>
-      <c r="K58" s="26">
-        <v>534.30350032287004</v>
-      </c>
-      <c r="L58" s="26">
-        <v>9.3807757333051001</v>
-      </c>
-      <c r="M58" s="27">
+      <c r="I58" s="13">
+        <v>90.4</v>
+      </c>
+      <c r="J58" s="13">
+        <v>5.0720630206267003</v>
+      </c>
+      <c r="K58" s="13">
+        <v>84.111858144086</v>
+      </c>
+      <c r="L58" s="13">
+        <v>4.9921546996049999</v>
+      </c>
+      <c r="M58" s="14">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N58" s="38" t="s">
-        <v>118</v>
-      </c>
-      <c r="O58" s="29">
-        <v>300000000</v>
+      <c r="N58" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="O58" s="16">
+        <v>500000000</v>
       </c>
       <c r="P58" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>42</v>
+      <c r="A59" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Occidental Petroleum</v>
+      </c>
+      <c r="B59" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Oil and Gas Extraction and Refining</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="E59" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Withdrawn/BB+/BBB-</v>
       </c>
       <c r="F59" s="36">
-        <v>4.7500000000000001E-2</v>
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.3749999999999999E-2</v>
       </c>
       <c r="G59" s="11">
-        <v>48215</v>
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>48214</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I59" s="13">
-        <v>97.382000000000005</v>
+        <v>101.77</v>
       </c>
       <c r="J59" s="13">
-        <v>5.3686118665361002</v>
+        <v>5.0642586010107999</v>
       </c>
       <c r="K59" s="13">
-        <v>115.79947915907999</v>
+        <v>85.485963290301001</v>
       </c>
       <c r="L59" s="13">
-        <v>5.2686449671825999</v>
+        <v>4.8638137088405999</v>
       </c>
       <c r="M59" s="14">
+        <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="O59" s="16">
-        <v>1150000000</v>
+        <v>1000000000</v>
       </c>
       <c r="P59" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="8" t="str">
+      <c r="A60" s="19" t="str">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
-        <v>Micron Technology</v>
-      </c>
-      <c r="B60" s="9" t="str">
+        <v>Methanex US Operations</v>
+      </c>
+      <c r="B60" s="20" t="str">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
-        <v>Semiconductors</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D60" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="F60" s="36">
+        <v>Food and Beverage Production</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="20" t="str">
+        <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>-/-/BB+</v>
+      </c>
+      <c r="F60" s="32">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
-        <v>5.6500000000000002E-2</v>
-      </c>
-      <c r="G60" s="11">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G60" s="33" t="str">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
-        <v>48224</v>
+        <v>15/03/2032</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I60" s="13">
-        <v>103.16925000000001</v>
+        <v>101.011</v>
       </c>
       <c r="J60" s="13">
-        <v>5.1199812746477997</v>
+        <v>6.1261381346982002</v>
       </c>
       <c r="K60" s="13">
-        <v>87.806085161064004</v>
+        <v>191.88007492214001</v>
       </c>
       <c r="L60" s="13">
-        <v>5.0980394520193997</v>
+        <v>5.8657497923847002</v>
       </c>
       <c r="M60" s="14">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
-      <c r="N60" s="15" t="s">
-        <v>122</v>
+      <c r="N60" s="35" t="s">
+        <v>115</v>
       </c>
       <c r="O60" s="16">
-        <v>500000000</v>
+        <v>600000000</v>
       </c>
       <c r="P60" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C61" s="9" t="str">
-        <f>+A61</f>
-        <v>HF Sinclair</v>
+      <c r="A61" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>British American Tobacco</v>
+      </c>
+      <c r="B61" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Tobacco</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E61" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="10">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G61" s="11">
-        <v>48458</v>
+      <c r="E61" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$D:$D,1,0,1)</f>
+        <v>Baa1/BBB+/BBB+</v>
+      </c>
+      <c r="F61" s="36">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.7419999999999997E-2</v>
+      </c>
+      <c r="G61" s="11" t="str">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>16/03/2032</v>
       </c>
       <c r="H61" s="12">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
       <c r="I61" s="13">
-        <v>101.663</v>
+        <v>99.3155</v>
       </c>
       <c r="J61" s="13">
-        <v>5.2464322657264004</v>
+        <v>4.9393697303708999</v>
       </c>
       <c r="K61" s="13">
-        <v>101.38634535505</v>
+        <v>72.074971640130002</v>
       </c>
       <c r="L61" s="13">
-        <v>5.3856085213808997</v>
+        <v>4.8443604233849999</v>
       </c>
       <c r="M61" s="14">
+        <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
         <v>2000</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="O61" s="16">
-        <v>500000000</v>
+        <v>900000000</v>
       </c>
       <c r="P61" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C62" s="9" t="str">
-        <f>+A62</f>
-        <v>Macy´s</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="A62" s="21" t="str">
+        <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Whirlpool</v>
+      </c>
+      <c r="B62" s="22" t="str">
+        <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Domestic Appliances</v>
+      </c>
+      <c r="C62" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D62" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E62" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F62" s="36">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="G62" s="11">
-        <v>48349</v>
-      </c>
-      <c r="H62" s="12">
+      <c r="E62" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F62" s="23">
+        <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>4.7E-2</v>
+      </c>
+      <c r="G62" s="24" t="str">
+        <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>14/05/2032</v>
+      </c>
+      <c r="H62" s="25">
+        <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="I62" s="13">
-        <v>96.5</v>
-      </c>
-      <c r="J62" s="13">
-        <v>7.8368882215886</v>
-      </c>
-      <c r="K62" s="13">
-        <v>364.54290681703998</v>
-      </c>
-      <c r="L62" s="13">
-        <v>7.8280887021760002</v>
-      </c>
-      <c r="M62" s="14">
-        <v>1000</v>
-      </c>
-      <c r="N62" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="O62" s="16">
-        <v>250000000</v>
+      <c r="I62" s="26">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="J62" s="26">
+        <v>9.5653205508415997</v>
+      </c>
+      <c r="K62" s="26">
+        <v>534.30350032287004</v>
+      </c>
+      <c r="L62" s="26">
+        <v>9.3807757333051001</v>
+      </c>
+      <c r="M62" s="27">
+        <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
+      </c>
+      <c r="N62" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="O62" s="29">
+        <v>300000000</v>
       </c>
       <c r="P62" s="17" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="39" t="s">
-        <v>102</v>
+      <c r="A63" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>125</v>
+        <v>42</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="F63" s="40">
-        <v>6.4210000000000003E-2</v>
-      </c>
-      <c r="G63" s="33">
-        <v>48793</v>
-      </c>
-      <c r="H63" s="41">
-        <v>2033</v>
+      <c r="E63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="36">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G63" s="11">
+        <v>48215</v>
+      </c>
+      <c r="H63" s="12">
+        <f t="shared" si="0"/>
+        <v>2032</v>
       </c>
       <c r="I63" s="13">
-        <v>107.76</v>
+        <v>97.382000000000005</v>
       </c>
       <c r="J63" s="13">
-        <v>5.1640210219803997</v>
+        <v>5.3686118665361002</v>
       </c>
       <c r="K63" s="13">
-        <v>90.100799827076997</v>
+        <v>115.79947915907999</v>
       </c>
       <c r="L63" s="13">
-        <v>5.0918269119830004</v>
-      </c>
-      <c r="M63" s="34">
+        <v>5.2686449671825999</v>
+      </c>
+      <c r="M63" s="14">
         <v>2000</v>
       </c>
-      <c r="N63" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="O63" s="42">
-        <v>1250000000</v>
+      <c r="N63" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="O63" s="16">
+        <v>1150000000</v>
       </c>
       <c r="P63" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>134</v>
+      <c r="A64" s="8" t="str">
+        <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$B:$B,1,0,1)</f>
+        <v>Micron Technology</v>
+      </c>
+      <c r="B64" s="9" t="str">
+        <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$C:$C,1,0,1)</f>
+        <v>Semiconductors</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F64" s="10">
-        <v>5.6000000000000001E-2</v>
+        <v>121</v>
+      </c>
+      <c r="F64" s="36">
+        <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$F:$F,1,0,1)</f>
+        <v>5.6500000000000002E-2</v>
       </c>
       <c r="G64" s="11">
-        <v>49218</v>
+        <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$G:$G,1,0,1)</f>
+        <v>48224</v>
       </c>
       <c r="H64" s="12">
-        <v>2034</v>
+        <f t="shared" si="0"/>
+        <v>2032</v>
       </c>
       <c r="I64" s="13">
-        <v>101.79</v>
+        <v>103.16925000000001</v>
       </c>
       <c r="J64" s="13">
-        <v>5.3474082910789997</v>
+        <v>5.1199812746477997</v>
       </c>
       <c r="K64" s="13">
-        <v>102.32605446818</v>
+        <v>87.806085161064004</v>
       </c>
       <c r="L64" s="13">
-        <v>5.1724981641551997</v>
+        <v>5.0980394520193997</v>
       </c>
       <c r="M64" s="14">
-        <v>1000</v>
+        <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
+        <v>2000</v>
       </c>
       <c r="N64" s="15" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="O64" s="16">
-        <v>1200000000</v>
+        <v>500000000</v>
       </c>
       <c r="P64" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" s="39" t="s">
-        <v>69</v>
+      <c r="A65" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>69</v>
+        <v>42</v>
+      </c>
+      <c r="C65" s="9" t="str">
+        <f>+A65</f>
+        <v>HF Sinclair</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="F65" s="10">
-        <v>5.3999999999999999E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G65" s="11">
-        <v>49589</v>
+        <v>48458</v>
       </c>
       <c r="H65" s="12">
-        <f>YEAR(G65)</f>
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="I65" s="13">
-        <v>96.627459999999999</v>
+        <v>101.663</v>
       </c>
       <c r="J65" s="13">
-        <v>5.9627747994528999</v>
+        <v>5.2464322657264004</v>
       </c>
       <c r="K65" s="13">
-        <v>159.65978946299001</v>
+        <v>101.38634535505</v>
       </c>
       <c r="L65" s="13">
-        <v>5.7431229949776004</v>
+        <v>5.3856085213808997</v>
       </c>
       <c r="M65" s="14">
         <v>2000</v>
       </c>
       <c r="N65" s="15" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="O65" s="16">
-        <v>600000000</v>
+        <v>500000000</v>
       </c>
       <c r="P65" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="66" spans="1:16">
       <c r="A66" s="8" t="s">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>83</v>
+        <v>34</v>
+      </c>
+      <c r="C66" s="9" t="str">
+        <f>+A66</f>
+        <v>Macy´s</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" s="10">
-        <v>5.9799999999999999E-2</v>
+        <v>77</v>
+      </c>
+      <c r="F66" s="36">
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G66" s="11">
-        <v>49351</v>
+        <v>48349</v>
       </c>
       <c r="H66" s="12">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="I66" s="13">
-        <v>104.18174999999999</v>
+        <v>96.5</v>
       </c>
       <c r="J66" s="13">
-        <v>5.4373842285820997</v>
+        <v>7.8368882215886</v>
       </c>
       <c r="K66" s="13">
-        <v>110.72756212295999</v>
+        <v>364.54290681703998</v>
       </c>
       <c r="L66" s="13">
-        <v>5.3727784157435998</v>
+        <v>7.8280887021760002</v>
       </c>
       <c r="M66" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N66" s="15" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="O66" s="16">
-        <v>650000000</v>
+        <v>250000000</v>
       </c>
       <c r="P66" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:16">
-      <c r="A67" s="8" t="s">
-        <v>112</v>
+      <c r="A67" s="39" t="s">
+        <v>102</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E67" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="F67" s="36">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G67" s="11">
-        <v>49379</v>
-      </c>
-      <c r="H67" s="12">
-        <f>YEAR(G67)</f>
-        <v>2035</v>
+      <c r="E67" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="40">
+        <v>6.4210000000000003E-2</v>
+      </c>
+      <c r="G67" s="33">
+        <v>48793</v>
+      </c>
+      <c r="H67" s="41">
+        <v>2033</v>
       </c>
       <c r="I67" s="13">
-        <v>100.16</v>
+        <v>107.76</v>
       </c>
       <c r="J67" s="13">
-        <v>5.5503247750032996</v>
+        <v>5.1640210219803997</v>
       </c>
       <c r="K67" s="13">
-        <v>120.89879267489</v>
+        <v>90.100799827076997</v>
       </c>
       <c r="L67" s="13">
-        <v>5.4514660395618</v>
-      </c>
-      <c r="M67" s="14">
+        <v>5.0918269119830004</v>
+      </c>
+      <c r="M67" s="34">
         <v>2000</v>
       </c>
-      <c r="N67" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="O67" s="16">
-        <v>750000000</v>
+      <c r="N67" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="O67" s="42">
+        <v>1250000000</v>
       </c>
       <c r="P67" s="17" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:16">
       <c r="A68" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F68" s="10">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G68" s="11">
+        <v>49218</v>
+      </c>
+      <c r="H68" s="12">
+        <v>2034</v>
+      </c>
+      <c r="I68" s="13">
+        <v>101.79</v>
+      </c>
+      <c r="J68" s="13">
+        <v>5.3474082910789997</v>
+      </c>
+      <c r="K68" s="13">
+        <v>102.32605446818</v>
+      </c>
+      <c r="L68" s="13">
+        <v>5.1724981641551997</v>
+      </c>
+      <c r="M68" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N68" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="O68" s="16">
+        <v>1200000000</v>
+      </c>
+      <c r="P68" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F69" s="10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G69" s="11">
+        <v>49589</v>
+      </c>
+      <c r="H69" s="12">
+        <f>YEAR(G69)</f>
+        <v>2035</v>
+      </c>
+      <c r="I69" s="13">
+        <v>96.627459999999999</v>
+      </c>
+      <c r="J69" s="13">
+        <v>5.9627747994528999</v>
+      </c>
+      <c r="K69" s="13">
+        <v>159.65978946299001</v>
+      </c>
+      <c r="L69" s="13">
+        <v>5.7431229949776004</v>
+      </c>
+      <c r="M69" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="O69" s="16">
+        <v>600000000</v>
+      </c>
+      <c r="P69" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="10">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="G70" s="11">
+        <v>49351</v>
+      </c>
+      <c r="H70" s="12">
+        <v>2035</v>
+      </c>
+      <c r="I70" s="13">
+        <v>104.18174999999999</v>
+      </c>
+      <c r="J70" s="13">
+        <v>5.4373842285820997</v>
+      </c>
+      <c r="K70" s="13">
+        <v>110.72756212295999</v>
+      </c>
+      <c r="L70" s="13">
+        <v>5.3727784157435998</v>
+      </c>
+      <c r="M70" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N70" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="O70" s="16">
+        <v>650000000</v>
+      </c>
+      <c r="P70" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F71" s="36">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G71" s="11">
+        <v>49379</v>
+      </c>
+      <c r="H71" s="12">
+        <f>YEAR(G71)</f>
+        <v>2035</v>
+      </c>
+      <c r="I71" s="13">
+        <v>100.16</v>
+      </c>
+      <c r="J71" s="13">
+        <v>5.5503247750032996</v>
+      </c>
+      <c r="K71" s="13">
+        <v>120.89879267489</v>
+      </c>
+      <c r="L71" s="13">
+        <v>5.4514660395618</v>
+      </c>
+      <c r="M71" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N71" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="O71" s="16">
+        <v>750000000</v>
+      </c>
+      <c r="P71" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B72" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C72" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="9" t="s">
+      <c r="D72" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="9" t="s">
+      <c r="E72" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F68" s="36">
+      <c r="F72" s="36">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G72" s="11">
         <v>49324</v>
       </c>
-      <c r="H68" s="12">
+      <c r="H72" s="12">
         <v>2035</v>
       </c>
-      <c r="I68" s="13">
+      <c r="I72" s="13">
         <v>100.685</v>
       </c>
-      <c r="J68" s="13">
+      <c r="J72" s="13">
         <v>5.6758894124054997</v>
       </c>
-      <c r="K68" s="13">
+      <c r="K72" s="13">
         <v>134.82334868976</v>
       </c>
-      <c r="L68" s="13">
+      <c r="L72" s="13">
         <v>5.5378214915232</v>
       </c>
-      <c r="M68" s="14">
+      <c r="M72" s="14">
         <v>2000</v>
       </c>
-      <c r="N68" s="15" t="s">
+      <c r="N72" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="O68" s="16">
+      <c r="O72" s="16">
         <v>750000000</v>
       </c>
-      <c r="P68" s="17" t="s">
-        <v>142</v>
+      <c r="P72" s="17" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N68">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="N2:N72">
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{F8829E3F-53D2-4C6C-9556-A1DDA13CBEA8}"/>
-    <hyperlink ref="N3" r:id="rId2" xr:uid="{493DE554-0834-4A5C-9D88-925D18050DB3}"/>
-    <hyperlink ref="N4" r:id="rId3" xr:uid="{5BE5A1EF-BB44-461F-9180-7B475B0E9396}"/>
-    <hyperlink ref="N5" r:id="rId4" xr:uid="{9ED42145-4DEF-4A63-82CC-C2C56C5E4860}"/>
-    <hyperlink ref="N6" r:id="rId5" xr:uid="{D4C53924-1412-406C-9692-2B99F5D2879B}"/>
-    <hyperlink ref="N7" r:id="rId6" xr:uid="{B8987634-CF7E-407B-AF46-09E5211D981E}"/>
-    <hyperlink ref="N8" r:id="rId7" xr:uid="{7D8E48B7-C6EA-48B6-AC74-0C8C0968DE3E}"/>
-    <hyperlink ref="N9" r:id="rId8" xr:uid="{845603A1-124D-4CA4-9856-9CC87EB7B9EF}"/>
-    <hyperlink ref="N10" r:id="rId9" xr:uid="{5BBB0919-A125-4DC8-8FEB-868401D698E1}"/>
-    <hyperlink ref="N11" r:id="rId10" xr:uid="{13B976B5-58F3-4D39-84F9-716FB2088569}"/>
-    <hyperlink ref="N12" r:id="rId11" xr:uid="{E3B7D5A1-5A80-4B4C-8CFE-D76B19230139}"/>
-    <hyperlink ref="N13" r:id="rId12" xr:uid="{B7CF9816-C500-4E7F-9269-2E696758B64B}"/>
-    <hyperlink ref="N17" r:id="rId13" xr:uid="{DE9DE913-BE83-48B3-9EDE-01DBAEB6486C}"/>
-    <hyperlink ref="N18" r:id="rId14" xr:uid="{435F6EF0-D8DA-4369-AB88-5D6430E3D047}"/>
-    <hyperlink ref="N19" r:id="rId15" xr:uid="{A4315895-83ED-4A4A-AFD7-25F372EAE814}"/>
-    <hyperlink ref="N20" r:id="rId16" xr:uid="{733C5B94-3883-4A88-9D48-9DA42C7476E7}"/>
-    <hyperlink ref="N21" r:id="rId17" xr:uid="{0E366B85-C215-4A7A-AD99-CDB93D72F7A7}"/>
-    <hyperlink ref="N22" r:id="rId18" xr:uid="{D4C2FA22-5BF8-4424-9CF7-8674E4A4106E}"/>
-    <hyperlink ref="N23" r:id="rId19" xr:uid="{322D778A-F1DD-4155-93A9-D5A6649DCF18}"/>
-    <hyperlink ref="N25" r:id="rId20" xr:uid="{EE50CE36-62A1-45DA-8F9C-E9E8F2808CF5}"/>
-    <hyperlink ref="N26" r:id="rId21" xr:uid="{21C5FF06-59F8-43DA-8AA1-2A52D01B5CB0}"/>
-    <hyperlink ref="N27" r:id="rId22" xr:uid="{F1FB2C44-DB61-43EC-A295-C27A79EEB202}"/>
-    <hyperlink ref="N29" r:id="rId23" xr:uid="{B67E00C8-419D-47DD-8CD4-7CA49E15BBF6}"/>
-    <hyperlink ref="N30" r:id="rId24" xr:uid="{E8F014BA-433D-4D7C-8B18-B51CE4B26F61}"/>
-    <hyperlink ref="N31" r:id="rId25" xr:uid="{3CC9971E-673D-44AD-B09A-6DB728D567F8}"/>
-    <hyperlink ref="N32" r:id="rId26" xr:uid="{02126DEA-8F82-41A4-9362-17A9C6D5E32B}"/>
-    <hyperlink ref="N33" r:id="rId27" xr:uid="{E7297F32-7C00-464C-AE99-69C36D1F1613}"/>
-    <hyperlink ref="N34" r:id="rId28" xr:uid="{F9131CCF-336C-4B24-B612-EEFD07BA775C}"/>
-    <hyperlink ref="N35" r:id="rId29" xr:uid="{BE9AE4CC-C3E1-4950-8D8B-270F02BF60B7}"/>
-    <hyperlink ref="N36" r:id="rId30" xr:uid="{624DE41A-68F3-48A5-869E-9700F9F71410}"/>
-    <hyperlink ref="N37" r:id="rId31" xr:uid="{A65F62BC-F37C-42BA-83ED-AB7D11F575A8}"/>
-    <hyperlink ref="N38" r:id="rId32" xr:uid="{40472BA3-E6DE-4439-9C52-41A140BBFC69}"/>
-    <hyperlink ref="N39" r:id="rId33" xr:uid="{4C8E626B-99D3-4420-9D92-F7AF982CD314}"/>
-    <hyperlink ref="N40" r:id="rId34" xr:uid="{D2EC59FA-A0E3-4B53-8889-82B0E55B21FE}"/>
-    <hyperlink ref="N41" r:id="rId35" xr:uid="{8FEE7385-3A2F-4BAE-B5B6-F5C4FE76B9BD}"/>
-    <hyperlink ref="N43" r:id="rId36" xr:uid="{1A2448D3-5A04-40FC-93A7-202A7D2069DE}"/>
-    <hyperlink ref="N45" r:id="rId37" xr:uid="{4566D9FA-63AE-4BE1-8327-384D1C03C900}"/>
-    <hyperlink ref="N47" r:id="rId38" xr:uid="{B518D265-7B19-4F7B-8C03-DEA09B0FB131}"/>
-    <hyperlink ref="N48" r:id="rId39" xr:uid="{4FBDB43C-AA47-4274-B352-31FF46C64F23}"/>
-    <hyperlink ref="N49" r:id="rId40" xr:uid="{1B7FF16F-B3D7-4BD0-A55C-FEDF4C93A0D0}"/>
-    <hyperlink ref="N50" r:id="rId41" xr:uid="{CE5DA5BA-1B3C-4844-9BFB-4DC0CFD3230D}"/>
-    <hyperlink ref="N51" r:id="rId42" xr:uid="{DDAC8608-E69D-4C8A-87A8-47130B585733}"/>
-    <hyperlink ref="N52" r:id="rId43" xr:uid="{C0A06BC2-023C-4659-8A6A-5A62E40D8F99}"/>
-    <hyperlink ref="N53" r:id="rId44" xr:uid="{908C235D-39F8-4709-B39E-0D750931FB85}"/>
-    <hyperlink ref="N54" r:id="rId45" xr:uid="{CA51059E-F0E2-448B-8395-327C75774534}"/>
-    <hyperlink ref="N55" r:id="rId46" xr:uid="{49C22A9E-9A0A-45EF-A986-867B41D22D38}"/>
-    <hyperlink ref="N56" r:id="rId47" xr:uid="{B818704F-053B-42E7-9E1A-033FC04780AC}"/>
-    <hyperlink ref="N57" r:id="rId48" xr:uid="{B2EC6875-55BE-4D4B-B44E-26B8D6E5B9BB}"/>
-    <hyperlink ref="N59" r:id="rId49" xr:uid="{E2C3E74C-A8FD-4744-9053-8C3F3D942DA0}"/>
-    <hyperlink ref="N60" r:id="rId50" xr:uid="{B1C63365-D207-4FD0-9BEF-62F44B06177D}"/>
-    <hyperlink ref="N65" r:id="rId51" xr:uid="{3DA7AD4B-F2D7-461E-8B1D-68CDC9F77197}"/>
-    <hyperlink ref="N66" r:id="rId52" xr:uid="{FAA16BC6-FB5D-4113-91BB-16E0EF112781}"/>
-    <hyperlink ref="N67" r:id="rId53" xr:uid="{1826AE20-917E-4600-97B8-3427D3AF5A7F}"/>
-    <hyperlink ref="N42" r:id="rId54" xr:uid="{84509A1E-478B-4F2F-A76B-7D3FDAC32567}"/>
-    <hyperlink ref="N61" r:id="rId55" xr:uid="{37272A85-48A2-49F3-B6B1-A1BF5108BB3B}"/>
-    <hyperlink ref="N68" r:id="rId56" xr:uid="{93FF6E81-D3CF-4DB1-A2BA-5C814E85A40B}"/>
-    <hyperlink ref="N62" r:id="rId57" xr:uid="{FA7152BA-C1C8-42D1-9AC6-1F8CE936EB1A}"/>
-    <hyperlink ref="N63" r:id="rId58" xr:uid="{30637A7A-0395-47CC-98DA-ED03C0640776}"/>
-    <hyperlink ref="N44" r:id="rId59" xr:uid="{3AAC5A48-F5CC-4389-AF46-D80EE222264C}"/>
-    <hyperlink ref="N58" r:id="rId60" xr:uid="{00C2204D-C3E0-426A-9CB0-6AE837769FCF}"/>
-    <hyperlink ref="N16" r:id="rId61" xr:uid="{46A1D7B2-C8AD-46A1-8875-A73F63E8C736}"/>
-    <hyperlink ref="N28" r:id="rId62" xr:uid="{1BFAF898-57E1-4C20-BA97-46B6F415E771}"/>
-    <hyperlink ref="N15" r:id="rId63" xr:uid="{568174ED-C9E1-47A7-9854-64812BFE8100}"/>
-    <hyperlink ref="N24" r:id="rId64" xr:uid="{E9207531-E5F0-470E-88F4-C6689BEA9BE5}"/>
-    <hyperlink ref="N14" r:id="rId65" xr:uid="{5F461451-0EE4-4113-8D8C-4CFED78CCF2D}"/>
-    <hyperlink ref="N64" r:id="rId66" xr:uid="{7C12EC03-B82E-4172-A765-7023385900B3}"/>
-    <hyperlink ref="N46" r:id="rId67" xr:uid="{D97CBE76-AC55-4BFA-8F7B-C7F4879E4141}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{388245D2-8DD6-4087-A7F8-8040150E97BC}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{1787DBED-81D4-4512-AAE1-8A6C5F68FA76}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{45766180-88CA-4ED2-8074-5E44DD7FF760}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{19DB2657-953E-464A-94AA-8A3F053005E0}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{73578B1E-F8E6-43BB-B71A-B46047D81383}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{582207F9-DAF8-43D8-9B59-BCFF2B48FDE2}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{4AAB2268-075D-4F51-A04A-C8678B42D2AE}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{E3922AA0-2B8F-45D5-9AD6-A8019D713F7D}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{C0C72420-4E37-4A66-A87D-33C9BD4B0B3C}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{79AC8E65-7DCA-40C6-97D7-9B4B6BBC7AD1}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{9EDA0AEC-DB10-4D8D-AD14-9B689E212E67}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{AC85EA30-A42D-4D9B-B32E-4AF675012F32}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{DD39554D-E52F-428B-AACE-D8F876B2C92F}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{DA401183-C542-435A-A956-9F4E60264F43}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{DF95C386-399A-4BEE-9EE7-1A40DAA6AE88}"/>
+    <hyperlink ref="N20" r:id="rId16" xr:uid="{08069BA9-9801-419C-825B-DB74431BCBB1}"/>
+    <hyperlink ref="N21" r:id="rId17" xr:uid="{C44016D9-1BBE-4C21-95A5-CEA414857EFE}"/>
+    <hyperlink ref="N22" r:id="rId18" xr:uid="{BCEE1BB4-7A08-4AAC-BE7A-C9FAA84A7CA0}"/>
+    <hyperlink ref="N23" r:id="rId19" xr:uid="{D93BB35A-044D-4236-AF93-9D66EF392147}"/>
+    <hyperlink ref="N24" r:id="rId20" xr:uid="{210C65A5-16B7-4F23-9E17-7E8EC7ECAE48}"/>
+    <hyperlink ref="N25" r:id="rId21" xr:uid="{FA84CA0B-C26E-4E1C-94CA-792AF502D0E5}"/>
+    <hyperlink ref="N26" r:id="rId22" xr:uid="{B1D1B7AB-AA6B-4EA9-9873-5AC34AD5B0EF}"/>
+    <hyperlink ref="N28" r:id="rId23" xr:uid="{9B8AD11E-3831-40CA-9FDD-A6C142546664}"/>
+    <hyperlink ref="N29" r:id="rId24" xr:uid="{41238C85-DA41-420E-8AE5-4133D4FA4531}"/>
+    <hyperlink ref="N30" r:id="rId25" xr:uid="{D54F90FD-5973-4C5E-BAAF-6FDE129B3BCE}"/>
+    <hyperlink ref="N31" r:id="rId26" xr:uid="{E329DA29-81F6-4F9B-9141-C86B9650D0B4}"/>
+    <hyperlink ref="N33" r:id="rId27" xr:uid="{A3634148-4321-4749-A16B-5F3ED8933349}"/>
+    <hyperlink ref="N34" r:id="rId28" xr:uid="{D470723C-5043-4B22-A669-B60D3D1F1C04}"/>
+    <hyperlink ref="N35" r:id="rId29" xr:uid="{C1DCB0A5-9CB2-43C9-BFBF-A17C192794A2}"/>
+    <hyperlink ref="N36" r:id="rId30" xr:uid="{C7C3D187-8B11-4995-B409-DD905158877B}"/>
+    <hyperlink ref="N37" r:id="rId31" xr:uid="{B9200BE9-E32A-49AB-9D4E-0C6D4D194E60}"/>
+    <hyperlink ref="N38" r:id="rId32" xr:uid="{E3BB1EDA-9DE0-452F-B653-5ACA209BBF6C}"/>
+    <hyperlink ref="N39" r:id="rId33" xr:uid="{FBFFB7BE-7898-4976-8389-A56004E9DE2F}"/>
+    <hyperlink ref="N40" r:id="rId34" xr:uid="{EBFE958C-420E-4E0F-BE4F-C7175591010A}"/>
+    <hyperlink ref="N41" r:id="rId35" xr:uid="{93574D83-47E3-40BC-BD8B-FA5112591208}"/>
+    <hyperlink ref="N42" r:id="rId36" xr:uid="{C84FB5CE-4CBD-4B3D-8BC0-7B17A496BC1B}"/>
+    <hyperlink ref="N43" r:id="rId37" xr:uid="{4F2538FE-C213-4CA9-8FA1-18BABD9B0B62}"/>
+    <hyperlink ref="N44" r:id="rId38" xr:uid="{4D7E96E9-048C-4EC4-84D2-1DE7C02645DB}"/>
+    <hyperlink ref="N45" r:id="rId39" xr:uid="{03375205-EB20-4E41-B3CF-54B820435C0E}"/>
+    <hyperlink ref="N47" r:id="rId40" xr:uid="{A2680AB3-C514-4A50-AA51-4EAB5F4494BC}"/>
+    <hyperlink ref="N49" r:id="rId41" xr:uid="{8E661B0F-D115-41DF-9F03-65695773A771}"/>
+    <hyperlink ref="N51" r:id="rId42" xr:uid="{BDDC8155-9A73-46EA-ADDE-E8E3FA9CF310}"/>
+    <hyperlink ref="N52" r:id="rId43" xr:uid="{261E1E8E-F47F-4289-BF62-502EBD95F09F}"/>
+    <hyperlink ref="N53" r:id="rId44" xr:uid="{AB24E5A9-B84E-4111-AF5E-E34C09E843E1}"/>
+    <hyperlink ref="N54" r:id="rId45" xr:uid="{EDFD14C9-58C7-4A90-B75B-FC59C9904543}"/>
+    <hyperlink ref="N55" r:id="rId46" xr:uid="{8E651C69-068E-4974-ADB2-15F9B4A345D4}"/>
+    <hyperlink ref="N56" r:id="rId47" xr:uid="{A18B9D51-3CC3-4D1B-9058-7CA971B4FEFE}"/>
+    <hyperlink ref="N57" r:id="rId48" xr:uid="{8E77C782-7F4A-42D8-92A7-0BFBC59BA738}"/>
+    <hyperlink ref="N58" r:id="rId49" xr:uid="{CA2CD777-5B48-4197-8BC2-EA29ECCA712E}"/>
+    <hyperlink ref="N59" r:id="rId50" xr:uid="{AE407265-FFC4-46BB-93E7-CA28E7C79B51}"/>
+    <hyperlink ref="N60" r:id="rId51" xr:uid="{D1ABB082-15BB-4AED-898A-4AA0318E41E8}"/>
+    <hyperlink ref="N61" r:id="rId52" xr:uid="{6E735788-6EA0-4AA4-ABD5-7442AE5349E8}"/>
+    <hyperlink ref="N63" r:id="rId53" xr:uid="{447B777D-195D-4187-AAE8-49E99E1CF92C}"/>
+    <hyperlink ref="N64" r:id="rId54" xr:uid="{509290E1-ADB3-4AE8-8B32-6871C3695877}"/>
+    <hyperlink ref="N69" r:id="rId55" xr:uid="{4E89D73A-3539-49AB-BCA0-7FD61E2EB35E}"/>
+    <hyperlink ref="N70" r:id="rId56" xr:uid="{B0A9DB4B-DF72-4520-BCE3-687191D9D821}"/>
+    <hyperlink ref="N71" r:id="rId57" xr:uid="{89F72D93-D0F3-4AD7-B7AE-FFB219591847}"/>
+    <hyperlink ref="N46" r:id="rId58" xr:uid="{3CDF5DDE-CFB7-40D2-A90E-1CB75F3BF644}"/>
+    <hyperlink ref="N65" r:id="rId59" xr:uid="{A60638F8-A009-4A91-A7C2-0B801C25F02F}"/>
+    <hyperlink ref="N72" r:id="rId60" xr:uid="{52CF0C58-75BA-4046-9CD9-89BFCD44489C}"/>
+    <hyperlink ref="N66" r:id="rId61" xr:uid="{E1FD5A46-89A7-4F84-B3EB-8E515029A5E6}"/>
+    <hyperlink ref="N67" r:id="rId62" xr:uid="{DF8DA8DD-7196-428B-9BEE-5EC17E5E3690}"/>
+    <hyperlink ref="N48" r:id="rId63" xr:uid="{751E1192-0D7C-45E0-98D0-88F9D9DC41A2}"/>
+    <hyperlink ref="N62" r:id="rId64" xr:uid="{9627C054-F53B-4951-A867-1CAFF03E890D}"/>
+    <hyperlink ref="N19" r:id="rId65" xr:uid="{1123F2A3-16A8-4665-98B1-23C12A68992A}"/>
+    <hyperlink ref="N32" r:id="rId66" xr:uid="{EDBF908D-B2E5-4842-9B28-34C8FC582098}"/>
+    <hyperlink ref="N18" r:id="rId67" xr:uid="{C2DE4F44-173C-4C5D-A20F-26B05F5CDB39}"/>
+    <hyperlink ref="N27" r:id="rId68" xr:uid="{A1A7852A-81C9-412F-AF54-C68B5936B6A5}"/>
+    <hyperlink ref="N17" r:id="rId69" xr:uid="{D0B249A0-F7A7-4C00-861A-973769BA5767}"/>
+    <hyperlink ref="N68" r:id="rId70" xr:uid="{FAD23788-5072-4C11-BAE0-284EDC71C04C}"/>
+    <hyperlink ref="N50" r:id="rId71" xr:uid="{2332F014-1F3A-43A5-A75B-A98D5C4F609C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId68"/>
+    <tablePart r:id="rId72"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Claude\Projects\Presentaciones de Quarter\Github Pagina\Bonos-FCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B1B998-071F-40EA-8800-7147CC2DB9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B7A19F-E3E0-4D41-BAA0-A222D0D9E8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -17,6 +17,7 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3472,26 +3473,3122 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="bonos"/>
+      <sheetName val="acciones"/>
+      <sheetName val="índices"/>
+      <sheetName val="etf &amp; funds"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>94.795000000000002</v>
+          </cell>
+          <cell r="K2">
+            <v>4.8898341721933001</v>
+          </cell>
+          <cell r="AG2" t="str">
+            <v>USU81522AD31</v>
+          </cell>
+          <cell r="AP2">
+            <v>80.942813493852995</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="H3">
+            <v>100</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v/>
+          </cell>
+          <cell r="AG3" t="str">
+            <v>XS1134541561</v>
+          </cell>
+          <cell r="AP3" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>98.9</v>
+          </cell>
+          <cell r="K4">
+            <v>5.1857528710981997</v>
+          </cell>
+          <cell r="AG4" t="str">
+            <v>XS1636266832</v>
+          </cell>
+          <cell r="AP4">
+            <v>112.49941078243999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>98.6</v>
+          </cell>
+          <cell r="K5">
+            <v>7.4004697437736002</v>
+          </cell>
+          <cell r="AG5" t="str">
+            <v>USL00849AA47</v>
+          </cell>
+          <cell r="AP5">
+            <v>333.53763720927998</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>99.5</v>
+          </cell>
+          <cell r="K6">
+            <v>4.3908531690574</v>
+          </cell>
+          <cell r="AG6" t="str">
+            <v>US00774MAV72</v>
+          </cell>
+          <cell r="AP6">
+            <v>35.044994044577003</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>99.905000000000001</v>
+          </cell>
+          <cell r="K7">
+            <v>4.7551093516370004</v>
+          </cell>
+          <cell r="AG7" t="str">
+            <v>US00774MAR60</v>
+          </cell>
+          <cell r="AP7">
+            <v>68.730736098094994</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="H8">
+            <v>99.915000000000006</v>
+          </cell>
+          <cell r="K8">
+            <v>5.3134796696329998</v>
+          </cell>
+          <cell r="AG8" t="str">
+            <v>USC01026BC38</v>
+          </cell>
+          <cell r="AP8">
+            <v>127.74388585951</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="H9">
+            <v>94.102000000000004</v>
+          </cell>
+          <cell r="K9">
+            <v>5.0342310397633003</v>
+          </cell>
+          <cell r="AG9" t="str">
+            <v>US02005NBP42</v>
+          </cell>
+          <cell r="AP9">
+            <v>92.363190210389007</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="H10">
+            <v>103.25</v>
+          </cell>
+          <cell r="K10">
+            <v>5.2262981503403001</v>
+          </cell>
+          <cell r="AG10" t="str">
+            <v>US02005NBT63</v>
+          </cell>
+          <cell r="AP10">
+            <v>113.49555342230001</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="H11">
+            <v>98.2</v>
+          </cell>
+          <cell r="K11">
+            <v>6.0892206099960999</v>
+          </cell>
+          <cell r="AG11" t="str">
+            <v>US04010LBK89</v>
+          </cell>
+          <cell r="AP11">
+            <v>190.23409560722999</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="H12">
+            <v>100.52500000000001</v>
+          </cell>
+          <cell r="K12">
+            <v>5.8378605733628</v>
+          </cell>
+          <cell r="AG12" t="str">
+            <v>US04010LBG77</v>
+          </cell>
+          <cell r="AP12">
+            <v>169.98240628127999</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="H13">
+            <v>87.075000000000003</v>
+          </cell>
+          <cell r="K13">
+            <v>8.1009002179056004</v>
+          </cell>
+          <cell r="AG13" t="str">
+            <v>US040114HS26</v>
+          </cell>
+          <cell r="AP13">
+            <v>399.57906669957998</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="H14">
+            <v>89.165000000000006</v>
+          </cell>
+          <cell r="K14">
+            <v>8.1715518170997008</v>
+          </cell>
+          <cell r="AG14" t="str">
+            <v>US040114HX11</v>
+          </cell>
+          <cell r="AP14">
+            <v>408.62989790303999</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="H15">
+            <v>79.185000000000002</v>
+          </cell>
+          <cell r="K15">
+            <v>9.2460530465932003</v>
+          </cell>
+          <cell r="AG15" t="str">
+            <v>US040114HT09</v>
+          </cell>
+          <cell r="AP15">
+            <v>493.38428751606</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="H16">
+            <v>56.16</v>
+          </cell>
+          <cell r="K16">
+            <v>35.215320050537997</v>
+          </cell>
+          <cell r="AG16" t="str">
+            <v>ARARGE3209S6</v>
+          </cell>
+          <cell r="AP16">
+            <v>3112.2784590568999</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="H17">
+            <v>77.628</v>
+          </cell>
+          <cell r="K17">
+            <v>9.6334393432876997</v>
+          </cell>
+          <cell r="AG17" t="str">
+            <v>ARARGE3209T4</v>
+          </cell>
+          <cell r="AP17">
+            <v>532.23688399647995</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="H18">
+            <v>99.626999999999995</v>
+          </cell>
+          <cell r="K18">
+            <v>4.7078388653495997</v>
+          </cell>
+          <cell r="AG18" t="str">
+            <v>AU3CB0236776</v>
+          </cell>
+          <cell r="AP18" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="H19">
+            <v>82.512500000000003</v>
+          </cell>
+          <cell r="K19">
+            <v>4.8183716353805996</v>
+          </cell>
+          <cell r="AG19" t="str">
+            <v>AU0000101792</v>
+          </cell>
+          <cell r="AP19" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="H20">
+            <v>48.831000000000003</v>
+          </cell>
+          <cell r="K20">
+            <v>5.6807205664540001</v>
+          </cell>
+          <cell r="AG20" t="str">
+            <v>AU0000097495</v>
+          </cell>
+          <cell r="AP20" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="H21">
+            <v>100.05</v>
+          </cell>
+          <cell r="K21">
+            <v>5.7761295322102999</v>
+          </cell>
+          <cell r="AG21" t="str">
+            <v>USU05375AS64</v>
+          </cell>
+          <cell r="AP21">
+            <v>171.61428222468001</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="H22">
+            <v>99.89</v>
+          </cell>
+          <cell r="K22">
+            <v>4.4478558571078004</v>
+          </cell>
+          <cell r="AG22" t="str">
+            <v>US05964HAB15</v>
+          </cell>
+          <cell r="AP22">
+            <v>39.59677205517</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="H23">
+            <v>101.75</v>
+          </cell>
+          <cell r="K23">
+            <v>5.4898642956866999</v>
+          </cell>
+          <cell r="AG23" t="str">
+            <v>US05968LAK89</v>
+          </cell>
+          <cell r="AP23">
+            <v>142.23114590387999</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="H24">
+            <v>99.342500000000001</v>
+          </cell>
+          <cell r="K24">
+            <v>4.7473948260665999</v>
+          </cell>
+          <cell r="AG24" t="str">
+            <v>US06051GGC78</v>
+          </cell>
+          <cell r="AP24">
+            <v>67.542521159898996</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="H25">
+            <v>99.412000000000006</v>
+          </cell>
+          <cell r="K25">
+            <v>4.8129105742923004</v>
+          </cell>
+          <cell r="AG25" t="str">
+            <v>US06738EAU91</v>
+          </cell>
+          <cell r="AP25">
+            <v>73.623480706421006</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="H26">
+            <v>53.604999999999997</v>
+          </cell>
+          <cell r="K26">
+            <v>61.799509103391003</v>
+          </cell>
+          <cell r="AG26" t="str">
+            <v>USN15516AB83</v>
+          </cell>
+          <cell r="AP26">
+            <v>5772.3409564223002</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="H27">
+            <v>99.575000000000003</v>
+          </cell>
+          <cell r="K27">
+            <v>6.1636266314597004</v>
+          </cell>
+          <cell r="AG27" t="str">
+            <v>US105756CF53</v>
+          </cell>
+          <cell r="AP27">
+            <v>183.23384875427001</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="H28">
+            <v>112.17</v>
+          </cell>
+          <cell r="K28">
+            <v>6.2906562882369998</v>
+          </cell>
+          <cell r="AG28" t="str">
+            <v>US105756BB58</v>
+          </cell>
+          <cell r="AP28">
+            <v>196.23823851303999</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="H29">
+            <v>90.408500000000004</v>
+          </cell>
+          <cell r="K29">
+            <v>5.1195611694260004</v>
+          </cell>
+          <cell r="AG29" t="str">
+            <v>US05526DBS36</v>
+          </cell>
+          <cell r="AP29">
+            <v>88.923315379433006</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="H30">
+            <v>98.137500000000003</v>
+          </cell>
+          <cell r="K30">
+            <v>5.1903522881253998</v>
+          </cell>
+          <cell r="AG30" t="str">
+            <v>US05526DBW48</v>
+          </cell>
+          <cell r="AP30">
+            <v>92.336058409939</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="H31">
+            <v>106.345</v>
+          </cell>
+          <cell r="K31">
+            <v>5.3970440982665</v>
+          </cell>
+          <cell r="AG31" t="str">
+            <v>US054989AB41</v>
+          </cell>
+          <cell r="AP31">
+            <v>108.21583503986</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="H32">
+            <v>99.845399999999998</v>
+          </cell>
+          <cell r="K32">
+            <v>4.4347616593610004</v>
+          </cell>
+          <cell r="AG32" t="str">
+            <v>US254709AM01</v>
+          </cell>
+          <cell r="AP32">
+            <v>38.770182521099997</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="H33">
+            <v>86.842500000000001</v>
+          </cell>
+          <cell r="K33">
+            <v>5.8792735535786003</v>
+          </cell>
+          <cell r="AG33" t="str">
+            <v>US15135BAX91</v>
+          </cell>
+          <cell r="AP33">
+            <v>165.20963267785999</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="H34">
+            <v>90.164500000000004</v>
+          </cell>
+          <cell r="K34">
+            <v>5.7259922256740001</v>
+          </cell>
+          <cell r="AG34" t="str">
+            <v>US15135BAW19</v>
+          </cell>
+          <cell r="AP34">
+            <v>152.08590784775001</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="H35">
+            <v>99.36</v>
+          </cell>
+          <cell r="K35">
+            <v>4.7825014422559997</v>
+          </cell>
+          <cell r="AG35" t="str">
+            <v>US15135BAR24</v>
+          </cell>
+          <cell r="AP35">
+            <v>70.846265349839001</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="H36">
+            <v>94.405000000000001</v>
+          </cell>
+          <cell r="K36">
+            <v>6.6349128086422002</v>
+          </cell>
+          <cell r="AG36" t="str">
+            <v>USU16309AJ22</v>
+          </cell>
+          <cell r="AP36">
+            <v>248.06042214619001</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="H37">
+            <v>100.625</v>
+          </cell>
+          <cell r="K37">
+            <v>4.8534507717641002</v>
+          </cell>
+          <cell r="AG37" t="str">
+            <v>US163851AE83</v>
+          </cell>
+          <cell r="AP37">
+            <v>99.653817680819998</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="H38">
+            <v>99.14</v>
+          </cell>
+          <cell r="K38">
+            <v>6.2446701815574999</v>
+          </cell>
+          <cell r="AG38" t="str">
+            <v>USU16309AH65</v>
+          </cell>
+          <cell r="AP38">
+            <v>213.61638444050001</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="H39">
+            <v>102.50449999999999</v>
+          </cell>
+          <cell r="K39">
+            <v>5.8064577333980996</v>
+          </cell>
+          <cell r="AG39" t="str">
+            <v>US17327CAR43</v>
+          </cell>
+          <cell r="AP39">
+            <v>149.16769989029001</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="H40">
+            <v>99.97</v>
+          </cell>
+          <cell r="K40">
+            <v>5.1257544897673997</v>
+          </cell>
+          <cell r="AG40" t="str">
+            <v>USU09784AC02</v>
+          </cell>
+          <cell r="AP40">
+            <v>139.97638675799999</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="H41">
+            <v>102.38549999999999</v>
+          </cell>
+          <cell r="K41">
+            <v>7.1566025866339</v>
+          </cell>
+          <cell r="AG41" t="str">
+            <v>USU1638HAA50</v>
+          </cell>
+          <cell r="AP41">
+            <v>306.39095720713999</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="H42">
+            <v>84.625</v>
+          </cell>
+          <cell r="K42">
+            <v>14.00107155779</v>
+          </cell>
+          <cell r="AG42" t="str">
+            <v>USU18510AE44</v>
+          </cell>
+          <cell r="AP42">
+            <v>990.35448851802005</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="H43">
+            <v>99.614999999999995</v>
+          </cell>
+          <cell r="K43">
+            <v>6.9211017911116999</v>
+          </cell>
+          <cell r="AG43" t="str">
+            <v>US20602DAB73</v>
+          </cell>
+          <cell r="AP43">
+            <v>282.63788339886997</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="H44">
+            <v>96.625</v>
+          </cell>
+          <cell r="K44">
+            <v>5.6884236132800998</v>
+          </cell>
+          <cell r="AG44" t="str">
+            <v>USU23888AE71</v>
+          </cell>
+          <cell r="AP44">
+            <v>150.74440510137001</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="H45">
+            <v>77.144999999999996</v>
+          </cell>
+          <cell r="K45">
+            <v>11.449925268537999</v>
+          </cell>
+          <cell r="AG45" t="str">
+            <v>US25470DCC11</v>
+          </cell>
+          <cell r="AP45">
+            <v>726.99066616861001</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="H46">
+            <v>91.35</v>
+          </cell>
+          <cell r="K46">
+            <v>6.2060902779280003</v>
+          </cell>
+          <cell r="AG46" t="str">
+            <v>US55903VBQ59</v>
+          </cell>
+          <cell r="AP46">
+            <v>193.71209862641001</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="H47">
+            <v>92.59</v>
+          </cell>
+          <cell r="K47">
+            <v>5.4655897091694996</v>
+          </cell>
+          <cell r="AG47" t="str">
+            <v>USU2689EAB66</v>
+          </cell>
+          <cell r="AP47">
+            <v>123.21302337231</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="H48">
+            <v>105.5663</v>
+          </cell>
+          <cell r="K48">
+            <v>5.3167478739792999</v>
+          </cell>
+          <cell r="AG48" t="str">
+            <v>US26884LAG41</v>
+          </cell>
+          <cell r="AP48">
+            <v>116.12869134604</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="H49">
+            <v>99.096599999999995</v>
+          </cell>
+          <cell r="K49">
+            <v>4.9684822597879998</v>
+          </cell>
+          <cell r="AG49" t="str">
+            <v>US277432AW04</v>
+          </cell>
+          <cell r="AP49">
+            <v>85.654212702403001</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="H50">
+            <v>97.14</v>
+          </cell>
+          <cell r="K50">
+            <v>5.2775961551588999</v>
+          </cell>
+          <cell r="AG50" t="str">
+            <v>US277432BB57</v>
+          </cell>
+          <cell r="AP50">
+            <v>106.35347008796001</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="H51">
+            <v>99.944999999999993</v>
+          </cell>
+          <cell r="K51">
+            <v>5.0823082063419003</v>
+          </cell>
+          <cell r="AG51" t="str">
+            <v>US277432AZ35</v>
+          </cell>
+          <cell r="AP51">
+            <v>94.394347920116005</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="H52">
+            <v>106.017</v>
+          </cell>
+          <cell r="K52">
+            <v>6.0768609608236996</v>
+          </cell>
+          <cell r="AG52" t="str">
+            <v>US279158AT64</v>
+          </cell>
+          <cell r="AP52">
+            <v>196.25440799008001</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="H53">
+            <v>102.9</v>
+          </cell>
+          <cell r="K53">
+            <v>5.6258500906032998</v>
+          </cell>
+          <cell r="AG53" t="str">
+            <v>US29082HAE27</v>
+          </cell>
+          <cell r="AP53">
+            <v>123.99159377725</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="H54">
+            <v>108.4</v>
+          </cell>
+          <cell r="K54">
+            <v>4.8028528899121001</v>
+          </cell>
+          <cell r="AG54" t="str">
+            <v>USN29505AB53</v>
+          </cell>
+          <cell r="AP54">
+            <v>76.010527540115007</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="H55">
+            <v>100.03</v>
+          </cell>
+          <cell r="K55">
+            <v>4.9154254315666996</v>
+          </cell>
+          <cell r="AG55" t="str">
+            <v>US29278DAA37</v>
+          </cell>
+          <cell r="AP55">
+            <v>82.304527828741001</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="H56">
+            <v>96.6</v>
+          </cell>
+          <cell r="K56">
+            <v>5.5462448562795998</v>
+          </cell>
+          <cell r="AG56" t="str">
+            <v>US845467AT68</v>
+          </cell>
+          <cell r="AP56">
+            <v>128.79822976643001</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="H57">
+            <v>97.866249999999994</v>
+          </cell>
+          <cell r="K57">
+            <v>6.4017870851897998</v>
+          </cell>
+          <cell r="AG57" t="str">
+            <v>USU84517AC25</v>
+          </cell>
+          <cell r="AP57">
+            <v>228.58962701914001</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="H58">
+            <v>99.981999999999999</v>
+          </cell>
+          <cell r="K58">
+            <v>5.4545154701668004</v>
+          </cell>
+          <cell r="AG58" t="str">
+            <v>US845467AR03</v>
+          </cell>
+          <cell r="AP58">
+            <v>133.84872855536</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="H59">
+            <v>99.394999999999996</v>
+          </cell>
+          <cell r="K59">
+            <v>5.8749240448719</v>
+          </cell>
+          <cell r="AG59" t="str">
+            <v>US165167DH73</v>
+          </cell>
+          <cell r="AP59">
+            <v>147.81754548412999</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="H60">
+            <v>100</v>
+          </cell>
+          <cell r="K60">
+            <v>5.9570770289033002</v>
+          </cell>
+          <cell r="AG60" t="str">
+            <v>USU16450BB00</v>
+          </cell>
+          <cell r="AP60">
+            <v>217.30190203868</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="H61">
+            <v>99.561999999999998</v>
+          </cell>
+          <cell r="K61">
+            <v>5.0459652692974997</v>
+          </cell>
+          <cell r="AG61" t="str">
+            <v>US302491AT29</v>
+          </cell>
+          <cell r="AP61">
+            <v>101.38411615989</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="H62">
+            <v>92.4816</v>
+          </cell>
+          <cell r="K62">
+            <v>6.1691679685506999</v>
+          </cell>
+          <cell r="AG62" t="str">
+            <v>US302491AU91</v>
+          </cell>
+          <cell r="AP62">
+            <v>201.85328135754</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="H63">
+            <v>89.665000000000006</v>
+          </cell>
+          <cell r="K63">
+            <v>5.6693575747171998</v>
+          </cell>
+          <cell r="AG63" t="str">
+            <v>USP3984LAA81</v>
+          </cell>
+          <cell r="AP63">
+            <v>139.69353136211001</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="H64">
+            <v>97.6</v>
+          </cell>
+          <cell r="K64">
+            <v>5.8138386217568003</v>
+          </cell>
+          <cell r="AG64" t="str">
+            <v>USP82290AR17</v>
+          </cell>
+          <cell r="AP64">
+            <v>174.43230620431001</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="H65">
+            <v>98.224999999999994</v>
+          </cell>
+          <cell r="K65">
+            <v>5.1978025665273</v>
+          </cell>
+          <cell r="AG65" t="str">
+            <v>US343412AF90</v>
+          </cell>
+          <cell r="AP65">
+            <v>109.54403223188</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="H66">
+            <v>99.853499999999997</v>
+          </cell>
+          <cell r="K66">
+            <v>4.4597400616087999</v>
+          </cell>
+          <cell r="AG66" t="str">
+            <v>US34540TNR94</v>
+          </cell>
+          <cell r="AP66">
+            <v>42.171916583030999</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="H67">
+            <v>100.54</v>
+          </cell>
+          <cell r="K67">
+            <v>5.2217860674756</v>
+          </cell>
+          <cell r="AG67" t="str">
+            <v>US345397E748</v>
+          </cell>
+          <cell r="AP67">
+            <v>116.70117695684</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="H68">
+            <v>102.745</v>
+          </cell>
+          <cell r="K68">
+            <v>5.5755940454813002</v>
+          </cell>
+          <cell r="AG68" t="str">
+            <v>US345397D591</v>
+          </cell>
+          <cell r="AP68">
+            <v>146.90426497843001</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="H69">
+            <v>99.831549999999993</v>
+          </cell>
+          <cell r="K69">
+            <v>4.8482022825154996</v>
+          </cell>
+          <cell r="AG69" t="str">
+            <v>US345370CR99</v>
+          </cell>
+          <cell r="AP69">
+            <v>80.523533755355004</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="H70">
+            <v>100.15</v>
+          </cell>
+          <cell r="K70">
+            <v>4.9840141275835004</v>
+          </cell>
+          <cell r="AG70" t="str">
+            <v>US37045VAS97</v>
+          </cell>
+          <cell r="AP70">
+            <v>88.034330463553005</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="H71">
+            <v>101.13500000000001</v>
+          </cell>
+          <cell r="K71">
+            <v>5.0747627537484998</v>
+          </cell>
+          <cell r="AG71" t="str">
+            <v>US37045VAY65</v>
+          </cell>
+          <cell r="AP71">
+            <v>92.635129430480006</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="H72">
+            <v>102.09399999999999</v>
+          </cell>
+          <cell r="K72">
+            <v>5.0174369973611004</v>
+          </cell>
+          <cell r="AG72" t="str">
+            <v>US37045VAU44</v>
+          </cell>
+          <cell r="AP72">
+            <v>95.152618110533993</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="H73">
+            <v>100.55</v>
+          </cell>
+          <cell r="K73">
+            <v>8.7479156676685008</v>
+          </cell>
+          <cell r="AG73" t="str">
+            <v>USG38327AD78</v>
+          </cell>
+          <cell r="AP73">
+            <v>459.86510364928</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="H74">
+            <v>97.279560000000004</v>
+          </cell>
+          <cell r="K74">
+            <v>5.5038780249519998</v>
+          </cell>
+          <cell r="AG74" t="str">
+            <v>USC39296AA34</v>
+          </cell>
+          <cell r="AP74">
+            <v>130.75487422077001</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="H75">
+            <v>96.317999999999998</v>
+          </cell>
+          <cell r="K75">
+            <v>6.0105975518405002</v>
+          </cell>
+          <cell r="AG75" t="str">
+            <v>USC39296AB17</v>
+          </cell>
+          <cell r="AP75">
+            <v>156.68037460471001</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="H76">
+            <v>25</v>
+          </cell>
+          <cell r="K76">
+            <v>84.183071575878003</v>
+          </cell>
+          <cell r="AG76" t="str">
+            <v>USU3826GAA59</v>
+          </cell>
+          <cell r="AP76">
+            <v>8050.2033254544003</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="H77">
+            <v>96.577600000000004</v>
+          </cell>
+          <cell r="K77">
+            <v>5.4958884088957003</v>
+          </cell>
+          <cell r="AG77" t="str">
+            <v>US436106AC21</v>
+          </cell>
+          <cell r="AP77">
+            <v>129.97234669082999</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="H78">
+            <v>99.830290000000005</v>
+          </cell>
+          <cell r="K78">
+            <v>5.6084038561996996</v>
+          </cell>
+          <cell r="AG78" t="str">
+            <v>US403949AT72</v>
+          </cell>
+          <cell r="AP78">
+            <v>132.64776343579999</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="H79">
+            <v>101.6</v>
+          </cell>
+          <cell r="K79">
+            <v>5.4144095584879999</v>
+          </cell>
+          <cell r="AG79" t="str">
+            <v>US403949AR17</v>
+          </cell>
+          <cell r="AP79">
+            <v>120.57510221228</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="H80">
+            <v>105.2</v>
+          </cell>
+          <cell r="K80">
+            <v>7.9082390117874999</v>
+          </cell>
+          <cell r="AG80" t="str">
+            <v>USU24437AG73</v>
+          </cell>
+          <cell r="AP80">
+            <v>439.38707483620999</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="H81">
+            <v>105.29</v>
+          </cell>
+          <cell r="K81">
+            <v>4.0278123846948004</v>
+          </cell>
+          <cell r="AG81" t="str">
+            <v>USU2465RAC52</v>
+          </cell>
+          <cell r="AP81">
+            <v>50.175595498462002</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="H82">
+            <v>97.075000000000003</v>
+          </cell>
+          <cell r="K82">
+            <v>6.2231615285378004</v>
+          </cell>
+          <cell r="AG82" t="str">
+            <v>USU4329KAA61</v>
+          </cell>
+          <cell r="AP82">
+            <v>209.00369911743999</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="H83">
+            <v>98.799000000000007</v>
+          </cell>
+          <cell r="K83">
+            <v>5.0774296035136004</v>
+          </cell>
+          <cell r="AG83" t="str">
+            <v>US46647PDF09</v>
+          </cell>
+          <cell r="AP83">
+            <v>94.157650321592996</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="H84">
+            <v>99.89</v>
+          </cell>
+          <cell r="K84">
+            <v>6.0411365730522997</v>
+          </cell>
+          <cell r="AG84" t="str">
+            <v>USG5002FAU06</v>
+          </cell>
+          <cell r="AP84">
+            <v>196.43375516239001</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="H85">
+            <v>99.814999999999998</v>
+          </cell>
+          <cell r="K85">
+            <v>6.0173203968370004</v>
+          </cell>
+          <cell r="AG85" t="str">
+            <v>USU5562LAH25</v>
+          </cell>
+          <cell r="AP85">
+            <v>185.23414711397001</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="H86">
+            <v>96.5</v>
+          </cell>
+          <cell r="K86">
+            <v>7.8425335089162003</v>
+          </cell>
+          <cell r="AG86" t="str">
+            <v>US577778BQ55</v>
+          </cell>
+          <cell r="AP86">
+            <v>359.51228942138999</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="H87">
+            <v>106.94</v>
+          </cell>
+          <cell r="K87">
+            <v>4.0562374651226003</v>
+          </cell>
+          <cell r="AG87" t="str">
+            <v>US55616XAC11</v>
+          </cell>
+          <cell r="AP87">
+            <v>43.068471953282</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="H88">
+            <v>99.744950000000003</v>
+          </cell>
+          <cell r="K88">
+            <v>4.8199978006009001</v>
+          </cell>
+          <cell r="AG88" t="str">
+            <v>US571903BB87</v>
+          </cell>
+          <cell r="AP88">
+            <v>70.819989140312998</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="H89">
+            <v>98.802350000000004</v>
+          </cell>
+          <cell r="K89">
+            <v>5.1835576186768</v>
+          </cell>
+          <cell r="AG89" t="str">
+            <v>USU5759TAC90</v>
+          </cell>
+          <cell r="AP89">
+            <v>108.51881434559</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="H90">
+            <v>99.984999999999999</v>
+          </cell>
+          <cell r="K90">
+            <v>3.4396145413841999</v>
+          </cell>
+          <cell r="AG90" t="str">
+            <v>USU57619AF25</v>
+          </cell>
+          <cell r="AP90">
+            <v>-31.650054489952002</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="H91">
+            <v>96.47</v>
+          </cell>
+          <cell r="K91">
+            <v>5.2374920160164997</v>
+          </cell>
+          <cell r="AG91" t="str">
+            <v>USU57619AG08</v>
+          </cell>
+          <cell r="AP91">
+            <v>111.06905121094999</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="H92">
+            <v>98.704999999999998</v>
+          </cell>
+          <cell r="K92">
+            <v>5.4091299597324998</v>
+          </cell>
+          <cell r="AG92" t="str">
+            <v>US577081BG67</v>
+          </cell>
+          <cell r="AP92">
+            <v>120.72910483749</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="H93">
+            <v>100.015</v>
+          </cell>
+          <cell r="K93">
+            <v>5.9442155867092001</v>
+          </cell>
+          <cell r="AG93" t="str">
+            <v>USU57619AE59</v>
+          </cell>
+          <cell r="AP93">
+            <v>187.06034786800001</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="H94">
+            <v>101.22</v>
+          </cell>
+          <cell r="K94">
+            <v>6.0798164504439001</v>
+          </cell>
+          <cell r="AG94" t="str">
+            <v>USU59224AA07</v>
+          </cell>
+          <cell r="AP94">
+            <v>182.48566773145001</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="H95">
+            <v>99.995000000000005</v>
+          </cell>
+          <cell r="K95">
+            <v>5.1881330347562997</v>
+          </cell>
+          <cell r="AG95" t="str">
+            <v>US59151KAM09</v>
+          </cell>
+          <cell r="AP95">
+            <v>112.04561605851001</v>
+          </cell>
+        </row>
+        <row r="96">
+          <cell r="H96">
+            <v>99.334999999999994</v>
+          </cell>
+          <cell r="K96">
+            <v>5.5401109236627999</v>
+          </cell>
+          <cell r="AG96" t="str">
+            <v>US59151KAL26</v>
+          </cell>
+          <cell r="AP96">
+            <v>138.23995836749</v>
+          </cell>
+        </row>
+        <row r="97">
+          <cell r="H97">
+            <v>101.80500000000001</v>
+          </cell>
+          <cell r="K97">
+            <v>4.9050583828213004</v>
+          </cell>
+          <cell r="AG97" t="str">
+            <v>US595112CD31</v>
+          </cell>
+          <cell r="AP97">
+            <v>69.431880707664007</v>
+          </cell>
+        </row>
+        <row r="98">
+          <cell r="H98">
+            <v>101.45</v>
+          </cell>
+          <cell r="K98">
+            <v>5.4450174366809998</v>
+          </cell>
+          <cell r="AG98" t="str">
+            <v>US595112CG61</v>
+          </cell>
+          <cell r="AP98">
+            <v>115.28441250944</v>
+          </cell>
+        </row>
+        <row r="99">
+          <cell r="H99">
+            <v>102.02</v>
+          </cell>
+          <cell r="K99">
+            <v>6.6785122790592002</v>
+          </cell>
+          <cell r="AG99" t="str">
+            <v>USQ60976AB51</v>
+          </cell>
+          <cell r="AP99">
+            <v>295.58820491820001</v>
+          </cell>
+        </row>
+        <row r="100">
+          <cell r="H100">
+            <v>92.135000000000005</v>
+          </cell>
+          <cell r="K100">
+            <v>6.0583846882100998</v>
+          </cell>
+          <cell r="AG100" t="str">
+            <v>USU60868AD52</v>
+          </cell>
+          <cell r="AP100">
+            <v>185.24321054836</v>
+          </cell>
+        </row>
+        <row r="101">
+          <cell r="H101">
+            <v>98.375</v>
+          </cell>
+          <cell r="K101">
+            <v>5.3547576737993001</v>
+          </cell>
+          <cell r="AG101" t="str">
+            <v>USU60868AC79</v>
+          </cell>
+          <cell r="AP101">
+            <v>126.1745027602</v>
+          </cell>
+        </row>
+        <row r="102">
+          <cell r="H102">
+            <v>99.224999999999994</v>
+          </cell>
+          <cell r="K102">
+            <v>5.2988830558807001</v>
+          </cell>
+          <cell r="AG102" t="str">
+            <v>US655664AS97</v>
+          </cell>
+          <cell r="AP102">
+            <v>124.9059765233</v>
+          </cell>
+        </row>
+        <row r="103">
+          <cell r="H103">
+            <v>95.935000000000002</v>
+          </cell>
+          <cell r="K103">
+            <v>5.6866903609593002</v>
+          </cell>
+          <cell r="AG103" t="str">
+            <v>US655664AT70</v>
+          </cell>
+          <cell r="AP103">
+            <v>151.45019039428001</v>
+          </cell>
+        </row>
+        <row r="104">
+          <cell r="H104">
+            <v>102.605</v>
+          </cell>
+          <cell r="K104">
+            <v>5.3389997638258997</v>
+          </cell>
+          <cell r="AG104" t="str">
+            <v>US655664AH33</v>
+          </cell>
+          <cell r="AP104">
+            <v>125.77745101456</v>
+          </cell>
+        </row>
+        <row r="105">
+          <cell r="H105">
+            <v>99.9</v>
+          </cell>
+          <cell r="K105">
+            <v>4.8816517612187997</v>
+          </cell>
+          <cell r="AG105" t="str">
+            <v>US674599CR48</v>
+          </cell>
+          <cell r="AP105">
+            <v>84.561095018073999</v>
+          </cell>
+        </row>
+        <row r="106">
+          <cell r="H106">
+            <v>100.65949999999999</v>
+          </cell>
+          <cell r="K106">
+            <v>5.3017698521792003</v>
+          </cell>
+          <cell r="AG106" t="str">
+            <v>US674599EK76</v>
+          </cell>
+          <cell r="AP106">
+            <v>104.48845243629</v>
+          </cell>
+        </row>
+        <row r="107">
+          <cell r="H107">
+            <v>100.35850000000001</v>
+          </cell>
+          <cell r="K107">
+            <v>5.5691708429039997</v>
+          </cell>
+          <cell r="AG107" t="str">
+            <v>US674599EL59</v>
+          </cell>
+          <cell r="AP107">
+            <v>118.94907886561001</v>
+          </cell>
+        </row>
+        <row r="108">
+          <cell r="H108">
+            <v>112</v>
+          </cell>
+          <cell r="K108">
+            <v>5.2534529008212996</v>
+          </cell>
+          <cell r="AG108" t="str">
+            <v>US674599DE26</v>
+          </cell>
+          <cell r="AP108">
+            <v>102.84299880966999</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="H109">
+            <v>97.375</v>
+          </cell>
+          <cell r="K109">
+            <v>5.9198386169269996</v>
+          </cell>
+          <cell r="AG109" t="str">
+            <v>US680665AK27</v>
+          </cell>
+          <cell r="AP109">
+            <v>175.90783354633001</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="H110">
+            <v>99.34</v>
+          </cell>
+          <cell r="K110">
+            <v>5.9529012337668004</v>
+          </cell>
+          <cell r="AG110" t="str">
+            <v>US680665AL00</v>
+          </cell>
+          <cell r="AP110">
+            <v>181.60886812977</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="H111">
+            <v>37.35</v>
+          </cell>
+          <cell r="K111">
+            <v>314.93117975012001</v>
+          </cell>
+          <cell r="AG111" t="str">
+            <v>XS0294364954</v>
+          </cell>
+          <cell r="AP111">
+            <v>31087.964580642001</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="H112">
+            <v>101.40499835097</v>
+          </cell>
+          <cell r="K112">
+            <v>3.7727843657881999</v>
+          </cell>
+          <cell r="AG112" t="str">
+            <v>AR0770773957</v>
+          </cell>
+          <cell r="AP112">
+            <v>-29.327093627549999</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="H113">
+            <v>103.55924658000001</v>
+          </cell>
+          <cell r="K113">
+            <v>4.6586168833709998</v>
+          </cell>
+          <cell r="AG113" t="str">
+            <v>AR0098578880</v>
+          </cell>
+          <cell r="AP113">
+            <v>55.042560673349001</v>
+          </cell>
+        </row>
+        <row r="114">
+          <cell r="H114">
+            <v>106.84006848999999</v>
+          </cell>
+          <cell r="K114">
+            <v>-1.5483801056004999E-3</v>
+          </cell>
+          <cell r="AG114" t="str">
+            <v>AR0554009248</v>
+          </cell>
+          <cell r="AP114">
+            <v>-406.29032526010002</v>
+          </cell>
+        </row>
+        <row r="115">
+          <cell r="H115">
+            <v>105.40396207006999</v>
+          </cell>
+          <cell r="K115">
+            <v>5.2005922944118002</v>
+          </cell>
+          <cell r="AG115" t="str">
+            <v>AR0623274765</v>
+          </cell>
+          <cell r="AP115">
+            <v>105.79305430166001</v>
+          </cell>
+        </row>
+        <row r="116">
+          <cell r="H116">
+            <v>98.744500000000002</v>
+          </cell>
+          <cell r="K116">
+            <v>5.5695677340319003</v>
+          </cell>
+          <cell r="AG116" t="str">
+            <v>US71647NBE85</v>
+          </cell>
+          <cell r="AP116">
+            <v>140.68770102907999</v>
+          </cell>
+        </row>
+        <row r="117">
+          <cell r="H117">
+            <v>100.045</v>
+          </cell>
+          <cell r="K117">
+            <v>5.6655276789892</v>
+          </cell>
+          <cell r="AG117" t="str">
+            <v>US71647NBH17</v>
+          </cell>
+          <cell r="AP117">
+            <v>145.84825050487001</v>
+          </cell>
+        </row>
+        <row r="118">
+          <cell r="H118">
+            <v>102.67163003648</v>
+          </cell>
+          <cell r="K118">
+            <v>4.2051064737701997</v>
+          </cell>
+          <cell r="AG118" t="str">
+            <v>AR0502588418</v>
+          </cell>
+          <cell r="AP118">
+            <v>12.76848700861</v>
+          </cell>
+        </row>
+        <row r="119">
+          <cell r="H119">
+            <v>104.09383561999999</v>
+          </cell>
+          <cell r="K119">
+            <v>4.8755731002726996</v>
+          </cell>
+          <cell r="AG119" t="str">
+            <v>AR0808016403</v>
+          </cell>
+          <cell r="AP119">
+            <v>79.056684616178003</v>
+          </cell>
+        </row>
+        <row r="120">
+          <cell r="H120">
+            <v>104.9675</v>
+          </cell>
+          <cell r="K120">
+            <v>7.5726415692896998</v>
+          </cell>
+          <cell r="AG120" t="str">
+            <v>USP7924AAA62</v>
+          </cell>
+          <cell r="AP120">
+            <v>332.01288130240999</v>
+          </cell>
+        </row>
+        <row r="121">
+          <cell r="H121">
+            <v>99.767499999999998</v>
+          </cell>
+          <cell r="K121">
+            <v>4.4523413550650002</v>
+          </cell>
+          <cell r="AG121" t="str">
+            <v>US80282KAZ93</v>
+          </cell>
+          <cell r="AP121">
+            <v>41.342591089473999</v>
+          </cell>
+        </row>
+        <row r="122">
+          <cell r="H122">
+            <v>99.9375</v>
+          </cell>
+          <cell r="K122">
+            <v>5.1261015299891</v>
+          </cell>
+          <cell r="AG122" t="str">
+            <v>USU82764AM01</v>
+          </cell>
+          <cell r="AP122">
+            <v>106.54769890657001</v>
+          </cell>
+        </row>
+        <row r="123">
+          <cell r="H123">
+            <v>99.54</v>
+          </cell>
+          <cell r="K123">
+            <v>4.6577610116169996</v>
+          </cell>
+          <cell r="AG123" t="str">
+            <v>USU82764AU27</v>
+          </cell>
+          <cell r="AP123">
+            <v>89.364821152114999</v>
+          </cell>
+        </row>
+        <row r="124">
+          <cell r="H124">
+            <v>97.27</v>
+          </cell>
+          <cell r="K124">
+            <v>5.5494499521960998</v>
+          </cell>
+          <cell r="AG124" t="str">
+            <v>USU82764AT53</v>
+          </cell>
+          <cell r="AP124">
+            <v>145.25790904621999</v>
+          </cell>
+        </row>
+        <row r="125">
+          <cell r="H125">
+            <v>94.394999999999996</v>
+          </cell>
+          <cell r="K125">
+            <v>7.2868473416138002</v>
+          </cell>
+          <cell r="AG125" t="str">
+            <v>USP8T88JAA61</v>
+          </cell>
+          <cell r="AP125">
+            <v>319.35177351455002</v>
+          </cell>
+        </row>
+        <row r="126">
+          <cell r="H126">
+            <v>89.334999999999994</v>
+          </cell>
+          <cell r="K126">
+            <v>5.3264553980798004</v>
+          </cell>
+          <cell r="AG126" t="str">
+            <v>US876030AA54</v>
+          </cell>
+          <cell r="AP126">
+            <v>104.58634938233</v>
+          </cell>
+        </row>
+        <row r="127">
+          <cell r="H127">
+            <v>99.476650000000006</v>
+          </cell>
+          <cell r="K127">
+            <v>4.7326289506507004</v>
+          </cell>
+          <cell r="AG127" t="str">
+            <v>US189754AC88</v>
+          </cell>
+          <cell r="AP127">
+            <v>67.260736242627999</v>
+          </cell>
+        </row>
+        <row r="128">
+          <cell r="H128">
+            <v>99.87</v>
+          </cell>
+          <cell r="K128">
+            <v>5.2037364813230003</v>
+          </cell>
+          <cell r="AG128" t="str">
+            <v>US876030AK37</v>
+          </cell>
+          <cell r="AP128">
+            <v>103.67747756588</v>
+          </cell>
+        </row>
+        <row r="129">
+          <cell r="H129">
+            <v>98.7</v>
+          </cell>
+          <cell r="K129">
+            <v>5.7725722026141</v>
+          </cell>
+          <cell r="AG129" t="str">
+            <v>US876030AL10</v>
+          </cell>
+          <cell r="AP129">
+            <v>137.50043898965001</v>
+          </cell>
+        </row>
+        <row r="130">
+          <cell r="H130">
+            <v>102.06712329</v>
+          </cell>
+          <cell r="K130">
+            <v>3.3277119984754</v>
+          </cell>
+          <cell r="AG130" t="str">
+            <v>AR0166027471</v>
+          </cell>
+          <cell r="AP130">
+            <v>-74.098228104897004</v>
+          </cell>
+        </row>
+        <row r="131">
+          <cell r="H131">
+            <v>104.32328767</v>
+          </cell>
+          <cell r="K131">
+            <v>5.4038473028715002</v>
+          </cell>
+          <cell r="AG131" t="str">
+            <v>AR0482976963</v>
+          </cell>
+          <cell r="AP131">
+            <v>125.68837867076</v>
+          </cell>
+        </row>
+        <row r="132">
+          <cell r="H132">
+            <v>103.9</v>
+          </cell>
+          <cell r="K132">
+            <v>6.8760196346331002</v>
+          </cell>
+          <cell r="AG132" t="str">
+            <v>USP90187AR99</v>
+          </cell>
+          <cell r="AP132">
+            <v>263.05651325325999</v>
+          </cell>
+        </row>
+        <row r="133">
+          <cell r="H133">
+            <v>99.75</v>
+          </cell>
+          <cell r="K133">
+            <v>4.8148080816137</v>
+          </cell>
+          <cell r="AG133" t="str">
+            <v>US87901JAJ43</v>
+          </cell>
+          <cell r="AP133">
+            <v>112.11380291259999</v>
+          </cell>
+        </row>
+        <row r="134">
+          <cell r="H134">
+            <v>99.962500000000006</v>
+          </cell>
+          <cell r="K134">
+            <v>4.8861631155782002</v>
+          </cell>
+          <cell r="AG134" t="str">
+            <v>USU8729JAC28</v>
+          </cell>
+          <cell r="AP134">
+            <v>108.26361325459</v>
+          </cell>
+        </row>
+        <row r="135">
+          <cell r="H135">
+            <v>105.845</v>
+          </cell>
+          <cell r="K135">
+            <v>7.2174107235134004</v>
+          </cell>
+          <cell r="AG135" t="str">
+            <v>USP9308RBA07</v>
+          </cell>
+          <cell r="AP135">
+            <v>300.67708168923002</v>
+          </cell>
+        </row>
+        <row r="136">
+          <cell r="H136">
+            <v>95.531999999999996</v>
+          </cell>
+          <cell r="K136">
+            <v>4.3204311882243998</v>
+          </cell>
+          <cell r="AG136" t="str">
+            <v>US91282CAL54</v>
+          </cell>
+          <cell r="AP136">
+            <v>25.291548261117001</v>
+          </cell>
+        </row>
+        <row r="137">
+          <cell r="H137">
+            <v>96.171999999999997</v>
+          </cell>
+          <cell r="K137">
+            <v>4.2950017077747997</v>
+          </cell>
+          <cell r="AG137" t="str">
+            <v>US91282CAD39</v>
+          </cell>
+          <cell r="AP137">
+            <v>23.327443611955001</v>
+          </cell>
+        </row>
+        <row r="138">
+          <cell r="H138">
+            <v>97.278499999999994</v>
+          </cell>
+          <cell r="K138">
+            <v>4.1708283830494004</v>
+          </cell>
+          <cell r="AG138" t="str">
+            <v>US912828ZN34</v>
+          </cell>
+          <cell r="AP138">
+            <v>11.708528741441</v>
+          </cell>
+        </row>
+        <row r="139">
+          <cell r="H139">
+            <v>95.340500000000006</v>
+          </cell>
+          <cell r="K139">
+            <v>4.3423253078339004</v>
+          </cell>
+          <cell r="AG139" t="str">
+            <v>US91282CAU53</v>
+          </cell>
+          <cell r="AP139">
+            <v>27.176614941072</v>
+          </cell>
+        </row>
+        <row r="140">
+          <cell r="H140">
+            <v>99.944500000000005</v>
+          </cell>
+          <cell r="K140">
+            <v>3.0608197011731999</v>
+          </cell>
+          <cell r="AG140" t="str">
+            <v>US91282CCP41</v>
+          </cell>
+          <cell r="AP140">
+            <v>-97.446929748656999</v>
+          </cell>
+        </row>
+        <row r="141">
+          <cell r="H141">
+            <v>94.780500000000004</v>
+          </cell>
+          <cell r="K141">
+            <v>4.3796505444385003</v>
+          </cell>
+          <cell r="AG141" t="str">
+            <v>US91282CBJ99</v>
+          </cell>
+          <cell r="AP141">
+            <v>29.975939736948</v>
+          </cell>
+        </row>
+        <row r="142">
+          <cell r="H142">
+            <v>93.534499999999994</v>
+          </cell>
+          <cell r="K142">
+            <v>4.4406962798284004</v>
+          </cell>
+          <cell r="AG142" t="str">
+            <v>US91282CCY57</v>
+          </cell>
+          <cell r="AP142">
+            <v>33.318192693989999</v>
+          </cell>
+        </row>
+        <row r="143">
+          <cell r="H143">
+            <v>91.9345</v>
+          </cell>
+          <cell r="K143">
+            <v>4.4568924684192002</v>
+          </cell>
+          <cell r="AG143" t="str">
+            <v>US912828YS30</v>
+          </cell>
+          <cell r="AP143">
+            <v>29.488010903976999</v>
+          </cell>
+        </row>
+        <row r="144">
+          <cell r="H144">
+            <v>99.420500000000004</v>
+          </cell>
+          <cell r="K144">
+            <v>3.9138245018361002</v>
+          </cell>
+          <cell r="AG144" t="str">
+            <v>US912828U246</v>
+          </cell>
+          <cell r="AP144">
+            <v>-12.764148223207</v>
+          </cell>
+        </row>
+        <row r="145">
+          <cell r="H145">
+            <v>99.377499999999998</v>
+          </cell>
+          <cell r="K145">
+            <v>4.3726187170564996</v>
+          </cell>
+          <cell r="AG145" t="str">
+            <v>US91282CGC91</v>
+          </cell>
+          <cell r="AP145">
+            <v>29.670021055751999</v>
+          </cell>
+        </row>
+        <row r="146">
+          <cell r="H146">
+            <v>97.739000000000004</v>
+          </cell>
+          <cell r="K146">
+            <v>4.5930821551605003</v>
+          </cell>
+          <cell r="AG146" t="str">
+            <v>US91282CFV81</v>
+          </cell>
+          <cell r="AP146">
+            <v>28.394678126346001</v>
+          </cell>
+        </row>
+        <row r="147">
+          <cell r="H147">
+            <v>100.27500000000001</v>
+          </cell>
+          <cell r="K147">
+            <v>4.1518552074799997</v>
+          </cell>
+          <cell r="AG147" t="str">
+            <v>US91282CKJ98</v>
+          </cell>
+          <cell r="AP147">
+            <v>9.9627229493212006</v>
+          </cell>
+        </row>
+        <row r="148">
+          <cell r="H148">
+            <v>95.647949999999994</v>
+          </cell>
+          <cell r="K148">
+            <v>4.2746687859305998</v>
+          </cell>
+          <cell r="AG148" t="str">
+            <v>US912803BL66</v>
+          </cell>
+          <cell r="AP148">
+            <v>21.145156672112002</v>
+          </cell>
+        </row>
+        <row r="149">
+          <cell r="H149">
+            <v>87.520949999999999</v>
+          </cell>
+          <cell r="K149">
+            <v>4.4561149730535003</v>
+          </cell>
+          <cell r="AG149" t="str">
+            <v>US912803CG62</v>
+          </cell>
+          <cell r="AP149">
+            <v>30.271816817544</v>
+          </cell>
+        </row>
+        <row r="150">
+          <cell r="H150">
+            <v>87.582849999999993</v>
+          </cell>
+          <cell r="K150">
+            <v>4.4319626034484001</v>
+          </cell>
+          <cell r="AG150" t="str">
+            <v>US912821CR42</v>
+          </cell>
+          <cell r="AP150">
+            <v>27.856579857042</v>
+          </cell>
+        </row>
+        <row r="151">
+          <cell r="H151">
+            <v>65.109849999999994</v>
+          </cell>
+          <cell r="K151" t="str">
+            <v/>
+          </cell>
+          <cell r="AG151" t="str">
+            <v>US9128335A44</v>
+          </cell>
+          <cell r="AP151" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="152">
+          <cell r="H152">
+            <v>35.597050000000003</v>
+          </cell>
+          <cell r="K152">
+            <v>5.5794200968601997</v>
+          </cell>
+          <cell r="AG152" t="str">
+            <v>US912834PM47</v>
+          </cell>
+          <cell r="AP152">
+            <v>46.684802720238999</v>
+          </cell>
+        </row>
+        <row r="153">
+          <cell r="H153">
+            <v>97.774100000000004</v>
+          </cell>
+          <cell r="K153">
+            <v>4.0490644002825</v>
+          </cell>
+          <cell r="AG153" t="str">
+            <v>US912803BK83</v>
+          </cell>
+          <cell r="AP153">
+            <v>0.11176213578805</v>
+          </cell>
+        </row>
+        <row r="154">
+          <cell r="H154">
+            <v>85.558949999999996</v>
+          </cell>
+          <cell r="K154">
+            <v>4.4782707797818997</v>
+          </cell>
+          <cell r="AG154" t="str">
+            <v>US912821DV45</v>
+          </cell>
+          <cell r="AP154">
+            <v>29.649496642170998</v>
+          </cell>
+        </row>
+        <row r="155">
+          <cell r="H155">
+            <v>28.710899999999999</v>
+          </cell>
+          <cell r="K155">
+            <v>5.4491502075203</v>
+          </cell>
+          <cell r="AG155" t="str">
+            <v>US912803FM04</v>
+          </cell>
+          <cell r="AP155">
+            <v>21.965821396532998</v>
+          </cell>
+        </row>
+        <row r="156">
+          <cell r="H156">
+            <v>25.98865</v>
+          </cell>
+          <cell r="K156">
+            <v>5.4234852564409</v>
+          </cell>
+          <cell r="AG156" t="str">
+            <v>US912803GE78</v>
+          </cell>
+          <cell r="AP156">
+            <v>16.955639475342</v>
+          </cell>
+        </row>
+        <row r="157">
+          <cell r="H157">
+            <v>23.150849999999998</v>
+          </cell>
+          <cell r="K157">
+            <v>5.4623580009020003</v>
+          </cell>
+          <cell r="AG157" t="str">
+            <v>US912834K567</v>
+          </cell>
+          <cell r="AP157">
+            <v>19.950063914238999</v>
+          </cell>
+        </row>
+        <row r="158">
+          <cell r="H158">
+            <v>22.81495</v>
+          </cell>
+          <cell r="K158">
+            <v>5.3203124155137997</v>
+          </cell>
+          <cell r="AG158" t="str">
+            <v>US912803HH90</v>
+          </cell>
+          <cell r="AP158">
+            <v>5.8441193336003003</v>
+          </cell>
+        </row>
+        <row r="159">
+          <cell r="H159">
+            <v>92.447999999999993</v>
+          </cell>
+          <cell r="K159">
+            <v>4.4369646724892</v>
+          </cell>
+          <cell r="AG159" t="str">
+            <v>US9128205B99</v>
+          </cell>
+          <cell r="AP159">
+            <v>34.489050271147001</v>
+          </cell>
+        </row>
+        <row r="160">
+          <cell r="H160">
+            <v>84.616</v>
+          </cell>
+          <cell r="K160">
+            <v>4.4900631138992004</v>
+          </cell>
+          <cell r="AG160" t="str">
+            <v>US912803CH46</v>
+          </cell>
+          <cell r="AP160">
+            <v>29.393632382789999</v>
+          </cell>
+        </row>
+        <row r="161">
+          <cell r="H161">
+            <v>84.559049999999999</v>
+          </cell>
+          <cell r="K161">
+            <v>4.5085618777847003</v>
+          </cell>
+          <cell r="AG161" t="str">
+            <v>US912821EK70</v>
+          </cell>
+          <cell r="AP161">
+            <v>31.243508771335001</v>
+          </cell>
+        </row>
+        <row r="162">
+          <cell r="H162">
+            <v>73.062200000000004</v>
+          </cell>
+          <cell r="K162">
+            <v>4.7253040479386001</v>
+          </cell>
+          <cell r="AG162" t="str">
+            <v>US9128337T17</v>
+          </cell>
+          <cell r="AP162">
+            <v>33.047484851028003</v>
+          </cell>
+        </row>
+        <row r="163">
+          <cell r="H163">
+            <v>37.004199999999997</v>
+          </cell>
+          <cell r="K163">
+            <v>5.4382347768113997</v>
+          </cell>
+          <cell r="AG163" t="str">
+            <v>US912803EN95</v>
+          </cell>
+          <cell r="AP163">
+            <v>33.483591579204997</v>
+          </cell>
+        </row>
+        <row r="164">
+          <cell r="H164">
+            <v>90.397000000000006</v>
+          </cell>
+          <cell r="K164">
+            <v>4.4645238708916999</v>
+          </cell>
+          <cell r="AG164" t="str">
+            <v>US912833WR77</v>
+          </cell>
+          <cell r="AP164">
+            <v>34.951592636748003</v>
+          </cell>
+        </row>
+        <row r="165">
+          <cell r="H165">
+            <v>74.8643</v>
+          </cell>
+          <cell r="K165" t="str">
+            <v/>
+          </cell>
+          <cell r="AG165" t="str">
+            <v>US9128337S34</v>
+          </cell>
+          <cell r="AP165" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="166">
+          <cell r="H166">
+            <v>35.112050000000004</v>
+          </cell>
+          <cell r="K166">
+            <v>5.5798084434895001</v>
+          </cell>
+          <cell r="AG166" t="str">
+            <v>US912834PT99</v>
+          </cell>
+          <cell r="AP166">
+            <v>45.834539935664999</v>
+          </cell>
+        </row>
+        <row r="167">
+          <cell r="H167">
+            <v>97.983500000000006</v>
+          </cell>
+          <cell r="K167" t="str">
+            <v/>
+          </cell>
+          <cell r="AG167" t="str">
+            <v>US91282CEJ62</v>
+          </cell>
+          <cell r="AP167" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="168">
+          <cell r="H168">
+            <v>93.358000000000004</v>
+          </cell>
+          <cell r="K168" t="str">
+            <v/>
+          </cell>
+          <cell r="AG168" t="str">
+            <v>US912828Z377</v>
+          </cell>
+          <cell r="AP168" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="H169">
+            <v>53.6845</v>
+          </cell>
+          <cell r="K169" t="str">
+            <v/>
+          </cell>
+          <cell r="AG169" t="str">
+            <v>US912810SM18</v>
+          </cell>
+          <cell r="AP169" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="170">
+          <cell r="H170">
+            <v>94.927999999999997</v>
+          </cell>
+          <cell r="K170" t="str">
+            <v/>
+          </cell>
+          <cell r="AG170" t="str">
+            <v>US9128287D64</v>
+          </cell>
+          <cell r="AP170" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="H171">
+            <v>97.245999999999995</v>
+          </cell>
+          <cell r="K171" t="str">
+            <v/>
+          </cell>
+          <cell r="AG171" t="str">
+            <v>US9128283R96</v>
+          </cell>
+          <cell r="AP171" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="H172">
+            <v>70.384500000000003</v>
+          </cell>
+          <cell r="K172" t="str">
+            <v/>
+          </cell>
+          <cell r="AG172" t="str">
+            <v>US912810RA88</v>
+          </cell>
+          <cell r="AP172" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="173">
+          <cell r="H173">
+            <v>68.63</v>
+          </cell>
+          <cell r="K173" t="str">
+            <v/>
+          </cell>
+          <cell r="AG173" t="str">
+            <v>US912810RL44</v>
+          </cell>
+          <cell r="AP173" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="174">
+          <cell r="H174">
+            <v>68.262500000000003</v>
+          </cell>
+          <cell r="K174" t="str">
+            <v/>
+          </cell>
+          <cell r="AG174" t="str">
+            <v>US912810RL44</v>
+          </cell>
+          <cell r="AP174" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="175">
+          <cell r="H175">
+            <v>96.831999999999994</v>
+          </cell>
+          <cell r="K175" t="str">
+            <v/>
+          </cell>
+          <cell r="AG175" t="str">
+            <v>US9128285W63</v>
+          </cell>
+          <cell r="AP175" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="176">
+          <cell r="H176">
+            <v>93.519499999999994</v>
+          </cell>
+          <cell r="K176" t="str">
+            <v/>
+          </cell>
+          <cell r="AG176" t="str">
+            <v>US91282CGK18</v>
+          </cell>
+          <cell r="AP176" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="177">
+          <cell r="H177">
+            <v>99.015000000000001</v>
+          </cell>
+          <cell r="K177" t="str">
+            <v/>
+          </cell>
+          <cell r="AG177" t="str">
+            <v>US912810PV44</v>
+          </cell>
+          <cell r="AP177" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="178">
+          <cell r="H178">
+            <v>96.412999999999997</v>
+          </cell>
+          <cell r="K178" t="str">
+            <v/>
+          </cell>
+          <cell r="AG178" t="str">
+            <v>US91282CJY84</v>
+          </cell>
+          <cell r="AP178" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="179">
+          <cell r="H179">
+            <v>98.272499999999994</v>
+          </cell>
+          <cell r="K179" t="str">
+            <v/>
+          </cell>
+          <cell r="AG179" t="str">
+            <v>US91282CML27</v>
+          </cell>
+          <cell r="AP179" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="180">
+          <cell r="H180">
+            <v>99.581999999999994</v>
+          </cell>
+          <cell r="K180" t="str">
+            <v/>
+          </cell>
+          <cell r="AG180" t="str">
+            <v>US912810PS15</v>
+          </cell>
+          <cell r="AP180" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="181">
+          <cell r="H181">
+            <v>100.03</v>
+          </cell>
+          <cell r="K181">
+            <v>7.6205214560192003</v>
+          </cell>
+          <cell r="AG181" t="str">
+            <v>USU9029YAC40</v>
+          </cell>
+          <cell r="AP181">
+            <v>405.69379915120999</v>
+          </cell>
+        </row>
+        <row r="182">
+          <cell r="H182">
+            <v>93.998500000000007</v>
+          </cell>
+          <cell r="K182">
+            <v>4.2716925537936001</v>
+          </cell>
+          <cell r="AG182" t="str">
+            <v>GB00BMBL1G81</v>
+          </cell>
+          <cell r="AP182" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="183">
+          <cell r="H183">
+            <v>99.734999999999999</v>
+          </cell>
+          <cell r="K183">
+            <v>4.2427965033564004</v>
+          </cell>
+          <cell r="AG183" t="str">
+            <v>GB00BPSNB460</v>
+          </cell>
+          <cell r="AP183" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="184">
+          <cell r="H184">
+            <v>95.001499999999993</v>
+          </cell>
+          <cell r="K184">
+            <v>5.2283698275725001</v>
+          </cell>
+          <cell r="AG184" t="str">
+            <v>US91911TAQ67</v>
+          </cell>
+          <cell r="AP184">
+            <v>103.82670854887</v>
+          </cell>
+        </row>
+        <row r="185">
+          <cell r="H185">
+            <v>97.647549999999995</v>
+          </cell>
+          <cell r="K185">
+            <v>5.0240797819032004</v>
+          </cell>
+          <cell r="AG185" t="str">
+            <v>US92556VAC00</v>
+          </cell>
+          <cell r="AP185">
+            <v>96.599163452865</v>
+          </cell>
+        </row>
+        <row r="186">
+          <cell r="H186">
+            <v>90.8078</v>
+          </cell>
+          <cell r="K186">
+            <v>5.4036479562327999</v>
+          </cell>
+          <cell r="AG186" t="str">
+            <v>US92556VAD82</v>
+          </cell>
+          <cell r="AP186">
+            <v>121.24208205215</v>
+          </cell>
+        </row>
+        <row r="187">
+          <cell r="H187">
+            <v>100.30500000000001</v>
+          </cell>
+          <cell r="K187" t="str">
+            <v/>
+          </cell>
+          <cell r="AG187" t="str">
+            <v>XS2837886105</v>
+          </cell>
+          <cell r="AP187" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="188">
+          <cell r="H188">
+            <v>71.2</v>
+          </cell>
+          <cell r="K188">
+            <v>10.358916231237</v>
+          </cell>
+          <cell r="AG188" t="str">
+            <v>US963320AY28</v>
+          </cell>
+          <cell r="AP188">
+            <v>612.04511247723997</v>
+          </cell>
+        </row>
+        <row r="189">
+          <cell r="H189">
+            <v>74.254999999999995</v>
+          </cell>
+          <cell r="K189">
+            <v>11.064452371603</v>
+          </cell>
+          <cell r="AG189" t="str">
+            <v>US963320AZ92</v>
+          </cell>
+          <cell r="AP189">
+            <v>679.54222114839001</v>
+          </cell>
+        </row>
+        <row r="190">
+          <cell r="H190">
+            <v>58.77</v>
+          </cell>
+          <cell r="K190">
+            <v>38.394083349233</v>
+          </cell>
+          <cell r="AG190" t="str">
+            <v>USU98401AB58</v>
+          </cell>
+          <cell r="AP190">
+            <v>3429.9292351184999</v>
+          </cell>
+        </row>
+        <row r="191">
+          <cell r="H191">
+            <v>104.04349315</v>
+          </cell>
+          <cell r="K191">
+            <v>4.6519277070285003</v>
+          </cell>
+          <cell r="AG191" t="str">
+            <v>AR0417757066</v>
+          </cell>
+          <cell r="AP191">
+            <v>54.764659405571003</v>
+          </cell>
+        </row>
+        <row r="192">
+          <cell r="H192">
+            <v>102.17777778</v>
+          </cell>
+          <cell r="K192">
+            <v>6.6270110071493997</v>
+          </cell>
+          <cell r="AG192" t="str">
+            <v>USP989MJBT72</v>
+          </cell>
+          <cell r="AP192">
+            <v>238.23238191935999</v>
+          </cell>
+        </row>
+        <row r="193">
+          <cell r="H193">
+            <v>104.55999125584</v>
+          </cell>
+          <cell r="K193">
+            <v>6.1653741240821001</v>
+          </cell>
+          <cell r="AG193" t="str">
+            <v>USP989MJBS99</v>
+          </cell>
+          <cell r="AP193">
+            <v>208.25993693701</v>
+          </cell>
+        </row>
+        <row r="194">
+          <cell r="H194">
+            <v>90.674999999999997</v>
+          </cell>
+          <cell r="K194" t="str">
+            <v/>
+          </cell>
+          <cell r="AG194" t="str">
+            <v>AR0344318156</v>
+          </cell>
+          <cell r="AP194">
+            <v>1.2806798037398E+19</v>
+          </cell>
+        </row>
+        <row r="195">
+          <cell r="H195">
+            <v>100</v>
+          </cell>
+          <cell r="K195">
+            <v>3.6994640620985999</v>
+          </cell>
+          <cell r="AG195" t="str">
+            <v>AU3CB0262673</v>
+          </cell>
+          <cell r="AP195" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="196">
+          <cell r="H196">
+            <v>99.745000000000005</v>
+          </cell>
+          <cell r="K196">
+            <v>28.039776097457001</v>
+          </cell>
+          <cell r="AG196" t="str">
+            <v>USU65478BU93</v>
+          </cell>
+          <cell r="AP196">
+            <v>2425.7094402531998</v>
+          </cell>
+        </row>
+        <row r="197">
+          <cell r="H197">
+            <v>100</v>
+          </cell>
+          <cell r="K197">
+            <v>1.4488474949886001</v>
+          </cell>
+          <cell r="AG197" t="str">
+            <v>NO0010757925</v>
+          </cell>
+          <cell r="AP197" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="198">
+          <cell r="H198">
+            <v>100</v>
+          </cell>
+          <cell r="K198">
+            <v>4.3456340281869998</v>
+          </cell>
+          <cell r="AG198" t="str">
+            <v>AU3CB0233898</v>
+          </cell>
+          <cell r="AP198" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="199">
+          <cell r="H199">
+            <v>100.1760274</v>
+          </cell>
+          <cell r="K199">
+            <v>-22.477546360068001</v>
+          </cell>
+          <cell r="AG199" t="str">
+            <v>AR0355743292</v>
+          </cell>
+          <cell r="AP199">
+            <v>-2636.1464057889002</v>
+          </cell>
+        </row>
+        <row r="200">
+          <cell r="H200">
+            <v>99.989850000000004</v>
+          </cell>
+          <cell r="K200">
+            <v>3.7217715369743001</v>
+          </cell>
+          <cell r="AG200" t="str">
+            <v>US912797QY62</v>
+          </cell>
+          <cell r="AP200">
+            <v>-3.5253367420720001</v>
+          </cell>
+        </row>
+        <row r="201">
+          <cell r="H201">
+            <v>99.990300000000005</v>
+          </cell>
+          <cell r="K201">
+            <v>3.5538616457616001</v>
+          </cell>
+          <cell r="AG201" t="str">
+            <v>US912797SB42</v>
+          </cell>
+          <cell r="AP201">
+            <v>-10.101934871438001</v>
+          </cell>
+        </row>
+        <row r="202">
+          <cell r="H202">
+            <v>99.961449999999999</v>
+          </cell>
+          <cell r="K202">
+            <v>3.5310818310497001</v>
+          </cell>
+          <cell r="AG202" t="str">
+            <v>US912797SF55</v>
+          </cell>
+          <cell r="AP202">
+            <v>-12.434386100986</v>
+          </cell>
+        </row>
+        <row r="203">
+          <cell r="H203">
+            <v>99.990300000000005</v>
+          </cell>
+          <cell r="K203">
+            <v>3.5538616457616001</v>
+          </cell>
+          <cell r="AG203" t="str">
+            <v>US912797PV33</v>
+          </cell>
+          <cell r="AP203">
+            <v>-17.18308834374</v>
+          </cell>
+        </row>
+        <row r="204">
+          <cell r="H204">
+            <v>99.989450000000005</v>
+          </cell>
+          <cell r="K204">
+            <v>3.8712539609302001</v>
+          </cell>
+          <cell r="AG204" t="str">
+            <v>US912797RQ20</v>
+          </cell>
+          <cell r="AP204">
+            <v>-1.668576738311</v>
+          </cell>
+        </row>
+        <row r="205">
+          <cell r="H205">
+            <v>100</v>
+          </cell>
+          <cell r="K205" t="str">
+            <v/>
+          </cell>
+          <cell r="AG205" t="str">
+            <v>US912797NU77</v>
+          </cell>
+          <cell r="AP205">
+            <v>-363.48975106099999</v>
+          </cell>
+        </row>
+        <row r="206">
+          <cell r="H206">
+            <v>99.990200000000002</v>
+          </cell>
+          <cell r="K206">
+            <v>3.5911513834556001</v>
+          </cell>
+          <cell r="AG206" t="str">
+            <v>US912797RK59</v>
+          </cell>
+          <cell r="AP206">
+            <v>-12.284892579960999</v>
+          </cell>
+        </row>
+        <row r="207">
+          <cell r="H207">
+            <v>99.990300000000005</v>
+          </cell>
+          <cell r="K207">
+            <v>3.5538616457616001</v>
+          </cell>
+          <cell r="AG207" t="str">
+            <v>US912797SD08</v>
+          </cell>
+          <cell r="AP207">
+            <v>-28.416536646337001</v>
+          </cell>
+        </row>
+        <row r="208">
+          <cell r="H208">
+            <v>99.989099999999993</v>
+          </cell>
+          <cell r="K208">
+            <v>4.0022282844174004</v>
+          </cell>
+          <cell r="AG208" t="str">
+            <v>US912797NA14</v>
+          </cell>
+          <cell r="AP208">
+            <v>9.0652453939745996</v>
+          </cell>
+        </row>
+        <row r="209">
+          <cell r="H209">
+            <v>99.990399999999994</v>
+          </cell>
+          <cell r="K209">
+            <v>3.5165853685486002</v>
+          </cell>
+          <cell r="AG209" t="str">
+            <v>US912797RH21</v>
+          </cell>
+          <cell r="AP209">
+            <v>-14.096211348745999</v>
+          </cell>
+        </row>
+        <row r="210">
+          <cell r="H210">
+            <v>99.990449999999996</v>
+          </cell>
+          <cell r="K210">
+            <v>3.4979522760948001</v>
+          </cell>
+          <cell r="AG210" t="str">
+            <v>US912797SL24</v>
+          </cell>
+          <cell r="AP210">
+            <v>-31.602529404496</v>
+          </cell>
+        </row>
+        <row r="211">
+          <cell r="H211">
+            <v>99.989599999999996</v>
+          </cell>
+          <cell r="K211">
+            <v>3.8151727525793002</v>
+          </cell>
+          <cell r="AG211" t="str">
+            <v>US912797RW97</v>
+          </cell>
+          <cell r="AP211">
+            <v>-9.7748175113641995</v>
+          </cell>
+        </row>
+        <row r="212">
+          <cell r="H212">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K212">
+            <v>33.880347549781</v>
+          </cell>
+          <cell r="AG212" t="str">
+            <v>US91282CAM38</v>
+          </cell>
+          <cell r="AP212">
+            <v>2990.5371269120001</v>
+          </cell>
+        </row>
+        <row r="213">
+          <cell r="H213">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K213">
+            <v>31.574377142797001</v>
+          </cell>
+          <cell r="AG213" t="str">
+            <v>US91282CBC47</v>
+          </cell>
+          <cell r="AP213">
+            <v>2793.8935283289002</v>
+          </cell>
+        </row>
+        <row r="214">
+          <cell r="H214">
+            <v>100</v>
+          </cell>
+          <cell r="K214">
+            <v>2.0151010123733002</v>
+          </cell>
+          <cell r="AG214" t="str">
+            <v>US91282CBQ33</v>
+          </cell>
+          <cell r="AP214">
+            <v>-169.67529816410001</v>
+          </cell>
+        </row>
+        <row r="215">
+          <cell r="H215">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K215">
+            <v>29.906694336208002</v>
+          </cell>
+          <cell r="AG215" t="str">
+            <v>US91282CBW01</v>
+          </cell>
+          <cell r="AP215">
+            <v>2616.7982502688001</v>
+          </cell>
+        </row>
+        <row r="216">
+          <cell r="H216">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K216">
+            <v>32.095666090904999</v>
+          </cell>
+          <cell r="AG216" t="str">
+            <v>US912828R366</v>
+          </cell>
+          <cell r="AP216">
+            <v>2833.8528505432</v>
+          </cell>
+        </row>
+        <row r="217">
+          <cell r="H217">
+            <v>99.930999999999997</v>
+          </cell>
+          <cell r="K217">
+            <v>33.862249696840003</v>
+          </cell>
+          <cell r="AG217" t="str">
+            <v>US912828M565</v>
+          </cell>
+          <cell r="AP217">
+            <v>3000.1324505521002</v>
+          </cell>
+        </row>
+        <row r="218">
+          <cell r="H218">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K218">
+            <v>38.254410932829003</v>
+          </cell>
+          <cell r="AG218" t="str">
+            <v>US9128285C00</v>
+          </cell>
+          <cell r="AP218">
+            <v>3427.9434652169002</v>
+          </cell>
+        </row>
+        <row r="219">
+          <cell r="H219">
+            <v>99.927000000000007</v>
+          </cell>
+          <cell r="K219">
+            <v>13.495734677210001</v>
+          </cell>
+          <cell r="AG219" t="str">
+            <v>US91282CGA36</v>
+          </cell>
+          <cell r="AP219">
+            <v>973.98190584545</v>
+          </cell>
+        </row>
+        <row r="220">
+          <cell r="H220">
+            <v>99.941500000000005</v>
+          </cell>
+          <cell r="K220">
+            <v>28.999788075103002</v>
+          </cell>
+          <cell r="AG220" t="str">
+            <v>US91282CFW64</v>
+          </cell>
+          <cell r="AP220">
+            <v>2513.8862883782999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F9929528-1208-47D6-904C-61B41F15758C}" name="Bonos3" displayName="Bonos3" ref="A1:P72" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
-  <autoFilter ref="A1:P72" xr:uid="{F9929528-1208-47D6-904C-61B41F15758C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}" name="Bonos" displayName="Bonos" ref="A1:P72" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
+  <autoFilter ref="A1:P72" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{2AFCD4C4-5B9C-440A-9683-35FF11067181}" name="Issuer" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{5C55692A-D8F0-41F9-9F66-0666D68A9ABF}" name="Industry" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{F1C64926-17FF-455B-AAC3-F27FBB15B9BC}" name="Guarantor/Organization" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{AD770398-EFFC-4459-B3A5-1E0BD5A40F05}" name="IG - HY" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{517E0FA1-FB77-43EF-9252-4C47F0184D4E}" name="Rating" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{22CBE1BC-7885-451C-869B-CCD041D42F18}" name="Coupon %" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{39F8CD2C-0C47-4F14-B173-0CF32C2C5AC8}" name="Maturity" dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{0CEC3680-E808-41F4-A878-27D6F8507BA9}" name="Year" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{DF407AB1-75BC-418E-BDF1-6D1121F02A3A}" name="Price" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{A384B870-24EE-4569-810D-C0F88E32F8DC}" name="YTW %" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{C8875639-D318-48B8-9F02-B7B7D622D498}" name="Gspread" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{649422D8-F09A-49AD-9529-4F730B728D67}" name="Prev month_x000a_YTW%" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{7C91DDB0-4115-49B6-A0DA-292DA98FEF04}" name="Minimum Settlement" dataDxfId="3" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{A4070786-5EAC-40CB-848C-778505997A11}" name="ISIN" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{7B2144E0-E5F2-4A2B-8D7B-1695805B7A02}" name="Outstanding_x000a_US$" dataDxfId="1" dataCellStyle="Millares 3"/>
-    <tableColumn id="22" xr3:uid="{4E6F3B99-052C-4999-8442-C6D182EEDFED}" name="Decisión" dataDxfId="0" dataCellStyle="Porcentaje"/>
+    <tableColumn id="1" xr3:uid="{EAF877B8-4926-4959-BBFA-585A75C8391D}" name="Issuer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{B2C00443-39F1-4600-BE48-DDA923D78603}" name="Industry" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{056A063A-7DD1-426B-801B-BA928025AEA7}" name="Guarantor/Organization" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{025668FE-93B1-4247-8E7A-ABE2826DECF9}" name="IG - HY" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{93EB2ECC-49AC-4CF3-BEA3-A986802A4943}" name="Rating" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{C652B961-0C28-471B-A2F2-0484E1BCEEA3}" name="Coupon %" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{BC3F132C-6722-43C0-8763-BCF6C453DE6C}" name="Maturity" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{186BEC2D-B3E8-4C1B-AF49-D26B793A588E}" name="Year" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{C5B9CC1E-2FA8-48FA-ACF8-02CFF554B424}" name="Price" dataDxfId="7">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{74DBEB6E-2B38-4756-9C55-DC41829F2AAE}" name="YTW %" dataDxfId="6">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{C7B9A70F-7A8D-4ECF-B313-D80162BEF2AC}" name="Gspread" dataDxfId="5">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{0445B399-F1E4-4E60-B4C4-F7BCF55169D7}" name="Prev month_x000a_YTW%" dataDxfId="4" dataCellStyle="Porcentaje"/>
+    <tableColumn id="16" xr3:uid="{598A638E-5D30-4402-8C03-7D8FB7026143}" name="Minimum Settlement" dataDxfId="3" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{6C62A4A4-AF52-466C-9C5B-18BFC7CB7F2E}" name="ISIN" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{1BC656B6-7DF8-499B-94D4-E75FA0DEE401}" name="Outstanding_x000a_US$" dataDxfId="1" dataCellStyle="Millares 3"/>
+    <tableColumn id="22" xr3:uid="{ACB77059-8EFE-49B1-BE87-11A1BB6FF77E}" name="Decisión" dataDxfId="0" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3817,6 +6914,7 @@
   <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.42578125" style="1"/>
     <col min="6" max="6" width="11.42578125" style="2"/>
@@ -3899,16 +6997,19 @@
         <v>2026</v>
       </c>
       <c r="I2" s="13">
-        <v>99.45</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.5</v>
       </c>
       <c r="J2" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>4.3908531690574</v>
+      </c>
+      <c r="K2" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>35.044994044577003</v>
+      </c>
+      <c r="L2" s="13">
         <v>4.2832431600931002</v>
-      </c>
-      <c r="K2" s="13">
-        <v>23.380165207560001</v>
-      </c>
-      <c r="L2" s="13">
-        <v>4.1399328878331998</v>
       </c>
       <c r="M2" s="14">
         <v>150000</v>
@@ -3949,16 +7050,19 @@
         <v>2027</v>
       </c>
       <c r="I3" s="13">
-        <v>100.705</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.54</v>
       </c>
       <c r="J3" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2217860674756</v>
+      </c>
+      <c r="K3" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>116.70117695684</v>
+      </c>
+      <c r="L3" s="13">
         <v>5.0570708139880001</v>
-      </c>
-      <c r="K3" s="13">
-        <v>100.39198362429001</v>
-      </c>
-      <c r="L3" s="13">
-        <v>5.0021200493173996</v>
       </c>
       <c r="M3" s="14">
         <v>2000</v>
@@ -3999,16 +7103,19 @@
         <v>2027</v>
       </c>
       <c r="I4" s="13">
-        <v>100.02975000000001</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.905000000000001</v>
       </c>
       <c r="J4" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>4.7551093516370004</v>
+      </c>
+      <c r="K4" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>68.730736098094994</v>
+      </c>
+      <c r="L4" s="13">
         <v>4.6481210859009998</v>
-      </c>
-      <c r="K4" s="13">
-        <v>58.889795147146003</v>
-      </c>
-      <c r="L4" s="13">
-        <v>4.5733580557196003</v>
       </c>
       <c r="M4" s="14">
         <v>150000</v>
@@ -4055,16 +7162,19 @@
         <v>2027</v>
       </c>
       <c r="I5" s="13">
-        <v>99.8125</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.9375</v>
       </c>
       <c r="J5" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.1261015299891</v>
+      </c>
+      <c r="K5" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>106.54769890657001</v>
+      </c>
+      <c r="L5" s="13">
         <v>5.2465634689330001</v>
-      </c>
-      <c r="K5" s="13">
-        <v>119.09045695966999</v>
-      </c>
-      <c r="L5" s="13">
-        <v>5.2345351627822003</v>
       </c>
       <c r="M5" s="14">
         <f>+_xlfn.XLOOKUP($N5,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4112,16 +7222,19 @@
         <v>2027</v>
       </c>
       <c r="I6" s="13">
-        <v>97.765500000000003</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.647549999999995</v>
       </c>
       <c r="J6" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.0240797819032004</v>
+      </c>
+      <c r="K6" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>96.599163452865</v>
+      </c>
+      <c r="L6" s="13">
         <v>4.7662251119193</v>
-      </c>
-      <c r="K6" s="13">
-        <v>71.170314572267003</v>
-      </c>
-      <c r="L6" s="13">
-        <v>4.6397379099930003</v>
       </c>
       <c r="M6" s="14">
         <f>+_xlfn.XLOOKUP($N6,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4169,16 +7282,19 @@
         <v>2027</v>
       </c>
       <c r="I7" s="26">
-        <v>97.98</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.6</v>
       </c>
       <c r="J7" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.8138386217568003</v>
+      </c>
+      <c r="K7" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>174.43230620431001</v>
+      </c>
+      <c r="L7" s="26">
         <v>5.4298213376745998</v>
-      </c>
-      <c r="K7" s="26">
-        <v>136.96816535228001</v>
-      </c>
-      <c r="L7" s="26">
-        <v>5.3351024156840996</v>
       </c>
       <c r="M7" s="27">
         <f>+_xlfn.XLOOKUP($N7,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4226,16 +7342,19 @@
         <v>2028</v>
       </c>
       <c r="I8" s="13">
-        <v>99.575299999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.096599999999995</v>
       </c>
       <c r="J8" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>4.9684822597879998</v>
+      </c>
+      <c r="K8" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>85.654212702403001</v>
+      </c>
+      <c r="L8" s="13">
         <v>4.7422361014980003</v>
-      </c>
-      <c r="K8" s="13">
-        <v>65.449731028407996</v>
-      </c>
-      <c r="L8" s="13">
-        <v>4.6684643359624003</v>
       </c>
       <c r="M8" s="14">
         <f>+_xlfn.XLOOKUP($N8,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4283,16 +7402,19 @@
         <v>2028</v>
       </c>
       <c r="I9" s="13">
-        <v>94.56</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>94.102000000000004</v>
       </c>
       <c r="J9" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.0342310397633003</v>
+      </c>
+      <c r="K9" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>92.363190210389007</v>
+      </c>
+      <c r="L9" s="13">
         <v>4.7570508823191</v>
-      </c>
-      <c r="K9" s="13">
-        <v>67.029007466332999</v>
-      </c>
-      <c r="L9" s="13">
-        <v>4.6571310242374002</v>
       </c>
       <c r="M9" s="14">
         <f>+_xlfn.XLOOKUP($N9,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4334,16 +7456,19 @@
         <v>2028</v>
       </c>
       <c r="I10" s="13">
-        <v>100.57445</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.15</v>
       </c>
       <c r="J10" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>4.9840141275835004</v>
+      </c>
+      <c r="K10" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>88.034330463553005</v>
+      </c>
+      <c r="L10" s="13">
         <v>4.7781681020595004</v>
-      </c>
-      <c r="K10" s="13">
-        <v>69.635516701835996</v>
-      </c>
-      <c r="L10" s="13">
-        <v>4.7356345400144004</v>
       </c>
       <c r="M10" s="14">
         <v>2000</v>
@@ -4390,16 +7515,19 @@
         <v>2028</v>
       </c>
       <c r="I11" s="13">
-        <v>99.028400000000005</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.224999999999994</v>
       </c>
       <c r="J11" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.1978025665273</v>
+      </c>
+      <c r="K11" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>109.54403223188</v>
+      </c>
+      <c r="L11" s="13">
         <v>4.7753751860465004</v>
-      </c>
-      <c r="K11" s="13">
-        <v>69.447301204604997</v>
-      </c>
-      <c r="L11" s="13">
-        <v>5.2044530096086996</v>
       </c>
       <c r="M11" s="14">
         <f>+_xlfn.XLOOKUP($N11,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4446,16 +7574,19 @@
         <v>2028</v>
       </c>
       <c r="I12" s="26">
-        <v>59</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>58.77</v>
       </c>
       <c r="J12" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>38.394083349233</v>
+      </c>
+      <c r="K12" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>3429.9292351184999</v>
+      </c>
+      <c r="L12" s="26">
         <v>37.372258361656002</v>
-      </c>
-      <c r="K12" s="26">
-        <v>3329.6521496261998</v>
-      </c>
-      <c r="L12" s="26">
-        <v>34.740173119189002</v>
       </c>
       <c r="M12" s="27">
         <f>+_xlfn.XLOOKUP($N12,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4502,16 +7633,19 @@
         <v>2028</v>
       </c>
       <c r="I13" s="26">
-        <v>59.997999999999998</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>53.604999999999997</v>
       </c>
       <c r="J13" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>61.799509103391003</v>
+      </c>
+      <c r="K13" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>5772.3409564223002</v>
+      </c>
+      <c r="L13" s="26">
         <v>47.992506623183999</v>
-      </c>
-      <c r="K13" s="26">
-        <v>4392.9748486176004</v>
-      </c>
-      <c r="L13" s="26">
-        <v>39.639584176063003</v>
       </c>
       <c r="M13" s="27">
         <f>+_xlfn.XLOOKUP($N13,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4555,16 +7689,19 @@
         <v>2028</v>
       </c>
       <c r="I14" s="13">
-        <v>103.351</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>102.605</v>
       </c>
       <c r="J14" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3389997638258997</v>
+      </c>
+      <c r="K14" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>125.77745101456</v>
+      </c>
+      <c r="L14" s="13">
         <v>4.9123728446805996</v>
-      </c>
-      <c r="K14" s="13">
-        <v>84.543917559760999</v>
-      </c>
-      <c r="L14" s="13">
-        <v>5.1733104559676999</v>
       </c>
       <c r="M14" s="14">
         <v>1000</v>
@@ -4607,16 +7744,19 @@
         <v>2028</v>
       </c>
       <c r="I15" s="26">
-        <v>81.990549999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>84.625</v>
       </c>
       <c r="J15" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>14.00107155779</v>
+      </c>
+      <c r="K15" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>990.35448851802005</v>
+      </c>
+      <c r="L15" s="26">
         <v>15.600562809316999</v>
-      </c>
-      <c r="K15" s="26">
-        <v>1152.3102255069</v>
-      </c>
-      <c r="L15" s="26">
-        <v>15.547750959159</v>
       </c>
       <c r="M15" s="27">
         <v>2000</v>
@@ -4658,16 +7798,19 @@
         <v>2028</v>
       </c>
       <c r="I16" s="13">
-        <v>103.23</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>102.745</v>
       </c>
       <c r="J16" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5755940454813002</v>
+      </c>
+      <c r="K16" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>146.90426497843001</v>
+      </c>
+      <c r="L16" s="13">
         <v>5.3738107752827</v>
-      </c>
-      <c r="K16" s="13">
-        <v>128.99535451521001</v>
-      </c>
-      <c r="L16" s="13">
-        <v>5.2212942271933001</v>
       </c>
       <c r="M16" s="14">
         <v>200000</v>
@@ -4708,16 +7851,19 @@
         <v>2028</v>
       </c>
       <c r="I17" s="13">
-        <v>97.474999999999994</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.27</v>
       </c>
       <c r="J17" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5494499521960998</v>
+      </c>
+      <c r="K17" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>145.25790904621999</v>
+      </c>
+      <c r="L17" s="13">
         <v>5.4043003750673</v>
-      </c>
-      <c r="K17" s="13">
-        <v>132.83722632353999</v>
-      </c>
-      <c r="L17" s="13">
-        <v>5.26</v>
       </c>
       <c r="M17" s="14">
         <v>1000</v>
@@ -4758,16 +7904,19 @@
         <v>2028</v>
       </c>
       <c r="I18" s="13">
-        <v>99.805000000000007</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.14</v>
       </c>
       <c r="J18" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.2446701815574999</v>
+      </c>
+      <c r="K18" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>213.61638444050001</v>
+      </c>
+      <c r="L18" s="13">
         <v>5.9208334278288</v>
-      </c>
-      <c r="K18" s="13">
-        <v>183.55708706243001</v>
-      </c>
-      <c r="L18" s="13">
-        <v>5.6758060419575997</v>
       </c>
       <c r="M18" s="14">
         <v>1000</v>
@@ -4809,16 +7958,19 @@
         <v>2028</v>
       </c>
       <c r="I19" s="13">
-        <v>98.55565</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.375</v>
       </c>
       <c r="J19" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3547576737993001</v>
+      </c>
+      <c r="K19" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>126.1745027602</v>
+      </c>
+      <c r="L19" s="13">
         <v>5.2324358555585997</v>
-      </c>
-      <c r="K19" s="13">
-        <v>115.79460654344</v>
-      </c>
-      <c r="L19" s="13">
-        <v>5.0951748613912002</v>
       </c>
       <c r="M19" s="14">
         <v>2000</v>
@@ -4861,16 +8013,19 @@
         <v>2029</v>
       </c>
       <c r="I20" s="13">
-        <v>106.2165</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>106.017</v>
       </c>
       <c r="J20" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0768609608236996</v>
+      </c>
+      <c r="K20" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>196.25440799008001</v>
+      </c>
+      <c r="L20" s="13">
         <v>6.0333288027999998</v>
-      </c>
-      <c r="K20" s="13">
-        <v>194.69832060189</v>
-      </c>
-      <c r="L20" s="13">
-        <v>5.7889043132677998</v>
       </c>
       <c r="M20" s="14">
         <v>1000</v>
@@ -4917,16 +8072,19 @@
         <v>2029</v>
       </c>
       <c r="I21" s="13">
-        <v>103.715</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>103.25</v>
       </c>
       <c r="J21" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2262981503403001</v>
+      </c>
+      <c r="K21" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>113.49555342230001</v>
+      </c>
+      <c r="L21" s="13">
         <v>5.0119989796673998</v>
-      </c>
-      <c r="K21" s="13">
-        <v>93.861399046453997</v>
-      </c>
-      <c r="L21" s="13">
-        <v>4.9966088021799999</v>
       </c>
       <c r="M21" s="14">
         <f>+_xlfn.XLOOKUP($N21,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -4973,16 +8131,19 @@
         <v>2029</v>
       </c>
       <c r="I22" s="26">
-        <v>99.4435</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.34</v>
       </c>
       <c r="J22" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.9529012337668004</v>
+      </c>
+      <c r="K22" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>181.60886812977</v>
+      </c>
+      <c r="L22" s="26">
         <v>5.9098961663083003</v>
-      </c>
-      <c r="K22" s="26">
-        <v>180.33250281859</v>
-      </c>
-      <c r="L22" s="26">
-        <v>5.8698164938724</v>
       </c>
       <c r="M22" s="27">
         <f>+_xlfn.XLOOKUP($N22,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5029,16 +8190,19 @@
         <v>2029</v>
       </c>
       <c r="I23" s="26">
-        <v>93.067499999999995</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>92.4816</v>
       </c>
       <c r="J23" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.1691679685506999</v>
+      </c>
+      <c r="K23" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>201.85328135754</v>
+      </c>
+      <c r="L23" s="26">
         <v>5.9164627873917004</v>
-      </c>
-      <c r="K23" s="26">
-        <v>179.88791852900999</v>
-      </c>
-      <c r="L23" s="26">
-        <v>6.1031278451061004</v>
       </c>
       <c r="M23" s="27">
         <f>+_xlfn.XLOOKUP($N23,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5085,16 +8249,19 @@
         <v>2029</v>
       </c>
       <c r="I24" s="13">
-        <v>99.635000000000005</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.334999999999994</v>
       </c>
       <c r="J24" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5401109236627999</v>
+      </c>
+      <c r="K24" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>138.23995836749</v>
+      </c>
+      <c r="L24" s="13">
         <v>5.4383914326443996</v>
-      </c>
-      <c r="K24" s="13">
-        <v>131.50867729941999</v>
-      </c>
-      <c r="L24" s="13">
-        <v>5.4047418010010997</v>
       </c>
       <c r="M24" s="14">
         <f>+_xlfn.XLOOKUP($N24,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5142,16 +8309,19 @@
         <v>2029</v>
       </c>
       <c r="I25" s="13">
-        <v>100.545</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.944999999999993</v>
       </c>
       <c r="J25" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.0823082063419003</v>
+      </c>
+      <c r="K25" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>94.394347920116005</v>
+      </c>
+      <c r="L25" s="13">
         <v>4.8633165071222004</v>
-      </c>
-      <c r="K25" s="13">
-        <v>75.549590736349998</v>
-      </c>
-      <c r="L25" s="13">
-        <v>4.7809946854473004</v>
       </c>
       <c r="M25" s="14">
         <f>+_xlfn.XLOOKUP($N25,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5195,16 +8365,19 @@
         <v>2029</v>
       </c>
       <c r="I26" s="13">
-        <v>97.070999999999998</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>96.47</v>
       </c>
       <c r="J26" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2374920160164997</v>
+      </c>
+      <c r="K26" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>111.06905121094999</v>
+      </c>
+      <c r="L26" s="13">
         <v>4.9660398867562003</v>
-      </c>
-      <c r="K26" s="13">
-        <v>86.719568477107998</v>
-      </c>
-      <c r="L26" s="13">
-        <v>4.9732958652243999</v>
       </c>
       <c r="M26" s="14">
         <v>1000</v>
@@ -5245,16 +8418,19 @@
         <v>2029</v>
       </c>
       <c r="I27" s="13">
-        <v>95.307500000000005</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>94.405000000000001</v>
       </c>
       <c r="J27" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.6349128086422002</v>
+      </c>
+      <c r="K27" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>248.06042214619001</v>
+      </c>
+      <c r="L27" s="13">
         <v>6.2886966914741</v>
-      </c>
-      <c r="K27" s="13">
-        <v>216.81147745448999</v>
-      </c>
-      <c r="L27" s="13">
-        <v>5.9796398973778002</v>
       </c>
       <c r="M27" s="14">
         <v>1000</v>
@@ -5296,16 +8472,19 @@
         <v>2029</v>
       </c>
       <c r="I28" s="13">
-        <v>100.99</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.52500000000001</v>
       </c>
       <c r="J28" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.8378605733628</v>
+      </c>
+      <c r="K28" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>169.98240628127999</v>
+      </c>
+      <c r="L28" s="13">
         <v>5.666805627924</v>
-      </c>
-      <c r="K28" s="13">
-        <v>156.25027537597001</v>
-      </c>
-      <c r="L28" s="13">
-        <v>5.6229573345007999</v>
       </c>
       <c r="M28" s="14">
         <v>2000</v>
@@ -5347,16 +8526,19 @@
         <v>2029</v>
       </c>
       <c r="I29" s="13">
-        <v>101.77</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>101.13500000000001</v>
       </c>
       <c r="J29" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.0747627537484998</v>
+      </c>
+      <c r="K29" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>92.635129430480006</v>
+      </c>
+      <c r="L29" s="13">
         <v>4.8640697328705</v>
-      </c>
-      <c r="K29" s="13">
-        <v>74.826815748252002</v>
-      </c>
-      <c r="L29" s="13">
-        <v>4.8014897953651996</v>
       </c>
       <c r="M29" s="14">
         <v>2000</v>
@@ -5398,16 +8580,19 @@
         <v>2030</v>
       </c>
       <c r="I30" s="26">
-        <v>97.005549999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>96.625</v>
       </c>
       <c r="J30" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6884236132800998</v>
+      </c>
+      <c r="K30" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>150.74440510137001</v>
+      </c>
+      <c r="L30" s="26">
         <v>5.5630820350621999</v>
-      </c>
-      <c r="K30" s="26">
-        <v>142.04326012195</v>
-      </c>
-      <c r="L30" s="26">
-        <v>5.5877308093684004</v>
       </c>
       <c r="M30" s="27">
         <v>1000</v>
@@ -5453,16 +8638,19 @@
         <v>2030</v>
       </c>
       <c r="I31" s="26">
-        <v>97.5</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.375</v>
       </c>
       <c r="J31" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.9198386169269996</v>
+      </c>
+      <c r="K31" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>175.90783354633001</v>
+      </c>
+      <c r="L31" s="26">
         <v>5.8680201805944998</v>
-      </c>
-      <c r="K31" s="26">
-        <v>174.22270862929</v>
-      </c>
-      <c r="L31" s="26">
-        <v>5.9763491100649997</v>
       </c>
       <c r="M31" s="27">
         <f>+_xlfn.XLOOKUP($N31,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5505,16 +8693,19 @@
         <v>2030</v>
       </c>
       <c r="I32" s="13">
-        <v>93.045000000000002</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>92.135000000000005</v>
       </c>
       <c r="J32" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0583846882100998</v>
+      </c>
+      <c r="K32" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>185.24321054836</v>
+      </c>
+      <c r="L32" s="13">
         <v>5.7805265387676004</v>
-      </c>
-      <c r="K32" s="13">
-        <v>161.64086280793001</v>
-      </c>
-      <c r="L32" s="13">
-        <v>5.8657650211977996</v>
       </c>
       <c r="M32" s="14">
         <v>2000</v>
@@ -5556,16 +8747,19 @@
         <v>2030</v>
       </c>
       <c r="I33" s="13">
-        <v>98.2928</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.279560000000004</v>
       </c>
       <c r="J33" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5038780249519998</v>
+      </c>
+      <c r="K33" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>130.75487422077001</v>
+      </c>
+      <c r="L33" s="13">
         <v>5.2167283875081001</v>
-      </c>
-      <c r="K33" s="13">
-        <v>106.09039282237001</v>
-      </c>
-      <c r="L33" s="13">
-        <v>5.0649725136379002</v>
       </c>
       <c r="M33" s="14">
         <v>2000</v>
@@ -5607,16 +8801,19 @@
         <v>2030</v>
       </c>
       <c r="I34" s="13">
-        <v>98.825000000000003</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.2</v>
       </c>
       <c r="J34" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0892206099960999</v>
+      </c>
+      <c r="K34" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>190.23409560722999</v>
+      </c>
+      <c r="L34" s="13">
         <v>5.9051997759867003</v>
-      </c>
-      <c r="K34" s="13">
-        <v>175.74953149757999</v>
-      </c>
-      <c r="L34" s="13">
-        <v>5.8612427880234002</v>
       </c>
       <c r="M34" s="34">
         <v>2000</v>
@@ -5659,16 +8856,19 @@
         <v>2030</v>
       </c>
       <c r="I35" s="13">
-        <v>98.35</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.55</v>
       </c>
       <c r="J35" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>8.7479156676685008</v>
+      </c>
+      <c r="K35" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>459.86510364928</v>
+      </c>
+      <c r="L35" s="13">
         <v>9.5170455367630993</v>
-      </c>
-      <c r="K35" s="13">
-        <v>540.09375815400995</v>
-      </c>
-      <c r="L35" s="13">
-        <v>9.5060902364221995</v>
       </c>
       <c r="M35" s="14">
         <v>200000</v>
@@ -5715,16 +8915,19 @@
         <v>2030</v>
       </c>
       <c r="I36" s="13">
-        <v>106.28435</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>105.5663</v>
       </c>
       <c r="J36" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3167478739792999</v>
+      </c>
+      <c r="K36" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>116.12869134604</v>
+      </c>
+      <c r="L36" s="13">
         <v>5.1146249720602004</v>
-      </c>
-      <c r="K36" s="13">
-        <v>99.309735596096999</v>
-      </c>
-      <c r="L36" s="13">
-        <v>5.0483463023033996</v>
       </c>
       <c r="M36" s="34">
         <f>+_xlfn.XLOOKUP($N36,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5768,16 +8971,19 @@
         <v>2030</v>
       </c>
       <c r="I37" s="13">
-        <v>100.1765</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.814999999999998</v>
       </c>
       <c r="J37" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0173203968370004</v>
+      </c>
+      <c r="K37" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>185.23414711397001</v>
+      </c>
+      <c r="L37" s="13">
         <v>5.9026780275639998</v>
-      </c>
-      <c r="K37" s="13">
-        <v>177.33893406474999</v>
-      </c>
-      <c r="L37" s="13">
-        <v>5.7934766468827998</v>
       </c>
       <c r="M37" s="14">
         <v>2000</v>
@@ -5820,16 +9026,19 @@
         <v>2030</v>
       </c>
       <c r="I38" s="13">
-        <v>97.102950000000007</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>96.577600000000004</v>
       </c>
       <c r="J38" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4958884088957003</v>
+      </c>
+      <c r="K38" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>129.97234669082999</v>
+      </c>
+      <c r="L38" s="13">
         <v>5.3399688621105996</v>
-      </c>
-      <c r="K38" s="13">
-        <v>118.43510796036</v>
-      </c>
-      <c r="L38" s="13">
-        <v>5.3782875807729003</v>
       </c>
       <c r="M38" s="34">
         <v>2000</v>
@@ -5876,16 +9085,19 @@
         <v>2030</v>
       </c>
       <c r="I39" s="13">
-        <v>99.224500000000006</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.744500000000002</v>
       </c>
       <c r="J39" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5695677340319003</v>
+      </c>
+      <c r="K39" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>140.68770102907999</v>
+      </c>
+      <c r="L39" s="13">
         <v>5.4081318780318997</v>
-      </c>
-      <c r="K39" s="13">
-        <v>128.44369795827001</v>
-      </c>
-      <c r="L39" s="13">
-        <v>5.3014347264678996</v>
       </c>
       <c r="M39" s="14">
         <f>+_xlfn.XLOOKUP($N39,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5933,16 +9145,19 @@
         <v>2030</v>
       </c>
       <c r="I40" s="13">
-        <v>91.300049999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>90.8078</v>
       </c>
       <c r="J40" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4036479562327999</v>
+      </c>
+      <c r="K40" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>121.24208205215</v>
+      </c>
+      <c r="L40" s="13">
         <v>5.2241215897703999</v>
-      </c>
-      <c r="K40" s="13">
-        <v>107.27688652632</v>
-      </c>
-      <c r="L40" s="13">
-        <v>5.0983610157478996</v>
       </c>
       <c r="M40" s="14">
         <f>+_xlfn.XLOOKUP($N40,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -5989,12 +9204,15 @@
         <v>2030</v>
       </c>
       <c r="I41" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
         <v>108.4</v>
       </c>
       <c r="J41" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
         <v>4.8028528899121001</v>
       </c>
       <c r="K41" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
         <v>76.010527540115007</v>
       </c>
       <c r="L41" s="13">
@@ -6045,16 +9263,19 @@
         <v>2030</v>
       </c>
       <c r="I42" s="13">
-        <v>95.340500000000006</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>95.001499999999993</v>
       </c>
       <c r="J42" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2283698275725001</v>
+      </c>
+      <c r="K42" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>103.82670854887</v>
+      </c>
+      <c r="L42" s="13">
         <v>5.1140232684006</v>
-      </c>
-      <c r="K42" s="13">
-        <v>96.726032319241995</v>
-      </c>
-      <c r="L42" s="13">
-        <v>5.0673822743828003</v>
       </c>
       <c r="M42" s="14">
         <f>+_xlfn.XLOOKUP($N42,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6098,16 +9319,19 @@
         <v>2030</v>
       </c>
       <c r="I43" s="13">
-        <v>96.63</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>95.935000000000002</v>
       </c>
       <c r="J43" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6866903609593002</v>
+      </c>
+      <c r="K43" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>151.45019039428001</v>
+      </c>
+      <c r="L43" s="13">
         <v>5.4537213017957997</v>
-      </c>
-      <c r="K43" s="13">
-        <v>131.84206806991</v>
-      </c>
-      <c r="L43" s="13">
-        <v>5.5730541855544997</v>
       </c>
       <c r="M43" s="14">
         <v>2000</v>
@@ -6153,16 +9377,19 @@
         <v>2030</v>
       </c>
       <c r="I44" s="13">
-        <v>90.455849999999998</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>90.164500000000004</v>
       </c>
       <c r="J44" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.7259922256740001</v>
+      </c>
+      <c r="K44" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>152.08590784775001</v>
+      </c>
+      <c r="L44" s="13">
         <v>5.6146107857010001</v>
-      </c>
-      <c r="K44" s="13">
-        <v>145.12849207442</v>
-      </c>
-      <c r="L44" s="13">
-        <v>5.5926404224787003</v>
       </c>
       <c r="M44" s="14">
         <f>+_xlfn.XLOOKUP($N44,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6205,16 +9432,19 @@
         <v>2030</v>
       </c>
       <c r="I45" s="13">
-        <v>80.66</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>77.144999999999996</v>
       </c>
       <c r="J45" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>11.449925268537999</v>
+      </c>
+      <c r="K45" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>726.99066616861001</v>
+      </c>
+      <c r="L45" s="13">
         <v>9.9952818659825997</v>
-      </c>
-      <c r="K45" s="13">
-        <v>593.69553893602995</v>
-      </c>
-      <c r="L45" s="13">
-        <v>5.1856108017900002</v>
       </c>
       <c r="M45" s="14">
         <v>2000</v>
@@ -6257,16 +9487,19 @@
         <v>2030</v>
       </c>
       <c r="I46" s="13">
-        <v>99.494249999999994</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.704999999999998</v>
       </c>
       <c r="J46" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4091299597324998</v>
+      </c>
+      <c r="K46" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>120.72910483749</v>
+      </c>
+      <c r="L46" s="13">
         <v>5.1950145746962004</v>
-      </c>
-      <c r="K46" s="13">
-        <v>103.44711103354</v>
-      </c>
-      <c r="L46" s="13">
-        <v>5.1281219620645997</v>
       </c>
       <c r="M46" s="14">
         <v>2000</v>
@@ -6309,16 +9542,19 @@
         <v>2031</v>
       </c>
       <c r="I47" s="13">
-        <v>102.045</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>101.6</v>
       </c>
       <c r="J47" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4144095584879999</v>
+      </c>
+      <c r="K47" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>120.57510221228</v>
+      </c>
+      <c r="L47" s="13">
         <v>5.3044691221645</v>
-      </c>
-      <c r="K47" s="13">
-        <v>114.38797755776</v>
-      </c>
-      <c r="L47" s="13">
-        <v>5.2067291788855998</v>
       </c>
       <c r="M47" s="14">
         <v>2000</v>
@@ -6364,16 +9600,19 @@
         <v>2031</v>
       </c>
       <c r="I48" s="13">
-        <v>87.472499999999997</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>86.842500000000001</v>
       </c>
       <c r="J48" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.8792735535786003</v>
+      </c>
+      <c r="K48" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>165.20963267785999</v>
+      </c>
+      <c r="L48" s="13">
         <v>5.6745121526288997</v>
-      </c>
-      <c r="K48" s="13">
-        <v>149.18257120941999</v>
-      </c>
-      <c r="L48" s="13">
-        <v>5.6366512377394002</v>
       </c>
       <c r="M48" s="14">
         <f>+_xlfn.XLOOKUP($N48,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6421,16 +9660,19 @@
         <v>2031</v>
       </c>
       <c r="I49" s="13">
-        <v>102.07</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>101.80500000000001</v>
       </c>
       <c r="J49" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>4.9050583828213004</v>
+      </c>
+      <c r="K49" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>69.431880707664007</v>
+      </c>
+      <c r="L49" s="13">
         <v>4.8424845463382002</v>
-      </c>
-      <c r="K49" s="13">
-        <v>67.974237180621998</v>
-      </c>
-      <c r="L49" s="13">
-        <v>4.7117258045619002</v>
       </c>
       <c r="M49" s="34">
         <f>+_xlfn.XLOOKUP($N49,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6472,15 +9714,18 @@
         <v>2031</v>
       </c>
       <c r="I50" s="43">
-        <v>97.59</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>97.14</v>
       </c>
       <c r="J50" s="43">
-        <v>5.1539999999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2775961551588999</v>
       </c>
       <c r="K50" s="43">
-        <v>91.02</v>
-      </c>
-      <c r="L50" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>106.35347008796001</v>
+      </c>
+      <c r="L50" s="43">
         <v>5.1539999999999999</v>
       </c>
       <c r="M50" s="34">
@@ -6528,16 +9773,19 @@
         <v>2031</v>
       </c>
       <c r="I51" s="13">
-        <v>100.818</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.045</v>
       </c>
       <c r="J51" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6655276789892</v>
+      </c>
+      <c r="K51" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>145.84825050487001</v>
+      </c>
+      <c r="L51" s="13">
         <v>5.4649379355078</v>
-      </c>
-      <c r="K51" s="13">
-        <v>129.98804491460999</v>
-      </c>
-      <c r="L51" s="13">
-        <v>5.4017667057769998</v>
       </c>
       <c r="M51" s="14">
         <f>+_xlfn.XLOOKUP($N51,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6585,16 +9833,19 @@
         <v>2031</v>
       </c>
       <c r="I52" s="13">
-        <v>91.26</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>90.408500000000004</v>
       </c>
       <c r="J52" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.1195611694260004</v>
+      </c>
+      <c r="K52" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>88.923315379433006</v>
+      </c>
+      <c r="L52" s="13">
         <v>4.8767534636613004</v>
-      </c>
-      <c r="K52" s="13">
-        <v>69.125403489383004</v>
-      </c>
-      <c r="L52" s="13">
-        <v>4.7999393948671001</v>
       </c>
       <c r="M52" s="14">
         <f>+_xlfn.XLOOKUP($N52,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6642,16 +9893,19 @@
         <v>2031</v>
       </c>
       <c r="I53" s="13">
-        <v>93.474999999999994</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>92.59</v>
       </c>
       <c r="J53" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4655897091694996</v>
+      </c>
+      <c r="K53" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>123.21302337231</v>
+      </c>
+      <c r="L53" s="13">
         <v>5.2268554977413002</v>
-      </c>
-      <c r="K53" s="13">
-        <v>103.85503999808</v>
-      </c>
-      <c r="L53" s="13">
-        <v>5.0978896042555002</v>
       </c>
       <c r="M53" s="14">
         <f>+_xlfn.XLOOKUP($N53,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6698,16 +9952,19 @@
         <v>2031</v>
       </c>
       <c r="I54" s="26">
-        <v>74.83</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>71.2</v>
       </c>
       <c r="J54" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>10.358916231237</v>
+      </c>
+      <c r="K54" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>612.04511247723997</v>
+      </c>
+      <c r="L54" s="26">
         <v>9.0926741364232999</v>
-      </c>
-      <c r="K54" s="26">
-        <v>489.94439984998002</v>
-      </c>
-      <c r="L54" s="26">
-        <v>8.6660091505333998</v>
       </c>
       <c r="M54" s="27">
         <f>+_xlfn.XLOOKUP($N54,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6754,16 +10011,19 @@
         <v>2031</v>
       </c>
       <c r="I55" s="13">
-        <v>112.6699</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>112</v>
       </c>
       <c r="J55" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.2534529008212996</v>
+      </c>
+      <c r="K55" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>102.84299880966999</v>
+      </c>
+      <c r="L55" s="13">
         <v>5.1303234644179003</v>
-      </c>
-      <c r="K55" s="13">
-        <v>94.948125726268998</v>
-      </c>
-      <c r="L55" s="13">
-        <v>4.9498674514266998</v>
       </c>
       <c r="M55" s="14">
         <f>+_xlfn.XLOOKUP($N55,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6810,16 +10070,19 @@
         <v>2032</v>
       </c>
       <c r="I56" s="26">
-        <v>90.457499999999996</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>89.665000000000006</v>
       </c>
       <c r="J56" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6693575747171998</v>
+      </c>
+      <c r="K56" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>139.69353136211001</v>
+      </c>
+      <c r="L56" s="26">
         <v>5.4688768811572004</v>
-      </c>
-      <c r="K56" s="26">
-        <v>125.09910315875</v>
-      </c>
-      <c r="L56" s="26">
-        <v>5.3674177412753004</v>
       </c>
       <c r="M56" s="27">
         <f>+_xlfn.XLOOKUP($N56,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6862,16 +10125,19 @@
         <v>2032</v>
       </c>
       <c r="I57" s="13">
-        <v>90.445499999999996</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>91.35</v>
       </c>
       <c r="J57" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.2060902779280003</v>
+      </c>
+      <c r="K57" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>193.71209862641001</v>
+      </c>
+      <c r="L57" s="13">
         <v>6.4012437882361999</v>
-      </c>
-      <c r="K57" s="13">
-        <v>218.13974059820001</v>
-      </c>
-      <c r="L57" s="13">
-        <v>6.2331151566388003</v>
       </c>
       <c r="M57" s="14">
         <v>2000</v>
@@ -6918,16 +10184,19 @@
         <v>2032</v>
       </c>
       <c r="I58" s="13">
-        <v>90.4</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>89.334999999999994</v>
       </c>
       <c r="J58" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3264553980798004</v>
+      </c>
+      <c r="K58" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>104.58634938233</v>
+      </c>
+      <c r="L58" s="13">
         <v>5.0720630206267003</v>
-      </c>
-      <c r="K58" s="13">
-        <v>84.111858144086</v>
-      </c>
-      <c r="L58" s="13">
-        <v>4.9921546996049999</v>
       </c>
       <c r="M58" s="14">
         <f>+_xlfn.XLOOKUP($N58,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -6975,16 +10244,19 @@
         <v>2032</v>
       </c>
       <c r="I59" s="13">
-        <v>101.77</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.65949999999999</v>
       </c>
       <c r="J59" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3017698521792003</v>
+      </c>
+      <c r="K59" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>104.48845243629</v>
+      </c>
+      <c r="L59" s="13">
         <v>5.0642586010107999</v>
-      </c>
-      <c r="K59" s="13">
-        <v>85.485963290301001</v>
-      </c>
-      <c r="L59" s="13">
-        <v>4.8638137088405999</v>
       </c>
       <c r="M59" s="14">
         <f>+_xlfn.XLOOKUP($N59,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -7032,16 +10304,19 @@
         <v>2032</v>
       </c>
       <c r="I60" s="13">
-        <v>101.011</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>101.22</v>
       </c>
       <c r="J60" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0798164504439001</v>
+      </c>
+      <c r="K60" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>182.48566773145001</v>
+      </c>
+      <c r="L60" s="13">
         <v>6.1261381346982002</v>
-      </c>
-      <c r="K60" s="13">
-        <v>191.88007492214001</v>
-      </c>
-      <c r="L60" s="13">
-        <v>5.8657497923847002</v>
       </c>
       <c r="M60" s="14">
         <f>+_xlfn.XLOOKUP($N60,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -7089,16 +10364,19 @@
         <v>2032</v>
       </c>
       <c r="I61" s="13">
-        <v>99.3155</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.137500000000003</v>
       </c>
       <c r="J61" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.1903522881253998</v>
+      </c>
+      <c r="K61" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>92.336058409939</v>
+      </c>
+      <c r="L61" s="13">
         <v>4.9393697303708999</v>
-      </c>
-      <c r="K61" s="13">
-        <v>72.074971640130002</v>
-      </c>
-      <c r="L61" s="13">
-        <v>4.8443604233849999</v>
       </c>
       <c r="M61" s="14">
         <f>+_xlfn.XLOOKUP($N61,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -7145,16 +10423,19 @@
         <v>2032</v>
       </c>
       <c r="I62" s="26">
-        <v>79.400000000000006</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>74.254999999999995</v>
       </c>
       <c r="J62" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>11.064452371603</v>
+      </c>
+      <c r="K62" s="26">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>679.54222114839001</v>
+      </c>
+      <c r="L62" s="26">
         <v>9.5653205508415997</v>
-      </c>
-      <c r="K62" s="26">
-        <v>534.30350032287004</v>
-      </c>
-      <c r="L62" s="26">
-        <v>9.3807757333051001</v>
       </c>
       <c r="M62" s="27">
         <f>+_xlfn.XLOOKUP($N62,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -7197,16 +10478,19 @@
         <v>2032</v>
       </c>
       <c r="I63" s="13">
-        <v>97.382000000000005</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>96.6</v>
       </c>
       <c r="J63" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5462448562795998</v>
+      </c>
+      <c r="K63" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>128.79822976643001</v>
+      </c>
+      <c r="L63" s="13">
         <v>5.3686118665361002</v>
-      </c>
-      <c r="K63" s="13">
-        <v>115.79947915907999</v>
-      </c>
-      <c r="L63" s="13">
-        <v>5.2686449671825999</v>
       </c>
       <c r="M63" s="14">
         <v>2000</v>
@@ -7252,16 +10536,19 @@
         <v>2032</v>
       </c>
       <c r="I64" s="13">
-        <v>103.16925000000001</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>101.45</v>
       </c>
       <c r="J64" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.4450174366809998</v>
+      </c>
+      <c r="K64" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>115.28441250944</v>
+      </c>
+      <c r="L64" s="13">
         <v>5.1199812746477997</v>
-      </c>
-      <c r="K64" s="13">
-        <v>87.806085161064004</v>
-      </c>
-      <c r="L64" s="13">
-        <v>5.0980394520193997</v>
       </c>
       <c r="M64" s="14">
         <f>+_xlfn.XLOOKUP($N64,'[1]Cbonds export 05.20.2025'!$K:$K,'[1]Cbonds export 05.20.2025'!$J:$J,1,0,1)</f>
@@ -7304,16 +10591,19 @@
         <v>2032</v>
       </c>
       <c r="I65" s="13">
-        <v>101.663</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.830290000000005</v>
       </c>
       <c r="J65" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6084038561996996</v>
+      </c>
+      <c r="K65" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>132.64776343579999</v>
+      </c>
+      <c r="L65" s="13">
         <v>5.2464322657264004</v>
-      </c>
-      <c r="K65" s="13">
-        <v>101.38634535505</v>
-      </c>
-      <c r="L65" s="13">
-        <v>5.3856085213808997</v>
       </c>
       <c r="M65" s="14">
         <v>2000</v>
@@ -7355,16 +10645,19 @@
         <v>2032</v>
       </c>
       <c r="I66" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
         <v>96.5</v>
       </c>
       <c r="J66" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>7.8425335089162003</v>
+      </c>
+      <c r="K66" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>359.51228942138999</v>
+      </c>
+      <c r="L66" s="13">
         <v>7.8368882215886</v>
-      </c>
-      <c r="K66" s="13">
-        <v>364.54290681703998</v>
-      </c>
-      <c r="L66" s="13">
-        <v>7.8280887021760002</v>
       </c>
       <c r="M66" s="14">
         <v>1000</v>
@@ -7405,16 +10698,19 @@
         <v>2033</v>
       </c>
       <c r="I67" s="13">
-        <v>107.76</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>106.345</v>
       </c>
       <c r="J67" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.3970440982665</v>
+      </c>
+      <c r="K67" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>108.21583503986</v>
+      </c>
+      <c r="L67" s="13">
         <v>5.1640210219803997</v>
-      </c>
-      <c r="K67" s="13">
-        <v>90.100799827076997</v>
-      </c>
-      <c r="L67" s="13">
-        <v>5.0918269119830004</v>
       </c>
       <c r="M67" s="34">
         <v>2000</v>
@@ -7455,16 +10751,19 @@
         <v>2034</v>
       </c>
       <c r="I68" s="13">
-        <v>101.79</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>100.35850000000001</v>
       </c>
       <c r="J68" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.5691708429039997</v>
+      </c>
+      <c r="K68" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>118.94907886561001</v>
+      </c>
+      <c r="L68" s="13">
         <v>5.3474082910789997</v>
-      </c>
-      <c r="K68" s="13">
-        <v>102.32605446818</v>
-      </c>
-      <c r="L68" s="13">
-        <v>5.1724981641551997</v>
       </c>
       <c r="M68" s="14">
         <v>1000</v>
@@ -7506,16 +10805,19 @@
         <v>2035</v>
       </c>
       <c r="I69" s="13">
-        <v>96.627459999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>96.317999999999998</v>
       </c>
       <c r="J69" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>6.0105975518405002</v>
+      </c>
+      <c r="K69" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>156.68037460471001</v>
+      </c>
+      <c r="L69" s="13">
         <v>5.9627747994528999</v>
-      </c>
-      <c r="K69" s="13">
-        <v>159.65978946299001</v>
-      </c>
-      <c r="L69" s="13">
-        <v>5.7431229949776004</v>
       </c>
       <c r="M69" s="14">
         <v>2000</v>
@@ -7556,16 +10858,19 @@
         <v>2035</v>
       </c>
       <c r="I70" s="13">
-        <v>104.18174999999999</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>102.9</v>
       </c>
       <c r="J70" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.6258500906032998</v>
+      </c>
+      <c r="K70" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>123.99159377725</v>
+      </c>
+      <c r="L70" s="13">
         <v>5.4373842285820997</v>
-      </c>
-      <c r="K70" s="13">
-        <v>110.72756212295999</v>
-      </c>
-      <c r="L70" s="13">
-        <v>5.3727784157435998</v>
       </c>
       <c r="M70" s="14">
         <v>2000</v>
@@ -7607,16 +10912,19 @@
         <v>2035</v>
       </c>
       <c r="I71" s="13">
-        <v>100.16</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>98.7</v>
       </c>
       <c r="J71" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.7725722026141</v>
+      </c>
+      <c r="K71" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>137.50043898965001</v>
+      </c>
+      <c r="L71" s="13">
         <v>5.5503247750032996</v>
-      </c>
-      <c r="K71" s="13">
-        <v>120.89879267489</v>
-      </c>
-      <c r="L71" s="13">
-        <v>5.4514660395618</v>
       </c>
       <c r="M71" s="14">
         <v>2000</v>
@@ -7657,16 +10965,19 @@
         <v>2035</v>
       </c>
       <c r="I72" s="13">
-        <v>100.685</v>
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$H$2:$H$220)</f>
+        <v>99.394999999999996</v>
       </c>
       <c r="J72" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$K$2:$K$220)</f>
+        <v>5.8749240448719</v>
+      </c>
+      <c r="K72" s="13">
+        <f>_xlfn.XLOOKUP(Bonos[[#This Row],[ISIN]],[2]bonos!$AG$2:$AG$220,[2]bonos!$AP$2:$AP$220)</f>
+        <v>147.81754548412999</v>
+      </c>
+      <c r="L72" s="13">
         <v>5.6758894124054997</v>
-      </c>
-      <c r="K72" s="13">
-        <v>134.82334868976</v>
-      </c>
-      <c r="L72" s="13">
-        <v>5.5378214915232</v>
       </c>
       <c r="M72" s="14">
         <v>2000</v>
@@ -7686,77 +10997,77 @@
     <cfRule type="duplicateValues" dxfId="18" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1" xr:uid="{388245D2-8DD6-4087-A7F8-8040150E97BC}"/>
-    <hyperlink ref="N3" r:id="rId2" xr:uid="{1787DBED-81D4-4512-AAE1-8A6C5F68FA76}"/>
-    <hyperlink ref="N4" r:id="rId3" xr:uid="{45766180-88CA-4ED2-8074-5E44DD7FF760}"/>
-    <hyperlink ref="N5" r:id="rId4" xr:uid="{19DB2657-953E-464A-94AA-8A3F053005E0}"/>
-    <hyperlink ref="N6" r:id="rId5" xr:uid="{73578B1E-F8E6-43BB-B71A-B46047D81383}"/>
-    <hyperlink ref="N7" r:id="rId6" xr:uid="{582207F9-DAF8-43D8-9B59-BCFF2B48FDE2}"/>
-    <hyperlink ref="N8" r:id="rId7" xr:uid="{4AAB2268-075D-4F51-A04A-C8678B42D2AE}"/>
-    <hyperlink ref="N9" r:id="rId8" xr:uid="{E3922AA0-2B8F-45D5-9AD6-A8019D713F7D}"/>
-    <hyperlink ref="N10" r:id="rId9" xr:uid="{C0C72420-4E37-4A66-A87D-33C9BD4B0B3C}"/>
-    <hyperlink ref="N11" r:id="rId10" xr:uid="{79AC8E65-7DCA-40C6-97D7-9B4B6BBC7AD1}"/>
-    <hyperlink ref="N12" r:id="rId11" xr:uid="{9EDA0AEC-DB10-4D8D-AD14-9B689E212E67}"/>
-    <hyperlink ref="N13" r:id="rId12" xr:uid="{AC85EA30-A42D-4D9B-B32E-4AF675012F32}"/>
-    <hyperlink ref="N14" r:id="rId13" xr:uid="{DD39554D-E52F-428B-AACE-D8F876B2C92F}"/>
-    <hyperlink ref="N15" r:id="rId14" xr:uid="{DA401183-C542-435A-A956-9F4E60264F43}"/>
-    <hyperlink ref="N16" r:id="rId15" xr:uid="{DF95C386-399A-4BEE-9EE7-1A40DAA6AE88}"/>
-    <hyperlink ref="N20" r:id="rId16" xr:uid="{08069BA9-9801-419C-825B-DB74431BCBB1}"/>
-    <hyperlink ref="N21" r:id="rId17" xr:uid="{C44016D9-1BBE-4C21-95A5-CEA414857EFE}"/>
-    <hyperlink ref="N22" r:id="rId18" xr:uid="{BCEE1BB4-7A08-4AAC-BE7A-C9FAA84A7CA0}"/>
-    <hyperlink ref="N23" r:id="rId19" xr:uid="{D93BB35A-044D-4236-AF93-9D66EF392147}"/>
-    <hyperlink ref="N24" r:id="rId20" xr:uid="{210C65A5-16B7-4F23-9E17-7E8EC7ECAE48}"/>
-    <hyperlink ref="N25" r:id="rId21" xr:uid="{FA84CA0B-C26E-4E1C-94CA-792AF502D0E5}"/>
-    <hyperlink ref="N26" r:id="rId22" xr:uid="{B1D1B7AB-AA6B-4EA9-9873-5AC34AD5B0EF}"/>
-    <hyperlink ref="N28" r:id="rId23" xr:uid="{9B8AD11E-3831-40CA-9FDD-A6C142546664}"/>
-    <hyperlink ref="N29" r:id="rId24" xr:uid="{41238C85-DA41-420E-8AE5-4133D4FA4531}"/>
-    <hyperlink ref="N30" r:id="rId25" xr:uid="{D54F90FD-5973-4C5E-BAAF-6FDE129B3BCE}"/>
-    <hyperlink ref="N31" r:id="rId26" xr:uid="{E329DA29-81F6-4F9B-9141-C86B9650D0B4}"/>
-    <hyperlink ref="N33" r:id="rId27" xr:uid="{A3634148-4321-4749-A16B-5F3ED8933349}"/>
-    <hyperlink ref="N34" r:id="rId28" xr:uid="{D470723C-5043-4B22-A669-B60D3D1F1C04}"/>
-    <hyperlink ref="N35" r:id="rId29" xr:uid="{C1DCB0A5-9CB2-43C9-BFBF-A17C192794A2}"/>
-    <hyperlink ref="N36" r:id="rId30" xr:uid="{C7C3D187-8B11-4995-B409-DD905158877B}"/>
-    <hyperlink ref="N37" r:id="rId31" xr:uid="{B9200BE9-E32A-49AB-9D4E-0C6D4D194E60}"/>
-    <hyperlink ref="N38" r:id="rId32" xr:uid="{E3BB1EDA-9DE0-452F-B653-5ACA209BBF6C}"/>
-    <hyperlink ref="N39" r:id="rId33" xr:uid="{FBFFB7BE-7898-4976-8389-A56004E9DE2F}"/>
-    <hyperlink ref="N40" r:id="rId34" xr:uid="{EBFE958C-420E-4E0F-BE4F-C7175591010A}"/>
-    <hyperlink ref="N41" r:id="rId35" xr:uid="{93574D83-47E3-40BC-BD8B-FA5112591208}"/>
-    <hyperlink ref="N42" r:id="rId36" xr:uid="{C84FB5CE-4CBD-4B3D-8BC0-7B17A496BC1B}"/>
-    <hyperlink ref="N43" r:id="rId37" xr:uid="{4F2538FE-C213-4CA9-8FA1-18BABD9B0B62}"/>
-    <hyperlink ref="N44" r:id="rId38" xr:uid="{4D7E96E9-048C-4EC4-84D2-1DE7C02645DB}"/>
-    <hyperlink ref="N45" r:id="rId39" xr:uid="{03375205-EB20-4E41-B3CF-54B820435C0E}"/>
-    <hyperlink ref="N47" r:id="rId40" xr:uid="{A2680AB3-C514-4A50-AA51-4EAB5F4494BC}"/>
-    <hyperlink ref="N49" r:id="rId41" xr:uid="{8E661B0F-D115-41DF-9F03-65695773A771}"/>
-    <hyperlink ref="N51" r:id="rId42" xr:uid="{BDDC8155-9A73-46EA-ADDE-E8E3FA9CF310}"/>
-    <hyperlink ref="N52" r:id="rId43" xr:uid="{261E1E8E-F47F-4289-BF62-502EBD95F09F}"/>
-    <hyperlink ref="N53" r:id="rId44" xr:uid="{AB24E5A9-B84E-4111-AF5E-E34C09E843E1}"/>
-    <hyperlink ref="N54" r:id="rId45" xr:uid="{EDFD14C9-58C7-4A90-B75B-FC59C9904543}"/>
-    <hyperlink ref="N55" r:id="rId46" xr:uid="{8E651C69-068E-4974-ADB2-15F9B4A345D4}"/>
-    <hyperlink ref="N56" r:id="rId47" xr:uid="{A18B9D51-3CC3-4D1B-9058-7CA971B4FEFE}"/>
-    <hyperlink ref="N57" r:id="rId48" xr:uid="{8E77C782-7F4A-42D8-92A7-0BFBC59BA738}"/>
-    <hyperlink ref="N58" r:id="rId49" xr:uid="{CA2CD777-5B48-4197-8BC2-EA29ECCA712E}"/>
-    <hyperlink ref="N59" r:id="rId50" xr:uid="{AE407265-FFC4-46BB-93E7-CA28E7C79B51}"/>
-    <hyperlink ref="N60" r:id="rId51" xr:uid="{D1ABB082-15BB-4AED-898A-4AA0318E41E8}"/>
-    <hyperlink ref="N61" r:id="rId52" xr:uid="{6E735788-6EA0-4AA4-ABD5-7442AE5349E8}"/>
-    <hyperlink ref="N63" r:id="rId53" xr:uid="{447B777D-195D-4187-AAE8-49E99E1CF92C}"/>
-    <hyperlink ref="N64" r:id="rId54" xr:uid="{509290E1-ADB3-4AE8-8B32-6871C3695877}"/>
-    <hyperlink ref="N69" r:id="rId55" xr:uid="{4E89D73A-3539-49AB-BCA0-7FD61E2EB35E}"/>
-    <hyperlink ref="N70" r:id="rId56" xr:uid="{B0A9DB4B-DF72-4520-BCE3-687191D9D821}"/>
-    <hyperlink ref="N71" r:id="rId57" xr:uid="{89F72D93-D0F3-4AD7-B7AE-FFB219591847}"/>
-    <hyperlink ref="N46" r:id="rId58" xr:uid="{3CDF5DDE-CFB7-40D2-A90E-1CB75F3BF644}"/>
-    <hyperlink ref="N65" r:id="rId59" xr:uid="{A60638F8-A009-4A91-A7C2-0B801C25F02F}"/>
-    <hyperlink ref="N72" r:id="rId60" xr:uid="{52CF0C58-75BA-4046-9CD9-89BFCD44489C}"/>
-    <hyperlink ref="N66" r:id="rId61" xr:uid="{E1FD5A46-89A7-4F84-B3EB-8E515029A5E6}"/>
-    <hyperlink ref="N67" r:id="rId62" xr:uid="{DF8DA8DD-7196-428B-9BEE-5EC17E5E3690}"/>
-    <hyperlink ref="N48" r:id="rId63" xr:uid="{751E1192-0D7C-45E0-98D0-88F9D9DC41A2}"/>
-    <hyperlink ref="N62" r:id="rId64" xr:uid="{9627C054-F53B-4951-A867-1CAFF03E890D}"/>
-    <hyperlink ref="N19" r:id="rId65" xr:uid="{1123F2A3-16A8-4665-98B1-23C12A68992A}"/>
-    <hyperlink ref="N32" r:id="rId66" xr:uid="{EDBF908D-B2E5-4842-9B28-34C8FC582098}"/>
-    <hyperlink ref="N18" r:id="rId67" xr:uid="{C2DE4F44-173C-4C5D-A20F-26B05F5CDB39}"/>
-    <hyperlink ref="N27" r:id="rId68" xr:uid="{A1A7852A-81C9-412F-AF54-C68B5936B6A5}"/>
-    <hyperlink ref="N17" r:id="rId69" xr:uid="{D0B249A0-F7A7-4C00-861A-973769BA5767}"/>
-    <hyperlink ref="N68" r:id="rId70" xr:uid="{FAD23788-5072-4C11-BAE0-284EDC71C04C}"/>
-    <hyperlink ref="N50" r:id="rId71" xr:uid="{2332F014-1F3A-43A5-A75B-A98D5C4F609C}"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{76725CEC-E542-4C48-B21D-3D1BE2EAA354}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{C370E2C9-29C4-4629-846C-C41B924A28B2}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{52E623B7-0DDA-41B8-9B6D-14FE6CE4B61F}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{01763600-0BAD-48FB-83ED-B8E6E458BB0F}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{C9A3109B-C836-47A0-8F96-1BA899EEEB7A}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{96B0B780-32F6-4B91-95C8-BC018A49D919}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{194A24F4-476A-4388-B158-B2C42C56C02F}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{93ED46B6-D159-4034-9C5E-8598E43493DB}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{1CE09E4A-8F37-45B3-A882-4C65EDBC6EAB}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{EF502E88-3B09-4D4A-BB30-129F827D1036}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{16FB8FFA-5146-40AB-B203-029CEEBBC78B}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{29710257-8F76-4091-8380-495A56252A67}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{9DCD5F39-3CF0-4AF0-BE79-4B0F7770B6A8}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{AB0101FD-CE2A-4999-BB68-467E6240CF68}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{65C920AE-93A3-4017-B8C7-9C8C8689190C}"/>
+    <hyperlink ref="N20" r:id="rId16" xr:uid="{34020D06-C622-4668-906A-D81FED824CC4}"/>
+    <hyperlink ref="N21" r:id="rId17" xr:uid="{C46F4249-F90B-4876-88E6-85DBF0E96860}"/>
+    <hyperlink ref="N22" r:id="rId18" xr:uid="{6FFF8185-6039-471A-B312-611B55599FF4}"/>
+    <hyperlink ref="N23" r:id="rId19" xr:uid="{92203DB2-6BB1-46F7-80A9-F51DCE1DF12F}"/>
+    <hyperlink ref="N24" r:id="rId20" xr:uid="{12A7386B-B570-43F7-94D1-597C611F7E1C}"/>
+    <hyperlink ref="N25" r:id="rId21" xr:uid="{FD5FDD6B-06D5-4491-820C-5C099B638AFA}"/>
+    <hyperlink ref="N26" r:id="rId22" xr:uid="{224637F3-9363-4689-882B-7E886B1CD14B}"/>
+    <hyperlink ref="N28" r:id="rId23" xr:uid="{350CCD17-6E59-4349-AAF3-B790F73C432C}"/>
+    <hyperlink ref="N29" r:id="rId24" xr:uid="{C3B9E9C0-C7D0-4CAE-A429-21597C8F4599}"/>
+    <hyperlink ref="N30" r:id="rId25" xr:uid="{34CFCE23-2BCF-4A96-9774-EE39CBE51F3F}"/>
+    <hyperlink ref="N31" r:id="rId26" xr:uid="{113F98A6-AEF5-4880-975D-D84F051AB347}"/>
+    <hyperlink ref="N33" r:id="rId27" xr:uid="{AA8253C7-0C75-4523-9E4E-7607118E633D}"/>
+    <hyperlink ref="N34" r:id="rId28" xr:uid="{BFDF88EC-D2F9-43A3-97A9-9369A0BF7FEC}"/>
+    <hyperlink ref="N35" r:id="rId29" xr:uid="{34742F6A-151D-4BCD-BC5F-6D5E0F071A8F}"/>
+    <hyperlink ref="N36" r:id="rId30" xr:uid="{34863CEB-6F75-4EE5-9783-4C5BDEF5A620}"/>
+    <hyperlink ref="N37" r:id="rId31" xr:uid="{35556A0E-1A29-4C25-BB86-E9425F9CFB41}"/>
+    <hyperlink ref="N38" r:id="rId32" xr:uid="{665880E9-C07B-48E5-8DC0-F8EA5CF2AAFD}"/>
+    <hyperlink ref="N39" r:id="rId33" xr:uid="{44566013-4EE1-411E-867C-2D029FC45F1D}"/>
+    <hyperlink ref="N40" r:id="rId34" xr:uid="{E6499354-F12C-44B1-AA84-AC4B3A53FADB}"/>
+    <hyperlink ref="N41" r:id="rId35" xr:uid="{167E816E-1227-455C-9627-E752D0FA0B05}"/>
+    <hyperlink ref="N42" r:id="rId36" xr:uid="{FCF2758D-F1F4-4119-9478-8B876D4A7A23}"/>
+    <hyperlink ref="N43" r:id="rId37" xr:uid="{74264922-A8E2-4FBA-89B6-46C6F25C37C2}"/>
+    <hyperlink ref="N44" r:id="rId38" xr:uid="{4C852086-4650-470A-80DB-02BE23CCF5F5}"/>
+    <hyperlink ref="N45" r:id="rId39" xr:uid="{B7B33836-6EF9-4212-B3A3-F17F72C50797}"/>
+    <hyperlink ref="N47" r:id="rId40" xr:uid="{B83712DA-E2CE-42D1-A08C-72863DD33658}"/>
+    <hyperlink ref="N49" r:id="rId41" xr:uid="{67AB54BD-AC34-4589-8F2C-F798B7A09F5D}"/>
+    <hyperlink ref="N51" r:id="rId42" xr:uid="{CFF01FF2-8DD0-4BF0-B544-C5D2B25FF19E}"/>
+    <hyperlink ref="N52" r:id="rId43" xr:uid="{AB4F5FEC-BF66-4432-B951-DBD067D1391D}"/>
+    <hyperlink ref="N53" r:id="rId44" xr:uid="{B44BC268-C9B1-4D35-8A61-B5775A5A028B}"/>
+    <hyperlink ref="N54" r:id="rId45" xr:uid="{5D7C9D53-2E84-40E8-BA61-5320181D091B}"/>
+    <hyperlink ref="N55" r:id="rId46" xr:uid="{A8795727-E8B3-4AE7-8AE9-E890BEE3C5BF}"/>
+    <hyperlink ref="N56" r:id="rId47" xr:uid="{E5D8DC37-A4A4-47F3-9BAE-98269CD6FD73}"/>
+    <hyperlink ref="N57" r:id="rId48" xr:uid="{F1B77FBB-ADBE-4A0B-B80D-CD50AB8D1438}"/>
+    <hyperlink ref="N58" r:id="rId49" xr:uid="{49EEE676-0394-429A-A3CD-0C344876B586}"/>
+    <hyperlink ref="N59" r:id="rId50" xr:uid="{B2458CC8-DBBF-4240-AF46-B0EB816B387B}"/>
+    <hyperlink ref="N60" r:id="rId51" xr:uid="{683745DC-55DF-41F7-8307-CEF93F48E5C0}"/>
+    <hyperlink ref="N61" r:id="rId52" xr:uid="{E9606208-82D7-456D-B718-676E7F873FB1}"/>
+    <hyperlink ref="N63" r:id="rId53" xr:uid="{5C401F55-C2CE-4185-867C-E277D8BA95A7}"/>
+    <hyperlink ref="N64" r:id="rId54" xr:uid="{9EB066EF-22C8-4939-8F9E-936B05907177}"/>
+    <hyperlink ref="N69" r:id="rId55" xr:uid="{F002B98D-F056-46A4-8F18-3310F4D41A2A}"/>
+    <hyperlink ref="N70" r:id="rId56" xr:uid="{E53E3A39-F1EC-4B1D-B7F5-4E698FFF5317}"/>
+    <hyperlink ref="N71" r:id="rId57" xr:uid="{621ECAFC-C556-4B2E-B329-17049D11A217}"/>
+    <hyperlink ref="N46" r:id="rId58" xr:uid="{C0611DEA-BF7F-4716-B3C9-2BC813F787D4}"/>
+    <hyperlink ref="N65" r:id="rId59" xr:uid="{BD7E47A4-B535-426E-8156-834959CA3564}"/>
+    <hyperlink ref="N72" r:id="rId60" xr:uid="{0FA04D43-9E13-4E05-89CF-73DA6D28DD73}"/>
+    <hyperlink ref="N66" r:id="rId61" xr:uid="{9AE054E2-3F35-4C66-A625-045E293BF79D}"/>
+    <hyperlink ref="N67" r:id="rId62" xr:uid="{A2BA32D4-C23A-419C-891C-75321C4FC367}"/>
+    <hyperlink ref="N48" r:id="rId63" xr:uid="{99871DF9-C5DC-4FDC-AD75-6713AF303BD8}"/>
+    <hyperlink ref="N62" r:id="rId64" xr:uid="{F7476DEC-EB35-440D-9F9E-3635F074F14B}"/>
+    <hyperlink ref="N19" r:id="rId65" xr:uid="{B7C0719D-12C1-440A-8E74-F1EC1FE01243}"/>
+    <hyperlink ref="N32" r:id="rId66" xr:uid="{1DA51581-72B9-4AC9-8F15-59F9AA508C44}"/>
+    <hyperlink ref="N18" r:id="rId67" xr:uid="{C34DF029-BA99-42A0-961A-6921DE05E2D1}"/>
+    <hyperlink ref="N27" r:id="rId68" xr:uid="{2423F2A3-29B1-4364-8C5F-252A0825106D}"/>
+    <hyperlink ref="N17" r:id="rId69" xr:uid="{9422EA53-8A22-4DAF-B976-9D98FC460BEA}"/>
+    <hyperlink ref="N68" r:id="rId70" xr:uid="{AF436497-81EB-4DC2-A4FA-7749A2F72423}"/>
+    <hyperlink ref="N50" r:id="rId71" xr:uid="{DC85DBED-8674-4EA2-A26E-18071782CF62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Bonos Ejemplo.xlsx
+++ b/Bonos Ejemplo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Claude\Projects\Presentaciones de Quarter\Github Pagina\Bonos-FCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F73195F-8E8D-453E-B2FE-65444130FC48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25B5536-5375-4A84-A11B-514384CF6E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8D98F1BD-7C59-42F2-9210-D24E4400257D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="219">
   <si>
     <t>Industry</t>
   </si>
@@ -284,9 +284,6 @@
     <t>Petrobras</t>
   </si>
   <si>
-    <t>US71647NBE85</t>
-  </si>
-  <si>
     <t>US92556VAD82</t>
   </si>
   <si>
@@ -335,9 +332,6 @@
     <t>Micron Technology</t>
   </si>
   <si>
-    <t>US595112CD31</t>
-  </si>
-  <si>
     <t>US71647NBH17</t>
   </si>
   <si>
@@ -396,9 +390,6 @@
   </si>
   <si>
     <t>BBB/BBB</t>
-  </si>
-  <si>
-    <t>US595112CG61</t>
   </si>
   <si>
     <t>US403949AT72</t>
@@ -634,9 +625,6 @@
     <t>Withdrawn/BBB-/BBB-</t>
   </si>
   <si>
-    <t>15/01/2030</t>
-  </si>
-  <si>
     <t>22/06/2030</t>
   </si>
   <si>
@@ -655,12 +643,6 @@
     <t>Semiconductors</t>
   </si>
   <si>
-    <t>-/BBB-/BBB</t>
-  </si>
-  <si>
-    <t>15/01/2031</t>
-  </si>
-  <si>
     <t>25/03/2031</t>
   </si>
   <si>
@@ -695,6 +677,27 @@
   </si>
   <si>
     <t>14/05/2032</t>
+  </si>
+  <si>
+    <t>Nexstar</t>
+  </si>
+  <si>
+    <t>Nexstar Broadcasting</t>
+  </si>
+  <si>
+    <t>BB-/BB</t>
+  </si>
+  <si>
+    <t>USU6497RAL88</t>
+  </si>
+  <si>
+    <t>US595112CB74</t>
+  </si>
+  <si>
+    <t>US595112CH45</t>
+  </si>
+  <si>
+    <t>US403949AS99</t>
   </si>
 </sst>
 </file>
@@ -753,7 +756,7 @@
       <name val="Comfortaa"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -784,8 +787,14 @@
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -893,6 +902,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -900,7 +922,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1004,12 +1026,6 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1025,21 +1041,41 @@
     <xf numFmtId="168" fontId="5" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1048,16 +1084,6 @@
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1641,6 +1667,16 @@
           <color indexed="64"/>
         </top>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1676,25 +1712,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}" name="Bonos" displayName="Bonos" ref="A1:P74" totalsRowShown="0" headerRowBorderDxfId="17" tableBorderDxfId="18">
-  <autoFilter ref="A1:P74" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}" name="Bonos" displayName="Bonos" ref="A1:P75" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="17">
+  <autoFilter ref="A1:P75" xr:uid="{230D75E2-0085-4336-AFA2-57D16F49E896}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{EAF877B8-4926-4959-BBFA-585A75C8391D}" name="Issuer" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{B2C00443-39F1-4600-BE48-DDA923D78603}" name="Industry" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{056A063A-7DD1-426B-801B-BA928025AEA7}" name="Guarantor/Organization" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{025668FE-93B1-4247-8E7A-ABE2826DECF9}" name="IG - HY" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{93EB2ECC-49AC-4CF3-BEA3-A986802A4943}" name="Rating" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{C652B961-0C28-471B-A2F2-0484E1BCEEA3}" name="Coupon %" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{BC3F132C-6722-43C0-8763-BCF6C453DE6C}" name="Maturity" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{186BEC2D-B3E8-4C1B-AF49-D26B793A588E}" name="Year" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{C5B9CC1E-2FA8-48FA-ACF8-02CFF554B424}" name="Price" dataDxfId="8"/>
-    <tableColumn id="9" xr3:uid="{74DBEB6E-2B38-4756-9C55-DC41829F2AAE}" name="YTW %" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{C7B9A70F-7A8D-4ECF-B313-D80162BEF2AC}" name="Gspread" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{0445B399-F1E4-4E60-B4C4-F7BCF55169D7}" name="Prev month_x000a_YTW%" dataDxfId="5" dataCellStyle="Porcentaje"/>
-    <tableColumn id="16" xr3:uid="{598A638E-5D30-4402-8C03-7D8FB7026143}" name="Minimum Settlement" dataDxfId="4" dataCellStyle="Millares 3"/>
-    <tableColumn id="17" xr3:uid="{6C62A4A4-AF52-466C-9C5B-18BFC7CB7F2E}" name="ISIN" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{1BC656B6-7DF8-499B-94D4-E75FA0DEE401}" name="Outstanding_x000a_US$" dataDxfId="2" dataCellStyle="Millares 3"/>
-    <tableColumn id="22" xr3:uid="{ACB77059-8EFE-49B1-BE87-11A1BB6FF77E}" name="Decisión" dataDxfId="1" dataCellStyle="Porcentaje"/>
+    <tableColumn id="1" xr3:uid="{EAF877B8-4926-4959-BBFA-585A75C8391D}" name="Issuer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{B2C00443-39F1-4600-BE48-DDA923D78603}" name="Industry" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{056A063A-7DD1-426B-801B-BA928025AEA7}" name="Guarantor/Organization" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{025668FE-93B1-4247-8E7A-ABE2826DECF9}" name="IG - HY" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{93EB2ECC-49AC-4CF3-BEA3-A986802A4943}" name="Rating" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{C652B961-0C28-471B-A2F2-0484E1BCEEA3}" name="Coupon %" dataDxfId="10" dataCellStyle="Porcentaje"/>
+    <tableColumn id="7" xr3:uid="{BC3F132C-6722-43C0-8763-BCF6C453DE6C}" name="Maturity" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{186BEC2D-B3E8-4C1B-AF49-D26B793A588E}" name="Year" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{C5B9CC1E-2FA8-48FA-ACF8-02CFF554B424}" name="Price" dataDxfId="7" dataCellStyle="Porcentaje"/>
+    <tableColumn id="9" xr3:uid="{74DBEB6E-2B38-4756-9C55-DC41829F2AAE}" name="YTW %" dataDxfId="6" dataCellStyle="Porcentaje"/>
+    <tableColumn id="21" xr3:uid="{C7B9A70F-7A8D-4ECF-B313-D80162BEF2AC}" name="Gspread" dataDxfId="5" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{0445B399-F1E4-4E60-B4C4-F7BCF55169D7}" name="Prev month_x000a_YTW%" dataDxfId="4" dataCellStyle="Porcentaje"/>
+    <tableColumn id="16" xr3:uid="{598A638E-5D30-4402-8C03-7D8FB7026143}" name="Minimum Settlement" dataDxfId="3" dataCellStyle="Millares 3"/>
+    <tableColumn id="17" xr3:uid="{6C62A4A4-AF52-466C-9C5B-18BFC7CB7F2E}" name="ISIN" dataDxfId="2" dataCellStyle="Hipervínculo"/>
+    <tableColumn id="18" xr3:uid="{1BC656B6-7DF8-499B-94D4-E75FA0DEE401}" name="Outstanding_x000a_US$" dataDxfId="1" dataCellStyle="Millares 3"/>
+    <tableColumn id="22" xr3:uid="{ACB77059-8EFE-49B1-BE87-11A1BB6FF77E}" name="Decisión" dataDxfId="0" dataCellStyle="Porcentaje"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2017,7 +2053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6EFF2F4-11C0-433C-9540-66AEF48816EC}">
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
@@ -2029,7 +2065,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="48" thickBot="1">
       <c r="A1" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -2053,16 +2089,16 @@
         <v>6</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>8</v>
@@ -2071,15 +2107,15 @@
         <v>9</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>10</v>
@@ -2097,19 +2133,19 @@
         <v>2.4500000000000001E-2</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H2" s="12">
         <v>2026</v>
       </c>
       <c r="I2" s="13">
-        <v>99.685000000000002</v>
+        <v>99.73</v>
       </c>
       <c r="J2" s="13">
-        <v>4.2751715585558001</v>
+        <v>4.2681325787883999</v>
       </c>
       <c r="K2" s="13">
-        <v>27.117862329451999</v>
+        <v>12.822129613775999</v>
       </c>
       <c r="L2" s="13">
         <v>4.3908531690574</v>
@@ -2124,12 +2160,12 @@
         <v>3750000000</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>15</v>
@@ -2153,13 +2189,13 @@
         <v>2027</v>
       </c>
       <c r="I3" s="13">
-        <v>100.645</v>
+        <v>100.565</v>
       </c>
       <c r="J3" s="13">
-        <v>4.9850285338565996</v>
+        <v>5.0713468228730001</v>
       </c>
       <c r="K3" s="13">
-        <v>93.572981922588994</v>
+        <v>89.547446774714999</v>
       </c>
       <c r="L3" s="13">
         <v>5.2217860674756</v>
@@ -2174,12 +2210,12 @@
         <v>1500000000</v>
       </c>
       <c r="P3" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="8" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>10</v>
@@ -2203,13 +2239,13 @@
         <v>2027</v>
       </c>
       <c r="I4" s="13">
-        <v>100</v>
+        <v>99.9298</v>
       </c>
       <c r="J4" s="13">
-        <v>4.6735271029955996</v>
+        <v>4.7409126459433004</v>
       </c>
       <c r="K4" s="13">
-        <v>59.080262986065001</v>
+        <v>53.841513991905003</v>
       </c>
       <c r="L4" s="13">
         <v>4.7551093516370004</v>
@@ -2224,7 +2260,7 @@
         <v>600000000</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2232,7 +2268,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>20</v>
@@ -2241,7 +2277,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F5" s="10">
         <v>0.05</v>
@@ -2253,13 +2289,13 @@
         <v>2027</v>
       </c>
       <c r="I5" s="13">
-        <v>99.847949999999997</v>
+        <v>99.719499999999996</v>
       </c>
       <c r="J5" s="13">
-        <v>5.2313833334266002</v>
+        <v>5.3852370152370002</v>
       </c>
       <c r="K5" s="13">
-        <v>116.44021798646</v>
+        <v>119.52893362655</v>
       </c>
       <c r="L5" s="13">
         <v>5.1261015299891</v>
@@ -2274,7 +2310,7 @@
         <v>1500000000</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2282,7 +2318,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>23</v>
@@ -2291,25 +2327,25 @@
         <v>21</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F6" s="10">
         <v>2.3E-2</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H6" s="12">
         <v>2027</v>
       </c>
       <c r="I6" s="13">
-        <v>97.986000000000004</v>
+        <v>98.011650000000003</v>
       </c>
       <c r="J6" s="13">
-        <v>4.8733743941504004</v>
+        <v>4.9189154981372996</v>
       </c>
       <c r="K6" s="13">
-        <v>81.508396187211005</v>
+        <v>73.588804077334999</v>
       </c>
       <c r="L6" s="13">
         <v>5.0240797819032004</v>
@@ -2324,42 +2360,42 @@
         <v>748995000</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="21" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>34</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D7" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F7" s="23">
         <v>3.7499999999999999E-2</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H7" s="25">
         <v>2027</v>
       </c>
       <c r="I7" s="26">
-        <v>97.79</v>
+        <v>97.775000000000006</v>
       </c>
       <c r="J7" s="26">
-        <v>5.7883568215804004</v>
+        <v>5.8457393832182003</v>
       </c>
       <c r="K7" s="26">
-        <v>170.15677143529999</v>
+        <v>163.99984454138999</v>
       </c>
       <c r="L7" s="26">
         <v>5.8138386217568003</v>
@@ -2368,13 +2404,13 @@
         <v>200000</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O7" s="29">
         <v>89906000</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2382,7 +2418,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>25</v>
@@ -2391,7 +2427,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F8" s="10">
         <v>4.4999999999999998E-2</v>
@@ -2403,13 +2439,13 @@
         <v>2028</v>
       </c>
       <c r="I8" s="13">
-        <v>99.372050000000002</v>
+        <v>99.247950000000003</v>
       </c>
       <c r="J8" s="13">
-        <v>4.8499595801598998</v>
+        <v>4.9138418529288996</v>
       </c>
       <c r="K8" s="13">
-        <v>67.648791341481001</v>
+        <v>63.867869142072003</v>
       </c>
       <c r="L8" s="13">
         <v>4.9684822597879998</v>
@@ -2424,7 +2460,7 @@
         <v>300000000</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2432,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>27</v>
@@ -2441,7 +2477,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F9" s="10">
         <v>2.1999999999999999E-2</v>
@@ -2453,13 +2489,13 @@
         <v>2028</v>
       </c>
       <c r="I9" s="13">
-        <v>94.65</v>
+        <v>94.47</v>
       </c>
       <c r="J9" s="13">
-        <v>4.8636154837822003</v>
+        <v>4.9881788772356996</v>
       </c>
       <c r="K9" s="13">
-        <v>69.259574156927997</v>
+        <v>71.498670192738004</v>
       </c>
       <c r="L9" s="13">
         <v>5.0342310397633003</v>
@@ -2474,7 +2510,7 @@
         <v>750000000</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2503,13 +2539,13 @@
         <v>2028</v>
       </c>
       <c r="I10" s="13">
-        <v>100.405</v>
+        <v>100.12235</v>
       </c>
       <c r="J10" s="13">
-        <v>4.8499941340286998</v>
+        <v>4.9961346783638998</v>
       </c>
       <c r="K10" s="13">
-        <v>69.185109144766997</v>
+        <v>73.329477774360001</v>
       </c>
       <c r="L10" s="13">
         <v>4.9840141275835004</v>
@@ -2524,7 +2560,7 @@
         <v>750000000</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2532,7 +2568,7 @@
         <v>32</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>32</v>
@@ -2541,25 +2577,25 @@
         <v>21</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F11" s="10">
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H11" s="12">
         <v>2028</v>
       </c>
       <c r="I11" s="13">
-        <v>98.725499999999997</v>
+        <v>98.314999999999998</v>
       </c>
       <c r="J11" s="13">
-        <v>4.9682437000966999</v>
+        <v>5.1995659267661001</v>
       </c>
       <c r="K11" s="13">
-        <v>81.257140253227007</v>
+        <v>93.871553431387994</v>
       </c>
       <c r="L11" s="13">
         <v>5.1978025665273</v>
@@ -2574,42 +2610,42 @@
         <v>600000000</v>
       </c>
       <c r="P11" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F12" s="23">
         <v>5.5E-2</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H12" s="25">
         <v>2028</v>
       </c>
       <c r="I12" s="26">
-        <v>55.125</v>
+        <v>56.375</v>
       </c>
       <c r="J12" s="26">
-        <v>44.879603601268002</v>
+        <v>43.659891083994999</v>
       </c>
       <c r="K12" s="26">
-        <v>4073.1900303038001</v>
+        <v>3940.5340841776001</v>
       </c>
       <c r="L12" s="26">
         <v>38.394083349233</v>
@@ -2618,30 +2654,30 @@
         <v>2000</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O12" s="29">
         <v>750000000</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D13" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F13" s="23">
         <v>4.4999999999999998E-2</v>
@@ -2653,13 +2689,13 @@
         <v>2028</v>
       </c>
       <c r="I13" s="26">
-        <v>60.115000000000002</v>
+        <v>57.465000000000003</v>
       </c>
       <c r="J13" s="26">
-        <v>52.564688836020999</v>
+        <v>58.923403312120001</v>
       </c>
       <c r="K13" s="26">
-        <v>4846.2639956558996</v>
+        <v>5470.5578829796004</v>
       </c>
       <c r="L13" s="26">
         <v>61.799509103391003</v>
@@ -2668,24 +2704,24 @@
         <v>200000</v>
       </c>
       <c r="N13" s="28" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O13" s="29">
         <v>1250000000</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>21</v>
@@ -2703,13 +2739,13 @@
         <v>2028</v>
       </c>
       <c r="I14" s="13">
-        <v>102.1035</v>
+        <v>102.0955</v>
       </c>
       <c r="J14" s="13">
-        <v>5.5931738158447999</v>
+        <v>5.5772476734794001</v>
       </c>
       <c r="K14" s="13">
-        <v>148.01234250936</v>
+        <v>135.05242362664001</v>
       </c>
       <c r="L14" s="13">
         <v>5.3389997638258997</v>
@@ -2724,24 +2760,24 @@
         <v>300000000</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="21" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D15" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F15" s="23">
         <v>4.7500000000000001E-2</v>
@@ -2753,13 +2789,13 @@
         <v>2028</v>
       </c>
       <c r="I15" s="26">
-        <v>91.045000000000002</v>
+        <v>90.25</v>
       </c>
       <c r="J15" s="26">
-        <v>10.097811976268</v>
+        <v>10.677957825858</v>
       </c>
       <c r="K15" s="26">
-        <v>594.67075528652003</v>
+        <v>642.07802695683995</v>
       </c>
       <c r="L15" s="26">
         <v>14.00107155779</v>
@@ -2768,18 +2804,18 @@
         <v>2000</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O15" s="29">
         <v>275000000</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="8" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>15</v>
@@ -2803,13 +2839,13 @@
         <v>2028</v>
       </c>
       <c r="I16" s="13">
-        <v>103.325</v>
+        <v>102.91</v>
       </c>
       <c r="J16" s="13">
-        <v>5.2413939062042001</v>
+        <v>5.4294939750011997</v>
       </c>
       <c r="K16" s="13">
-        <v>107.78055424713</v>
+        <v>116.22917685029</v>
       </c>
       <c r="L16" s="13">
         <v>5.5755940454813002</v>
@@ -2824,7 +2860,7 @@
         <v>1500000000</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2832,7 +2868,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>20</v>
@@ -2841,7 +2877,7 @@
         <v>21</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F17" s="10">
         <v>0.04</v>
@@ -2853,13 +2889,13 @@
         <v>2028</v>
       </c>
       <c r="I17" s="13">
-        <v>97.83</v>
+        <v>97.525000000000006</v>
       </c>
       <c r="J17" s="13">
-        <v>5.2868471177987004</v>
+        <v>5.4839640856787</v>
       </c>
       <c r="K17" s="13">
-        <v>114.17707973957999</v>
+        <v>123.16011934216</v>
       </c>
       <c r="L17" s="13">
         <v>5.5494499521960998</v>
@@ -2868,30 +2904,30 @@
         <v>1000</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O17" s="16">
         <v>2000000000</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="8" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F18" s="10">
         <v>5.7500000000000002E-2</v>
@@ -2903,13 +2939,13 @@
         <v>2028</v>
       </c>
       <c r="I18" s="13">
-        <v>99.515500000000003</v>
+        <v>99.364999999999995</v>
       </c>
       <c r="J18" s="13">
-        <v>6.0705172334795998</v>
+        <v>6.1496878290132004</v>
       </c>
       <c r="K18" s="13">
-        <v>190.33318983952</v>
+        <v>187.95797393151</v>
       </c>
       <c r="L18" s="13">
         <v>6.2446701815574999</v>
@@ -2918,13 +2954,13 @@
         <v>1000</v>
       </c>
       <c r="N18" s="15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O18" s="16">
         <v>800000000</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2953,13 +2989,13 @@
         <v>2028</v>
       </c>
       <c r="I19" s="13">
-        <v>98.25</v>
+        <v>98.375</v>
       </c>
       <c r="J19" s="13">
-        <v>5.4742560648790004</v>
+        <v>5.4109207834262998</v>
       </c>
       <c r="K19" s="13">
-        <v>133.68191707310999</v>
+        <v>116.46709430260999</v>
       </c>
       <c r="L19" s="13">
         <v>5.3547576737993001</v>
@@ -2974,1007 +3010,1005 @@
         <v>800000000</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="8" t="s">
-        <v>133</v>
+      <c r="A20" s="19" t="s">
+        <v>212</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="10">
-        <v>8.6249999999999993E-2</v>
-      </c>
-      <c r="G20" s="11">
-        <v>47137</v>
-      </c>
-      <c r="H20" s="12">
-        <v>2029</v>
-      </c>
-      <c r="I20" s="13">
-        <v>106.43</v>
-      </c>
-      <c r="J20" s="13">
-        <v>5.7979342120346002</v>
-      </c>
-      <c r="K20" s="13">
-        <v>162.01136749777999</v>
-      </c>
-      <c r="L20" s="13">
-        <v>6.0768609608236996</v>
-      </c>
-      <c r="M20" s="14">
-        <v>1000</v>
-      </c>
-      <c r="N20" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="O20" s="16">
-        <v>1200000000</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>158</v>
+      <c r="E20" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="F20" s="42">
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G20" s="33">
+        <v>47058</v>
+      </c>
+      <c r="H20" s="39">
+        <v>2028</v>
+      </c>
+      <c r="I20" s="43">
+        <v>98.462500000000006</v>
+      </c>
+      <c r="J20" s="43">
+        <v>5.5877525475952998</v>
+      </c>
+      <c r="K20" s="43">
+        <v>131.88228951236999</v>
+      </c>
+      <c r="L20" s="43"/>
+      <c r="M20" s="34">
+        <v>2000</v>
+      </c>
+      <c r="N20" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="O20" s="40">
+        <v>1000000000</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:16">
       <c r="A21" s="8" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>174</v>
+        <v>42</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="F21" s="10">
-        <v>6.9919999999999996E-2</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>193</v>
+        <v>8.6249999999999993E-2</v>
+      </c>
+      <c r="G21" s="11">
+        <v>47137</v>
       </c>
       <c r="H21" s="12">
         <v>2029</v>
       </c>
       <c r="I21" s="13">
-        <v>103.325</v>
+        <v>105.88500000000001</v>
       </c>
       <c r="J21" s="13">
-        <v>5.0938475189597003</v>
+        <v>6.0156756141776002</v>
       </c>
       <c r="K21" s="13">
-        <v>95.974057001199</v>
+        <v>173.70459371056</v>
       </c>
       <c r="L21" s="13">
+        <v>6.0768609608236996</v>
+      </c>
+      <c r="M21" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N21" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="O21" s="16">
+        <v>1200000000</v>
+      </c>
+      <c r="P21" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="10">
+        <v>6.9919999999999996E-2</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="H22" s="12">
+        <v>2029</v>
+      </c>
+      <c r="I22" s="13">
+        <v>103.04</v>
+      </c>
+      <c r="J22" s="13">
+        <v>5.2378702423809997</v>
+      </c>
+      <c r="K22" s="13">
+        <v>99.430164232725005</v>
+      </c>
+      <c r="L22" s="13">
         <v>5.2262981503403001</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M22" s="14">
         <v>2000</v>
       </c>
-      <c r="N21" s="15" t="s">
+      <c r="N22" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O22" s="16">
         <v>750000000</v>
       </c>
-      <c r="P21" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="F22" s="23">
-        <v>5.6250000000000001E-2</v>
-      </c>
-      <c r="G22" s="24">
-        <v>47126</v>
-      </c>
-      <c r="H22" s="25">
-        <v>2029</v>
-      </c>
-      <c r="I22" s="26">
-        <v>99.4375</v>
-      </c>
-      <c r="J22" s="26">
-        <v>5.9208324614586996</v>
-      </c>
-      <c r="K22" s="26">
-        <v>169.74843167449001</v>
-      </c>
-      <c r="L22" s="26">
-        <v>5.9529012337668004</v>
-      </c>
-      <c r="M22" s="27">
-        <v>1000</v>
-      </c>
-      <c r="N22" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="O22" s="29">
-        <v>750000000</v>
-      </c>
       <c r="P22" s="17" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:16">
       <c r="A23" s="21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>194</v>
+        <v>128</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D23" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F23" s="23">
-        <v>3.4500000000000003E-2</v>
+        <v>5.6250000000000001E-2</v>
       </c>
       <c r="G23" s="24">
-        <v>47128</v>
+        <v>47126</v>
       </c>
       <c r="H23" s="25">
         <v>2029</v>
       </c>
       <c r="I23" s="26">
-        <v>92.980199999999996</v>
+        <v>99.647499999999994</v>
       </c>
       <c r="J23" s="26">
-        <v>6.0510687789919997</v>
+        <v>5.8398616930685998</v>
       </c>
       <c r="K23" s="26">
-        <v>181.18509604673</v>
+        <v>152.45026586841001</v>
       </c>
       <c r="L23" s="26">
+        <v>5.9529012337668004</v>
+      </c>
+      <c r="M23" s="27">
+        <v>1000</v>
+      </c>
+      <c r="N23" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O23" s="29">
+        <v>750000000</v>
+      </c>
+      <c r="P23" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="23">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="G24" s="24">
+        <v>47128</v>
+      </c>
+      <c r="H24" s="25">
+        <v>2029</v>
+      </c>
+      <c r="I24" s="26">
+        <v>93.243849999999995</v>
+      </c>
+      <c r="J24" s="26">
+        <v>5.9691721250835998</v>
+      </c>
+      <c r="K24" s="26">
+        <v>164.09955391976001</v>
+      </c>
+      <c r="L24" s="26">
         <v>6.1691679685506999</v>
       </c>
-      <c r="M23" s="27">
+      <c r="M24" s="27">
         <v>2000</v>
       </c>
-      <c r="N23" s="28" t="s">
+      <c r="N24" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="O23" s="29">
+      <c r="O24" s="29">
         <v>500000000</v>
       </c>
-      <c r="P23" s="17" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="8" t="s">
+      <c r="P24" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B25" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F25" s="10">
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="H24" s="12">
-        <v>2029</v>
-      </c>
-      <c r="I24" s="13">
-        <v>99.727500000000006</v>
-      </c>
-      <c r="J24" s="13">
-        <v>5.4094608316338002</v>
-      </c>
-      <c r="K24" s="13">
-        <v>115.90288659236001</v>
-      </c>
-      <c r="L24" s="13">
-        <v>5.5401109236627999</v>
-      </c>
-      <c r="M24" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N24" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" s="16">
-        <v>700000000</v>
-      </c>
-      <c r="P24" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F25" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="G25" s="11">
-        <v>47126</v>
+      <c r="G25" s="11" t="s">
+        <v>192</v>
       </c>
       <c r="H25" s="12">
         <v>2029</v>
       </c>
       <c r="I25" s="13">
-        <v>100.34</v>
+        <v>99.614999999999995</v>
       </c>
       <c r="J25" s="13">
-        <v>4.9322233789808001</v>
+        <v>5.4489955471522</v>
       </c>
       <c r="K25" s="13">
-        <v>70.698609186876993</v>
+        <v>111.17864154713</v>
       </c>
       <c r="L25" s="13">
-        <v>5.0823082063419003</v>
+        <v>5.5401109236627999</v>
       </c>
       <c r="M25" s="14">
         <v>2000</v>
       </c>
       <c r="N25" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O25" s="16">
-        <v>750000000</v>
+        <v>700000000</v>
       </c>
       <c r="P25" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>56</v>
+      <c r="A26" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>128</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="F26" s="10">
-        <v>3.7499999999999999E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G26" s="11">
-        <v>47209</v>
+        <v>47126</v>
       </c>
       <c r="H26" s="12">
         <v>2029</v>
       </c>
       <c r="I26" s="13">
-        <v>96.347999999999999</v>
+        <v>99.954999999999998</v>
       </c>
       <c r="J26" s="13">
-        <v>5.3374257116923003</v>
+        <v>5.0779074037698999</v>
       </c>
       <c r="K26" s="13">
-        <v>119.64898118794</v>
+        <v>76.106996433296004</v>
       </c>
       <c r="L26" s="13">
-        <v>5.2374920160164997</v>
+        <v>5.0823082063419003</v>
       </c>
       <c r="M26" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N26" s="15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O26" s="16">
-        <v>600000000</v>
+        <v>750000000</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" s="8" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="D27" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>148</v>
+        <v>57</v>
       </c>
       <c r="F27" s="10">
-        <v>4.5999999999999999E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G27" s="11">
-        <v>47437</v>
+        <v>47209</v>
       </c>
       <c r="H27" s="12">
         <v>2029</v>
       </c>
       <c r="I27" s="13">
-        <v>94.965000000000003</v>
+        <v>96.313812999999996</v>
       </c>
       <c r="J27" s="13">
-        <v>6.4768268711432002</v>
+        <v>5.3690344270854</v>
       </c>
       <c r="K27" s="13">
-        <v>223.17464281472999</v>
+        <v>107.27530987961001</v>
       </c>
       <c r="L27" s="13">
-        <v>6.6349128086422002</v>
+        <v>5.2374920160164997</v>
       </c>
       <c r="M27" s="14">
         <v>1000</v>
       </c>
       <c r="N27" s="15" t="s">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="O27" s="16">
-        <v>650000000</v>
+        <v>600000000</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="8" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>61</v>
+        <v>145</v>
       </c>
       <c r="F28" s="10">
-        <v>5.9499999999999997E-2</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="G28" s="11">
-        <v>47314</v>
+        <v>47437</v>
       </c>
       <c r="H28" s="12">
         <v>2029</v>
       </c>
       <c r="I28" s="13">
-        <v>100.99</v>
+        <v>94.575000000000003</v>
       </c>
       <c r="J28" s="13">
-        <v>5.6492222563989003</v>
+        <v>6.6359049956831999</v>
       </c>
       <c r="K28" s="13">
-        <v>143.04765781011</v>
+        <v>230.30584597747</v>
       </c>
       <c r="L28" s="13">
-        <v>5.8378605733628</v>
+        <v>6.6349128086422002</v>
       </c>
       <c r="M28" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N28" s="15" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="O28" s="16">
-        <v>850000000</v>
+        <v>650000000</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" s="8" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F29" s="10">
-        <v>5.3999999999999999E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="G29" s="11">
-        <v>47437</v>
+        <v>47314</v>
       </c>
       <c r="H29" s="12">
         <v>2029</v>
       </c>
       <c r="I29" s="13">
-        <v>101.38500000000001</v>
+        <v>100.68</v>
       </c>
       <c r="J29" s="13">
-        <v>4.9765817469703002</v>
+        <v>5.7669682902319002</v>
       </c>
       <c r="K29" s="13">
-        <v>74.092106591806001</v>
+        <v>145.53670567766</v>
       </c>
       <c r="L29" s="13">
-        <v>5.0747627537484998</v>
+        <v>5.8378605733628</v>
       </c>
       <c r="M29" s="14">
         <v>2000</v>
       </c>
       <c r="N29" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="O29" s="16">
+        <v>850000000</v>
+      </c>
+      <c r="P29" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G30" s="11">
+        <v>47437</v>
+      </c>
+      <c r="H30" s="12">
+        <v>2029</v>
+      </c>
+      <c r="I30" s="13">
+        <v>100.91500000000001</v>
+      </c>
+      <c r="J30" s="13">
+        <v>5.1409446522528004</v>
+      </c>
+      <c r="K30" s="13">
+        <v>81.571719175072005</v>
+      </c>
+      <c r="L30" s="13">
+        <v>5.0747627537484998</v>
+      </c>
+      <c r="M30" s="14">
+        <v>2000</v>
+      </c>
+      <c r="N30" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="O29" s="16">
+      <c r="O30" s="16">
         <v>1000000000</v>
       </c>
-      <c r="P29" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="30" t="s">
-        <v>171</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="23">
-        <v>4.6249999999999999E-2</v>
-      </c>
-      <c r="G30" s="24">
-        <v>47489</v>
-      </c>
-      <c r="H30" s="25">
-        <v>2030</v>
-      </c>
-      <c r="I30" s="26">
-        <v>96.5625</v>
-      </c>
-      <c r="J30" s="26">
-        <v>5.7294618848532997</v>
-      </c>
-      <c r="K30" s="26">
-        <v>144.36334205385</v>
-      </c>
-      <c r="L30" s="26">
-        <v>5.6884236132800998</v>
-      </c>
-      <c r="M30" s="27">
-        <v>1000</v>
-      </c>
-      <c r="N30" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="O30" s="29">
-        <v>2750000000</v>
-      </c>
       <c r="P30" s="17" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" s="30" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="D31" s="22" t="s">
         <v>21</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="F31" s="23">
-        <v>0.05</v>
+        <v>4.6249999999999999E-2</v>
       </c>
       <c r="G31" s="24">
-        <v>47485</v>
+        <v>47489</v>
       </c>
       <c r="H31" s="25">
         <v>2030</v>
       </c>
       <c r="I31" s="26">
-        <v>97.156999999999996</v>
+        <v>96.1875</v>
       </c>
       <c r="J31" s="26">
-        <v>6.0138516899332002</v>
+        <v>5.8542755439225997</v>
       </c>
       <c r="K31" s="26">
-        <v>175.17154233367</v>
+        <v>148.84439078667</v>
       </c>
       <c r="L31" s="26">
-        <v>5.9198386169269996</v>
+        <v>5.6884236132800998</v>
       </c>
       <c r="M31" s="27">
         <v>1000</v>
       </c>
       <c r="N31" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="O31" s="29">
+        <v>2750000000</v>
+      </c>
+      <c r="P31" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="F32" s="23">
+        <v>0.05</v>
+      </c>
+      <c r="G32" s="24">
+        <v>47485</v>
+      </c>
+      <c r="H32" s="25">
+        <v>2030</v>
+      </c>
+      <c r="I32" s="26">
+        <v>97.875</v>
+      </c>
+      <c r="J32" s="26">
+        <v>5.7741469376597001</v>
+      </c>
+      <c r="K32" s="26">
+        <v>142.73774065224001</v>
+      </c>
+      <c r="L32" s="26">
+        <v>5.9198386169269996</v>
+      </c>
+      <c r="M32" s="27">
+        <v>1000</v>
+      </c>
+      <c r="N32" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="O31" s="29">
+      <c r="O32" s="29">
         <v>550000000</v>
       </c>
-      <c r="P31" s="17" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="10">
-        <v>3.875E-2</v>
-      </c>
-      <c r="G32" s="11">
-        <v>47802</v>
-      </c>
-      <c r="H32" s="12">
-        <v>2030</v>
-      </c>
-      <c r="I32" s="13">
-        <v>92.875</v>
-      </c>
-      <c r="J32" s="13">
-        <v>5.8839950463993</v>
-      </c>
-      <c r="K32" s="13">
-        <v>156.18410393782</v>
-      </c>
-      <c r="L32" s="13">
-        <v>6.0583846882100998</v>
-      </c>
-      <c r="M32" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N32" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="O32" s="16">
-        <v>650000000</v>
-      </c>
       <c r="P32" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="8" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>70</v>
+        <v>21</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="F33" s="10">
-        <v>4.7E-2</v>
+        <v>3.875E-2</v>
       </c>
       <c r="G33" s="11">
-        <v>47763</v>
+        <v>47802</v>
       </c>
       <c r="H33" s="12">
         <v>2030</v>
       </c>
       <c r="I33" s="13">
-        <v>97.829859999999996</v>
+        <v>92.69</v>
       </c>
       <c r="J33" s="13">
-        <v>5.3621402560357998</v>
+        <v>5.9490377206004998</v>
       </c>
       <c r="K33" s="13">
-        <v>105.37326039262</v>
+        <v>155.36857559785</v>
       </c>
       <c r="L33" s="13">
-        <v>5.5038780249519998</v>
+        <v>6.0583846882100998</v>
       </c>
       <c r="M33" s="14">
         <v>2000</v>
       </c>
       <c r="N33" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="O33" s="16">
-        <v>600000000</v>
+        <v>650000000</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="20" t="s">
-        <v>60</v>
+      <c r="A34" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="32">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G34" s="33">
-        <v>47727</v>
+      <c r="E34" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="10">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G34" s="11">
+        <v>47763</v>
       </c>
       <c r="H34" s="12">
         <v>2030</v>
       </c>
       <c r="I34" s="13">
-        <v>98.73</v>
+        <v>97.096000000000004</v>
       </c>
       <c r="J34" s="13">
-        <v>5.9448429119051003</v>
+        <v>5.5749934984258003</v>
       </c>
       <c r="K34" s="13">
-        <v>165.01529476025999</v>
+        <v>119.03341952106</v>
       </c>
       <c r="L34" s="13">
-        <v>6.0892206099960999</v>
-      </c>
-      <c r="M34" s="34">
+        <v>5.5038780249519998</v>
+      </c>
+      <c r="M34" s="14">
         <v>2000</v>
       </c>
-      <c r="N34" s="35" t="s">
-        <v>72</v>
+      <c r="N34" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="O34" s="16">
-        <v>750000000</v>
+        <v>600000000</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>135</v>
+      <c r="A35" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F35" s="10">
-        <v>8.7499999999999994E-2</v>
-      </c>
-      <c r="G35" s="11">
-        <v>47514</v>
+        <v>12</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="F35" s="32">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G35" s="33">
+        <v>47727</v>
       </c>
       <c r="H35" s="12">
         <v>2030</v>
       </c>
       <c r="I35" s="13">
-        <v>103.3</v>
+        <v>98.314999999999998</v>
       </c>
       <c r="J35" s="13">
-        <v>7.7808904012364</v>
+        <v>6.0699501856192004</v>
       </c>
       <c r="K35" s="13">
-        <v>353.21827572695003</v>
+        <v>169.00296560749999</v>
       </c>
       <c r="L35" s="13">
-        <v>8.7479156676685008</v>
-      </c>
-      <c r="M35" s="14">
-        <v>200000</v>
-      </c>
-      <c r="N35" s="15" t="s">
-        <v>74</v>
+        <v>6.0892206099960999</v>
+      </c>
+      <c r="M35" s="34">
+        <v>2000</v>
+      </c>
+      <c r="N35" s="35" t="s">
+        <v>72</v>
       </c>
       <c r="O35" s="16">
-        <v>550000000</v>
+        <v>750000000</v>
       </c>
       <c r="P35" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" s="8" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F36" s="32">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G36" s="33">
-        <v>47485</v>
+        <v>73</v>
+      </c>
+      <c r="F36" s="10">
+        <v>8.7499999999999994E-2</v>
+      </c>
+      <c r="G36" s="11">
+        <v>47514</v>
       </c>
       <c r="H36" s="12">
         <v>2030</v>
       </c>
       <c r="I36" s="13">
-        <v>105.88235</v>
+        <v>103.35</v>
       </c>
       <c r="J36" s="13">
-        <v>5.1739800877194</v>
+        <v>7.7554154542336997</v>
       </c>
       <c r="K36" s="13">
-        <v>91.825220237422997</v>
+        <v>341.95756408994998</v>
       </c>
       <c r="L36" s="13">
-        <v>5.3167478739792999</v>
-      </c>
-      <c r="M36" s="34">
-        <v>2000</v>
-      </c>
-      <c r="N36" s="35" t="s">
-        <v>76</v>
+        <v>8.7479156676685008</v>
+      </c>
+      <c r="M36" s="14">
+        <v>200000</v>
+      </c>
+      <c r="N36" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="O36" s="16">
-        <v>750000000</v>
+        <v>550000000</v>
       </c>
       <c r="P36" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>136</v>
+        <v>75</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="F37" s="10">
-        <v>5.8749999999999997E-2</v>
-      </c>
-      <c r="G37" s="11">
-        <v>47557</v>
+        <v>193</v>
+      </c>
+      <c r="F37" s="32">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G37" s="33">
+        <v>47485</v>
       </c>
       <c r="H37" s="12">
         <v>2030</v>
       </c>
       <c r="I37" s="13">
-        <v>100.38</v>
+        <v>105.4798</v>
       </c>
       <c r="J37" s="13">
-        <v>5.8368011731741003</v>
+        <v>5.2901152395817999</v>
       </c>
       <c r="K37" s="13">
-        <v>157.50134700074</v>
+        <v>94.865592489555993</v>
       </c>
       <c r="L37" s="13">
-        <v>6.0173203968370004</v>
-      </c>
-      <c r="M37" s="14">
+        <v>5.3167478739792999</v>
+      </c>
+      <c r="M37" s="34">
         <v>2000</v>
       </c>
-      <c r="N37" s="15" t="s">
-        <v>78</v>
+      <c r="N37" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="O37" s="16">
-        <v>425000000</v>
+        <v>750000000</v>
       </c>
       <c r="P37" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" s="20" t="s">
-        <v>137</v>
+      <c r="A38" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="32">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G38" s="33">
-        <v>47757</v>
+        <v>21</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="10">
+        <v>5.8749999999999997E-2</v>
+      </c>
+      <c r="G38" s="11">
+        <v>47557</v>
       </c>
       <c r="H38" s="12">
         <v>2030</v>
       </c>
       <c r="I38" s="13">
-        <v>96.875600000000006</v>
+        <v>100.965</v>
       </c>
       <c r="J38" s="13">
-        <v>5.4293774821294001</v>
+        <v>5.6469503158355003</v>
       </c>
       <c r="K38" s="13">
-        <v>112.12689375801</v>
+        <v>130.04377649553001</v>
       </c>
       <c r="L38" s="13">
-        <v>5.4958884088957003</v>
-      </c>
-      <c r="M38" s="34">
+        <v>6.0173203968370004</v>
+      </c>
+      <c r="M38" s="14">
         <v>2000</v>
       </c>
-      <c r="N38" s="35" t="s">
-        <v>79</v>
+      <c r="N38" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="O38" s="16">
-        <v>75000000</v>
+        <v>425000000</v>
       </c>
       <c r="P38" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="9" t="s">
+      <c r="A39" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>80</v>
+      <c r="C39" s="20" t="s">
+        <v>134</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="F39" s="10">
-        <v>5.0930000000000003E-2</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>197</v>
+        <v>12</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="32">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G39" s="33">
+        <v>47757</v>
       </c>
       <c r="H39" s="12">
         <v>2030</v>
       </c>
       <c r="I39" s="13">
-        <v>99.3245</v>
+        <v>96.214449999999999</v>
       </c>
       <c r="J39" s="13">
-        <v>5.3820503008867</v>
+        <v>5.6266469601304996</v>
       </c>
       <c r="K39" s="13">
-        <v>112.38401797244001</v>
+        <v>124.27998471902001</v>
       </c>
       <c r="L39" s="13">
-        <v>5.5695677340319003</v>
-      </c>
-      <c r="M39" s="14">
+        <v>5.4958884088957003</v>
+      </c>
+      <c r="M39" s="34">
         <v>2000</v>
       </c>
-      <c r="N39" s="15" t="s">
-        <v>81</v>
+      <c r="N39" s="35" t="s">
+        <v>79</v>
       </c>
       <c r="O39" s="16">
-        <v>375896000</v>
+        <v>75000000</v>
       </c>
       <c r="P39" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3982,7 +4016,7 @@
         <v>23</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>23</v>
@@ -3991,25 +4025,25 @@
         <v>21</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F40" s="10">
         <v>2.7E-2</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H40" s="12">
         <v>2030</v>
       </c>
       <c r="I40" s="13">
-        <v>91.275000000000006</v>
+        <v>90.76885</v>
       </c>
       <c r="J40" s="13">
-        <v>5.3148880671191003</v>
+        <v>5.4927621945273</v>
       </c>
       <c r="K40" s="13">
-        <v>101.39460079680001</v>
+        <v>111.46628690679</v>
       </c>
       <c r="L40" s="13">
         <v>5.4036479562327999</v>
@@ -4018,24 +4052,24 @@
         <v>2000</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O40" s="16">
         <v>1449500000</v>
       </c>
       <c r="P40" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>12</v>
@@ -4047,7 +4081,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H41" s="12">
         <v>2030</v>
@@ -4068,30 +4102,30 @@
         <v>200000</v>
       </c>
       <c r="N41" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="O41" s="16">
         <v>750000000</v>
       </c>
       <c r="P41" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F42" s="10">
         <v>3.7499999999999999E-2</v>
@@ -4103,13 +4137,13 @@
         <v>2030</v>
       </c>
       <c r="I42" s="13">
-        <v>95.135000000000005</v>
+        <v>95.055000000000007</v>
       </c>
       <c r="J42" s="13">
-        <v>5.2178748869831004</v>
+        <v>5.2508752956864999</v>
       </c>
       <c r="K42" s="13">
-        <v>91.859768039079995</v>
+        <v>87.408701228468004</v>
       </c>
       <c r="L42" s="13">
         <v>5.2283698275725001</v>
@@ -4118,24 +4152,24 @@
         <v>2000</v>
       </c>
       <c r="N42" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O42" s="16">
         <v>1500000000</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" s="8" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D43" s="9" t="s">
         <v>21</v>
@@ -4153,13 +4187,13 @@
         <v>2030</v>
       </c>
       <c r="I43" s="13">
-        <v>95.784999999999997</v>
+        <v>95.15</v>
       </c>
       <c r="J43" s="13">
-        <v>5.7654861636771004</v>
+        <v>5.9851877038083998</v>
       </c>
       <c r="K43" s="13">
-        <v>149.28564063300999</v>
+        <v>163.00940593465</v>
       </c>
       <c r="L43" s="13">
         <v>5.6866903609593002</v>
@@ -4168,48 +4202,48 @@
         <v>2000</v>
       </c>
       <c r="N43" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="O43" s="16">
         <v>500000000</v>
       </c>
       <c r="P43" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F44" s="10">
         <v>0.03</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H44" s="12">
         <v>2030</v>
       </c>
       <c r="I44" s="13">
-        <v>90.250349999999997</v>
+        <v>90.444599999999994</v>
       </c>
       <c r="J44" s="13">
-        <v>5.7555105428557001</v>
+        <v>5.7129658016827003</v>
       </c>
       <c r="K44" s="13">
-        <v>143.46581793229001</v>
+        <v>131.86145800772999</v>
       </c>
       <c r="L44" s="13">
         <v>5.7259922256740001</v>
@@ -4218,24 +4252,24 @@
         <v>2000</v>
       </c>
       <c r="N44" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O44" s="16">
         <v>2200000000</v>
       </c>
       <c r="P44" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B45" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="D45" s="9" t="s">
         <v>21</v>
@@ -4253,13 +4287,13 @@
         <v>2031</v>
       </c>
       <c r="I45" s="13">
-        <v>96.1875</v>
+        <v>96.5625</v>
       </c>
       <c r="J45" s="13">
-        <v>8.8232382204128008</v>
+        <v>8.7216901556814008</v>
       </c>
       <c r="K45" s="13">
-        <v>450.18443819914</v>
+        <v>432.67935216674999</v>
       </c>
       <c r="L45" s="13">
         <v>8.3729999999999993</v>
@@ -4268,24 +4302,24 @@
         <v>1000</v>
       </c>
       <c r="N45" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O45" s="16">
         <v>32518000</v>
       </c>
       <c r="P45" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>12</v>
@@ -4303,13 +4337,13 @@
         <v>2030</v>
       </c>
       <c r="I46" s="13">
-        <v>99.33</v>
+        <v>98.76</v>
       </c>
       <c r="J46" s="13">
-        <v>5.2433889595245002</v>
+        <v>5.4021781154344</v>
       </c>
       <c r="K46" s="13">
-        <v>92.706226168865001</v>
+        <v>101.16352064285999</v>
       </c>
       <c r="L46" s="13">
         <v>5.4091299597324998</v>
@@ -4318,24 +4352,24 @@
         <v>2000</v>
       </c>
       <c r="N46" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O46" s="16">
         <v>600000000</v>
       </c>
       <c r="P46" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" s="8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>12</v>
@@ -4353,13 +4387,13 @@
         <v>2031</v>
       </c>
       <c r="I47" s="13">
-        <v>102.105</v>
+        <v>101.63</v>
       </c>
       <c r="J47" s="13">
-        <v>5.2733936569621003</v>
+        <v>5.3954506689577997</v>
       </c>
       <c r="K47" s="13">
-        <v>94.741362868383007</v>
+        <v>99.704044171359996</v>
       </c>
       <c r="L47" s="13">
         <v>5.4144095584879999</v>
@@ -4368,30 +4402,30 @@
         <v>2000</v>
       </c>
       <c r="N47" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O47" s="16">
         <v>650000000</v>
       </c>
       <c r="P47" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F48" s="10">
         <v>2.5000000000000001E-2</v>
@@ -4403,13 +4437,13 @@
         <v>2031</v>
       </c>
       <c r="I48" s="13">
-        <v>87.58</v>
+        <v>87.017499999999998</v>
       </c>
       <c r="J48" s="13">
-        <v>5.7340887881656997</v>
+        <v>5.9114713747104002</v>
       </c>
       <c r="K48" s="13">
-        <v>138.24503004908999</v>
+        <v>148.79608629984</v>
       </c>
       <c r="L48" s="13">
         <v>5.8792735535786003</v>
@@ -4417,152 +4451,152 @@
       <c r="M48" s="14">
         <v>2000</v>
       </c>
-      <c r="N48" s="37" t="s">
-        <v>96</v>
+      <c r="N48" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="O48" s="16">
         <v>2200000000</v>
       </c>
       <c r="P48" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:16">
       <c r="A49" s="8" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E49" s="20" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="F49" s="32">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="G49" s="33" t="s">
-        <v>205</v>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G49" s="33">
+        <v>47899</v>
       </c>
       <c r="H49" s="12">
         <v>2031</v>
       </c>
-      <c r="I49" s="13">
-        <v>101.8475</v>
-      </c>
-      <c r="J49" s="13">
-        <v>4.8921479540058002</v>
-      </c>
-      <c r="K49" s="13">
-        <v>53.250594472223</v>
-      </c>
-      <c r="L49" s="13">
-        <v>4.9050583828213004</v>
+      <c r="I49" s="41">
+        <v>96.66</v>
+      </c>
+      <c r="J49" s="41">
+        <v>5.4225723523394</v>
+      </c>
+      <c r="K49" s="41">
+        <v>101.15941487599</v>
+      </c>
+      <c r="L49" s="41">
+        <v>5.2775961551588999</v>
       </c>
       <c r="M49" s="34">
         <v>2000</v>
       </c>
       <c r="N49" s="15" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="O49" s="16">
-        <v>1000000000</v>
+        <v>600000000</v>
       </c>
       <c r="P49" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:16">
       <c r="A50" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>25</v>
+        <v>80</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F50" s="32">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="G50" s="33">
-        <v>47899</v>
+        <v>21</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="F50" s="10">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="G50" s="11">
+        <v>47908</v>
       </c>
       <c r="H50" s="12">
         <v>2031</v>
       </c>
-      <c r="I50" s="43">
-        <v>97.295000000000002</v>
-      </c>
-      <c r="J50" s="43">
-        <v>5.2505089069888999</v>
-      </c>
-      <c r="K50" s="43">
-        <v>90.906654248665006</v>
-      </c>
-      <c r="L50" s="43">
-        <v>5.2775961551588999</v>
-      </c>
-      <c r="M50" s="34">
+      <c r="I50" s="13">
+        <v>99.83</v>
+      </c>
+      <c r="J50" s="13">
+        <v>5.7220640321167</v>
+      </c>
+      <c r="K50" s="13">
+        <v>132.55607873254999</v>
+      </c>
+      <c r="L50" s="13">
+        <v>5.6655276789892</v>
+      </c>
+      <c r="M50" s="14">
         <v>2000</v>
       </c>
       <c r="N50" s="15" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="O50" s="16">
-        <v>600000000</v>
+        <v>823936000</v>
       </c>
       <c r="P50" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:16">
       <c r="A51" s="8" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="F51" s="10">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="G51" s="11">
-        <v>47908</v>
+        <v>2.726E-2</v>
+      </c>
+      <c r="G51" s="11" t="s">
+        <v>200</v>
       </c>
       <c r="H51" s="12">
         <v>2031</v>
       </c>
       <c r="I51" s="13">
-        <v>100.1675</v>
+        <v>90.21</v>
       </c>
       <c r="J51" s="13">
-        <v>5.6312089605731996</v>
+        <v>5.2300494909572004</v>
       </c>
       <c r="K51" s="13">
-        <v>130.76030224799999</v>
+        <v>80.730206876188007</v>
       </c>
       <c r="L51" s="13">
-        <v>5.6655276789892</v>
+        <v>5.1195611694260004</v>
       </c>
       <c r="M51" s="14">
         <v>2000</v>
@@ -4571,594 +4605,594 @@
         <v>99</v>
       </c>
       <c r="O51" s="16">
-        <v>823936000</v>
+        <v>1250000000</v>
       </c>
       <c r="P51" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" spans="1:16">
       <c r="A52" s="8" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>122</v>
+        <v>42</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" s="20" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="F52" s="10">
-        <v>2.726E-2</v>
+        <v>3.6249999999999998E-2</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H52" s="12">
         <v>2031</v>
       </c>
       <c r="I52" s="13">
-        <v>90.885000000000005</v>
+        <v>93.09</v>
       </c>
       <c r="J52" s="13">
-        <v>5.0357762546918998</v>
+        <v>5.3752904280538001</v>
       </c>
       <c r="K52" s="13">
-        <v>67.988193755471002</v>
+        <v>94.894318581121993</v>
       </c>
       <c r="L52" s="13">
-        <v>5.1195611694260004</v>
+        <v>5.4655897091694996</v>
       </c>
       <c r="M52" s="14">
         <v>2000</v>
       </c>
       <c r="N52" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="O52" s="16">
+        <v>500000000</v>
+      </c>
+      <c r="P52" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="O52" s="16">
-        <v>1250000000</v>
-      </c>
-      <c r="P52" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="C53" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="F53" s="23">
+        <v>2.4E-2</v>
+      </c>
+      <c r="G53" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53" s="25">
+        <v>2031</v>
+      </c>
+      <c r="I53" s="26">
+        <v>74.52</v>
+      </c>
+      <c r="J53" s="26">
+        <v>9.4128437749018001</v>
+      </c>
+      <c r="K53" s="26">
+        <v>498.04902846331998</v>
+      </c>
+      <c r="L53" s="26">
+        <v>10.358916231237</v>
+      </c>
+      <c r="M53" s="27">
+        <v>2000</v>
+      </c>
+      <c r="N53" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="O53" s="29">
+        <v>300000000</v>
+      </c>
+      <c r="P53" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="F53" s="10">
-        <v>3.6249999999999998E-2</v>
-      </c>
-      <c r="G53" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="H53" s="12">
+      <c r="C54" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F54" s="36">
+        <v>7.8750000000000001E-2</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="H54" s="12">
         <v>2031</v>
       </c>
-      <c r="I53" s="13">
-        <v>93.35</v>
-      </c>
-      <c r="J53" s="13">
-        <v>5.2995728414976</v>
-      </c>
-      <c r="K53" s="13">
-        <v>93.933861809701</v>
-      </c>
-      <c r="L53" s="13">
-        <v>5.4655897091694996</v>
-      </c>
-      <c r="M53" s="14">
-        <v>2000</v>
-      </c>
-      <c r="N53" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="O53" s="16">
-        <v>500000000</v>
-      </c>
-      <c r="P53" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="F54" s="23">
-        <v>2.4E-2</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="H54" s="25">
-        <v>2031</v>
-      </c>
-      <c r="I54" s="26">
-        <v>76.069999999999993</v>
-      </c>
-      <c r="J54" s="26">
-        <v>8.8719487836319004</v>
-      </c>
-      <c r="K54" s="26">
-        <v>450.40316112375001</v>
-      </c>
-      <c r="L54" s="26">
-        <v>10.358916231237</v>
-      </c>
-      <c r="M54" s="27">
-        <v>2000</v>
-      </c>
-      <c r="N54" s="28" t="s">
-        <v>105</v>
-      </c>
-      <c r="O54" s="29">
-        <v>300000000</v>
+      <c r="I54" s="13">
+        <v>111.47185</v>
+      </c>
+      <c r="J54" s="13">
+        <v>5.3198340474597003</v>
+      </c>
+      <c r="K54" s="13">
+        <v>90.302899028504996</v>
+      </c>
+      <c r="L54" s="13">
+        <v>5.2534529008212996</v>
+      </c>
+      <c r="M54" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N54" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="O54" s="16">
+        <v>484677000</v>
       </c>
       <c r="P54" s="17" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:16">
       <c r="A55" s="8" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>42</v>
+        <v>171</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>107</v>
+        <v>172</v>
       </c>
       <c r="F55" s="36">
-        <v>7.8750000000000001E-2</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>209</v>
+        <v>0.08</v>
+      </c>
+      <c r="G55" s="11">
+        <v>48153</v>
       </c>
       <c r="H55" s="12">
         <v>2031</v>
       </c>
       <c r="I55" s="13">
-        <v>111.8263</v>
+        <v>109.82</v>
       </c>
       <c r="J55" s="13">
-        <v>5.2528794683438003</v>
+        <v>5.8522373926566997</v>
       </c>
       <c r="K55" s="13">
-        <v>90.429087873016996</v>
-      </c>
-      <c r="L55" s="13">
-        <v>5.2534529008212996</v>
-      </c>
+        <v>142.79885209638999</v>
+      </c>
+      <c r="L55" s="13"/>
       <c r="M55" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N55" s="15" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="O55" s="16">
-        <v>484677000</v>
-      </c>
-      <c r="P55" s="17" t="s">
-        <v>158</v>
-      </c>
+        <v>1995021000</v>
+      </c>
+      <c r="P55" s="17"/>
     </row>
     <row r="56" spans="1:16">
       <c r="A56" s="21" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="F56" s="23">
-        <v>0.08</v>
-      </c>
-      <c r="G56" s="24">
-        <v>48153</v>
+        <v>3.3750000000000002E-2</v>
+      </c>
+      <c r="G56" s="24" t="s">
+        <v>204</v>
       </c>
       <c r="H56" s="25">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="I56" s="26">
-        <v>110.36</v>
+        <v>89.474999999999994</v>
       </c>
       <c r="J56" s="26">
-        <v>5.7428667829803999</v>
+        <v>5.7581994025252001</v>
       </c>
       <c r="K56" s="26">
-        <v>138.50630017579999</v>
-      </c>
-      <c r="L56" s="26"/>
+        <v>129.00269383359</v>
+      </c>
+      <c r="L56" s="26">
+        <v>5.6693575747171998</v>
+      </c>
       <c r="M56" s="27">
-        <v>2000</v>
+        <v>200000</v>
       </c>
       <c r="N56" s="28" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="O56" s="29">
-        <v>1995021000</v>
-      </c>
-      <c r="P56" s="17"/>
+        <v>650000000</v>
+      </c>
+      <c r="P56" s="17" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="57" spans="1:16">
       <c r="A57" s="19" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="F57" s="36">
-        <v>3.3750000000000002E-2</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>210</v>
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="G57" s="11">
+        <v>48335</v>
       </c>
       <c r="H57" s="12">
         <v>2032</v>
       </c>
       <c r="I57" s="13">
-        <v>89.495000000000005</v>
+        <v>96.875</v>
       </c>
       <c r="J57" s="13">
-        <v>5.7435157016053999</v>
+        <v>8.5777644223365002</v>
       </c>
       <c r="K57" s="13">
-        <v>133.21551698824999</v>
+        <v>413.35687340899</v>
       </c>
       <c r="L57" s="13">
-        <v>5.6693575747171998</v>
+        <v>8.3640000000000008</v>
       </c>
       <c r="M57" s="14">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="N57" s="15" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="O57" s="16">
-        <v>650000000</v>
+        <v>39042000</v>
       </c>
       <c r="P57" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:16">
       <c r="A58" s="8" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>92</v>
+        <v>34</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="F58" s="36">
-        <v>7.6999999999999999E-2</v>
-      </c>
-      <c r="G58" s="11">
-        <v>48335</v>
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="G58" s="11" t="s">
+        <v>205</v>
       </c>
       <c r="H58" s="12">
         <v>2032</v>
       </c>
       <c r="I58" s="13">
-        <v>96.5</v>
+        <v>88.944999999999993</v>
       </c>
       <c r="J58" s="13">
-        <v>8.6647982727177997</v>
+        <v>5.4603663593239</v>
       </c>
       <c r="K58" s="13">
-        <v>428.29860578813998</v>
+        <v>98.369769712587001</v>
       </c>
       <c r="L58" s="13">
-        <v>8.3640000000000008</v>
+        <v>5.3264553980798004</v>
       </c>
       <c r="M58" s="14">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="N58" s="15" t="s">
-        <v>177</v>
+        <v>108</v>
       </c>
       <c r="O58" s="16">
-        <v>39042000</v>
+        <v>500000000</v>
       </c>
       <c r="P58" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" spans="1:16">
       <c r="A59" s="8" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>128</v>
+        <v>206</v>
       </c>
       <c r="F59" s="36">
-        <v>3.0499999999999999E-2</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>211</v>
+        <v>5.3749999999999999E-2</v>
+      </c>
+      <c r="G59" s="11">
+        <v>48214</v>
       </c>
       <c r="H59" s="12">
         <v>2032</v>
       </c>
       <c r="I59" s="13">
-        <v>90.04</v>
+        <v>100.685</v>
       </c>
       <c r="J59" s="13">
-        <v>5.1987859420152001</v>
+        <v>5.2925250185391999</v>
       </c>
       <c r="K59" s="13">
-        <v>77.670632925549</v>
+        <v>84.075873437753998</v>
       </c>
       <c r="L59" s="13">
-        <v>5.3264553980798004</v>
+        <v>5.3017698521792003</v>
       </c>
       <c r="M59" s="14">
         <v>2000</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O59" s="16">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="P59" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:16">
       <c r="A60" s="19" t="s">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="D60" s="20" t="s">
         <v>21</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F60" s="32">
-        <v>5.3749999999999999E-2</v>
-      </c>
-      <c r="G60" s="33">
-        <v>48214</v>
+        <v>6.25E-2</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>205</v>
       </c>
       <c r="H60" s="12">
         <v>2032</v>
       </c>
       <c r="I60" s="13">
-        <v>101.532</v>
+        <v>101.443</v>
       </c>
       <c r="J60" s="13">
-        <v>5.1067222031488004</v>
+        <v>6.0277034789700998</v>
       </c>
       <c r="K60" s="13">
-        <v>71.514046628098995</v>
+        <v>157.79216548617001</v>
       </c>
       <c r="L60" s="13">
-        <v>5.3017698521792003</v>
+        <v>6.0798164504439001</v>
       </c>
       <c r="M60" s="14">
         <v>2000</v>
       </c>
       <c r="N60" s="35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O60" s="16">
-        <v>1000000000</v>
+        <v>600000000</v>
       </c>
       <c r="P60" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" spans="1:16">
       <c r="A61" s="8" t="s">
-        <v>213</v>
+        <v>98</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="F61" s="36">
-        <v>6.25E-2</v>
+        <v>4.7419999999999997E-2</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H61" s="12">
         <v>2032</v>
       </c>
       <c r="I61" s="13">
-        <v>101.75</v>
+        <v>97.665000000000006</v>
       </c>
       <c r="J61" s="13">
-        <v>5.9615262344869997</v>
+        <v>5.301533709468</v>
       </c>
       <c r="K61" s="13">
-        <v>157.25167050991001</v>
+        <v>83.918070499116993</v>
       </c>
       <c r="L61" s="13">
-        <v>6.0798164504439001</v>
+        <v>5.1903522881253998</v>
       </c>
       <c r="M61" s="14">
         <v>2000</v>
       </c>
       <c r="N61" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O61" s="16">
-        <v>600000000</v>
+        <v>900000000</v>
       </c>
       <c r="P61" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" spans="1:16">
       <c r="A62" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B62" s="22" t="s">
-        <v>122</v>
+        <v>202</v>
       </c>
       <c r="C62" s="22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D62" s="22" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F62" s="23">
-        <v>4.7419999999999997E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H62" s="25">
         <v>2032</v>
       </c>
       <c r="I62" s="26">
-        <v>98.54</v>
+        <v>78.349999999999994</v>
       </c>
       <c r="J62" s="26">
-        <v>5.1094912936631998</v>
+        <v>9.9769033974563008</v>
       </c>
       <c r="K62" s="26">
-        <v>70.490061696756996</v>
+        <v>551.04177974332003</v>
       </c>
       <c r="L62" s="26">
-        <v>5.1903522881253998</v>
+        <v>11.064452371603</v>
       </c>
       <c r="M62" s="27">
         <v>2000</v>
       </c>
-      <c r="N62" s="38" t="s">
+      <c r="N62" s="46" t="s">
         <v>113</v>
       </c>
       <c r="O62" s="29">
-        <v>900000000</v>
+        <v>300000000</v>
       </c>
       <c r="P62" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:16">
       <c r="A63" s="8" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>208</v>
+        <v>42</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="F63" s="36">
-        <v>4.7E-2</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>217</v>
+        <v>4.7500000000000001E-2</v>
+      </c>
+      <c r="G63" s="11">
+        <v>48215</v>
       </c>
       <c r="H63" s="12">
         <v>2032</v>
       </c>
       <c r="I63" s="13">
-        <v>80.144999999999996</v>
+        <v>96.56</v>
       </c>
       <c r="J63" s="13">
-        <v>9.4582761766657999</v>
+        <v>5.5682038964628999</v>
       </c>
       <c r="K63" s="13">
-        <v>504.79550365848002</v>
+        <v>110.68437055962001</v>
       </c>
       <c r="L63" s="13">
-        <v>11.064452371603</v>
+        <v>5.5462448562795998</v>
       </c>
       <c r="M63" s="14">
         <v>2000</v>
@@ -5167,21 +5201,21 @@
         <v>115</v>
       </c>
       <c r="O63" s="16">
-        <v>300000000</v>
+        <v>1150000000</v>
       </c>
       <c r="P63" s="17" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:16">
       <c r="A64" s="8" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>12</v>
@@ -5189,26 +5223,26 @@
       <c r="E64" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F64" s="36">
-        <v>4.7500000000000001E-2</v>
+      <c r="F64" s="10">
+        <v>5.5E-2</v>
       </c>
       <c r="G64" s="11">
-        <v>48215</v>
+        <v>48458</v>
       </c>
       <c r="H64" s="12">
         <v>2032</v>
       </c>
       <c r="I64" s="13">
-        <v>97.424999999999997</v>
+        <v>99.915253000000007</v>
       </c>
       <c r="J64" s="13">
-        <v>5.3711769281036004</v>
+        <v>5.5927321848644</v>
       </c>
       <c r="K64" s="13">
-        <v>96.786963543889996</v>
+        <v>110.48649252062999</v>
       </c>
       <c r="L64" s="13">
-        <v>5.5462448562795998</v>
+        <v>5.6084038561996996</v>
       </c>
       <c r="M64" s="14">
         <v>2000</v>
@@ -5217,592 +5251,639 @@
         <v>117</v>
       </c>
       <c r="O64" s="16">
-        <v>1150000000</v>
+        <v>500000000</v>
       </c>
       <c r="P64" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:16">
       <c r="A65" s="8" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" s="10">
-        <v>5.6500000000000002E-2</v>
+        <v>77</v>
+      </c>
+      <c r="F65" s="36">
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="G65" s="11">
-        <v>48224</v>
+        <v>48349</v>
       </c>
       <c r="H65" s="12">
         <v>2032</v>
       </c>
       <c r="I65" s="13">
-        <v>102.01</v>
+        <v>96.5</v>
       </c>
       <c r="J65" s="13">
-        <v>5.3326047550346001</v>
+        <v>7.8544664558505</v>
       </c>
       <c r="K65" s="13">
-        <v>89.575916002962998</v>
+        <v>341.29423902876999</v>
       </c>
       <c r="L65" s="13">
-        <v>5.4450174366809998</v>
+        <v>7.8425335089162003</v>
       </c>
       <c r="M65" s="14">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="N65" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="O65" s="16">
+        <v>250000000</v>
+      </c>
+      <c r="P65" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="O65" s="16">
-        <v>500000000</v>
-      </c>
-      <c r="P65" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
-      <c r="A66" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>42</v>
-      </c>
       <c r="C66" s="9" t="s">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" s="36">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G66" s="11">
-        <v>48458</v>
-      </c>
-      <c r="H66" s="12">
-        <v>2032</v>
+      <c r="E66" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F66" s="38">
+        <v>6.4210000000000003E-2</v>
+      </c>
+      <c r="G66" s="33">
+        <v>48793</v>
+      </c>
+      <c r="H66" s="39">
+        <v>2033</v>
       </c>
       <c r="I66" s="13">
-        <v>100.664</v>
+        <v>105.4045</v>
       </c>
       <c r="J66" s="13">
-        <v>5.4411983772386003</v>
+        <v>5.5450216433819</v>
       </c>
       <c r="K66" s="13">
-        <v>101.71757138737</v>
+        <v>102.17337922183</v>
       </c>
       <c r="L66" s="13">
-        <v>5.6084038561996996</v>
-      </c>
-      <c r="M66" s="14">
+        <v>5.3970440982665</v>
+      </c>
+      <c r="M66" s="34">
         <v>2000</v>
       </c>
-      <c r="N66" s="15" t="s">
+      <c r="N66" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="O66" s="40">
+        <v>1250000000</v>
+      </c>
+      <c r="P66" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="O66" s="16">
-        <v>500000000</v>
-      </c>
-      <c r="P66" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
-      <c r="A67" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D67" s="9" t="s">
+      <c r="F67" s="38">
+        <v>5.8749999999999997E-2</v>
+      </c>
+      <c r="G67" s="33">
+        <v>48837</v>
+      </c>
+      <c r="H67" s="39">
+        <v>2033</v>
+      </c>
+      <c r="I67" s="43">
+        <v>102.401</v>
+      </c>
+      <c r="J67" s="47">
+        <v>5.5332916851778</v>
+      </c>
+      <c r="K67" s="47">
+        <v>100.82357842934</v>
+      </c>
+      <c r="L67" s="48"/>
+      <c r="M67" s="34">
+        <v>2000</v>
+      </c>
+      <c r="N67" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="O67" s="40">
+        <v>900000000</v>
+      </c>
+      <c r="P67" s="44" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D68" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E67" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F67" s="40">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="G67" s="33">
-        <v>48349</v>
-      </c>
-      <c r="H67" s="41">
-        <v>2032</v>
-      </c>
-      <c r="I67" s="13">
-        <v>96.5</v>
-      </c>
-      <c r="J67" s="13">
-        <v>7.8515312039078999</v>
-      </c>
-      <c r="K67" s="13">
-        <v>347.27670204506001</v>
-      </c>
-      <c r="L67" s="13">
-        <v>7.8425335089162003</v>
-      </c>
-      <c r="M67" s="34">
-        <v>1000</v>
-      </c>
-      <c r="N67" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="O67" s="42">
-        <v>250000000</v>
-      </c>
-      <c r="P67" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
-      <c r="A68" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="F68" s="10">
-        <v>6.4210000000000003E-2</v>
-      </c>
-      <c r="G68" s="11">
-        <v>48793</v>
-      </c>
-      <c r="H68" s="12">
+      <c r="E68" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="F68" s="38">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G68" s="33">
+        <v>48763</v>
+      </c>
+      <c r="H68" s="39">
         <v>2033</v>
       </c>
       <c r="I68" s="13">
-        <v>106.30500000000001</v>
+        <v>101.85</v>
       </c>
       <c r="J68" s="13">
-        <v>5.3920483177523</v>
+        <v>6.25</v>
       </c>
       <c r="K68" s="13">
-        <v>91.306853114060004</v>
-      </c>
-      <c r="L68" s="13">
-        <v>5.3970440982665</v>
-      </c>
-      <c r="M68" s="14">
+        <v>171.82</v>
+      </c>
+      <c r="L68" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="M68" s="34">
         <v>2000</v>
       </c>
-      <c r="N68" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="O68" s="16">
+      <c r="N68" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="O68" s="40">
         <v>1250000000</v>
       </c>
       <c r="P68" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:16">
-      <c r="A69" s="39" t="s">
-        <v>80</v>
+      <c r="A69" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>21</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>178</v>
+        <v>145</v>
       </c>
       <c r="F69" s="10">
-        <v>6.5000000000000002E-2</v>
+        <v>5.6000000000000001E-2</v>
       </c>
       <c r="G69" s="11">
-        <v>48763</v>
+        <v>49218</v>
       </c>
       <c r="H69" s="12">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="I69" s="13">
-        <v>102.25</v>
+        <v>100.72</v>
       </c>
       <c r="J69" s="13">
-        <v>6.1829999999999998</v>
+        <v>5.5117947971856003</v>
       </c>
       <c r="K69" s="13">
-        <v>171.7</v>
-      </c>
-      <c r="L69" s="13" t="s">
-        <v>179</v>
+        <v>93.567859241316</v>
+      </c>
+      <c r="L69" s="13">
+        <v>5.5691708429039997</v>
       </c>
       <c r="M69" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N69" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="O69" s="16">
+        <v>1200000000</v>
+      </c>
+      <c r="P69" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F70" s="10">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G70" s="11">
+        <v>49589</v>
+      </c>
+      <c r="H70" s="12">
+        <v>2035</v>
+      </c>
+      <c r="I70" s="13">
+        <v>95.191999999999993</v>
+      </c>
+      <c r="J70" s="13">
+        <v>6.1882973947832998</v>
+      </c>
+      <c r="K70" s="13">
+        <v>157.05624498166</v>
+      </c>
+      <c r="L70" s="13">
+        <v>6.0105975518405002</v>
+      </c>
+      <c r="M70" s="14">
         <v>2000</v>
       </c>
-      <c r="N69" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="O69" s="16">
-        <v>1250000000</v>
-      </c>
-      <c r="P69" s="17" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
-      <c r="A70" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F70" s="10">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="G70" s="11">
-        <v>49218</v>
-      </c>
-      <c r="H70" s="12">
-        <v>2034</v>
-      </c>
-      <c r="I70" s="13">
-        <v>101.60899999999999</v>
-      </c>
-      <c r="J70" s="13">
-        <v>5.3724648973517004</v>
-      </c>
-      <c r="K70" s="13">
-        <v>82.925494940375998</v>
-      </c>
-      <c r="L70" s="13">
-        <v>5.5691708429039997</v>
-      </c>
-      <c r="M70" s="14">
-        <v>1000</v>
-      </c>
       <c r="N70" s="15" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="O70" s="16">
-        <v>1200000000</v>
+        <v>600000000</v>
       </c>
       <c r="P70" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" spans="1:16">
       <c r="A71" s="8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F71" s="36">
-        <v>5.3999999999999999E-2</v>
+        <v>57</v>
+      </c>
+      <c r="F71" s="10">
+        <v>5.9799999999999999E-2</v>
       </c>
       <c r="G71" s="11">
-        <v>49589</v>
+        <v>49351</v>
       </c>
       <c r="H71" s="12">
         <v>2035</v>
       </c>
       <c r="I71" s="13">
-        <v>96.468000000000004</v>
+        <v>101.77500000000001</v>
       </c>
       <c r="J71" s="13">
-        <v>5.9927658030374999</v>
+        <v>5.7927671304618</v>
       </c>
       <c r="K71" s="13">
-        <v>139.91849399364</v>
+        <v>119.86471577723</v>
       </c>
       <c r="L71" s="13">
-        <v>6.0105975518405002</v>
+        <v>5.6258500906032998</v>
       </c>
       <c r="M71" s="14">
         <v>2000</v>
       </c>
       <c r="N71" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O71" s="16">
-        <v>600000000</v>
+        <v>650000000</v>
       </c>
       <c r="P71" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="1:16">
       <c r="A72" s="8" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="D72" s="9" t="s">
         <v>12</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="F72" s="36">
-        <v>5.9799999999999999E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G72" s="11">
-        <v>49351</v>
+        <v>49379</v>
       </c>
       <c r="H72" s="12">
         <v>2035</v>
       </c>
       <c r="I72" s="13">
-        <v>103.07299999999999</v>
+        <v>97.935000000000002</v>
       </c>
       <c r="J72" s="13">
-        <v>5.5962652705313003</v>
+        <v>5.8949361096607999</v>
       </c>
       <c r="K72" s="13">
-        <v>103.09938952736999</v>
+        <v>130.25242073086</v>
       </c>
       <c r="L72" s="13">
-        <v>5.6258500906032998</v>
+        <v>5.7725722026141</v>
       </c>
       <c r="M72" s="14">
         <v>2000</v>
       </c>
       <c r="N72" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O72" s="16">
-        <v>650000000</v>
+        <v>750000000</v>
       </c>
       <c r="P72" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:16">
       <c r="A73" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="F73" s="45">
-        <v>5.5E-2</v>
+      <c r="E73" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="36">
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="G73" s="11">
-        <v>49379</v>
-      </c>
-      <c r="H73" s="46">
+        <v>49324</v>
+      </c>
+      <c r="H73" s="12">
         <v>2035</v>
       </c>
       <c r="I73" s="13">
-        <v>99.174999999999997</v>
-      </c>
-      <c r="J73" s="47">
-        <v>5.7014990274377002</v>
-      </c>
-      <c r="K73" s="47">
-        <v>113.8173323125</v>
+        <v>99.325000000000003</v>
+      </c>
+      <c r="J73" s="13">
+        <v>5.8859011998991004</v>
+      </c>
+      <c r="K73" s="13">
+        <v>129.37199231726001</v>
       </c>
       <c r="L73" s="13">
-        <v>5.7725722026141</v>
+        <v>5.8749240448719</v>
       </c>
       <c r="M73" s="14">
         <v>2000</v>
       </c>
-      <c r="N73" s="48" t="s">
-        <v>129</v>
+      <c r="N73" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="O73" s="16">
         <v>750000000</v>
       </c>
       <c r="P73" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:16">
-      <c r="A74" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>116</v>
+      <c r="A74" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>96</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="44" t="s">
+      <c r="E74" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F74" s="38">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="G74" s="50">
+        <v>49614</v>
+      </c>
+      <c r="H74" s="51">
+        <v>2035</v>
+      </c>
+      <c r="I74" s="52">
+        <v>104.1</v>
+      </c>
+      <c r="J74" s="53">
+        <v>5.5484722201552996</v>
+      </c>
+      <c r="K74" s="53">
+        <v>93.211405245397003</v>
+      </c>
+      <c r="L74" s="53"/>
+      <c r="M74" s="34">
+        <v>2000</v>
+      </c>
+      <c r="N74" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="O74" s="40">
+        <v>1250000000</v>
+      </c>
+      <c r="P74" s="54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F74" s="45">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="G74" s="11">
+      <c r="F75" s="42">
+        <v>6.25E-2</v>
+      </c>
+      <c r="G75" s="33">
         <v>49324</v>
       </c>
-      <c r="H74" s="46">
+      <c r="H75" s="39">
         <v>2035</v>
       </c>
-      <c r="I74" s="13">
-        <v>100.19499999999999</v>
-      </c>
-      <c r="J74" s="47">
-        <v>5.7497590757896004</v>
-      </c>
-      <c r="K74" s="47">
-        <v>118.71511344616999</v>
-      </c>
-      <c r="L74" s="13">
-        <v>5.8749240448719</v>
-      </c>
-      <c r="M74" s="14">
+      <c r="I75" s="43">
+        <v>102.47</v>
+      </c>
+      <c r="J75" s="43">
+        <v>5.9568662113695003</v>
+      </c>
+      <c r="K75" s="43">
+        <v>137.14105464784001</v>
+      </c>
+      <c r="L75" s="43"/>
+      <c r="M75" s="34">
         <v>2000</v>
       </c>
-      <c r="N74" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="O74" s="16">
+      <c r="N75" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="O75" s="40">
         <v>750000000</v>
       </c>
-      <c r="P74" s="17" t="s">
-        <v>158</v>
+      <c r="P75" s="44" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N74">
-    <cfRule type="duplicateValues" dxfId="20" priority="1"/>
+  <conditionalFormatting sqref="N2:N75">
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N50" r:id="rId1" xr:uid="{DC85DBED-8674-4EA2-A26E-18071782CF62}"/>
-    <hyperlink ref="N68" r:id="rId2" display="US674599EL59" xr:uid="{AF436497-81EB-4DC2-A4FA-7749A2F72423}"/>
-    <hyperlink ref="N17" r:id="rId3" xr:uid="{9422EA53-8A22-4DAF-B976-9D98FC460BEA}"/>
-    <hyperlink ref="N27" r:id="rId4" xr:uid="{2423F2A3-29B1-4364-8C5F-252A0825106D}"/>
-    <hyperlink ref="N18" r:id="rId5" xr:uid="{C34DF029-BA99-42A0-961A-6921DE05E2D1}"/>
-    <hyperlink ref="N32" r:id="rId6" xr:uid="{1DA51581-72B9-4AC9-8F15-59F9AA508C44}"/>
-    <hyperlink ref="N19" r:id="rId7" xr:uid="{B7C0719D-12C1-440A-8E74-F1EC1FE01243}"/>
-    <hyperlink ref="N62" r:id="rId8" display="US963320AZ92" xr:uid="{F7476DEC-EB35-440D-9F9E-3635F074F14B}"/>
-    <hyperlink ref="N48" r:id="rId9" xr:uid="{99871DF9-C5DC-4FDC-AD75-6713AF303BD8}"/>
-    <hyperlink ref="N67" r:id="rId10" display="US054989AB41" xr:uid="{A2BA32D4-C23A-419C-891C-75321C4FC367}"/>
-    <hyperlink ref="N66" r:id="rId11" display="US577778BQ55" xr:uid="{9AE054E2-3F35-4C66-A625-045E293BF79D}"/>
-    <hyperlink ref="N72" r:id="rId12" display="US165167DH73" xr:uid="{0FA04D43-9E13-4E05-89CF-73DA6D28DD73}"/>
-    <hyperlink ref="N65" r:id="rId13" display="US403949AT72" xr:uid="{BD7E47A4-B535-426E-8156-834959CA3564}"/>
-    <hyperlink ref="N46" r:id="rId14" xr:uid="{C0611DEA-BF7F-4716-B3C9-2BC813F787D4}"/>
-    <hyperlink ref="N71" r:id="rId15" display="US876030AL10" xr:uid="{621ECAFC-C556-4B2E-B329-17049D11A217}"/>
-    <hyperlink ref="N70" r:id="rId16" display="US29082HAE27" xr:uid="{E53E3A39-F1EC-4B1D-B7F5-4E698FFF5317}"/>
-    <hyperlink ref="N69" r:id="rId17" display="USC39296AB17" xr:uid="{F002B98D-F056-46A4-8F18-3310F4D41A2A}"/>
-    <hyperlink ref="N64" r:id="rId18" display="US595112CG61" xr:uid="{9EB066EF-22C8-4939-8F9E-936B05907177}"/>
-    <hyperlink ref="N63" r:id="rId19" display="US845467AT68" xr:uid="{5C401F55-C2CE-4185-867C-E277D8BA95A7}"/>
-    <hyperlink ref="N61" r:id="rId20" display="US05526DBW48" xr:uid="{E9606208-82D7-456D-B718-676E7F873FB1}"/>
-    <hyperlink ref="N60" r:id="rId21" display="USU59224AA07" xr:uid="{683745DC-55DF-41F7-8307-CEF93F48E5C0}"/>
-    <hyperlink ref="N59" r:id="rId22" display="US674599EK76" xr:uid="{B2458CC8-DBBF-4240-AF46-B0EB816B387B}"/>
-    <hyperlink ref="N58" r:id="rId23" display="US876030AA54" xr:uid="{49EEE676-0394-429A-A3CD-0C344876B586}"/>
-    <hyperlink ref="N57" r:id="rId24" display="US55903VBQ59" xr:uid="{F1B77FBB-ADBE-4A0B-B80D-CD50AB8D1438}"/>
-    <hyperlink ref="N56" r:id="rId25" display="USP3984LAA81" xr:uid="{E5D8DC37-A4A4-47F3-9BAE-98269CD6FD73}"/>
-    <hyperlink ref="N55" r:id="rId26" xr:uid="{A8795727-E8B3-4AE7-8AE9-E890BEE3C5BF}"/>
-    <hyperlink ref="N54" r:id="rId27" xr:uid="{5D7C9D53-2E84-40E8-BA61-5320181D091B}"/>
-    <hyperlink ref="N53" r:id="rId28" xr:uid="{B44BC268-C9B1-4D35-8A61-B5775A5A028B}"/>
-    <hyperlink ref="N52" r:id="rId29" xr:uid="{AB4F5FEC-BF66-4432-B951-DBD067D1391D}"/>
-    <hyperlink ref="N51" r:id="rId30" xr:uid="{CFF01FF2-8DD0-4BF0-B544-C5D2B25FF19E}"/>
-    <hyperlink ref="N49" r:id="rId31" xr:uid="{67AB54BD-AC34-4589-8F2C-F798B7A09F5D}"/>
-    <hyperlink ref="N47" r:id="rId32" xr:uid="{B83712DA-E2CE-42D1-A08C-72863DD33658}"/>
-    <hyperlink ref="N45" r:id="rId33" display="US25470DCC11" xr:uid="{B7B33836-6EF9-4212-B3A3-F17F72C50797}"/>
-    <hyperlink ref="N44" r:id="rId34" xr:uid="{4C852086-4650-470A-80DB-02BE23CCF5F5}"/>
-    <hyperlink ref="N43" r:id="rId35" xr:uid="{74264922-A8E2-4FBA-89B6-46C6F25C37C2}"/>
-    <hyperlink ref="N42" r:id="rId36" xr:uid="{FCF2758D-F1F4-4119-9478-8B876D4A7A23}"/>
-    <hyperlink ref="N41" r:id="rId37" xr:uid="{167E816E-1227-455C-9627-E752D0FA0B05}"/>
-    <hyperlink ref="N40" r:id="rId38" xr:uid="{E6499354-F12C-44B1-AA84-AC4B3A53FADB}"/>
-    <hyperlink ref="N39" r:id="rId39" xr:uid="{44566013-4EE1-411E-867C-2D029FC45F1D}"/>
-    <hyperlink ref="N38" r:id="rId40" xr:uid="{665880E9-C07B-48E5-8DC0-F8EA5CF2AAFD}"/>
-    <hyperlink ref="N37" r:id="rId41" xr:uid="{35556A0E-1A29-4C25-BB86-E9425F9CFB41}"/>
-    <hyperlink ref="N36" r:id="rId42" xr:uid="{34863CEB-6F75-4EE5-9783-4C5BDEF5A620}"/>
-    <hyperlink ref="N35" r:id="rId43" xr:uid="{34742F6A-151D-4BCD-BC5F-6D5E0F071A8F}"/>
-    <hyperlink ref="N34" r:id="rId44" xr:uid="{BFDF88EC-D2F9-43A3-97A9-9369A0BF7FEC}"/>
-    <hyperlink ref="N33" r:id="rId45" xr:uid="{AA8253C7-0C75-4523-9E4E-7607118E633D}"/>
-    <hyperlink ref="N31" r:id="rId46" xr:uid="{113F98A6-AEF5-4880-975D-D84F051AB347}"/>
-    <hyperlink ref="N30" r:id="rId47" xr:uid="{34CFCE23-2BCF-4A96-9774-EE39CBE51F3F}"/>
-    <hyperlink ref="N29" r:id="rId48" xr:uid="{C3B9E9C0-C7D0-4CAE-A429-21597C8F4599}"/>
-    <hyperlink ref="N28" r:id="rId49" xr:uid="{350CCD17-6E59-4349-AAF3-B790F73C432C}"/>
-    <hyperlink ref="N26" r:id="rId50" xr:uid="{224637F3-9363-4689-882B-7E886B1CD14B}"/>
-    <hyperlink ref="N25" r:id="rId51" xr:uid="{FD5FDD6B-06D5-4491-820C-5C099B638AFA}"/>
-    <hyperlink ref="N24" r:id="rId52" xr:uid="{12A7386B-B570-43F7-94D1-597C611F7E1C}"/>
-    <hyperlink ref="N23" r:id="rId53" xr:uid="{92203DB2-6BB1-46F7-80A9-F51DCE1DF12F}"/>
-    <hyperlink ref="N22" r:id="rId54" xr:uid="{6FFF8185-6039-471A-B312-611B55599FF4}"/>
-    <hyperlink ref="N21" r:id="rId55" xr:uid="{C46F4249-F90B-4876-88E6-85DBF0E96860}"/>
-    <hyperlink ref="N20" r:id="rId56" xr:uid="{34020D06-C622-4668-906A-D81FED824CC4}"/>
-    <hyperlink ref="N16" r:id="rId57" xr:uid="{65C920AE-93A3-4017-B8C7-9C8C8689190C}"/>
-    <hyperlink ref="N15" r:id="rId58" xr:uid="{AB0101FD-CE2A-4999-BB68-467E6240CF68}"/>
-    <hyperlink ref="N14" r:id="rId59" xr:uid="{9DCD5F39-3CF0-4AF0-BE79-4B0F7770B6A8}"/>
-    <hyperlink ref="N13" r:id="rId60" xr:uid="{29710257-8F76-4091-8380-495A56252A67}"/>
-    <hyperlink ref="N12" r:id="rId61" xr:uid="{16FB8FFA-5146-40AB-B203-029CEEBBC78B}"/>
-    <hyperlink ref="N11" r:id="rId62" xr:uid="{EF502E88-3B09-4D4A-BB30-129F827D1036}"/>
-    <hyperlink ref="N10" r:id="rId63" xr:uid="{1CE09E4A-8F37-45B3-A882-4C65EDBC6EAB}"/>
-    <hyperlink ref="N9" r:id="rId64" xr:uid="{93ED46B6-D159-4034-9C5E-8598E43493DB}"/>
-    <hyperlink ref="N8" r:id="rId65" xr:uid="{194A24F4-476A-4388-B158-B2C42C56C02F}"/>
-    <hyperlink ref="N7" r:id="rId66" xr:uid="{96B0B780-32F6-4B91-95C8-BC018A49D919}"/>
-    <hyperlink ref="N6" r:id="rId67" xr:uid="{C9A3109B-C836-47A0-8F96-1BA899EEEB7A}"/>
-    <hyperlink ref="N5" r:id="rId68" xr:uid="{01763600-0BAD-48FB-83ED-B8E6E458BB0F}"/>
-    <hyperlink ref="N4" r:id="rId69" xr:uid="{52E623B7-0DDA-41B8-9B6D-14FE6CE4B61F}"/>
-    <hyperlink ref="N3" r:id="rId70" xr:uid="{C370E2C9-29C4-4629-846C-C41B924A28B2}"/>
-    <hyperlink ref="N2" r:id="rId71" xr:uid="{76725CEC-E542-4C48-B21D-3D1BE2EAA354}"/>
+    <hyperlink ref="N20" r:id="rId1" xr:uid="{3CEEF2ED-B85B-401B-B147-FD6122AB6935}"/>
+    <hyperlink ref="N75" r:id="rId2" xr:uid="{5120308C-F889-4F03-9EEB-FD0BE167278B}"/>
+    <hyperlink ref="N74" r:id="rId3" xr:uid="{470888B0-C9E7-43B4-AD84-17BE4B2818B8}"/>
+    <hyperlink ref="N67" r:id="rId4" xr:uid="{75B54B15-917A-4DFD-9164-80F0B54A51CA}"/>
+    <hyperlink ref="N55" r:id="rId5" xr:uid="{C6B59A78-B2EF-4307-A06A-D33A4724A104}"/>
+    <hyperlink ref="N68" r:id="rId6" xr:uid="{466BB3CB-BA8D-47DB-8013-83CE97181A34}"/>
+    <hyperlink ref="N45" r:id="rId7" xr:uid="{9D798FFC-4749-451C-AF8E-CBE975D54D5C}"/>
+    <hyperlink ref="N57" r:id="rId8" xr:uid="{B8B48AA6-9B7E-4941-80D0-D47D125A8D20}"/>
+    <hyperlink ref="N49" r:id="rId9" xr:uid="{95A148FB-ACFC-4C22-ADAE-5602DF3CBD07}"/>
+    <hyperlink ref="N69" r:id="rId10" xr:uid="{556A9096-F54D-4194-A145-AAA43EDD9AF7}"/>
+    <hyperlink ref="N17" r:id="rId11" xr:uid="{0FB3A616-D4CA-4B87-89FB-5D910B1529B4}"/>
+    <hyperlink ref="N28" r:id="rId12" xr:uid="{F56DE0F0-54C8-4378-8BFB-23DB4520FFBA}"/>
+    <hyperlink ref="N18" r:id="rId13" xr:uid="{F26664B4-1804-4144-858F-06647863D521}"/>
+    <hyperlink ref="N33" r:id="rId14" xr:uid="{00E92F10-37FD-4CB7-A107-5DE23A9AAB26}"/>
+    <hyperlink ref="N19" r:id="rId15" xr:uid="{9615C840-613A-4F6C-8A6D-08342F799FE4}"/>
+    <hyperlink ref="N62" r:id="rId16" xr:uid="{E901981A-96C1-45D8-AF94-E833540F497D}"/>
+    <hyperlink ref="N48" r:id="rId17" xr:uid="{D4F362FF-94C8-4498-AB53-FC0940A6DB7D}"/>
+    <hyperlink ref="N66" r:id="rId18" xr:uid="{E904D32F-40C3-4A61-B579-89529A884DA4}"/>
+    <hyperlink ref="N65" r:id="rId19" xr:uid="{BF1E8D9A-29AF-4860-A0BE-8AFA5BC76BE6}"/>
+    <hyperlink ref="N73" r:id="rId20" xr:uid="{9E91844A-2668-4F2A-A1A4-4783D27AD03F}"/>
+    <hyperlink ref="N64" r:id="rId21" xr:uid="{36806609-FF7C-4ABB-A86D-E22550A0CC8E}"/>
+    <hyperlink ref="N46" r:id="rId22" xr:uid="{642624BF-9362-4109-96C3-D60B0983F3E8}"/>
+    <hyperlink ref="N72" r:id="rId23" xr:uid="{7CF58E79-D078-4706-BEEA-6F4CFFF2DD9F}"/>
+    <hyperlink ref="N71" r:id="rId24" xr:uid="{B39A6D0E-1F29-450E-88C7-E329FC170333}"/>
+    <hyperlink ref="N70" r:id="rId25" xr:uid="{50660C6A-7660-4601-B164-C79B9663B6D2}"/>
+    <hyperlink ref="N63" r:id="rId26" xr:uid="{52284187-5295-4F5D-B52B-2DE3C2FEA4F3}"/>
+    <hyperlink ref="N61" r:id="rId27" xr:uid="{83808C55-2D9B-49A1-952D-B1F54D6FF105}"/>
+    <hyperlink ref="N60" r:id="rId28" xr:uid="{C2BF2D99-3B7D-4887-ACE7-85B566F1E086}"/>
+    <hyperlink ref="N59" r:id="rId29" xr:uid="{1F75F08F-64FA-4441-A601-E7DB43E94CD4}"/>
+    <hyperlink ref="N58" r:id="rId30" xr:uid="{2227F70C-B061-4EBC-9FA6-07A059BC3945}"/>
+    <hyperlink ref="N56" r:id="rId31" xr:uid="{7099E3BD-C2D7-4B18-B1B8-C28E2E7AAAE8}"/>
+    <hyperlink ref="N54" r:id="rId32" xr:uid="{D3D61966-9C3E-428A-A278-A954052C6F2B}"/>
+    <hyperlink ref="N53" r:id="rId33" xr:uid="{675EB51C-90F0-4A47-A8F7-9B9D0DFEEEFC}"/>
+    <hyperlink ref="N52" r:id="rId34" xr:uid="{2920045D-B8A6-4188-AADA-C62404AC3709}"/>
+    <hyperlink ref="N51" r:id="rId35" xr:uid="{CB6923F2-1CB5-436B-BC03-EC9FFA88049F}"/>
+    <hyperlink ref="N50" r:id="rId36" xr:uid="{5E4E4BD7-A620-43C5-B81C-E524811E3B0E}"/>
+    <hyperlink ref="N47" r:id="rId37" xr:uid="{672FAB3F-DB7A-47AD-998A-30B77BFF028D}"/>
+    <hyperlink ref="N44" r:id="rId38" xr:uid="{6D32E887-3644-4070-803D-22427AE238C2}"/>
+    <hyperlink ref="N43" r:id="rId39" xr:uid="{77B34750-77BE-4583-8D9B-F96467838F57}"/>
+    <hyperlink ref="N42" r:id="rId40" xr:uid="{EAD7B080-0C35-4EDB-82E2-9B4419BDB30D}"/>
+    <hyperlink ref="N41" r:id="rId41" xr:uid="{00770F81-546F-44C9-93A6-390FB0531E99}"/>
+    <hyperlink ref="N40" r:id="rId42" xr:uid="{5B09663E-C9D5-43CC-B64A-EA30067BCF78}"/>
+    <hyperlink ref="N39" r:id="rId43" xr:uid="{FC70D7EB-4516-433B-8116-26AF0850B062}"/>
+    <hyperlink ref="N38" r:id="rId44" xr:uid="{00815C44-7CB7-4491-8FFF-BE379406DED4}"/>
+    <hyperlink ref="N37" r:id="rId45" xr:uid="{492DD138-1744-4E1A-91FD-8AF27FE419A9}"/>
+    <hyperlink ref="N36" r:id="rId46" xr:uid="{A0AD9F8E-A436-4571-BC76-63AFB0DC8FA5}"/>
+    <hyperlink ref="N35" r:id="rId47" xr:uid="{73C28C97-324C-488B-AFCB-8DFD4D0D8700}"/>
+    <hyperlink ref="N34" r:id="rId48" xr:uid="{7DCEFBF2-A34A-4ABF-8409-27FC889AD396}"/>
+    <hyperlink ref="N32" r:id="rId49" xr:uid="{9D7086E6-F85C-409E-9406-D27C435EA1E8}"/>
+    <hyperlink ref="N31" r:id="rId50" xr:uid="{E1A51EBB-9A6E-4D5B-850B-83652F570339}"/>
+    <hyperlink ref="N30" r:id="rId51" xr:uid="{936DEDE7-0905-48E2-A215-192B35EC6DA7}"/>
+    <hyperlink ref="N29" r:id="rId52" xr:uid="{23A869E0-5462-400C-AC92-6D73F7FC1CA6}"/>
+    <hyperlink ref="N27" r:id="rId53" xr:uid="{35CCD69D-4746-43F0-A7E1-2F564D903988}"/>
+    <hyperlink ref="N26" r:id="rId54" xr:uid="{7167CE3A-6FFD-40CC-A4F5-AE8B4834B25F}"/>
+    <hyperlink ref="N25" r:id="rId55" xr:uid="{D0172DCD-9F10-4ACB-90F4-6273FF66EE05}"/>
+    <hyperlink ref="N24" r:id="rId56" xr:uid="{8DE016F3-9307-413A-A607-C5DC7CE8E56E}"/>
+    <hyperlink ref="N23" r:id="rId57" xr:uid="{8BE54014-5C10-48FD-8854-F09A34EAB479}"/>
+    <hyperlink ref="N22" r:id="rId58" xr:uid="{8692D00F-6BE6-46B4-9A20-2AEDE28BF4DA}"/>
+    <hyperlink ref="N21" r:id="rId59" xr:uid="{589DF66F-EF33-4245-BE03-FDC69FAC5A61}"/>
+    <hyperlink ref="N16" r:id="rId60" xr:uid="{553455E3-7F8F-4EB0-95A8-E53A7C7974AB}"/>
+    <hyperlink ref="N15" r:id="rId61" xr:uid="{BC50BDAD-6898-43AB-9AA5-68952716D186}"/>
+    <hyperlink ref="N14" r:id="rId62" xr:uid="{721F42A6-3B1C-4DD9-A775-49EB04E6A7B1}"/>
+    <hyperlink ref="N13" r:id="rId63" xr:uid="{850A9D8A-0BD3-4718-9D73-8A4FDB8D69CE}"/>
+    <hyperlink ref="N12" r:id="rId64" xr:uid="{5F52ED13-B032-4675-9413-9EB6AD0EB850}"/>
+    <hyperlink ref="N11" r:id="rId65" xr:uid="{386BD35D-62BD-4659-9147-EDAE9679886D}"/>
+    <hyperlink ref="N10" r:id="rId66" xr:uid="{E3C8A810-3A57-4182-AAEA-9D249D253950}"/>
+    <hyperlink ref="N9" r:id="rId67" xr:uid="{46F0C65D-6AD9-48AA-A10D-E62AC1B57E60}"/>
+    <hyperlink ref="N8" r:id="rId68" xr:uid="{10080408-AF85-410B-A9AF-1FABA1EEB3DA}"/>
+    <hyperlink ref="N7" r:id="rId69" xr:uid="{C72DFF8A-E07D-414D-8E10-CD4B64018D9C}"/>
+    <hyperlink ref="N6" r:id="rId70" xr:uid="{ACD093F2-AEF8-4C4E-8CE8-091A44331939}"/>
+    <hyperlink ref="N5" r:id="rId71" xr:uid="{5716CAC3-8FA8-4E87-9166-88C382D5BCFC}"/>
+    <hyperlink ref="N4" r:id="rId72" xr:uid="{6D218C44-2BF8-456A-A150-B47CD7C3EECA}"/>
+    <hyperlink ref="N3" r:id="rId73" xr:uid="{C5161E25-941C-44CA-B200-3B80E48C499F}"/>
+    <hyperlink ref="N2" r:id="rId74" xr:uid="{8E0DBDD4-2339-4968-A16F-9D10B882AA51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId72"/>
+    <tablePart r:id="rId75"/>
   </tableParts>
 </worksheet>
 </file>